--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Books" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Papers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newspaper Articles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magazines &amp; Journals" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Records" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Method" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Books" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Research Papers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Newspaper Articles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Magazines &amp; Journals" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="All Records" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sources &amp; Method" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Books'!$A$1:$M$33</definedName>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Books" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Papers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newspaper Articles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magazines &amp; Journals" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web Articles" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Records" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Method" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Books" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Research Papers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Newspaper Articles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Magazines &amp; Journals" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Web Articles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="All Records" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sources &amp; Method" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Books'!$A$1:$M$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Papers'!$A$1:$M$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspaper Articles'!$A$1:$M$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Magazines &amp; Journals'!$A$1:$M$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$461</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$465</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$461,A6)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$465,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$461,A6,'All Records'!$L$2:$L$461,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$465,A6,'All Records'!$L$2:$L$465,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$461,A7)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$465,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$461,A7,'All Records'!$L$2:$L$461,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$465,A7,'All Records'!$L$2:$L$465,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$461,A8)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$465,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$461,A8,'All Records'!$L$2:$L$461,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$465,A8,'All Records'!$L$2:$L$465,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$461,A9)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$465,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$461,A9,'All Records'!$L$2:$L$461,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$465,A9,'All Records'!$L$2:$L$465,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$461,A10)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$465,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$461,A10,'All Records'!$L$2:$L$461,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$465,A10,'All Records'!$L$2:$L$465,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$461,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$465,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$461,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$465,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$461,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$465,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$461,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$465,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$461,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$465,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$461,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$465,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -787,23 +787,23 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="G23" s="4">
@@ -818,23 +818,23 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="G24" s="4">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="G25" s="4">
@@ -880,23 +880,23 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="G26" s="4">
@@ -911,23 +911,23 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="G27" s="4">
@@ -942,23 +942,23 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$461="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$461,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$465="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$465,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="G28" s="4">
@@ -25180,7 +25180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25399,33 +25399,29 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Sankiliyatital Archaeological Site in Jaffna</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Nishan Weerasooriya</t>
-        </is>
-      </c>
+          <t>யாழ்ப்பாணம். கோட்டையை சுற்றி எல்லைக்கல் நாட்டுப் பணியில் தொல்லியல் ...</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n"/>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>uthayannews.ca</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
@@ -25435,7 +25431,7 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Jaffna</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -25443,10 +25439,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L4" s="9" t="n"/>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/sankiliyatital/</t>
+          <t>https://uthayannews.ca/2025/12/19/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AF%88-%E0%AE%9A%E0%AF%81/</t>
         </is>
       </c>
     </row>
@@ -25461,51 +25461,51 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
+      <c r="C5" s="11" t="n"/>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>தேவனாம்பிரியா</t>
+          <t>Sankiliyatital Archaeological Site in Jaffna</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia contributors</t>
+          <t>Nishan Weerasooriya</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Jaffna</t>
+        </is>
+      </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L5" s="13" t="n"/>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%87%E0%AE%B5%E0%AE%A9%E0%AE%BE%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%AF%E0%AE%BE</t>
+          <t>https://amazinglanka.com/wp/sankiliyatital/</t>
         </is>
       </c>
     </row>
@@ -25522,12 +25522,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-11-13</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>கோமரங்கடவலை கல்வெட்டு</t>
+          <t>தேவனாம்பிரியா</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -25550,16 +25550,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
       <c r="K6" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25572,7 +25564,7 @@
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AE%E0%AE%B0%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%9F%E0%AE%B5%E0%AE%B2%E0%AF%88_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%87%E0%AE%B5%E0%AE%A9%E0%AE%BE%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%AF%E0%AE%BE</t>
         </is>
       </c>
     </row>
@@ -25584,37 +25576,37 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Tamil Inscriptions in Sri Lanka (list)</t>
+          <t>கோமரங்கடவலை கல்வெட்டு</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Lanka Pradeepa</t>
+          <t>Wikipedia contributors</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Lanka Pradeepa (lankapradeepa.com)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -25624,7 +25616,7 @@
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; list; bibliography</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
@@ -25634,12 +25626,12 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>Updated May 2023; 27 references</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>https://www.lankapradeepa.com/2020/04/tamil-inscriptions-in-sri-lanka_16.html</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AE%E0%AE%B0%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%9F%E0%AE%B5%E0%AE%B2%E0%AF%88_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -25656,27 +25648,27 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Pottery of Sri Lanka</t>
+          <t>Tamil Inscriptions in Sri Lanka (list)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia contributors</t>
+          <t>Lanka Pradeepa</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Lanka Pradeepa (lankapradeepa.com)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -25684,8 +25676,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; list; bibliography</t>
+        </is>
+      </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25693,12 +25693,12 @@
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Updated May 2023; 27 references</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pottery_of_Sri_Lanka</t>
+          <t>https://www.lankapradeepa.com/2020/04/tamil-inscriptions-in-sri-lanka_16.html</t>
         </is>
       </c>
     </row>
@@ -25710,17 +25710,17 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions</t>
+          <t>Pottery of Sri Lanka</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -25743,16 +25743,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25765,7 +25757,7 @@
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tamil_inscriptions</t>
+          <t>https://en.wikipedia.org/wiki/Pottery_of_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -25782,12 +25774,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>வெடுக்குநாறிமலை ஆதி லிங்கேஸ்வரர் ஆலயம்</t>
+          <t>Tamil inscriptions</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -25797,7 +25789,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -25807,11 +25799,19 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25824,7 +25824,7 @@
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%81%E0%AE%A8%E0%AE%BE%E0%AE%B1%E0%AE%BF%E0%AE%AE%E0%AE%B2%E0%AF%88_%E0%AE%86%E0%AE%A4%E0%AE%BF_%E0%AE%B2%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%87%E0%AE%B8%E0%AF%8D%E0%AE%B5%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%86%E0%AE%B2%E0%AE%AF%E0%AE%AE%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Tamil_inscriptions</t>
         </is>
       </c>
     </row>
@@ -25836,17 +25836,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>2017-01-15</t>
+          <t>2019-09-08</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Mantri Manai</t>
+          <t>வெடுக்குநாறிமலை ஆதி லிங்கேஸ்வரர் ஆலயம்</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -25866,7 +25866,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I11" s="13" t="n"/>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Mantri_Manai</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%81%E0%AE%A8%E0%AE%BE%E0%AE%B1%E0%AE%BF%E0%AE%AE%E0%AE%B2%E0%AF%88_%E0%AE%86%E0%AE%A4%E0%AE%BF_%E0%AE%B2%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%87%E0%AE%B8%E0%AF%8D%E0%AE%B5%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%86%E0%AE%B2%E0%AE%AF%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -25895,17 +25895,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>2016-01-15</t>
+          <t>2017-01-15</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>நாடு காட்டுப் பரவணிக் கல்வெட்டு</t>
+          <t>Mantri Manai</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -25925,19 +25925,11 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
       <c r="K12" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25950,7 +25942,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81_%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AE%B0%E0%AE%B5%E0%AE%A3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://en.wikipedia.org/wiki/Mantri_Manai</t>
         </is>
       </c>
     </row>
@@ -25967,12 +25959,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-01-15</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Velgam Vehera</t>
+          <t>நாடு காட்டுப் பரவணிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -25982,7 +25974,7 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -25992,11 +25984,19 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="n"/>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="M13" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Velgam_Vehera</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81_%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AE%B0%E0%AE%B5%E0%AE%A3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -26026,12 +26026,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>2016-04-03</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Kulakkottan</t>
+          <t>Velgam Vehera</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -26068,7 +26068,7 @@
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Kulakkottan</t>
+          <t>https://en.wikipedia.org/wiki/Velgam_Vehera</t>
         </is>
       </c>
     </row>
@@ -26085,12 +26085,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-03</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண மாவட்டத்தில் தொல்லியல் ரீதியாக பாதுகாக்கப்பட்ட நினைவுச் சின்னங்களின் பட்டியல்</t>
+          <t>Kulakkottan</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -26100,7 +26100,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -26110,19 +26110,11 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
       <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -26135,7 +26127,7 @@
       </c>
       <c r="M15" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3_%E0%AE%AE%E0%AE%BE%E0%AE%B5%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%B0%E0%AF%80%E0%AE%A4%E0%AE%BF%E0%AE%AF%E0%AE%BE%E0%AE%95_%E0%AE%AA%E0%AE%BE%E0%AE%A4%E0%AF%81%E0%AE%95%E0%AE%BE%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F_%E0%AE%A8%E0%AE%BF%E0%AE%A9%E0%AF%88%E0%AE%B5%E0%AF%81%E0%AE%9A%E0%AF%8D_%E0%AE%9A%E0%AE%BF%E0%AE%A9%E0%AF%8D%E0%AE%A9%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Kulakkottan</t>
         </is>
       </c>
     </row>
@@ -26152,12 +26144,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>2016-12-31</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>கந்தரோடை தொல்லியல் களம்</t>
+          <t>யாழ்ப்பாண மாவட்டத்தில் தொல்லியல் ரீதியாக பாதுகாக்கப்பட்ட நினைவுச் சின்னங்களின் பட்டியல்</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -26202,7 +26194,7 @@
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%B0%E0%AF%8B%E0%AE%9F%E0%AF%88_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%AE%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3_%E0%AE%AE%E0%AE%BE%E0%AE%B5%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%B0%E0%AF%80%E0%AE%A4%E0%AE%BF%E0%AE%AF%E0%AE%BE%E0%AE%95_%E0%AE%AA%E0%AE%BE%E0%AE%A4%E0%AF%81%E0%AE%95%E0%AE%BE%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F_%E0%AE%A8%E0%AE%BF%E0%AE%A9%E0%AF%88%E0%AE%B5%E0%AF%81%E0%AE%9A%E0%AF%8D_%E0%AE%9A%E0%AE%BF%E0%AE%A9%E0%AF%8D%E0%AE%A9%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -26214,17 +26206,17 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>2015-02-22</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>ஆ. வேலுப்பிள்ளை</t>
+          <t>கந்தரோடை தொல்லியல் களம்</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -26247,8 +26239,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -26261,7 +26261,7 @@
       </c>
       <c r="M17" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%86._%E0%AE%B5%E0%AF%87%E0%AE%B2%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B3%E0%AF%8D%E0%AE%B3%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%B0%E0%AF%8B%E0%AE%9F%E0%AF%88_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -26278,12 +26278,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
+          <t>2015-02-22</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>வெஸ்ஸகிரிய</t>
+          <t>ஆ. வேலுப்பிள்ளை</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -26320,7 +26320,7 @@
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%86%E0%AE%B8%E0%AF%8D%E0%AE%B8%E0%AE%95%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%AF</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%86._%E0%AE%B5%E0%AF%87%E0%AE%B2%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B3%E0%AF%8D%E0%AE%B3%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -26337,12 +26337,12 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் அருங்காட்சியகம்</t>
+          <t>வெஸ்ஸகிரிய</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M19" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%85%E0%AE%B0%E0%AF%81%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%86%E0%AE%B8%E0%AF%8D%E0%AE%B8%E0%AE%95%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%AF</t>
         </is>
       </c>
     </row>
@@ -26401,7 +26401,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>சேனரத் பரணவிதான</t>
+          <t>அனுராதபுரம் அருங்காட்சியகம்</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -26438,7 +26438,7 @@
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AF%87%E0%AE%A9%E0%AE%B0%E0%AE%A4%E0%AF%8D_%E0%AE%AA%E0%AE%B0%E0%AE%A3%E0%AE%B5%E0%AE%BF%E0%AE%A4%E0%AE%BE%E0%AE%A9</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%85%E0%AE%B0%E0%AF%81%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -26460,7 +26460,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>தொல்பொருள் காட்சிச்சாலை, வவுனியா</t>
+          <t>சேனரத் பரணவிதான</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -26483,16 +26483,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>தொல்பொருள்</t>
-        </is>
-      </c>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -26505,7 +26497,7 @@
       </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%AA%E0%AF%8A%E0%AE%B0%E0%AF%81%E0%AE%B3%E0%AF%8D_%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BE%E0%AE%B2%E0%AF%88%2C_%E0%AE%B5%E0%AE%B5%E0%AF%81%E0%AE%A9%E0%AE%BF%E0%AE%AF%E0%AE%BE</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AF%87%E0%AE%A9%E0%AE%B0%E0%AE%A4%E0%AF%8D_%E0%AE%AA%E0%AE%B0%E0%AE%A3%E0%AE%B5%E0%AE%BF%E0%AE%A4%E0%AE%BE%E0%AE%A9</t>
         </is>
       </c>
     </row>
@@ -26522,12 +26514,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>2015-07-23</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>சிரான் உபேந்திர தெரணியகல</t>
+          <t>தொல்பொருள் காட்சிச்சாலை, வவுனியா</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -26550,8 +26542,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>தொல்பொருள்</t>
+        </is>
+      </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -26564,7 +26564,7 @@
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%A9%E0%AF%8D_%E0%AE%89%E0%AE%AA%E0%AF%87%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B0_%E0%AE%A4%E0%AF%86%E0%AE%B0%E0%AE%A3%E0%AE%BF%E0%AE%AF%E0%AE%95%E0%AE%B2</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%AA%E0%AF%8A%E0%AE%B0%E0%AF%81%E0%AE%B3%E0%AF%8D_%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BE%E0%AE%B2%E0%AF%88%2C_%E0%AE%B5%E0%AE%B5%E0%AF%81%E0%AE%A9%E0%AE%BF%E0%AE%AF%E0%AE%BE</t>
         </is>
       </c>
     </row>
@@ -26581,12 +26581,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
+          <t>2015-07-23</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>தொல்பொருளியல் திணைக்களம், இலங்கை</t>
+          <t>சிரான் உபேந்திர தெரணியகல</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="M23" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%AA%E0%AF%8A%E0%AE%B0%E0%AF%81%E0%AE%B3%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AE%BF%E0%AE%A3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%AE%E0%AF%8D%2C_%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%A9%E0%AF%8D_%E0%AE%89%E0%AE%AA%E0%AF%87%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B0_%E0%AE%A4%E0%AF%86%E0%AE%B0%E0%AE%A3%E0%AE%BF%E0%AE%AF%E0%AE%95%E0%AE%B2</t>
         </is>
       </c>
     </row>
@@ -26640,12 +26640,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2015-07-24</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>அபயகிரித் தமிழ்க் கல்வெட்டு</t>
+          <t>தொல்பொருளியல் திணைக்களம், இலங்கை</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -26668,16 +26668,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
       <c r="K24" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -26690,7 +26682,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%AA%E0%AE%AF%E0%AE%95%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%AA%E0%AF%8A%E0%AE%B0%E0%AF%81%E0%AE%B3%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AE%BF%E0%AE%A3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%AE%E0%AF%8D%2C_%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -26712,7 +26704,7 @@
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>இலங்கைத் தமிழ்க் கல்வெட்டுக்களின் பட்டியல்</t>
+          <t>அபயகிரித் தமிழ்க் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -26757,7 +26749,7 @@
       </c>
       <c r="M25" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%AA%E0%AE%AF%E0%AE%95%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -26774,12 +26766,12 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் குமாரகணத்துப் பேரூரார் கல்வெட்டுக்கள்</t>
+          <t>இலங்கைத் தமிழ்க் கல்வெட்டுக்களின் பட்டியல்</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -26809,7 +26801,7 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுக்கள்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -26824,7 +26816,7 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%95%E0%AF%81%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AE%95%E0%AE%A3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%81%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AF%87%E0%AE%B0%E0%AF%82%E0%AE%B0%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -26841,12 +26833,12 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>தாழிகுமாரன் கல்வெட்டு (மாதோட்டம்)</t>
+          <t>அனுராதபுரம் குமாரகணத்துப் பேரூரார் கல்வெட்டுக்கள்</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -26876,7 +26868,7 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுக்கள்</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
@@ -26891,7 +26883,7 @@
       </c>
       <c r="M27" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%BE%E0%AE%B4%E0%AE%BF%E0%AE%95%E0%AF%81%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81_%28%E0%AE%AE%E0%AE%BE%E0%AE%A4%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%AE%E0%AF%8D%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%95%E0%AF%81%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AE%95%E0%AE%A3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%81%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AF%87%E0%AE%B0%E0%AF%82%E0%AE%B0%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -26913,7 +26905,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>பளமோட்டைக் கல்வெட்டு</t>
+          <t>தாழிகுமாரன் கல்வெட்டு (மாதோட்டம்)</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -26958,7 +26950,7 @@
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%B3%E0%AE%AE%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%BE%E0%AE%B4%E0%AE%BF%E0%AE%95%E0%AF%81%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81_%28%E0%AE%AE%E0%AE%BE%E0%AE%A4%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%AE%E0%AF%8D%29</t>
         </is>
       </c>
     </row>
@@ -26975,12 +26967,12 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>2015-10-11</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>மானாங்கேணிக் கல்வெட்டு</t>
+          <t>பளமோட்டைக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -27025,7 +27017,7 @@
       </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%BE%E0%AE%A9%E0%AE%BE%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%87%E0%AE%A3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%B3%E0%AE%AE%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27042,12 +27034,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>2015-10-13</t>
+          <t>2015-10-11</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>நிலாவெளிக் கல்வெட்டு</t>
+          <t>மானாங்கேணிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -27092,7 +27084,7 @@
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BF%E0%AE%B2%E0%AE%BE%E0%AE%B5%E0%AF%86%E0%AE%B3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%BE%E0%AE%A9%E0%AE%BE%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%87%E0%AE%A3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27109,12 +27101,12 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>2015-10-14</t>
+          <t>2015-10-13</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>அதரகுளிய கல்வெட்டு</t>
+          <t>நிலாவெளிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -27159,7 +27151,7 @@
       </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A4%E0%AE%B0%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%BF%E0%AE%AF_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BF%E0%AE%B2%E0%AE%BE%E0%AE%B5%E0%AF%86%E0%AE%B3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27173,7 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>ஆதகட கல்வெட்டு</t>
+          <t>அதரகுளிய கல்வெட்டு</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -27226,7 +27218,7 @@
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%86%E0%AE%A4%E0%AE%95%E0%AE%9F_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A4%E0%AE%B0%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%BF%E0%AE%AF_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27243,12 +27235,12 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2015-10-14</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>சிறுகுளத்தூர் உடையான் கல்வெட்டு</t>
+          <t>ஆதகட கல்வெட்டு</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -27293,7 +27285,7 @@
       </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AE%BF%E0%AE%B1%E0%AF%81%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%82%E0%AE%B0%E0%AF%8D_%E0%AE%89%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BE%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%86%E0%AE%A4%E0%AE%95%E0%AE%9F_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27315,7 +27307,7 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>பொலநறுவை வேளைக்காரர் கல்வெட்டு</t>
+          <t>சிறுகுளத்தூர் உடையான் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -27360,7 +27352,7 @@
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A%E0%AE%B2%E0%AE%A8%E0%AE%B1%E0%AF%81%E0%AE%B5%E0%AF%88_%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AE%BF%E0%AE%B1%E0%AF%81%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%82%E0%AE%B0%E0%AF%8D_%E0%AE%89%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BE%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27382,7 +27374,7 @@
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>மயிலன் குளம் வேளைக்காரர் கல்வெட்டு</t>
+          <t>பொலநறுவை வேளைக்காரர் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -27427,7 +27419,7 @@
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%AE%E0%AF%8D_%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A%E0%AE%B2%E0%AE%A8%E0%AE%B1%E0%AF%81%E0%AE%B5%E0%AF%88_%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27444,12 +27436,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>2015-11-29</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Department of Archaeology (Sri Lanka)</t>
+          <t>மயிலன் குளம் வேளைக்காரர் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -27459,7 +27451,7 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -27469,17 +27461,17 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
@@ -27494,7 +27486,7 @@
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Department_of_Archaeology_%28Sri_Lanka%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%AE%E0%AF%8D_%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27506,17 +27498,17 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>2014-01-12</t>
+          <t>2015-11-29</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Megalithic graffiti symbols</t>
+          <t>Department of Archaeology (Sri Lanka)</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -27541,12 +27533,12 @@
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி; Archaeology / தொல்லியல்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>megalithic</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
@@ -27561,7 +27553,7 @@
       </c>
       <c r="M37" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Megalithic_graffiti_symbols</t>
+          <t>https://en.wikipedia.org/wiki/Department_of_Archaeology_%28Sri_Lanka%29</t>
         </is>
       </c>
     </row>
@@ -27578,12 +27570,12 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2014-01-12</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் (சிற்றம்பலம்)</t>
+          <t>Megalithic graffiti symbols</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -27593,7 +27585,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -27603,11 +27595,19 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி; Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>megalithic</t>
+        </is>
+      </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -27620,7 +27620,7 @@
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3_%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D_%28%E0%AE%9A%E0%AE%BF%E0%AE%B1%E0%AF%8D%E0%AE%B1%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%B2%E0%AE%AE%E0%AF%8D%29</t>
+          <t>https://en.wikipedia.org/wiki/Megalithic_graffiti_symbols</t>
         </is>
       </c>
     </row>
@@ -27637,12 +27637,12 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>காலி மும்மொழிக் கல்வெட்டு</t>
+          <t>யாழ்ப்பாண இராச்சியம் (சிற்றம்பலம்)</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -27665,16 +27665,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="13" t="n"/>
       <c r="K39" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -27687,7 +27679,7 @@
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%BE%E0%AE%B2%E0%AE%BF_%E0%AE%AE%E0%AF%81%E0%AE%AE%E0%AF%8D%E0%AE%AE%E0%AF%8A%E0%AE%B4%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3_%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D_%28%E0%AE%9A%E0%AE%BF%E0%AE%B1%E0%AF%8D%E0%AE%B1%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%B2%E0%AE%AE%E0%AF%8D%29</t>
         </is>
       </c>
     </row>
@@ -27704,12 +27696,12 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>2014-10-08</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணத்துச் சாசனங்கள்</t>
+          <t>காலி மும்மொழிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -27737,7 +27729,11 @@
           <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
-      <c r="J40" s="9" t="n"/>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -27750,7 +27746,7 @@
       </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%81%E0%AE%9A%E0%AF%8D_%E0%AE%9A%E0%AE%BE%E0%AE%9A%E0%AE%A9%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%BE%E0%AE%B2%E0%AE%BF_%E0%AE%AE%E0%AF%81%E0%AE%AE%E0%AF%8D%E0%AE%AE%E0%AF%8A%E0%AE%B4%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27767,12 +27763,12 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>2014-10-10</t>
+          <t>2014-10-08</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>இலங்கையில் சங்ககால நாணயங்கள்</t>
+          <t>யாழ்ப்பாணத்துச் சாசனங்கள்</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -27797,7 +27793,7 @@
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J41" s="13" t="n"/>
@@ -27813,7 +27809,7 @@
       </c>
       <c r="M41" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%95%E0%AE%BE%E0%AE%B2_%E0%AE%A8%E0%AE%BE%E0%AE%A3%E0%AE%AF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%81%E0%AE%9A%E0%AF%8D_%E0%AE%9A%E0%AE%BE%E0%AE%9A%E0%AE%A9%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -27835,7 +27831,7 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>நயினாதீவுக் கல்வெட்டு</t>
+          <t>இலங்கையில் சங்ககால நாணயங்கள்</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -27860,14 +27856,10 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n"/>
       <c r="K42" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -27880,7 +27872,7 @@
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%AF%E0%AE%BF%E0%AE%A9%E0%AE%BE%E0%AE%A4%E0%AF%80%E0%AE%B5%E0%AF%81%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%95%E0%AE%BE%E0%AE%B2_%E0%AE%A8%E0%AE%BE%E0%AE%A3%E0%AE%AF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -27897,12 +27889,12 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>2014-10-11</t>
+          <t>2014-10-10</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் பிரதான வீதிக் கல்வெட்டு</t>
+          <t>நயினாதீவுக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -27947,7 +27939,7 @@
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D_%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%A4%E0%AE%BE%E0%AE%A9_%E0%AE%B5%E0%AF%80%E0%AE%A4%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%AF%E0%AE%BF%E0%AE%A9%E0%AE%BE%E0%AE%A4%E0%AF%80%E0%AE%B5%E0%AF%81%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -27964,12 +27956,12 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>2014-10-25</t>
+          <t>2014-10-11</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>கருணாகரப் பிள்ளையார் கோயிற் கல்வெட்டு</t>
+          <t>யாழ்ப்பாணம் பிரதான வீதிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -28014,7 +28006,7 @@
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%B0%E0%AF%81%E0%AE%A3%E0%AE%BE%E0%AE%95%E0%AE%B0%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AE%BF%E0%AE%B3%E0%AF%8D%E0%AE%B3%E0%AF%88%E0%AE%AF%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%AF%E0%AE%BF%E0%AE%B1%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D_%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%A4%E0%AE%BE%E0%AE%A9_%E0%AE%B5%E0%AF%80%E0%AE%A4%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -28031,12 +28023,12 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2014-10-25</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>இரத்தினபுரி தேசிய நூதனசாலை</t>
+          <t>கருணாகரப் பிள்ளையார் கோயிற் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -28059,8 +28051,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -28073,7 +28073,7 @@
       </c>
       <c r="M45" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B0%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%A9%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%BF_%E0%AE%A4%E0%AF%87%E0%AE%9A%E0%AE%BF%E0%AE%AF_%E0%AE%A8%E0%AF%82%E0%AE%A4%E0%AE%A9%E0%AE%9A%E0%AE%BE%E0%AE%B2%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%B0%E0%AF%81%E0%AE%A3%E0%AE%BE%E0%AE%95%E0%AE%B0%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AE%BF%E0%AE%B3%E0%AF%8D%E0%AE%B3%E0%AF%88%E0%AE%AF%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%AF%E0%AE%BF%E0%AE%B1%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -28085,17 +28085,17 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>2013-02-02</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>சீனர் - தமிழர் தொடர்புகள்</t>
+          <t>இரத்தினபுரி தேசிய நூதனசாலை</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AF%80%E0%AE%A9%E0%AE%B0%E0%AF%8D_-_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%B0%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%9F%E0%AE%B0%E0%AF%8D%E0%AE%AA%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B0%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%A9%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%BF_%E0%AE%A4%E0%AF%87%E0%AE%9A%E0%AE%BF%E0%AE%AF_%E0%AE%A8%E0%AF%82%E0%AE%A4%E0%AE%A9%E0%AE%9A%E0%AE%BE%E0%AE%B2%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -28149,12 +28149,12 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>2013-05-10</t>
+          <t>2013-02-02</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>வேளிர் (ஈழம்)</t>
+          <t>சீனர் - தமிழர் தொடர்புகள்</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -28191,7 +28191,7 @@
       </c>
       <c r="M47" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AE%BF%E0%AE%B0%E0%AF%8D_%28%E0%AE%88%E0%AE%B4%E0%AE%AE%E0%AF%8D%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AF%80%E0%AE%A9%E0%AE%B0%E0%AF%8D_-_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%B0%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%9F%E0%AE%B0%E0%AF%8D%E0%AE%AA%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -28208,12 +28208,12 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>2013-08-21</t>
+          <t>2013-05-10</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Archaeological Museum, Jaffna</t>
+          <t>வேளிர் (ஈழம்)</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -28223,7 +28223,7 @@
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -28233,19 +28233,11 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="n"/>
       <c r="K48" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -28258,7 +28250,7 @@
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Archaeological_Museum%2C_Jaffna</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AE%BF%E0%AE%B0%E0%AF%8D_%28%E0%AE%88%E0%AE%B4%E0%AE%AE%E0%AF%8D%29</t>
         </is>
       </c>
     </row>
@@ -28270,17 +28262,17 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>2012-01-17</t>
+          <t>2013-08-21</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>History of the Jaffna kingdom</t>
+          <t>Archaeological Museum, Jaffna</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -28303,8 +28295,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I49" s="13" t="n"/>
-      <c r="J49" s="13" t="n"/>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -28317,7 +28317,7 @@
       </c>
       <c r="M49" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/History_of_the_Jaffna_kingdom</t>
+          <t>https://en.wikipedia.org/wiki/Archaeological_Museum%2C_Jaffna</t>
         </is>
       </c>
     </row>
@@ -28334,23 +28334,27 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>2012-06-27</t>
+          <t>2012-01-17</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Prehistoric skeleton found in Sri Lanka</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="n"/>
+          <t>History of the Jaffna kingdom</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>SEAArch (Southeast Asian Archaeology)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -28358,25 +28362,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>prehistory; archaeology</t>
-        </is>
-      </c>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
       <c r="K50" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L50" s="9" t="n"/>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M50" s="10" t="inlineStr">
         <is>
-          <t>https://southeastasianarchaeology.com/2012/06/27/prehistoric-skeleton-found-in-sri-lanka</t>
+          <t>https://en.wikipedia.org/wiki/History_of_the_Jaffna_kingdom</t>
         </is>
       </c>
     </row>
@@ -28393,27 +28393,23 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>2012-07-22</t>
+          <t>2012-06-27</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Anaikoddai seal</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Prehistoric skeleton found in Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="n"/>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>SEAArch (Southeast Asian Archaeology)</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -28423,23 +28419,23 @@
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>prehistory; archaeology</t>
+        </is>
+      </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L51" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L51" s="13" t="n"/>
       <c r="M51" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Anaikoddai_seal</t>
+          <t>https://southeastasianarchaeology.com/2012/06/27/prehistoric-skeleton-found-in-sri-lanka</t>
         </is>
       </c>
     </row>
@@ -28451,17 +28447,17 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>2011-02-03</t>
+          <t>2012-07-22</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>இலங்கைத் தமிழர் வரலாறு - தமிழ் நூல் பட்டியல்</t>
+          <t>Anaikoddai seal</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -28471,7 +28467,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -28481,10 +28477,14 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="J52" s="9" t="n"/>
       <c r="K52" s="7" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
       </c>
       <c r="M52" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%B0%E0%AF%8D_%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81_-_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D_%E0%AE%A8%E0%AF%82%E0%AE%B2%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Anaikoddai_seal</t>
         </is>
       </c>
     </row>
@@ -28515,12 +28515,12 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>2011-09-01</t>
+          <t>2011-02-03</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>மட்டக்களப்பு மான்மியம்</t>
+          <t>இலங்கைத் தமிழர் வரலாறு - தமிழ் நூல் பட்டியல்</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -28557,7 +28557,7 @@
       </c>
       <c r="M53" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81_%E0%AE%AE%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%AE%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%B0%E0%AF%8D_%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81_-_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D_%E0%AE%A8%E0%AF%82%E0%AE%B2%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -28569,17 +28569,17 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>2010-08-06</t>
+          <t>2011-09-01</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>நாயன்மார்கட்டுக் கல்வெட்டு</t>
+          <t>மட்டக்களப்பு மான்மியம்</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -28602,16 +28602,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="n"/>
       <c r="K54" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -28624,7 +28616,7 @@
       </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%AF%E0%AE%A9%E0%AF%8D%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AF%8D%E0%AE%95%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81_%E0%AE%AE%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%AE%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -28641,12 +28633,12 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>2010-11-01</t>
+          <t>2010-08-06</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Tissamaharama inscription No. 53</t>
+          <t>நாயன்மார்கட்டுக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -28656,7 +28648,7 @@
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -28666,7 +28658,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I55" s="13" t="inlineStr">
@@ -28676,7 +28668,7 @@
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
@@ -28691,7 +28683,7 @@
       </c>
       <c r="M55" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tissamaharama_inscription_No._53</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%AF%E0%AE%A9%E0%AF%8D%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AF%8D%E0%AE%95%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -28703,17 +28695,17 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>2008-08-09</t>
+          <t>2010-11-01</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Prehistory of Sri Lanka</t>
+          <t>Tissamaharama inscription No. 53</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -28736,8 +28728,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -28750,7 +28750,7 @@
       </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Prehistory_of_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Tissamaharama_inscription_No._53</t>
         </is>
       </c>
     </row>
@@ -28767,12 +28767,12 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>2008-10-12</t>
+          <t>2008-08-09</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>கா. இந்திரபாலா</t>
+          <t>Prehistory of Sri Lanka</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -28782,7 +28782,7 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I57" s="13" t="n"/>
@@ -28809,7 +28809,7 @@
       </c>
       <c r="M57" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%BE._%E0%AE%87%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B0%E0%AE%AA%E0%AE%BE%E0%AE%B2%E0%AE%BE</t>
+          <t>https://en.wikipedia.org/wiki/Prehistory_of_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -28826,12 +28826,12 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>2008-12-27</t>
+          <t>2008-10-12</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Kandarodai</t>
+          <t>கா. இந்திரபாலா</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I58" s="9" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="M58" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Kandarodai</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%BE._%E0%AE%87%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B0%E0%AE%AA%E0%AE%BE%E0%AE%B2%E0%AE%BE</t>
         </is>
       </c>
     </row>
@@ -28880,17 +28880,17 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>2007-12-07</t>
+          <t>2008-12-27</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>தமிழி</t>
+          <t>Kandarodai</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -28900,7 +28900,7 @@
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -28910,7 +28910,7 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I59" s="13" t="n"/>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="M59" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%BF</t>
+          <t>https://en.wikipedia.org/wiki/Kandarodai</t>
         </is>
       </c>
     </row>
@@ -28944,12 +28944,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>2007-12-26</t>
+          <t>2007-12-07</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Naga people (Lanka)</t>
+          <t>தமிழி</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -28959,7 +28959,7 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -28969,7 +28969,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I60" s="9" t="n"/>
@@ -28986,7 +28986,7 @@
       </c>
       <c r="M60" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Naga_people_%28Lanka%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%BF</t>
         </is>
       </c>
     </row>
@@ -28998,17 +28998,17 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>2006-04-29</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>பொ. பூலோகசிங்கம்</t>
+          <t>Naga people (Lanka)</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I61" s="13" t="n"/>
@@ -29045,7 +29045,7 @@
       </c>
       <c r="M61" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A._%E0%AE%AA%E0%AF%82%E0%AE%B2%E0%AF%8B%E0%AE%95%E0%AE%9A%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Naga_people_%28Lanka%29</t>
         </is>
       </c>
     </row>
@@ -29062,12 +29062,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>2006-08-30</t>
+          <t>2006-04-29</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Velanai</t>
+          <t>பொ. பூலோகசிங்கம்</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -29077,7 +29077,7 @@
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -29087,7 +29087,7 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I62" s="9" t="n"/>
@@ -29104,7 +29104,7 @@
       </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Velanai</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A._%E0%AE%AA%E0%AF%82%E0%AE%B2%E0%AF%8B%E0%AE%95%E0%AE%9A%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -29121,12 +29121,12 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>2006-10-24</t>
+          <t>2006-08-30</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>நாடுகள் அடிப்படையில் தொல்லியல் களங்களின் பட்டியல்</t>
+          <t>Velanai</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -29136,7 +29136,7 @@
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -29146,19 +29146,11 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J63" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="n"/>
+      <c r="J63" s="13" t="n"/>
       <c r="K63" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -29171,7 +29163,7 @@
       </c>
       <c r="M63" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D_%E0%AE%85%E0%AE%9F%E0%AE%BF%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Velanai</t>
         </is>
       </c>
     </row>
@@ -29188,12 +29180,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>2006-11-07</t>
+          <t>2006-10-24</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Tamil-Brahmi</t>
+          <t>நாடுகள் அடிப்படையில் தொல்லியல் களங்களின் பட்டியல்</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -29203,7 +29195,7 @@
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -29213,17 +29205,17 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
@@ -29238,7 +29230,7 @@
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tamil-Brahmi</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D_%E0%AE%85%E0%AE%9F%E0%AE%BF%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -29248,22 +29240,34 @@
           <t>WB-0064</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="11" t="n"/>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>2006-11-07</t>
+        </is>
+      </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="n"/>
+          <t>Tamil-Brahmi</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -29273,23 +29277,27 @@
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J65" s="13" t="inlineStr">
         <is>
-          <t>archaeology; East</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="L65" s="13" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M65" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
+          <t>https://en.wikipedia.org/wiki/Tamil-Brahmi</t>
         </is>
       </c>
     </row>
@@ -29303,22 +29311,18 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Buddhism amongst Tamils in Sri Lanka</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n"/>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
@@ -29326,21 +29330,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I66" s="9" t="n"/>
-      <c r="J66" s="9" t="n"/>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>archaeology; East</t>
+        </is>
+      </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L66" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L66" s="9" t="n"/>
       <c r="M66" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
+          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
         </is>
       </c>
     </row>
@@ -29354,18 +29362,22 @@
       <c r="C67" s="11" t="n"/>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Buddhist Remains in the Jaffna Peninsula</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="n"/>
+          <t>Buddhism amongst Tamils in Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -29373,25 +29385,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J67" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; Jaffna</t>
-        </is>
-      </c>
+      <c r="I67" s="13" t="n"/>
+      <c r="J67" s="13" t="n"/>
       <c r="K67" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L67" s="13" t="n"/>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M67" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna/</t>
+          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -29405,7 +29413,7 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+          <t>Buddhist Remains in the Jaffna Peninsula</t>
         </is>
       </c>
       <c r="E68" s="9" t="n"/>
@@ -29431,7 +29439,7 @@
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Pungudutivu</t>
+          <t>தொல்லியல்; Jaffna</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
@@ -29442,7 +29450,7 @@
       <c r="L68" s="9" t="n"/>
       <c r="M68" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/tikali/</t>
+          <t>https://amazinglanka.com/wp/jaffna/</t>
         </is>
       </c>
     </row>
@@ -29456,22 +29464,18 @@
       <c r="C69" s="11" t="n"/>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Cankilian Thoppu</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="n"/>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -29479,21 +29483,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I69" s="13" t="n"/>
-      <c r="J69" s="13" t="n"/>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Pungudutivu</t>
+        </is>
+      </c>
       <c r="K69" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L69" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L69" s="13" t="n"/>
       <c r="M69" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
+          <t>https://amazinglanka.com/wp/tikali/</t>
         </is>
       </c>
     </row>
@@ -29507,7 +29515,7 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+          <t>Cankilian Thoppu</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -29530,16 +29538,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="9" t="n"/>
       <c r="K70" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -29552,7 +29552,7 @@
       </c>
       <c r="M70" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
         </is>
       </c>
     </row>
@@ -29566,18 +29566,22 @@
       <c r="C71" s="11" t="n"/>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -29592,7 +29596,7 @@
       </c>
       <c r="J71" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr">
@@ -29600,10 +29604,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L71" s="13" t="n"/>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M71" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -29617,22 +29625,18 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="n"/>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -29640,21 +29644,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I72" s="9" t="n"/>
-      <c r="J72" s="9" t="n"/>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; settlement</t>
+        </is>
+      </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L72" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L72" s="9" t="n"/>
       <c r="M72" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -29668,7 +29676,7 @@
       <c r="C73" s="11" t="n"/>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
+          <t>Sources of ancient Tamil history</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -29705,7 +29713,7 @@
       </c>
       <c r="M73" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -29719,18 +29727,22 @@
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
@@ -29738,25 +29750,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>memorial stone; Vanni</t>
-        </is>
-      </c>
+      <c r="I74" s="9" t="n"/>
+      <c r="J74" s="9" t="n"/>
       <c r="K74" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L74" s="9" t="n"/>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -29770,37 +29778,33 @@
       <c r="C75" s="11" t="n"/>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E75" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="n"/>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J75" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
@@ -29808,14 +29812,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L75" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L75" s="13" t="n"/>
       <c r="M75" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -29829,7 +29829,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -29852,8 +29852,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I76" s="9" t="n"/>
-      <c r="J76" s="9" t="n"/>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -29866,7 +29874,7 @@
       </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -29880,7 +29888,7 @@
       <c r="C77" s="11" t="n"/>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -29903,16 +29911,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J77" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+      <c r="I77" s="13" t="n"/>
+      <c r="J77" s="13" t="n"/>
       <c r="K77" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -29925,7 +29925,7 @@
       </c>
       <c r="M77" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -29939,57 +29939,269 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="9" t="inlineStr">
         <is>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia (ta)</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Encyclopedia article</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
+      <c r="M78" s="10" t="inlineStr">
+        <is>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>WB-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n"/>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
           <t>தம்பிலுவில் கல்வெட்டு</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E79" s="13" t="inlineStr">
         <is>
           <t>Wikipedia contributors</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
+      <c r="F79" s="13" t="inlineStr">
         <is>
           <t>Wikipedia (ta)</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr">
         <is>
           <t>Encyclopedia article</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="H79" s="11" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I79" s="13" t="inlineStr">
         <is>
           <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="J79" s="13" t="inlineStr">
         <is>
           <t>கல்வெட்டு</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K79" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L78" s="9" t="inlineStr">
+      <c r="L79" s="13" t="inlineStr">
         <is>
           <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
-      <c r="M78" s="10" t="inlineStr">
+      <c r="M79" s="14" t="inlineStr">
         <is>
           <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>WB-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n"/>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M80" s="10" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>WB-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="n"/>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I81" s="13" t="n"/>
+      <c r="J81" s="13" t="n"/>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L81" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M81" s="14" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>WB-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M82" s="10" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M78"/>
+  <autoFilter ref="A1:M82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -30068,6 +30280,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30079,7 +30295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N461"/>
+  <dimension ref="A1:N465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -55651,33 +55867,29 @@
       </c>
       <c r="C387" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D387" s="11" t="n"/>
       <c r="E387" s="13" t="inlineStr">
         <is>
-          <t>Sankiliyatital Archaeological Site in Jaffna</t>
-        </is>
-      </c>
-      <c r="F387" s="13" t="inlineStr">
-        <is>
-          <t>Nishan Weerasooriya</t>
-        </is>
-      </c>
+          <t>யாழ்ப்பாணம். கோட்டையை சுற்றி எல்லைக்கல் நாட்டுப் பணியில் தொல்லியல் ...</t>
+        </is>
+      </c>
+      <c r="F387" s="13" t="n"/>
       <c r="G387" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>uthayannews.ca</t>
         </is>
       </c>
       <c r="H387" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I387" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J387" s="13" t="inlineStr">
@@ -55687,7 +55899,7 @@
       </c>
       <c r="K387" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Jaffna</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="L387" s="11" t="inlineStr">
@@ -55695,10 +55907,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M387" s="13" t="n"/>
+      <c r="M387" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N387" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/sankiliyatital/</t>
+          <t>https://uthayannews.ca/2025/12/19/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AF%88-%E0%AE%9A%E0%AF%81/</t>
         </is>
       </c>
     </row>
@@ -55718,51 +55934,51 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D388" s="7" t="inlineStr">
-        <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
+      <c r="D388" s="7" t="n"/>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>தேவனாம்பிரியா</t>
+          <t>Sankiliyatital Archaeological Site in Jaffna</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia contributors</t>
+          <t>Nishan Weerasooriya</t>
         </is>
       </c>
       <c r="G388" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H388" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I388" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J388" s="9" t="n"/>
-      <c r="K388" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J388" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K388" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Jaffna</t>
+        </is>
+      </c>
       <c r="L388" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M388" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M388" s="9" t="n"/>
       <c r="N388" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%87%E0%AE%B5%E0%AE%A9%E0%AE%BE%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%AF%E0%AE%BE</t>
+          <t>https://amazinglanka.com/wp/sankiliyatital/</t>
         </is>
       </c>
     </row>
@@ -55784,12 +56000,12 @@
       </c>
       <c r="D389" s="11" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-11-13</t>
         </is>
       </c>
       <c r="E389" s="13" t="inlineStr">
         <is>
-          <t>கோமரங்கடவலை கல்வெட்டு</t>
+          <t>தேவனாம்பிரியா</t>
         </is>
       </c>
       <c r="F389" s="13" t="inlineStr">
@@ -55812,16 +56028,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J389" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K389" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J389" s="13" t="n"/>
+      <c r="K389" s="13" t="n"/>
       <c r="L389" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -55834,7 +56042,7 @@
       </c>
       <c r="N389" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AE%E0%AE%B0%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%9F%E0%AE%B5%E0%AE%B2%E0%AF%88_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%87%E0%AE%B5%E0%AE%A9%E0%AE%BE%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%AF%E0%AE%BE</t>
         </is>
       </c>
     </row>
@@ -55851,37 +56059,37 @@
       </c>
       <c r="C390" s="8" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D390" s="7" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>Tamil Inscriptions in Sri Lanka (list)</t>
+          <t>கோமரங்கடவலை கல்வெட்டு</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>Lanka Pradeepa</t>
+          <t>Wikipedia contributors</t>
         </is>
       </c>
       <c r="G390" s="9" t="inlineStr">
         <is>
-          <t>Lanka Pradeepa (lankapradeepa.com)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H390" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I390" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J390" s="9" t="inlineStr">
@@ -55891,7 +56099,7 @@
       </c>
       <c r="K390" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; list; bibliography</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L390" s="7" t="inlineStr">
@@ -55901,12 +56109,12 @@
       </c>
       <c r="M390" s="9" t="inlineStr">
         <is>
-          <t>Updated May 2023; 27 references</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N390" s="10" t="inlineStr">
         <is>
-          <t>https://www.lankapradeepa.com/2020/04/tamil-inscriptions-in-sri-lanka_16.html</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AE%E0%AE%B0%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%9F%E0%AE%B5%E0%AE%B2%E0%AF%88_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -55928,27 +56136,27 @@
       </c>
       <c r="D391" s="11" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="E391" s="13" t="inlineStr">
         <is>
-          <t>Pottery of Sri Lanka</t>
+          <t>Tamil Inscriptions in Sri Lanka (list)</t>
         </is>
       </c>
       <c r="F391" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia contributors</t>
+          <t>Lanka Pradeepa</t>
         </is>
       </c>
       <c r="G391" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Lanka Pradeepa (lankapradeepa.com)</t>
         </is>
       </c>
       <c r="H391" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I391" s="11" t="inlineStr">
@@ -55956,8 +56164,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J391" s="13" t="n"/>
-      <c r="K391" s="13" t="n"/>
+      <c r="J391" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K391" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; list; bibliography</t>
+        </is>
+      </c>
       <c r="L391" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -55965,12 +56181,12 @@
       </c>
       <c r="M391" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Updated May 2023; 27 references</t>
         </is>
       </c>
       <c r="N391" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pottery_of_Sri_Lanka</t>
+          <t>https://www.lankapradeepa.com/2020/04/tamil-inscriptions-in-sri-lanka_16.html</t>
         </is>
       </c>
     </row>
@@ -55987,17 +56203,17 @@
       </c>
       <c r="C392" s="8" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D392" s="7" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions</t>
+          <t>Pottery of Sri Lanka</t>
         </is>
       </c>
       <c r="F392" s="9" t="inlineStr">
@@ -56020,16 +56236,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J392" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K392" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="J392" s="9" t="n"/>
+      <c r="K392" s="9" t="n"/>
       <c r="L392" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -56042,7 +56250,7 @@
       </c>
       <c r="N392" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tamil_inscriptions</t>
+          <t>https://en.wikipedia.org/wiki/Pottery_of_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -56064,12 +56272,12 @@
       </c>
       <c r="D393" s="11" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="E393" s="13" t="inlineStr">
         <is>
-          <t>வெடுக்குநாறிமலை ஆதி லிங்கேஸ்வரர் ஆலயம்</t>
+          <t>Tamil inscriptions</t>
         </is>
       </c>
       <c r="F393" s="13" t="inlineStr">
@@ -56079,7 +56287,7 @@
       </c>
       <c r="G393" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H393" s="11" t="inlineStr">
@@ -56089,11 +56297,19 @@
       </c>
       <c r="I393" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J393" s="13" t="n"/>
-      <c r="K393" s="13" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J393" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K393" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="L393" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -56106,7 +56322,7 @@
       </c>
       <c r="N393" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%81%E0%AE%A8%E0%AE%BE%E0%AE%B1%E0%AE%BF%E0%AE%AE%E0%AE%B2%E0%AF%88_%E0%AE%86%E0%AE%A4%E0%AE%BF_%E0%AE%B2%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%87%E0%AE%B8%E0%AF%8D%E0%AE%B5%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%86%E0%AE%B2%E0%AE%AF%E0%AE%AE%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Tamil_inscriptions</t>
         </is>
       </c>
     </row>
@@ -56123,17 +56339,17 @@
       </c>
       <c r="C394" s="8" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D394" s="7" t="inlineStr">
         <is>
-          <t>2017-01-15</t>
+          <t>2019-09-08</t>
         </is>
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>Mantri Manai</t>
+          <t>வெடுக்குநாறிமலை ஆதி லிங்கேஸ்வரர் ஆலயம்</t>
         </is>
       </c>
       <c r="F394" s="9" t="inlineStr">
@@ -56143,7 +56359,7 @@
       </c>
       <c r="G394" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H394" s="7" t="inlineStr">
@@ -56153,7 +56369,7 @@
       </c>
       <c r="I394" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J394" s="9" t="n"/>
@@ -56170,7 +56386,7 @@
       </c>
       <c r="N394" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Mantri_Manai</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%81%E0%AE%A8%E0%AE%BE%E0%AE%B1%E0%AE%BF%E0%AE%AE%E0%AE%B2%E0%AF%88_%E0%AE%86%E0%AE%A4%E0%AE%BF_%E0%AE%B2%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%87%E0%AE%B8%E0%AF%8D%E0%AE%B5%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%86%E0%AE%B2%E0%AE%AF%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -56187,17 +56403,17 @@
       </c>
       <c r="C395" s="12" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D395" s="11" t="inlineStr">
         <is>
-          <t>2016-01-15</t>
+          <t>2017-01-15</t>
         </is>
       </c>
       <c r="E395" s="13" t="inlineStr">
         <is>
-          <t>நாடு காட்டுப் பரவணிக் கல்வெட்டு</t>
+          <t>Mantri Manai</t>
         </is>
       </c>
       <c r="F395" s="13" t="inlineStr">
@@ -56207,7 +56423,7 @@
       </c>
       <c r="G395" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H395" s="11" t="inlineStr">
@@ -56217,19 +56433,11 @@
       </c>
       <c r="I395" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J395" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K395" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J395" s="13" t="n"/>
+      <c r="K395" s="13" t="n"/>
       <c r="L395" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -56242,7 +56450,7 @@
       </c>
       <c r="N395" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81_%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AE%B0%E0%AE%B5%E0%AE%A3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://en.wikipedia.org/wiki/Mantri_Manai</t>
         </is>
       </c>
     </row>
@@ -56264,12 +56472,12 @@
       </c>
       <c r="D396" s="7" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-01-15</t>
         </is>
       </c>
       <c r="E396" s="9" t="inlineStr">
         <is>
-          <t>Velgam Vehera</t>
+          <t>நாடு காட்டுப் பரவணிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F396" s="9" t="inlineStr">
@@ -56279,7 +56487,7 @@
       </c>
       <c r="G396" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H396" s="7" t="inlineStr">
@@ -56289,11 +56497,19 @@
       </c>
       <c r="I396" s="7" t="inlineStr">
         <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="J396" s="9" t="n"/>
-      <c r="K396" s="9" t="n"/>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J396" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K396" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L396" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -56306,7 +56522,7 @@
       </c>
       <c r="N396" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Velgam_Vehera</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81_%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AE%B0%E0%AE%B5%E0%AE%A3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -56328,12 +56544,12 @@
       </c>
       <c r="D397" s="11" t="inlineStr">
         <is>
-          <t>2016-04-03</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="E397" s="13" t="inlineStr">
         <is>
-          <t>Kulakkottan</t>
+          <t>Velgam Vehera</t>
         </is>
       </c>
       <c r="F397" s="13" t="inlineStr">
@@ -56370,7 +56586,7 @@
       </c>
       <c r="N397" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Kulakkottan</t>
+          <t>https://en.wikipedia.org/wiki/Velgam_Vehera</t>
         </is>
       </c>
     </row>
@@ -56392,12 +56608,12 @@
       </c>
       <c r="D398" s="7" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-03</t>
         </is>
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண மாவட்டத்தில் தொல்லியல் ரீதியாக பாதுகாக்கப்பட்ட நினைவுச் சின்னங்களின் பட்டியல்</t>
+          <t>Kulakkottan</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
@@ -56407,7 +56623,7 @@
       </c>
       <c r="G398" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H398" s="7" t="inlineStr">
@@ -56417,19 +56633,11 @@
       </c>
       <c r="I398" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J398" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K398" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J398" s="9" t="n"/>
+      <c r="K398" s="9" t="n"/>
       <c r="L398" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -56442,7 +56650,7 @@
       </c>
       <c r="N398" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3_%E0%AE%AE%E0%AE%BE%E0%AE%B5%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%B0%E0%AF%80%E0%AE%A4%E0%AE%BF%E0%AE%AF%E0%AE%BE%E0%AE%95_%E0%AE%AA%E0%AE%BE%E0%AE%A4%E0%AF%81%E0%AE%95%E0%AE%BE%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F_%E0%AE%A8%E0%AE%BF%E0%AE%A9%E0%AF%88%E0%AE%B5%E0%AF%81%E0%AE%9A%E0%AF%8D_%E0%AE%9A%E0%AE%BF%E0%AE%A9%E0%AF%8D%E0%AE%A9%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Kulakkottan</t>
         </is>
       </c>
     </row>
@@ -56464,12 +56672,12 @@
       </c>
       <c r="D399" s="11" t="inlineStr">
         <is>
-          <t>2016-12-31</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="E399" s="13" t="inlineStr">
         <is>
-          <t>கந்தரோடை தொல்லியல் களம்</t>
+          <t>யாழ்ப்பாண மாவட்டத்தில் தொல்லியல் ரீதியாக பாதுகாக்கப்பட்ட நினைவுச் சின்னங்களின் பட்டியல்</t>
         </is>
       </c>
       <c r="F399" s="13" t="inlineStr">
@@ -56514,7 +56722,7 @@
       </c>
       <c r="N399" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%B0%E0%AF%8B%E0%AE%9F%E0%AF%88_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%AE%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3_%E0%AE%AE%E0%AE%BE%E0%AE%B5%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%B0%E0%AF%80%E0%AE%A4%E0%AE%BF%E0%AE%AF%E0%AE%BE%E0%AE%95_%E0%AE%AA%E0%AE%BE%E0%AE%A4%E0%AF%81%E0%AE%95%E0%AE%BE%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F_%E0%AE%A8%E0%AE%BF%E0%AE%A9%E0%AF%88%E0%AE%B5%E0%AF%81%E0%AE%9A%E0%AF%8D_%E0%AE%9A%E0%AE%BF%E0%AE%A9%E0%AF%8D%E0%AE%A9%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -56531,17 +56739,17 @@
       </c>
       <c r="C400" s="8" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D400" s="7" t="inlineStr">
         <is>
-          <t>2015-02-22</t>
+          <t>2016-12-31</t>
         </is>
       </c>
       <c r="E400" s="9" t="inlineStr">
         <is>
-          <t>ஆ. வேலுப்பிள்ளை</t>
+          <t>கந்தரோடை தொல்லியல் களம்</t>
         </is>
       </c>
       <c r="F400" s="9" t="inlineStr">
@@ -56564,8 +56772,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J400" s="9" t="n"/>
-      <c r="K400" s="9" t="n"/>
+      <c r="J400" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K400" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
       <c r="L400" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -56578,7 +56794,7 @@
       </c>
       <c r="N400" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%86._%E0%AE%B5%E0%AF%87%E0%AE%B2%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B3%E0%AF%8D%E0%AE%B3%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%B0%E0%AF%8B%E0%AE%9F%E0%AF%88_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -56600,12 +56816,12 @@
       </c>
       <c r="D401" s="11" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
+          <t>2015-02-22</t>
         </is>
       </c>
       <c r="E401" s="13" t="inlineStr">
         <is>
-          <t>வெஸ்ஸகிரிய</t>
+          <t>ஆ. வேலுப்பிள்ளை</t>
         </is>
       </c>
       <c r="F401" s="13" t="inlineStr">
@@ -56642,7 +56858,7 @@
       </c>
       <c r="N401" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%86%E0%AE%B8%E0%AF%8D%E0%AE%B8%E0%AE%95%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%AF</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%86._%E0%AE%B5%E0%AF%87%E0%AE%B2%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B3%E0%AF%8D%E0%AE%B3%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -56664,12 +56880,12 @@
       </c>
       <c r="D402" s="7" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="E402" s="9" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் அருங்காட்சியகம்</t>
+          <t>வெஸ்ஸகிரிய</t>
         </is>
       </c>
       <c r="F402" s="9" t="inlineStr">
@@ -56706,7 +56922,7 @@
       </c>
       <c r="N402" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%85%E0%AE%B0%E0%AF%81%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%86%E0%AE%B8%E0%AF%8D%E0%AE%B8%E0%AE%95%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%AF</t>
         </is>
       </c>
     </row>
@@ -56733,7 +56949,7 @@
       </c>
       <c r="E403" s="13" t="inlineStr">
         <is>
-          <t>சேனரத் பரணவிதான</t>
+          <t>அனுராதபுரம் அருங்காட்சியகம்</t>
         </is>
       </c>
       <c r="F403" s="13" t="inlineStr">
@@ -56770,7 +56986,7 @@
       </c>
       <c r="N403" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AF%87%E0%AE%A9%E0%AE%B0%E0%AE%A4%E0%AF%8D_%E0%AE%AA%E0%AE%B0%E0%AE%A3%E0%AE%B5%E0%AE%BF%E0%AE%A4%E0%AE%BE%E0%AE%A9</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%85%E0%AE%B0%E0%AF%81%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -56797,7 +57013,7 @@
       </c>
       <c r="E404" s="9" t="inlineStr">
         <is>
-          <t>தொல்பொருள் காட்சிச்சாலை, வவுனியா</t>
+          <t>சேனரத் பரணவிதான</t>
         </is>
       </c>
       <c r="F404" s="9" t="inlineStr">
@@ -56820,16 +57036,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J404" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K404" s="9" t="inlineStr">
-        <is>
-          <t>தொல்பொருள்</t>
-        </is>
-      </c>
+      <c r="J404" s="9" t="n"/>
+      <c r="K404" s="9" t="n"/>
       <c r="L404" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -56842,7 +57050,7 @@
       </c>
       <c r="N404" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%AA%E0%AF%8A%E0%AE%B0%E0%AF%81%E0%AE%B3%E0%AF%8D_%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BE%E0%AE%B2%E0%AF%88%2C_%E0%AE%B5%E0%AE%B5%E0%AF%81%E0%AE%A9%E0%AE%BF%E0%AE%AF%E0%AE%BE</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AF%87%E0%AE%A9%E0%AE%B0%E0%AE%A4%E0%AF%8D_%E0%AE%AA%E0%AE%B0%E0%AE%A3%E0%AE%B5%E0%AE%BF%E0%AE%A4%E0%AE%BE%E0%AE%A9</t>
         </is>
       </c>
     </row>
@@ -56864,12 +57072,12 @@
       </c>
       <c r="D405" s="11" t="inlineStr">
         <is>
-          <t>2015-07-23</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="E405" s="13" t="inlineStr">
         <is>
-          <t>சிரான் உபேந்திர தெரணியகல</t>
+          <t>தொல்பொருள் காட்சிச்சாலை, வவுனியா</t>
         </is>
       </c>
       <c r="F405" s="13" t="inlineStr">
@@ -56892,8 +57100,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J405" s="13" t="n"/>
-      <c r="K405" s="13" t="n"/>
+      <c r="J405" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K405" s="13" t="inlineStr">
+        <is>
+          <t>தொல்பொருள்</t>
+        </is>
+      </c>
       <c r="L405" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -56906,7 +57122,7 @@
       </c>
       <c r="N405" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%A9%E0%AF%8D_%E0%AE%89%E0%AE%AA%E0%AF%87%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B0_%E0%AE%A4%E0%AF%86%E0%AE%B0%E0%AE%A3%E0%AE%BF%E0%AE%AF%E0%AE%95%E0%AE%B2</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%AA%E0%AF%8A%E0%AE%B0%E0%AF%81%E0%AE%B3%E0%AF%8D_%E0%AE%95%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BE%E0%AE%B2%E0%AF%88%2C_%E0%AE%B5%E0%AE%B5%E0%AF%81%E0%AE%A9%E0%AE%BF%E0%AE%AF%E0%AE%BE</t>
         </is>
       </c>
     </row>
@@ -56928,12 +57144,12 @@
       </c>
       <c r="D406" s="7" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
+          <t>2015-07-23</t>
         </is>
       </c>
       <c r="E406" s="9" t="inlineStr">
         <is>
-          <t>தொல்பொருளியல் திணைக்களம், இலங்கை</t>
+          <t>சிரான் உபேந்திர தெரணியகல</t>
         </is>
       </c>
       <c r="F406" s="9" t="inlineStr">
@@ -56970,7 +57186,7 @@
       </c>
       <c r="N406" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%AA%E0%AF%8A%E0%AE%B0%E0%AF%81%E0%AE%B3%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AE%BF%E0%AE%A3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%AE%E0%AF%8D%2C_%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%A9%E0%AF%8D_%E0%AE%89%E0%AE%AA%E0%AF%87%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B0_%E0%AE%A4%E0%AF%86%E0%AE%B0%E0%AE%A3%E0%AE%BF%E0%AE%AF%E0%AE%95%E0%AE%B2</t>
         </is>
       </c>
     </row>
@@ -56992,12 +57208,12 @@
       </c>
       <c r="D407" s="11" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2015-07-24</t>
         </is>
       </c>
       <c r="E407" s="13" t="inlineStr">
         <is>
-          <t>அபயகிரித் தமிழ்க் கல்வெட்டு</t>
+          <t>தொல்பொருளியல் திணைக்களம், இலங்கை</t>
         </is>
       </c>
       <c r="F407" s="13" t="inlineStr">
@@ -57020,16 +57236,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J407" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K407" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J407" s="13" t="n"/>
+      <c r="K407" s="13" t="n"/>
       <c r="L407" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -57042,7 +57250,7 @@
       </c>
       <c r="N407" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%AA%E0%AE%AF%E0%AE%95%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%AA%E0%AF%8A%E0%AE%B0%E0%AF%81%E0%AE%B3%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AE%BF%E0%AE%A3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%AE%E0%AF%8D%2C_%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -57069,7 +57277,7 @@
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>இலங்கைத் தமிழ்க் கல்வெட்டுக்களின் பட்டியல்</t>
+          <t>அபயகிரித் தமிழ்க் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F408" s="9" t="inlineStr">
@@ -57114,7 +57322,7 @@
       </c>
       <c r="N408" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%AA%E0%AE%AF%E0%AE%95%E0%AE%BF%E0%AE%B0%E0%AE%BF%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57136,12 +57344,12 @@
       </c>
       <c r="D409" s="11" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="E409" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் குமாரகணத்துப் பேரூரார் கல்வெட்டுக்கள்</t>
+          <t>இலங்கைத் தமிழ்க் கல்வெட்டுக்களின் பட்டியல்</t>
         </is>
       </c>
       <c r="F409" s="13" t="inlineStr">
@@ -57171,7 +57379,7 @@
       </c>
       <c r="K409" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுக்கள்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L409" s="11" t="inlineStr">
@@ -57186,7 +57394,7 @@
       </c>
       <c r="N409" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%95%E0%AF%81%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AE%95%E0%AE%A3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%81%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AF%87%E0%AE%B0%E0%AF%82%E0%AE%B0%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -57208,12 +57416,12 @@
       </c>
       <c r="D410" s="7" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="E410" s="9" t="inlineStr">
         <is>
-          <t>தாழிகுமாரன் கல்வெட்டு (மாதோட்டம்)</t>
+          <t>அனுராதபுரம் குமாரகணத்துப் பேரூரார் கல்வெட்டுக்கள்</t>
         </is>
       </c>
       <c r="F410" s="9" t="inlineStr">
@@ -57243,7 +57451,7 @@
       </c>
       <c r="K410" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுக்கள்</t>
         </is>
       </c>
       <c r="L410" s="7" t="inlineStr">
@@ -57258,7 +57466,7 @@
       </c>
       <c r="N410" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%BE%E0%AE%B4%E0%AE%BF%E0%AE%95%E0%AF%81%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81_%28%E0%AE%AE%E0%AE%BE%E0%AE%A4%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%AE%E0%AF%8D%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%95%E0%AF%81%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AE%95%E0%AE%A3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%81%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AF%87%E0%AE%B0%E0%AF%82%E0%AE%B0%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -57285,7 +57493,7 @@
       </c>
       <c r="E411" s="13" t="inlineStr">
         <is>
-          <t>பளமோட்டைக் கல்வெட்டு</t>
+          <t>தாழிகுமாரன் கல்வெட்டு (மாதோட்டம்)</t>
         </is>
       </c>
       <c r="F411" s="13" t="inlineStr">
@@ -57330,7 +57538,7 @@
       </c>
       <c r="N411" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%B3%E0%AE%AE%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%BE%E0%AE%B4%E0%AE%BF%E0%AE%95%E0%AF%81%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81_%28%E0%AE%AE%E0%AE%BE%E0%AE%A4%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%AE%E0%AF%8D%29</t>
         </is>
       </c>
     </row>
@@ -57352,12 +57560,12 @@
       </c>
       <c r="D412" s="7" t="inlineStr">
         <is>
-          <t>2015-10-11</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="E412" s="9" t="inlineStr">
         <is>
-          <t>மானாங்கேணிக் கல்வெட்டு</t>
+          <t>பளமோட்டைக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F412" s="9" t="inlineStr">
@@ -57402,7 +57610,7 @@
       </c>
       <c r="N412" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%BE%E0%AE%A9%E0%AE%BE%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%87%E0%AE%A3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%B3%E0%AE%AE%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57424,12 +57632,12 @@
       </c>
       <c r="D413" s="11" t="inlineStr">
         <is>
-          <t>2015-10-13</t>
+          <t>2015-10-11</t>
         </is>
       </c>
       <c r="E413" s="13" t="inlineStr">
         <is>
-          <t>நிலாவெளிக் கல்வெட்டு</t>
+          <t>மானாங்கேணிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F413" s="13" t="inlineStr">
@@ -57474,7 +57682,7 @@
       </c>
       <c r="N413" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BF%E0%AE%B2%E0%AE%BE%E0%AE%B5%E0%AF%86%E0%AE%B3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%BE%E0%AE%A9%E0%AE%BE%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%87%E0%AE%A3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57496,12 +57704,12 @@
       </c>
       <c r="D414" s="7" t="inlineStr">
         <is>
-          <t>2015-10-14</t>
+          <t>2015-10-13</t>
         </is>
       </c>
       <c r="E414" s="9" t="inlineStr">
         <is>
-          <t>அதரகுளிய கல்வெட்டு</t>
+          <t>நிலாவெளிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F414" s="9" t="inlineStr">
@@ -57546,7 +57754,7 @@
       </c>
       <c r="N414" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A4%E0%AE%B0%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%BF%E0%AE%AF_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BF%E0%AE%B2%E0%AE%BE%E0%AE%B5%E0%AF%86%E0%AE%B3%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57573,7 +57781,7 @@
       </c>
       <c r="E415" s="13" t="inlineStr">
         <is>
-          <t>ஆதகட கல்வெட்டு</t>
+          <t>அதரகுளிய கல்வெட்டு</t>
         </is>
       </c>
       <c r="F415" s="13" t="inlineStr">
@@ -57618,7 +57826,7 @@
       </c>
       <c r="N415" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%86%E0%AE%A4%E0%AE%95%E0%AE%9F_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A4%E0%AE%B0%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%BF%E0%AE%AF_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57640,12 +57848,12 @@
       </c>
       <c r="D416" s="7" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2015-10-14</t>
         </is>
       </c>
       <c r="E416" s="9" t="inlineStr">
         <is>
-          <t>சிறுகுளத்தூர் உடையான் கல்வெட்டு</t>
+          <t>ஆதகட கல்வெட்டு</t>
         </is>
       </c>
       <c r="F416" s="9" t="inlineStr">
@@ -57690,7 +57898,7 @@
       </c>
       <c r="N416" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AE%BF%E0%AE%B1%E0%AF%81%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%82%E0%AE%B0%E0%AF%8D_%E0%AE%89%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BE%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%86%E0%AE%A4%E0%AE%95%E0%AE%9F_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57717,7 +57925,7 @@
       </c>
       <c r="E417" s="13" t="inlineStr">
         <is>
-          <t>பொலநறுவை வேளைக்காரர் கல்வெட்டு</t>
+          <t>சிறுகுளத்தூர் உடையான் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F417" s="13" t="inlineStr">
@@ -57762,7 +57970,7 @@
       </c>
       <c r="N417" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A%E0%AE%B2%E0%AE%A8%E0%AE%B1%E0%AF%81%E0%AE%B5%E0%AF%88_%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AE%BF%E0%AE%B1%E0%AF%81%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%82%E0%AE%B0%E0%AF%8D_%E0%AE%89%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BE%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57789,7 +57997,7 @@
       </c>
       <c r="E418" s="9" t="inlineStr">
         <is>
-          <t>மயிலன் குளம் வேளைக்காரர் கல்வெட்டு</t>
+          <t>பொலநறுவை வேளைக்காரர் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F418" s="9" t="inlineStr">
@@ -57834,7 +58042,7 @@
       </c>
       <c r="N418" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%AE%E0%AF%8D_%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A%E0%AE%B2%E0%AE%A8%E0%AE%B1%E0%AF%81%E0%AE%B5%E0%AF%88_%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57856,12 +58064,12 @@
       </c>
       <c r="D419" s="11" t="inlineStr">
         <is>
-          <t>2015-11-29</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="E419" s="13" t="inlineStr">
         <is>
-          <t>Department of Archaeology (Sri Lanka)</t>
+          <t>மயிலன் குளம் வேளைக்காரர் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F419" s="13" t="inlineStr">
@@ -57871,7 +58079,7 @@
       </c>
       <c r="G419" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H419" s="11" t="inlineStr">
@@ -57881,17 +58089,17 @@
       </c>
       <c r="I419" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J419" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K419" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L419" s="11" t="inlineStr">
@@ -57906,7 +58114,7 @@
       </c>
       <c r="N419" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Department_of_Archaeology_%28Sri_Lanka%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%81%E0%AE%B3%E0%AE%AE%E0%AF%8D_%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%BE%E0%AE%B0%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -57923,17 +58131,17 @@
       </c>
       <c r="C420" s="8" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D420" s="7" t="inlineStr">
         <is>
-          <t>2014-01-12</t>
+          <t>2015-11-29</t>
         </is>
       </c>
       <c r="E420" s="9" t="inlineStr">
         <is>
-          <t>Megalithic graffiti symbols</t>
+          <t>Department of Archaeology (Sri Lanka)</t>
         </is>
       </c>
       <c r="F420" s="9" t="inlineStr">
@@ -57958,12 +58166,12 @@
       </c>
       <c r="J420" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி; Archaeology / தொல்லியல்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K420" s="9" t="inlineStr">
         <is>
-          <t>megalithic</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="L420" s="7" t="inlineStr">
@@ -57978,7 +58186,7 @@
       </c>
       <c r="N420" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Megalithic_graffiti_symbols</t>
+          <t>https://en.wikipedia.org/wiki/Department_of_Archaeology_%28Sri_Lanka%29</t>
         </is>
       </c>
     </row>
@@ -58000,12 +58208,12 @@
       </c>
       <c r="D421" s="11" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2014-01-12</t>
         </is>
       </c>
       <c r="E421" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் (சிற்றம்பலம்)</t>
+          <t>Megalithic graffiti symbols</t>
         </is>
       </c>
       <c r="F421" s="13" t="inlineStr">
@@ -58015,7 +58223,7 @@
       </c>
       <c r="G421" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H421" s="11" t="inlineStr">
@@ -58025,11 +58233,19 @@
       </c>
       <c r="I421" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J421" s="13" t="n"/>
-      <c r="K421" s="13" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J421" s="13" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி; Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K421" s="13" t="inlineStr">
+        <is>
+          <t>megalithic</t>
+        </is>
+      </c>
       <c r="L421" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -58042,7 +58258,7 @@
       </c>
       <c r="N421" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3_%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D_%28%E0%AE%9A%E0%AE%BF%E0%AE%B1%E0%AF%8D%E0%AE%B1%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%B2%E0%AE%AE%E0%AF%8D%29</t>
+          <t>https://en.wikipedia.org/wiki/Megalithic_graffiti_symbols</t>
         </is>
       </c>
     </row>
@@ -58064,12 +58280,12 @@
       </c>
       <c r="D422" s="7" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="E422" s="9" t="inlineStr">
         <is>
-          <t>காலி மும்மொழிக் கல்வெட்டு</t>
+          <t>யாழ்ப்பாண இராச்சியம் (சிற்றம்பலம்)</t>
         </is>
       </c>
       <c r="F422" s="9" t="inlineStr">
@@ -58092,16 +58308,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J422" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K422" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J422" s="9" t="n"/>
+      <c r="K422" s="9" t="n"/>
       <c r="L422" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -58114,7 +58322,7 @@
       </c>
       <c r="N422" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%BE%E0%AE%B2%E0%AE%BF_%E0%AE%AE%E0%AF%81%E0%AE%AE%E0%AF%8D%E0%AE%AE%E0%AF%8A%E0%AE%B4%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3_%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D_%28%E0%AE%9A%E0%AE%BF%E0%AE%B1%E0%AF%8D%E0%AE%B1%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%B2%E0%AE%AE%E0%AF%8D%29</t>
         </is>
       </c>
     </row>
@@ -58136,12 +58344,12 @@
       </c>
       <c r="D423" s="11" t="inlineStr">
         <is>
-          <t>2014-10-08</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="E423" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணத்துச் சாசனங்கள்</t>
+          <t>காலி மும்மொழிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F423" s="13" t="inlineStr">
@@ -58169,7 +58377,11 @@
           <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
-      <c r="K423" s="13" t="n"/>
+      <c r="K423" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L423" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -58182,7 +58394,7 @@
       </c>
       <c r="N423" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%81%E0%AE%9A%E0%AF%8D_%E0%AE%9A%E0%AE%BE%E0%AE%9A%E0%AE%A9%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%BE%E0%AE%B2%E0%AE%BF_%E0%AE%AE%E0%AF%81%E0%AE%AE%E0%AF%8D%E0%AE%AE%E0%AF%8A%E0%AE%B4%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -58204,12 +58416,12 @@
       </c>
       <c r="D424" s="7" t="inlineStr">
         <is>
-          <t>2014-10-10</t>
+          <t>2014-10-08</t>
         </is>
       </c>
       <c r="E424" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் சங்ககால நாணயங்கள்</t>
+          <t>யாழ்ப்பாணத்துச் சாசனங்கள்</t>
         </is>
       </c>
       <c r="F424" s="9" t="inlineStr">
@@ -58234,7 +58446,7 @@
       </c>
       <c r="J424" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K424" s="9" t="n"/>
@@ -58250,7 +58462,7 @@
       </c>
       <c r="N424" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%95%E0%AE%BE%E0%AE%B2_%E0%AE%A8%E0%AE%BE%E0%AE%A3%E0%AE%AF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AF%81%E0%AE%9A%E0%AF%8D_%E0%AE%9A%E0%AE%BE%E0%AE%9A%E0%AE%A9%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -58277,7 +58489,7 @@
       </c>
       <c r="E425" s="13" t="inlineStr">
         <is>
-          <t>நயினாதீவுக் கல்வெட்டு</t>
+          <t>இலங்கையில் சங்ககால நாணயங்கள்</t>
         </is>
       </c>
       <c r="F425" s="13" t="inlineStr">
@@ -58302,14 +58514,10 @@
       </c>
       <c r="J425" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K425" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K425" s="13" t="n"/>
       <c r="L425" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -58322,7 +58530,7 @@
       </c>
       <c r="N425" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%AF%E0%AE%BF%E0%AE%A9%E0%AE%BE%E0%AE%A4%E0%AF%80%E0%AE%B5%E0%AF%81%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%95%E0%AE%BE%E0%AE%B2_%E0%AE%A8%E0%AE%BE%E0%AE%A3%E0%AE%AF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -58344,12 +58552,12 @@
       </c>
       <c r="D426" s="7" t="inlineStr">
         <is>
-          <t>2014-10-11</t>
+          <t>2014-10-10</t>
         </is>
       </c>
       <c r="E426" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் பிரதான வீதிக் கல்வெட்டு</t>
+          <t>நயினாதீவுக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F426" s="9" t="inlineStr">
@@ -58394,7 +58602,7 @@
       </c>
       <c r="N426" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D_%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%A4%E0%AE%BE%E0%AE%A9_%E0%AE%B5%E0%AF%80%E0%AE%A4%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%AF%E0%AE%BF%E0%AE%A9%E0%AE%BE%E0%AE%A4%E0%AF%80%E0%AE%B5%E0%AF%81%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -58416,12 +58624,12 @@
       </c>
       <c r="D427" s="11" t="inlineStr">
         <is>
-          <t>2014-10-25</t>
+          <t>2014-10-11</t>
         </is>
       </c>
       <c r="E427" s="13" t="inlineStr">
         <is>
-          <t>கருணாகரப் பிள்ளையார் கோயிற் கல்வெட்டு</t>
+          <t>யாழ்ப்பாணம் பிரதான வீதிக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F427" s="13" t="inlineStr">
@@ -58466,7 +58674,7 @@
       </c>
       <c r="N427" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%B0%E0%AF%81%E0%AE%A3%E0%AE%BE%E0%AE%95%E0%AE%B0%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AE%BF%E0%AE%B3%E0%AF%8D%E0%AE%B3%E0%AF%88%E0%AE%AF%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%AF%E0%AE%BF%E0%AE%B1%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D_%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%A4%E0%AE%BE%E0%AE%A9_%E0%AE%B5%E0%AF%80%E0%AE%A4%E0%AE%BF%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -58488,12 +58696,12 @@
       </c>
       <c r="D428" s="7" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2014-10-25</t>
         </is>
       </c>
       <c r="E428" s="9" t="inlineStr">
         <is>
-          <t>இரத்தினபுரி தேசிய நூதனசாலை</t>
+          <t>கருணாகரப் பிள்ளையார் கோயிற் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F428" s="9" t="inlineStr">
@@ -58516,8 +58724,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J428" s="9" t="n"/>
-      <c r="K428" s="9" t="n"/>
+      <c r="J428" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K428" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L428" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -58530,7 +58746,7 @@
       </c>
       <c r="N428" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B0%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%A9%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%BF_%E0%AE%A4%E0%AF%87%E0%AE%9A%E0%AE%BF%E0%AE%AF_%E0%AE%A8%E0%AF%82%E0%AE%A4%E0%AE%A9%E0%AE%9A%E0%AE%BE%E0%AE%B2%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%B0%E0%AF%81%E0%AE%A3%E0%AE%BE%E0%AE%95%E0%AE%B0%E0%AE%AA%E0%AF%8D_%E0%AE%AA%E0%AE%BF%E0%AE%B3%E0%AF%8D%E0%AE%B3%E0%AF%88%E0%AE%AF%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%AF%E0%AE%BF%E0%AE%B1%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -58547,17 +58763,17 @@
       </c>
       <c r="C429" s="12" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D429" s="11" t="inlineStr">
         <is>
-          <t>2013-02-02</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="E429" s="13" t="inlineStr">
         <is>
-          <t>சீனர் - தமிழர் தொடர்புகள்</t>
+          <t>இரத்தினபுரி தேசிய நூதனசாலை</t>
         </is>
       </c>
       <c r="F429" s="13" t="inlineStr">
@@ -58594,7 +58810,7 @@
       </c>
       <c r="N429" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AF%80%E0%AE%A9%E0%AE%B0%E0%AF%8D_-_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%B0%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%9F%E0%AE%B0%E0%AF%8D%E0%AE%AA%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B0%E0%AE%A4%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%A9%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%BF_%E0%AE%A4%E0%AF%87%E0%AE%9A%E0%AE%BF%E0%AE%AF_%E0%AE%A8%E0%AF%82%E0%AE%A4%E0%AE%A9%E0%AE%9A%E0%AE%BE%E0%AE%B2%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -58616,12 +58832,12 @@
       </c>
       <c r="D430" s="7" t="inlineStr">
         <is>
-          <t>2013-05-10</t>
+          <t>2013-02-02</t>
         </is>
       </c>
       <c r="E430" s="9" t="inlineStr">
         <is>
-          <t>வேளிர் (ஈழம்)</t>
+          <t>சீனர் - தமிழர் தொடர்புகள்</t>
         </is>
       </c>
       <c r="F430" s="9" t="inlineStr">
@@ -58658,7 +58874,7 @@
       </c>
       <c r="N430" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AE%BF%E0%AE%B0%E0%AF%8D_%28%E0%AE%88%E0%AE%B4%E0%AE%AE%E0%AF%8D%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%9A%E0%AF%80%E0%AE%A9%E0%AE%B0%E0%AF%8D_-_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%B0%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%9F%E0%AE%B0%E0%AF%8D%E0%AE%AA%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -58680,12 +58896,12 @@
       </c>
       <c r="D431" s="11" t="inlineStr">
         <is>
-          <t>2013-08-21</t>
+          <t>2013-05-10</t>
         </is>
       </c>
       <c r="E431" s="13" t="inlineStr">
         <is>
-          <t>Archaeological Museum, Jaffna</t>
+          <t>வேளிர் (ஈழம்)</t>
         </is>
       </c>
       <c r="F431" s="13" t="inlineStr">
@@ -58695,7 +58911,7 @@
       </c>
       <c r="G431" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H431" s="11" t="inlineStr">
@@ -58705,19 +58921,11 @@
       </c>
       <c r="I431" s="11" t="inlineStr">
         <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="J431" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K431" s="13" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J431" s="13" t="n"/>
+      <c r="K431" s="13" t="n"/>
       <c r="L431" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -58730,7 +58938,7 @@
       </c>
       <c r="N431" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Archaeological_Museum%2C_Jaffna</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AF%87%E0%AE%B3%E0%AE%BF%E0%AE%B0%E0%AF%8D_%28%E0%AE%88%E0%AE%B4%E0%AE%AE%E0%AF%8D%29</t>
         </is>
       </c>
     </row>
@@ -58747,17 +58955,17 @@
       </c>
       <c r="C432" s="8" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D432" s="7" t="inlineStr">
         <is>
-          <t>2012-01-17</t>
+          <t>2013-08-21</t>
         </is>
       </c>
       <c r="E432" s="9" t="inlineStr">
         <is>
-          <t>History of the Jaffna kingdom</t>
+          <t>Archaeological Museum, Jaffna</t>
         </is>
       </c>
       <c r="F432" s="9" t="inlineStr">
@@ -58780,8 +58988,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J432" s="9" t="n"/>
-      <c r="K432" s="9" t="n"/>
+      <c r="J432" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K432" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L432" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -58794,7 +59010,7 @@
       </c>
       <c r="N432" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/History_of_the_Jaffna_kingdom</t>
+          <t>https://en.wikipedia.org/wiki/Archaeological_Museum%2C_Jaffna</t>
         </is>
       </c>
     </row>
@@ -58816,23 +59032,27 @@
       </c>
       <c r="D433" s="11" t="inlineStr">
         <is>
-          <t>2012-06-27</t>
+          <t>2012-01-17</t>
         </is>
       </c>
       <c r="E433" s="13" t="inlineStr">
         <is>
-          <t>Prehistoric skeleton found in Sri Lanka</t>
-        </is>
-      </c>
-      <c r="F433" s="13" t="n"/>
+          <t>History of the Jaffna kingdom</t>
+        </is>
+      </c>
+      <c r="F433" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G433" s="13" t="inlineStr">
         <is>
-          <t>SEAArch (Southeast Asian Archaeology)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H433" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I433" s="11" t="inlineStr">
@@ -58840,25 +59060,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J433" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K433" s="13" t="inlineStr">
-        <is>
-          <t>prehistory; archaeology</t>
-        </is>
-      </c>
+      <c r="J433" s="13" t="n"/>
+      <c r="K433" s="13" t="n"/>
       <c r="L433" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M433" s="13" t="n"/>
+      <c r="M433" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N433" s="14" t="inlineStr">
         <is>
-          <t>https://southeastasianarchaeology.com/2012/06/27/prehistoric-skeleton-found-in-sri-lanka</t>
+          <t>https://en.wikipedia.org/wiki/History_of_the_Jaffna_kingdom</t>
         </is>
       </c>
     </row>
@@ -58880,27 +59096,23 @@
       </c>
       <c r="D434" s="7" t="inlineStr">
         <is>
-          <t>2012-07-22</t>
+          <t>2012-06-27</t>
         </is>
       </c>
       <c r="E434" s="9" t="inlineStr">
         <is>
-          <t>Anaikoddai seal</t>
-        </is>
-      </c>
-      <c r="F434" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Prehistoric skeleton found in Sri Lanka</t>
+        </is>
+      </c>
+      <c r="F434" s="9" t="n"/>
       <c r="G434" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>SEAArch (Southeast Asian Archaeology)</t>
         </is>
       </c>
       <c r="H434" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I434" s="7" t="inlineStr">
@@ -58910,23 +59122,23 @@
       </c>
       <c r="J434" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K434" s="9" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K434" s="9" t="inlineStr">
+        <is>
+          <t>prehistory; archaeology</t>
+        </is>
+      </c>
       <c r="L434" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M434" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M434" s="9" t="n"/>
       <c r="N434" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Anaikoddai_seal</t>
+          <t>https://southeastasianarchaeology.com/2012/06/27/prehistoric-skeleton-found-in-sri-lanka</t>
         </is>
       </c>
     </row>
@@ -58943,17 +59155,17 @@
       </c>
       <c r="C435" s="12" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D435" s="11" t="inlineStr">
         <is>
-          <t>2011-02-03</t>
+          <t>2012-07-22</t>
         </is>
       </c>
       <c r="E435" s="13" t="inlineStr">
         <is>
-          <t>இலங்கைத் தமிழர் வரலாறு - தமிழ் நூல் பட்டியல்</t>
+          <t>Anaikoddai seal</t>
         </is>
       </c>
       <c r="F435" s="13" t="inlineStr">
@@ -58963,7 +59175,7 @@
       </c>
       <c r="G435" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H435" s="11" t="inlineStr">
@@ -58973,10 +59185,14 @@
       </c>
       <c r="I435" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J435" s="13" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J435" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K435" s="13" t="n"/>
       <c r="L435" s="11" t="inlineStr">
         <is>
@@ -58990,7 +59206,7 @@
       </c>
       <c r="N435" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%B0%E0%AF%8D_%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81_-_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D_%E0%AE%A8%E0%AF%82%E0%AE%B2%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Anaikoddai_seal</t>
         </is>
       </c>
     </row>
@@ -59012,12 +59228,12 @@
       </c>
       <c r="D436" s="7" t="inlineStr">
         <is>
-          <t>2011-09-01</t>
+          <t>2011-02-03</t>
         </is>
       </c>
       <c r="E436" s="9" t="inlineStr">
         <is>
-          <t>மட்டக்களப்பு மான்மியம்</t>
+          <t>இலங்கைத் தமிழர் வரலாறு - தமிழ் நூல் பட்டியல்</t>
         </is>
       </c>
       <c r="F436" s="9" t="inlineStr">
@@ -59054,7 +59270,7 @@
       </c>
       <c r="N436" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81_%E0%AE%AE%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%AE%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%B0%E0%AF%8D_%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81_-_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D_%E0%AE%A8%E0%AF%82%E0%AE%B2%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -59071,17 +59287,17 @@
       </c>
       <c r="C437" s="12" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D437" s="11" t="inlineStr">
         <is>
-          <t>2010-08-06</t>
+          <t>2011-09-01</t>
         </is>
       </c>
       <c r="E437" s="13" t="inlineStr">
         <is>
-          <t>நாயன்மார்கட்டுக் கல்வெட்டு</t>
+          <t>மட்டக்களப்பு மான்மியம்</t>
         </is>
       </c>
       <c r="F437" s="13" t="inlineStr">
@@ -59104,16 +59320,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J437" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K437" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J437" s="13" t="n"/>
+      <c r="K437" s="13" t="n"/>
       <c r="L437" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -59126,7 +59334,7 @@
       </c>
       <c r="N437" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%AF%E0%AE%A9%E0%AF%8D%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AF%8D%E0%AE%95%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81_%E0%AE%AE%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%AE%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -59148,12 +59356,12 @@
       </c>
       <c r="D438" s="7" t="inlineStr">
         <is>
-          <t>2010-11-01</t>
+          <t>2010-08-06</t>
         </is>
       </c>
       <c r="E438" s="9" t="inlineStr">
         <is>
-          <t>Tissamaharama inscription No. 53</t>
+          <t>நாயன்மார்கட்டுக் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F438" s="9" t="inlineStr">
@@ -59163,7 +59371,7 @@
       </c>
       <c r="G438" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H438" s="7" t="inlineStr">
@@ -59173,7 +59381,7 @@
       </c>
       <c r="I438" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J438" s="9" t="inlineStr">
@@ -59183,7 +59391,7 @@
       </c>
       <c r="K438" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L438" s="7" t="inlineStr">
@@ -59198,7 +59406,7 @@
       </c>
       <c r="N438" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tissamaharama_inscription_No._53</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%AF%E0%AE%A9%E0%AF%8D%E0%AE%AE%E0%AE%BE%E0%AE%B0%E0%AF%8D%E0%AE%95%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -59215,17 +59423,17 @@
       </c>
       <c r="C439" s="12" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D439" s="11" t="inlineStr">
         <is>
-          <t>2008-08-09</t>
+          <t>2010-11-01</t>
         </is>
       </c>
       <c r="E439" s="13" t="inlineStr">
         <is>
-          <t>Prehistory of Sri Lanka</t>
+          <t>Tissamaharama inscription No. 53</t>
         </is>
       </c>
       <c r="F439" s="13" t="inlineStr">
@@ -59248,8 +59456,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J439" s="13" t="n"/>
-      <c r="K439" s="13" t="n"/>
+      <c r="J439" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K439" s="13" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L439" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -59262,7 +59478,7 @@
       </c>
       <c r="N439" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Prehistory_of_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Tissamaharama_inscription_No._53</t>
         </is>
       </c>
     </row>
@@ -59284,12 +59500,12 @@
       </c>
       <c r="D440" s="7" t="inlineStr">
         <is>
-          <t>2008-10-12</t>
+          <t>2008-08-09</t>
         </is>
       </c>
       <c r="E440" s="9" t="inlineStr">
         <is>
-          <t>கா. இந்திரபாலா</t>
+          <t>Prehistory of Sri Lanka</t>
         </is>
       </c>
       <c r="F440" s="9" t="inlineStr">
@@ -59299,7 +59515,7 @@
       </c>
       <c r="G440" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H440" s="7" t="inlineStr">
@@ -59309,7 +59525,7 @@
       </c>
       <c r="I440" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J440" s="9" t="n"/>
@@ -59326,7 +59542,7 @@
       </c>
       <c r="N440" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%BE._%E0%AE%87%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B0%E0%AE%AA%E0%AE%BE%E0%AE%B2%E0%AE%BE</t>
+          <t>https://en.wikipedia.org/wiki/Prehistory_of_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -59348,12 +59564,12 @@
       </c>
       <c r="D441" s="11" t="inlineStr">
         <is>
-          <t>2008-12-27</t>
+          <t>2008-10-12</t>
         </is>
       </c>
       <c r="E441" s="13" t="inlineStr">
         <is>
-          <t>Kandarodai</t>
+          <t>கா. இந்திரபாலா</t>
         </is>
       </c>
       <c r="F441" s="13" t="inlineStr">
@@ -59363,7 +59579,7 @@
       </c>
       <c r="G441" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H441" s="11" t="inlineStr">
@@ -59373,7 +59589,7 @@
       </c>
       <c r="I441" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J441" s="13" t="n"/>
@@ -59390,7 +59606,7 @@
       </c>
       <c r="N441" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Kandarodai</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AE%BE._%E0%AE%87%E0%AE%A8%E0%AF%8D%E0%AE%A4%E0%AE%BF%E0%AE%B0%E0%AE%AA%E0%AE%BE%E0%AE%B2%E0%AE%BE</t>
         </is>
       </c>
     </row>
@@ -59407,17 +59623,17 @@
       </c>
       <c r="C442" s="8" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D442" s="7" t="inlineStr">
         <is>
-          <t>2007-12-07</t>
+          <t>2008-12-27</t>
         </is>
       </c>
       <c r="E442" s="9" t="inlineStr">
         <is>
-          <t>தமிழி</t>
+          <t>Kandarodai</t>
         </is>
       </c>
       <c r="F442" s="9" t="inlineStr">
@@ -59427,7 +59643,7 @@
       </c>
       <c r="G442" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H442" s="7" t="inlineStr">
@@ -59437,7 +59653,7 @@
       </c>
       <c r="I442" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J442" s="9" t="n"/>
@@ -59454,7 +59670,7 @@
       </c>
       <c r="N442" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%BF</t>
+          <t>https://en.wikipedia.org/wiki/Kandarodai</t>
         </is>
       </c>
     </row>
@@ -59476,12 +59692,12 @@
       </c>
       <c r="D443" s="11" t="inlineStr">
         <is>
-          <t>2007-12-26</t>
+          <t>2007-12-07</t>
         </is>
       </c>
       <c r="E443" s="13" t="inlineStr">
         <is>
-          <t>Naga people (Lanka)</t>
+          <t>தமிழி</t>
         </is>
       </c>
       <c r="F443" s="13" t="inlineStr">
@@ -59491,7 +59707,7 @@
       </c>
       <c r="G443" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H443" s="11" t="inlineStr">
@@ -59501,7 +59717,7 @@
       </c>
       <c r="I443" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J443" s="13" t="n"/>
@@ -59518,7 +59734,7 @@
       </c>
       <c r="N443" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Naga_people_%28Lanka%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%BF</t>
         </is>
       </c>
     </row>
@@ -59535,17 +59751,17 @@
       </c>
       <c r="C444" s="8" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D444" s="7" t="inlineStr">
         <is>
-          <t>2006-04-29</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="E444" s="9" t="inlineStr">
         <is>
-          <t>பொ. பூலோகசிங்கம்</t>
+          <t>Naga people (Lanka)</t>
         </is>
       </c>
       <c r="F444" s="9" t="inlineStr">
@@ -59555,7 +59771,7 @@
       </c>
       <c r="G444" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H444" s="7" t="inlineStr">
@@ -59565,7 +59781,7 @@
       </c>
       <c r="I444" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J444" s="9" t="n"/>
@@ -59582,7 +59798,7 @@
       </c>
       <c r="N444" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A._%E0%AE%AA%E0%AF%82%E0%AE%B2%E0%AF%8B%E0%AE%95%E0%AE%9A%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Naga_people_%28Lanka%29</t>
         </is>
       </c>
     </row>
@@ -59604,12 +59820,12 @@
       </c>
       <c r="D445" s="11" t="inlineStr">
         <is>
-          <t>2006-08-30</t>
+          <t>2006-04-29</t>
         </is>
       </c>
       <c r="E445" s="13" t="inlineStr">
         <is>
-          <t>Velanai</t>
+          <t>பொ. பூலோகசிங்கம்</t>
         </is>
       </c>
       <c r="F445" s="13" t="inlineStr">
@@ -59619,7 +59835,7 @@
       </c>
       <c r="G445" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H445" s="11" t="inlineStr">
@@ -59629,7 +59845,7 @@
       </c>
       <c r="I445" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J445" s="13" t="n"/>
@@ -59646,7 +59862,7 @@
       </c>
       <c r="N445" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Velanai</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A._%E0%AE%AA%E0%AF%82%E0%AE%B2%E0%AF%8B%E0%AE%95%E0%AE%9A%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -59668,12 +59884,12 @@
       </c>
       <c r="D446" s="7" t="inlineStr">
         <is>
-          <t>2006-10-24</t>
+          <t>2006-08-30</t>
         </is>
       </c>
       <c r="E446" s="9" t="inlineStr">
         <is>
-          <t>நாடுகள் அடிப்படையில் தொல்லியல் களங்களின் பட்டியல்</t>
+          <t>Velanai</t>
         </is>
       </c>
       <c r="F446" s="9" t="inlineStr">
@@ -59683,7 +59899,7 @@
       </c>
       <c r="G446" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H446" s="7" t="inlineStr">
@@ -59693,19 +59909,11 @@
       </c>
       <c r="I446" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J446" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K446" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J446" s="9" t="n"/>
+      <c r="K446" s="9" t="n"/>
       <c r="L446" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -59718,7 +59926,7 @@
       </c>
       <c r="N446" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D_%E0%AE%85%E0%AE%9F%E0%AE%BF%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Velanai</t>
         </is>
       </c>
     </row>
@@ -59740,12 +59948,12 @@
       </c>
       <c r="D447" s="11" t="inlineStr">
         <is>
-          <t>2006-11-07</t>
+          <t>2006-10-24</t>
         </is>
       </c>
       <c r="E447" s="13" t="inlineStr">
         <is>
-          <t>Tamil-Brahmi</t>
+          <t>நாடுகள் அடிப்படையில் தொல்லியல் களங்களின் பட்டியல்</t>
         </is>
       </c>
       <c r="F447" s="13" t="inlineStr">
@@ -59755,7 +59963,7 @@
       </c>
       <c r="G447" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H447" s="11" t="inlineStr">
@@ -59765,17 +59973,17 @@
       </c>
       <c r="I447" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J447" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K447" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="L447" s="11" t="inlineStr">
@@ -59790,7 +59998,7 @@
       </c>
       <c r="N447" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tamil-Brahmi</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D_%E0%AE%85%E0%AE%9F%E0%AE%BF%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -59805,22 +60013,34 @@
           <t>Web Articles</t>
         </is>
       </c>
-      <c r="C448" s="8" t="n"/>
-      <c r="D448" s="7" t="n"/>
+      <c r="C448" s="8" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D448" s="7" t="inlineStr">
+        <is>
+          <t>2006-11-07</t>
+        </is>
+      </c>
       <c r="E448" s="9" t="inlineStr">
         <is>
-          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
-        </is>
-      </c>
-      <c r="F448" s="9" t="n"/>
+          <t>Tamil-Brahmi</t>
+        </is>
+      </c>
+      <c r="F448" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G448" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H448" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I448" s="7" t="inlineStr">
@@ -59830,23 +60050,27 @@
       </c>
       <c r="J448" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K448" s="9" t="inlineStr">
         <is>
-          <t>archaeology; East</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="L448" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M448" s="9" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M448" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N448" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
+          <t>https://en.wikipedia.org/wiki/Tamil-Brahmi</t>
         </is>
       </c>
     </row>
@@ -59865,22 +60089,18 @@
       <c r="D449" s="11" t="n"/>
       <c r="E449" s="13" t="inlineStr">
         <is>
-          <t>Buddhism amongst Tamils in Sri Lanka</t>
-        </is>
-      </c>
-      <c r="F449" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
+        </is>
+      </c>
+      <c r="F449" s="13" t="n"/>
       <c r="G449" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H449" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I449" s="11" t="inlineStr">
@@ -59888,21 +60108,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J449" s="13" t="n"/>
-      <c r="K449" s="13" t="n"/>
+      <c r="J449" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K449" s="13" t="inlineStr">
+        <is>
+          <t>archaeology; East</t>
+        </is>
+      </c>
       <c r="L449" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M449" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M449" s="13" t="n"/>
       <c r="N449" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
+          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
         </is>
       </c>
     </row>
@@ -59921,18 +60145,22 @@
       <c r="D450" s="7" t="n"/>
       <c r="E450" s="9" t="inlineStr">
         <is>
-          <t>Buddhist Remains in the Jaffna Peninsula</t>
-        </is>
-      </c>
-      <c r="F450" s="9" t="n"/>
+          <t>Buddhism amongst Tamils in Sri Lanka</t>
+        </is>
+      </c>
+      <c r="F450" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G450" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H450" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I450" s="7" t="inlineStr">
@@ -59940,25 +60168,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J450" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K450" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; Jaffna</t>
-        </is>
-      </c>
+      <c r="J450" s="9" t="n"/>
+      <c r="K450" s="9" t="n"/>
       <c r="L450" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M450" s="9" t="n"/>
+      <c r="M450" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N450" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna/</t>
+          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -59977,7 +60201,7 @@
       <c r="D451" s="11" t="n"/>
       <c r="E451" s="13" t="inlineStr">
         <is>
-          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+          <t>Buddhist Remains in the Jaffna Peninsula</t>
         </is>
       </c>
       <c r="F451" s="13" t="n"/>
@@ -60003,7 +60227,7 @@
       </c>
       <c r="K451" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Pungudutivu</t>
+          <t>தொல்லியல்; Jaffna</t>
         </is>
       </c>
       <c r="L451" s="11" t="inlineStr">
@@ -60014,7 +60238,7 @@
       <c r="M451" s="13" t="n"/>
       <c r="N451" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/tikali/</t>
+          <t>https://amazinglanka.com/wp/jaffna/</t>
         </is>
       </c>
     </row>
@@ -60033,22 +60257,18 @@
       <c r="D452" s="7" t="n"/>
       <c r="E452" s="9" t="inlineStr">
         <is>
-          <t>Cankilian Thoppu</t>
-        </is>
-      </c>
-      <c r="F452" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+        </is>
+      </c>
+      <c r="F452" s="9" t="n"/>
       <c r="G452" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H452" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I452" s="7" t="inlineStr">
@@ -60056,21 +60276,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J452" s="9" t="n"/>
-      <c r="K452" s="9" t="n"/>
+      <c r="J452" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K452" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Pungudutivu</t>
+        </is>
+      </c>
       <c r="L452" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M452" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M452" s="9" t="n"/>
       <c r="N452" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
+          <t>https://amazinglanka.com/wp/tikali/</t>
         </is>
       </c>
     </row>
@@ -60089,7 +60313,7 @@
       <c r="D453" s="11" t="n"/>
       <c r="E453" s="13" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+          <t>Cankilian Thoppu</t>
         </is>
       </c>
       <c r="F453" s="13" t="inlineStr">
@@ -60112,16 +60336,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J453" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K453" s="13" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+      <c r="J453" s="13" t="n"/>
+      <c r="K453" s="13" t="n"/>
       <c r="L453" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -60134,7 +60350,7 @@
       </c>
       <c r="N453" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
         </is>
       </c>
     </row>
@@ -60153,18 +60369,22 @@
       <c r="D454" s="7" t="n"/>
       <c r="E454" s="9" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="F454" s="9" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="F454" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G454" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H454" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I454" s="7" t="inlineStr">
@@ -60179,7 +60399,7 @@
       </c>
       <c r="K454" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L454" s="7" t="inlineStr">
@@ -60187,10 +60407,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M454" s="9" t="n"/>
+      <c r="M454" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N454" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -60209,22 +60433,18 @@
       <c r="D455" s="11" t="n"/>
       <c r="E455" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="F455" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
+        </is>
+      </c>
+      <c r="F455" s="13" t="n"/>
       <c r="G455" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H455" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I455" s="11" t="inlineStr">
@@ -60232,21 +60452,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J455" s="13" t="n"/>
-      <c r="K455" s="13" t="n"/>
+      <c r="J455" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K455" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; settlement</t>
+        </is>
+      </c>
       <c r="L455" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M455" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M455" s="13" t="n"/>
       <c r="N455" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -60265,7 +60489,7 @@
       <c r="D456" s="7" t="n"/>
       <c r="E456" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
+          <t>Sources of ancient Tamil history</t>
         </is>
       </c>
       <c r="F456" s="9" t="inlineStr">
@@ -60302,7 +60526,7 @@
       </c>
       <c r="N456" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -60321,18 +60545,22 @@
       <c r="D457" s="11" t="n"/>
       <c r="E457" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
-        </is>
-      </c>
-      <c r="F457" s="13" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="F457" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G457" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H457" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I457" s="11" t="inlineStr">
@@ -60340,25 +60568,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J457" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K457" s="13" t="inlineStr">
-        <is>
-          <t>memorial stone; Vanni</t>
-        </is>
-      </c>
+      <c r="J457" s="13" t="n"/>
+      <c r="K457" s="13" t="n"/>
       <c r="L457" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M457" s="13" t="n"/>
+      <c r="M457" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N457" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -60377,37 +60601,33 @@
       <c r="D458" s="7" t="n"/>
       <c r="E458" s="9" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F458" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+        </is>
+      </c>
+      <c r="F458" s="9" t="n"/>
       <c r="G458" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H458" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I458" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J458" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K458" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="L458" s="7" t="inlineStr">
@@ -60415,14 +60635,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M458" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M458" s="9" t="n"/>
       <c r="N458" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -60441,7 +60657,7 @@
       <c r="D459" s="11" t="n"/>
       <c r="E459" s="13" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F459" s="13" t="inlineStr">
@@ -60464,8 +60680,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J459" s="13" t="n"/>
-      <c r="K459" s="13" t="n"/>
+      <c r="J459" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K459" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L459" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -60478,7 +60702,7 @@
       </c>
       <c r="N459" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -60497,7 +60721,7 @@
       <c r="D460" s="7" t="n"/>
       <c r="E460" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="F460" s="9" t="inlineStr">
@@ -60520,16 +60744,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J460" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K460" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+      <c r="J460" s="9" t="n"/>
+      <c r="K460" s="9" t="n"/>
       <c r="L460" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -60542,7 +60758,7 @@
       </c>
       <c r="N460" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -60561,57 +60777,289 @@
       <c r="D461" s="11" t="n"/>
       <c r="E461" s="13" t="inlineStr">
         <is>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="F461" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
+      <c r="G461" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia (ta)</t>
+        </is>
+      </c>
+      <c r="H461" s="11" t="inlineStr">
+        <is>
+          <t>Encyclopedia article</t>
+        </is>
+      </c>
+      <c r="I461" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J461" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K461" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="L461" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M461" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
+      <c r="N461" s="14" t="inlineStr">
+        <is>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0461</t>
+        </is>
+      </c>
+      <c r="B462" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C462" s="8" t="n"/>
+      <c r="D462" s="7" t="n"/>
+      <c r="E462" s="9" t="inlineStr">
+        <is>
           <t>தம்பிலுவில் கல்வெட்டு</t>
         </is>
       </c>
-      <c r="F461" s="13" t="inlineStr">
+      <c r="F462" s="9" t="inlineStr">
         <is>
           <t>Wikipedia contributors</t>
         </is>
       </c>
-      <c r="G461" s="13" t="inlineStr">
+      <c r="G462" s="9" t="inlineStr">
         <is>
           <t>Wikipedia (ta)</t>
         </is>
       </c>
-      <c r="H461" s="11" t="inlineStr">
+      <c r="H462" s="7" t="inlineStr">
         <is>
           <t>Encyclopedia article</t>
         </is>
       </c>
-      <c r="I461" s="11" t="inlineStr">
+      <c r="I462" s="7" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J461" s="13" t="inlineStr">
+      <c r="J462" s="9" t="inlineStr">
         <is>
           <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
-      <c r="K461" s="13" t="inlineStr">
+      <c r="K462" s="9" t="inlineStr">
         <is>
           <t>கல்வெட்டு</t>
         </is>
       </c>
-      <c r="L461" s="11" t="inlineStr">
+      <c r="L462" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M461" s="13" t="inlineStr">
+      <c r="M462" s="9" t="inlineStr">
         <is>
           <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
-      <c r="N461" s="14" t="inlineStr">
+      <c r="N462" s="10" t="inlineStr">
         <is>
           <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0462</t>
+        </is>
+      </c>
+      <c r="B463" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C463" s="12" t="n"/>
+      <c r="D463" s="11" t="n"/>
+      <c r="E463" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="F463" s="13" t="n"/>
+      <c r="G463" s="13" t="inlineStr">
+        <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="H463" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I463" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J463" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K463" s="13" t="n"/>
+      <c r="L463" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M463" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N463" s="14" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0463</t>
+        </is>
+      </c>
+      <c r="B464" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C464" s="8" t="n"/>
+      <c r="D464" s="7" t="n"/>
+      <c r="E464" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="F464" s="9" t="n"/>
+      <c r="G464" s="9" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="H464" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I464" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J464" s="9" t="n"/>
+      <c r="K464" s="9" t="n"/>
+      <c r="L464" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M464" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N464" s="10" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0464</t>
+        </is>
+      </c>
+      <c r="B465" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C465" s="12" t="n"/>
+      <c r="D465" s="11" t="n"/>
+      <c r="E465" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="F465" s="13" t="n"/>
+      <c r="G465" s="13" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="H465" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I465" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J465" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K465" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="L465" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M465" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N465" s="14" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N461"/>
+  <autoFilter ref="A1:N465"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -61073,6 +61521,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N459" r:id="rId458"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N460" r:id="rId459"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N465" r:id="rId464"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Papers'!$A$1:$M$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspaper Articles'!$A$1:$M$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Magazines &amp; Journals'!$A$1:$M$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$535</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$540</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-15. Counts below are live formulas over the 'All Records' sheet.</t>
+          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-16. Counts below are live formulas over the 'All Records' sheet.</t>
         </is>
       </c>
     </row>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$535,A6)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$540,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$535,A6,'All Records'!$L$2:$L$535,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$540,A6,'All Records'!$L$2:$L$540,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$535,A7)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$540,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$535,A7,'All Records'!$L$2:$L$535,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$540,A7,'All Records'!$L$2:$L$540,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$535,A8)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$540,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$535,A8,'All Records'!$L$2:$L$535,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$540,A8,'All Records'!$L$2:$L$540,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$535,A9)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$540,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$535,A9,'All Records'!$L$2:$L$535,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$540,A9,'All Records'!$L$2:$L$540,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$535,A10)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$540,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$535,A10,'All Records'!$L$2:$L$535,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$540,A10,'All Records'!$L$2:$L$540,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$535,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$535,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$535,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$535,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$535,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$535,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -787,23 +787,23 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="G23" s="4">
@@ -818,23 +818,23 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="G24" s="4">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="G25" s="4">
@@ -880,23 +880,23 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="G26" s="4">
@@ -911,23 +911,23 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="G27" s="4">
@@ -942,23 +942,23 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$535="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$535,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="G28" s="4">
@@ -26144,7 +26144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -30478,12 +30478,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>2007-12-07</t>
+          <t>2007-12-04</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>தமிழி</t>
+          <t>Kotagama inscription</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -30493,7 +30493,7 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -30503,11 +30503,19 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I70" s="9" t="n"/>
-      <c r="J70" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -30515,12 +30523,12 @@
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-16 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%BF</t>
+          <t>https://en.wikipedia.org/wiki/Kotagama_inscription</t>
         </is>
       </c>
     </row>
@@ -30537,12 +30545,12 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>2007-12-26</t>
+          <t>2007-12-07</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Naga people (Lanka)</t>
+          <t>தமிழி</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -30552,7 +30560,7 @@
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -30562,7 +30570,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I71" s="13" t="n"/>
@@ -30579,7 +30587,7 @@
       </c>
       <c r="M71" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Naga_people_%28Lanka%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%BF</t>
         </is>
       </c>
     </row>
@@ -30591,17 +30599,17 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>2006-02-15</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Jaffna kingdom</t>
+          <t>Naga people (Lanka)</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -30633,12 +30641,12 @@
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Jaffna_kingdom</t>
+          <t>https://en.wikipedia.org/wiki/Naga_people_%28Lanka%29</t>
         </is>
       </c>
     </row>
@@ -30655,12 +30663,12 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>2006-02-16</t>
+          <t>2006-02-15</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Sri Lankan Tamils</t>
+          <t>Jaffna kingdom</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -30697,7 +30705,7 @@
       </c>
       <c r="M73" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sri_Lankan_Tamils</t>
+          <t>https://en.wikipedia.org/wiki/Jaffna_kingdom</t>
         </is>
       </c>
     </row>
@@ -30714,12 +30722,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>2006-04-29</t>
+          <t>2006-02-16</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>பொ. பூலோகசிங்கம்</t>
+          <t>Sri Lankan Tamils</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -30729,7 +30737,7 @@
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -30739,7 +30747,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I74" s="9" t="n"/>
@@ -30751,12 +30759,12 @@
       </c>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A._%E0%AE%AA%E0%AF%82%E0%AE%B2%E0%AF%8B%E0%AE%95%E0%AE%9A%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Sri_Lankan_Tamils</t>
         </is>
       </c>
     </row>
@@ -30773,12 +30781,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>2006-08-30</t>
+          <t>2006-04-29</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Velanai</t>
+          <t>பொ. பூலோகசிங்கம்</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -30788,7 +30796,7 @@
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -30798,7 +30806,7 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I75" s="13" t="n"/>
@@ -30815,7 +30823,7 @@
       </c>
       <c r="M75" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Velanai</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A._%E0%AE%AA%E0%AF%82%E0%AE%B2%E0%AF%8B%E0%AE%95%E0%AE%9A%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -30832,12 +30840,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>2006-10-24</t>
+          <t>2006-08-30</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>நாடுகள் அடிப்படையில் தொல்லியல் களங்களின் பட்டியல்</t>
+          <t>Velanai</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -30847,7 +30855,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
@@ -30857,19 +30865,11 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="n"/>
+      <c r="J76" s="9" t="n"/>
       <c r="K76" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D_%E0%AE%85%E0%AE%9F%E0%AE%BF%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Velanai</t>
         </is>
       </c>
     </row>
@@ -30899,12 +30899,12 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>2006-11-07</t>
+          <t>2006-10-24</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Tamil-Brahmi</t>
+          <t>நாடுகள் அடிப்படையில் தொல்லியல் களங்களின் பட்டியல்</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -30914,7 +30914,7 @@
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -30924,17 +30924,17 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J77" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
@@ -30949,7 +30949,7 @@
       </c>
       <c r="M77" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tamil-Brahmi</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D_%E0%AE%85%E0%AE%9F%E0%AE%BF%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -30959,22 +30959,34 @@
           <t>WB-0077</t>
         </is>
       </c>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="7" t="n"/>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>2006-11-07</t>
+        </is>
+      </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>(PDF) Contested Histories, Multi-Religious Space and ... - ResearchGate</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="n"/>
+          <t>Tamil-Brahmi</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>researchgate.net</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -30982,21 +30994,29 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I78" s="9" t="n"/>
-      <c r="J78" s="9" t="n"/>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/publication/335939791_Contested_Histories_Multi-Religious_Space_and_Conflict_A_Case_Study_of_Kantarodai_in_Northern_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Tamil-Brahmi</t>
         </is>
       </c>
     </row>
@@ -31006,22 +31026,34 @@
           <t>WB-0078</t>
         </is>
       </c>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="11" t="n"/>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>2005-01-07</t>
+        </is>
+      </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>(PDF) Contested Histories, Multi-Religious Space and Conflict: A Case ...</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="n"/>
+          <t>Batticaloa</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
@@ -31033,17 +31065,17 @@
       <c r="J79" s="13" t="n"/>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L79" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-16 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M79" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/83422032/Contested_Histories_Multi_Religious_Space_and_Conflict_A_Case_Study_of_Kantarodai_in_Northern_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Batticaloa</t>
         </is>
       </c>
     </row>
@@ -31057,13 +31089,13 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>(PDF) Lifeways of Early Kantharodai, Sri Lanka - ResearchGate</t>
+          <t>'Kantarodai Civilization of Ancient Jaffna' - Sangam</t>
         </is>
       </c>
       <c r="E80" s="9" t="n"/>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>researchgate.net</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -31085,12 +31117,12 @@
       </c>
       <c r="L80" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/publication/365603730_Lifeways_of_Early_Kantharodai_Sri_Lanka</t>
+          <t>https://sangam.org/kantarodai-civilization-ancient-jaffna/</t>
         </is>
       </c>
     </row>
@@ -31104,13 +31136,13 @@
       <c r="C81" s="11" t="n"/>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>(PDF) Lifeways of Early Kantharodai, Sri Lanka | Academia</t>
+          <t>(PDF) Contested Histories, Multi-Religious Space and ... - ResearchGate</t>
         </is>
       </c>
       <c r="E81" s="13" t="n"/>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>researchgate.net</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -31137,7 +31169,7 @@
       </c>
       <c r="M81" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/123922554/Lifeways_of_Early_Kantharodai_Sri_Lanka</t>
+          <t>https://www.researchgate.net/publication/335939791_Contested_Histories_Multi-Religious_Space_and_Conflict_A_Case_Study_of_Kantarodai_in_Northern_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -31151,18 +31183,18 @@
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
+          <t>(PDF) Contested Histories, Multi-Religious Space and Conflict: A Case ...</t>
         </is>
       </c>
       <c r="E82" s="9" t="n"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -31170,25 +31202,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>archaeology; East</t>
-        </is>
-      </c>
+      <c r="I82" s="9" t="n"/>
+      <c r="J82" s="9" t="n"/>
       <c r="K82" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L82" s="9" t="n"/>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
+          <t>https://www.academia.edu/83422032/Contested_Histories_Multi_Religious_Space_and_Conflict_A_Case_Study_of_Kantarodai_in_Northern_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -31202,13 +31230,13 @@
       <c r="C83" s="11" t="n"/>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>Ancient Coins - Archaeology</t>
+          <t>(PDF) Lifeways of Early Kantharodai, Sri Lanka - ResearchGate</t>
         </is>
       </c>
       <c r="E83" s="13" t="n"/>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>researchgate.net</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -31221,16 +31249,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J83" s="13" t="inlineStr">
-        <is>
-          <t>archaeology; ancient coins</t>
-        </is>
-      </c>
+      <c r="I83" s="13" t="n"/>
+      <c r="J83" s="13" t="n"/>
       <c r="K83" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -31238,12 +31258,12 @@
       </c>
       <c r="L83" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M83" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/ancient-coins</t>
+          <t>https://www.researchgate.net/publication/365603730_Lifeways_of_Early_Kantharodai_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -31257,13 +31277,13 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Ancient Coins and Trade Evidence | Lanka Websites</t>
+          <t>(PDF) Lifeways of Early Kantharodai, Sri Lanka | Academia</t>
         </is>
       </c>
       <c r="E84" s="9" t="n"/>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>lankawebsites.com</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -31276,16 +31296,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>ancient coins</t>
-        </is>
-      </c>
+      <c r="I84" s="9" t="n"/>
+      <c r="J84" s="9" t="n"/>
       <c r="K84" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -31293,12 +31305,12 @@
       </c>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
-          <t>https://lankawebsites.com/blog/ancient-civilization-archaeology/ancient-coins-and-trade-evidence</t>
+          <t>https://www.academia.edu/123922554/Lifeways_of_Early_Kantharodai_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -31312,18 +31324,18 @@
       <c r="C85" s="11" t="n"/>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Ancient Pandyan coins unearthed in Mannar | Tamil Guardian</t>
+          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
         </is>
       </c>
       <c r="E85" s="13" t="n"/>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>tamilguardian.com</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -31333,23 +31345,23 @@
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J85" s="13" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J85" s="13" t="inlineStr">
+        <is>
+          <t>archaeology; East</t>
+        </is>
+      </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L85" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L85" s="13" t="n"/>
       <c r="M85" s="14" t="inlineStr">
         <is>
-          <t>https://www.tamilguardian.com/content/ancient-pandyan-coins-unearthed-mannar</t>
+          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
         </is>
       </c>
     </row>
@@ -31363,13 +31375,13 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Archaeological Museum, Jaffna - Wikipedia</t>
+          <t>Ancient Coins - Archaeology</t>
         </is>
       </c>
       <c r="E86" s="9" t="n"/>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
@@ -31384,12 +31396,12 @@
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>archaeology; ancient coins</t>
         </is>
       </c>
       <c r="K86" s="7" t="inlineStr">
@@ -31399,12 +31411,12 @@
       </c>
       <c r="L86" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Archaeological_Museum,_Jaffna</t>
+          <t>https://archaeology.gov.lk/index.php/ancient-coins</t>
         </is>
       </c>
     </row>
@@ -31418,13 +31430,13 @@
       <c r="C87" s="11" t="n"/>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+          <t>Ancient Coins and Trade Evidence | Lanka Websites</t>
         </is>
       </c>
       <c r="E87" s="13" t="n"/>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>lankawebsites.com</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -31439,12 +31451,12 @@
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Coins / நாணயம்</t>
         </is>
       </c>
       <c r="J87" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>ancient coins</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr">
@@ -31454,12 +31466,12 @@
       </c>
       <c r="L87" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M87" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
+          <t>https://lankawebsites.com/blog/ancient-civilization-archaeology/ancient-coins-and-trade-evidence</t>
         </is>
       </c>
     </row>
@@ -31473,22 +31485,18 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Brahmi script</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Ancient Pandyan coins unearthed in Mannar | Tamil Guardian</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="n"/>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>tamilguardian.com</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -31498,14 +31506,10 @@
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n"/>
       <c r="K88" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -31513,12 +31517,12 @@
       </c>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
+          <t>https://www.tamilguardian.com/content/ancient-pandyan-coins-unearthed-mannar</t>
         </is>
       </c>
     </row>
@@ -31532,22 +31536,18 @@
       <c r="C89" s="11" t="n"/>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Buddhism amongst Tamils in Sri Lanka</t>
-        </is>
-      </c>
-      <c r="E89" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Archaeological Museum, Jaffna - Wikipedia</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="n"/>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
@@ -31555,8 +31555,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I89" s="13" t="n"/>
-      <c r="J89" s="13" t="n"/>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J89" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -31564,12 +31572,12 @@
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M89" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Archaeological_Museum,_Jaffna</t>
         </is>
       </c>
     </row>
@@ -31583,18 +31591,18 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Buddhist Remains in the Jaffna Peninsula</t>
+          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
         </is>
       </c>
       <c r="E90" s="9" t="n"/>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -31604,12 +31612,12 @@
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Jaffna</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr">
@@ -31617,10 +31625,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L90" s="9" t="n"/>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna/</t>
+          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
         </is>
       </c>
     </row>
@@ -31634,18 +31646,22 @@
       <c r="C91" s="11" t="n"/>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
-        </is>
-      </c>
-      <c r="E91" s="13" t="n"/>
+          <t>Brahmi script</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -31655,12 +31671,12 @@
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J91" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Pungudutivu</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
@@ -31668,10 +31684,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L91" s="13" t="n"/>
+      <c r="L91" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M91" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/tikali/</t>
+          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
         </is>
       </c>
     </row>
@@ -31685,7 +31705,7 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Cankilian Thoppu</t>
+          <t>Buddhism amongst Tamils in Sri Lanka</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
@@ -31722,7 +31742,7 @@
       </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
+          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -31736,18 +31756,18 @@
       <c r="C93" s="11" t="n"/>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>Coins DB| Home - archaeology.gov.lk</t>
+          <t>Buddhist Remains in the Jaffna Peninsula</t>
         </is>
       </c>
       <c r="E93" s="13" t="n"/>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -31757,12 +31777,12 @@
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J93" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>தொல்லியல்; Jaffna</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
@@ -31770,14 +31790,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L93" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L93" s="13" t="n"/>
       <c r="M93" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
+          <t>https://amazinglanka.com/wp/jaffna/</t>
         </is>
       </c>
     </row>
@@ -31791,18 +31807,18 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
+          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
         </is>
       </c>
       <c r="E94" s="9" t="n"/>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>dainst.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -31810,21 +31826,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I94" s="9" t="n"/>
-      <c r="J94" s="9" t="n"/>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Pungudutivu</t>
+        </is>
+      </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L94" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L94" s="9" t="n"/>
       <c r="M94" s="10" t="inlineStr">
         <is>
-          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
+          <t>https://amazinglanka.com/wp/tikali/</t>
         </is>
       </c>
     </row>
@@ -31838,18 +31858,22 @@
       <c r="C95" s="11" t="n"/>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="n"/>
+          <t>Cankilian Thoppu</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>elanka.com.au</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
@@ -31857,16 +31881,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J95" s="13" t="inlineStr">
-        <is>
-          <t>hero stone</t>
-        </is>
-      </c>
+      <c r="I95" s="13" t="n"/>
+      <c r="J95" s="13" t="n"/>
       <c r="K95" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -31874,12 +31890,12 @@
       </c>
       <c r="L95" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M95" s="14" t="inlineStr">
         <is>
-          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
+          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
         </is>
       </c>
     </row>
@@ -31893,13 +31909,13 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
+          <t>Coins DB| Home - archaeology.gov.lk</t>
         </is>
       </c>
       <c r="E96" s="9" t="n"/>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>searchworks.stanford.edu</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
@@ -31912,10 +31928,14 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I96" s="9" t="n"/>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+        </is>
+      </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>hero-stone</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr">
@@ -31925,12 +31945,12 @@
       </c>
       <c r="L96" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
-          <t>https://searchworks.stanford.edu/view/14451040</t>
+          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
         </is>
       </c>
     </row>
@@ -31944,13 +31964,13 @@
       <c r="C97" s="11" t="n"/>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
+          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
         </is>
       </c>
       <c r="E97" s="13" t="n"/>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>dainst.org</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -31963,16 +31983,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J97" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="I97" s="13" t="n"/>
+      <c r="J97" s="13" t="n"/>
       <c r="K97" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -31980,12 +31992,12 @@
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M97" s="14" t="inlineStr">
         <is>
-          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
+          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
         </is>
       </c>
     </row>
@@ -31999,13 +32011,13 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
+          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
         </is>
       </c>
       <c r="E98" s="9" t="n"/>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>elanka.com.au</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -32020,12 +32032,12 @@
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
@@ -32035,12 +32047,12 @@
       </c>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/?lang=en</t>
+          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
         </is>
       </c>
     </row>
@@ -32054,13 +32066,13 @@
       <c r="C99" s="11" t="n"/>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
+          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
         </is>
       </c>
       <c r="E99" s="13" t="n"/>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>tripadvisor.com</t>
+          <t>searchworks.stanford.edu</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -32073,14 +32085,10 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="I99" s="13" t="n"/>
       <c r="J99" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>hero-stone</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr">
@@ -32090,12 +32098,12 @@
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M99" s="14" t="inlineStr">
         <is>
-          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
+          <t>https://searchworks.stanford.edu/view/14451040</t>
         </is>
       </c>
     </row>
@@ -32109,13 +32117,13 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
+          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
         </is>
       </c>
       <c r="E100" s="9" t="n"/>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>jaffna.top</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -32130,12 +32138,12 @@
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K100" s="7" t="inlineStr">
@@ -32145,12 +32153,12 @@
       </c>
       <c r="L100" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
+          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
         </is>
       </c>
     </row>
@@ -32164,13 +32172,13 @@
       <c r="C101" s="11" t="n"/>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
+          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
         </is>
       </c>
       <c r="E101" s="13" t="n"/>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>srilankatourhelp.org</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -32185,12 +32193,12 @@
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J101" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr">
@@ -32200,12 +32208,12 @@
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M101" s="14" t="inlineStr">
         <is>
-          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
+          <t>https://www.inscriptions.lk/?lang=en</t>
         </is>
       </c>
     </row>
@@ -32219,13 +32227,13 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | About.lk</t>
+          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
         </is>
       </c>
       <c r="E102" s="9" t="n"/>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
+          <t>tripadvisor.com</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
@@ -32260,7 +32268,7 @@
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
         </is>
       </c>
     </row>
@@ -32274,13 +32282,13 @@
       <c r="C103" s="11" t="n"/>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
         </is>
       </c>
       <c r="E103" s="13" t="n"/>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>jaffna.top</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
@@ -32315,7 +32323,7 @@
       </c>
       <c r="M103" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
+          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
         </is>
       </c>
     </row>
@@ -32329,13 +32337,13 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
         </is>
       </c>
       <c r="E104" s="9" t="n"/>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>srilankatravelpages.com</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -32348,8 +32356,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I104" s="9" t="n"/>
-      <c r="J104" s="9" t="n"/>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32357,12 +32373,12 @@
       </c>
       <c r="L104" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
         </is>
       </c>
     </row>
@@ -32376,13 +32392,13 @@
       <c r="C105" s="11" t="n"/>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
         </is>
       </c>
       <c r="E105" s="13" t="n"/>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>srilankatourhelp.org</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
@@ -32395,8 +32411,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I105" s="13" t="n"/>
-      <c r="J105" s="13" t="n"/>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J105" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K105" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32404,12 +32428,12 @@
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M105" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
         </is>
       </c>
     </row>
@@ -32423,13 +32447,13 @@
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Jaffna Archaeological Museum | About.lk</t>
         </is>
       </c>
       <c r="E106" s="9" t="n"/>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -32444,12 +32468,12 @@
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>rock art</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
@@ -32459,12 +32483,12 @@
       </c>
       <c r="L106" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
         </is>
       </c>
     </row>
@@ -32478,22 +32502,18 @@
       <c r="C107" s="11" t="n"/>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="E107" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="n"/>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
@@ -32518,12 +32538,12 @@
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M107" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
         </is>
       </c>
     </row>
@@ -32537,18 +32557,18 @@
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="E108" s="9" t="n"/>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -32556,25 +32576,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J108" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; settlement</t>
-        </is>
-      </c>
+      <c r="I108" s="9" t="n"/>
+      <c r="J108" s="9" t="n"/>
       <c r="K108" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L108" s="9" t="n"/>
+      <c r="L108" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -32588,13 +32604,13 @@
       <c r="C109" s="11" t="n"/>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="E109" s="13" t="n"/>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -32607,16 +32623,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J109" s="13" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+      <c r="I109" s="13" t="n"/>
+      <c r="J109" s="13" t="n"/>
       <c r="K109" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32624,12 +32632,12 @@
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M109" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -32643,13 +32651,13 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
         </is>
       </c>
       <c r="E110" s="9" t="n"/>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -32664,12 +32672,12 @@
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>inscription; brahmi</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr">
@@ -32679,12 +32687,12 @@
       </c>
       <c r="L110" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -32698,18 +32706,22 @@
       <c r="C111" s="11" t="n"/>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
-        </is>
-      </c>
-      <c r="E111" s="13" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -32719,10 +32731,14 @@
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J111" s="13" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J111" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32730,12 +32746,12 @@
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M111" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -32749,18 +32765,18 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="E112" s="9" t="n"/>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -32770,12 +32786,12 @@
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>rock art</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr">
@@ -32783,14 +32799,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L112" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L112" s="9" t="n"/>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -32804,13 +32816,13 @@
       <c r="C113" s="11" t="n"/>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="E113" s="13" t="n"/>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
@@ -32825,12 +32837,12 @@
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J113" s="13" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
@@ -32840,12 +32852,12 @@
       </c>
       <c r="L113" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M113" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -32859,13 +32871,13 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="E114" s="9" t="n"/>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -32880,12 +32892,12 @@
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>inscription; brahmi</t>
         </is>
       </c>
       <c r="K114" s="7" t="inlineStr">
@@ -32895,12 +32907,12 @@
       </c>
       <c r="L114" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -32914,22 +32926,18 @@
       <c r="C115" s="11" t="n"/>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="E115" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Pandya coinage - Wikipedia</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="n"/>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
@@ -32937,7 +32945,11 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I115" s="13" t="n"/>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
       <c r="J115" s="13" t="n"/>
       <c r="K115" s="11" t="inlineStr">
         <is>
@@ -32946,12 +32958,12 @@
       </c>
       <c r="L115" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M115" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -32965,13 +32977,13 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E116" s="9" t="n"/>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -32986,12 +32998,12 @@
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K116" s="7" t="inlineStr">
@@ -33001,12 +33013,12 @@
       </c>
       <c r="L116" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -33020,13 +33032,13 @@
       <c r="C117" s="11" t="n"/>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E117" s="13" t="n"/>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
@@ -33041,12 +33053,12 @@
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J117" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
@@ -33056,12 +33068,12 @@
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M117" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -33075,13 +33087,13 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Sinhalese Hero Stone Analysis</t>
         </is>
       </c>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
@@ -33096,12 +33108,12 @@
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="K118" s="7" t="inlineStr">
@@ -33111,12 +33123,12 @@
       </c>
       <c r="L118" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -33130,18 +33142,22 @@
       <c r="C119" s="11" t="n"/>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
-        </is>
-      </c>
-      <c r="E119" s="13" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
@@ -33149,16 +33165,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J119" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="I119" s="13" t="n"/>
+      <c r="J119" s="13" t="n"/>
       <c r="K119" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33166,12 +33174,12 @@
       </c>
       <c r="L119" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M119" s="14" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -33185,13 +33193,13 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="E120" s="9" t="n"/>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -33204,8 +33212,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I120" s="9" t="n"/>
-      <c r="J120" s="9" t="n"/>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33213,12 +33229,12 @@
       </c>
       <c r="L120" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -33232,13 +33248,13 @@
       <c r="C121" s="11" t="n"/>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="E121" s="13" t="n"/>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr">
@@ -33253,14 +33269,10 @@
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J121" s="13" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J121" s="13" t="n"/>
       <c r="K121" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33268,12 +33280,12 @@
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M121" s="14" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -33287,13 +33299,13 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="E122" s="9" t="n"/>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -33308,12 +33320,12 @@
       </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K122" s="7" t="inlineStr">
@@ -33323,12 +33335,12 @@
       </c>
       <c r="L122" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -33342,22 +33354,18 @@
       <c r="C123" s="11" t="n"/>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="E123" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="n"/>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
@@ -33365,8 +33373,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I123" s="13" t="n"/>
-      <c r="J123" s="13" t="n"/>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J123" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="K123" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33374,12 +33390,12 @@
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M123" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -33393,18 +33409,18 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="E124" s="9" t="n"/>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -33414,12 +33430,12 @@
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K124" s="7" t="inlineStr">
@@ -33427,10 +33443,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L124" s="9" t="n"/>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -33444,13 +33464,13 @@
       <c r="C125" s="11" t="n"/>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="E125" s="13" t="n"/>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
@@ -33460,7 +33480,7 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I125" s="13" t="n"/>
@@ -33477,7 +33497,7 @@
       </c>
       <c r="M125" s="14" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -33491,27 +33511,23 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="n"/>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I126" s="9" t="inlineStr">
@@ -33521,7 +33537,7 @@
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="K126" s="7" t="inlineStr">
@@ -33531,12 +33547,12 @@
       </c>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -33550,13 +33566,13 @@
       <c r="C127" s="11" t="n"/>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="E127" s="13" t="n"/>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
@@ -33566,17 +33582,17 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J127" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="K127" s="11" t="inlineStr">
@@ -33586,12 +33602,12 @@
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -33605,35 +33621,31 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I128" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J128" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I128" s="9" t="n"/>
+      <c r="J128" s="9" t="n"/>
       <c r="K128" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33641,12 +33653,12 @@
       </c>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -33660,44 +33672,44 @@
       <c r="C129" s="11" t="n"/>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="E129" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="n"/>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I129" s="13" t="n"/>
-      <c r="J129" s="13" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="J129" s="13" t="inlineStr">
+        <is>
+          <t>memorial stone; Vanni</t>
+        </is>
+      </c>
       <c r="K129" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L129" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L129" s="13" t="n"/>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -33711,13 +33723,13 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="E130" s="9" t="n"/>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -33730,16 +33742,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I130" s="9" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J130" s="9" t="inlineStr">
-        <is>
-          <t>நடுகல்</t>
-        </is>
-      </c>
+      <c r="I130" s="9" t="n"/>
+      <c r="J130" s="9" t="n"/>
       <c r="K130" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33747,12 +33751,12 @@
       </c>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -33766,7 +33770,7 @@
       <c r="C131" s="11" t="n"/>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
@@ -33796,7 +33800,7 @@
       </c>
       <c r="J131" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K131" s="11" t="inlineStr">
@@ -33811,7 +33815,7 @@
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -33825,22 +33829,18 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E132" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="n"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
@@ -33850,12 +33850,12 @@
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="K132" s="7" t="inlineStr">
@@ -33865,12 +33865,12 @@
       </c>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -33884,13 +33884,13 @@
       <c r="C133" s="11" t="n"/>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
         </is>
       </c>
       <c r="E133" s="13" t="n"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
@@ -33905,12 +33905,12 @@
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J133" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="K133" s="11" t="inlineStr">
@@ -33920,12 +33920,12 @@
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -33939,18 +33939,22 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
-        </is>
-      </c>
-      <c r="E134" s="9" t="n"/>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
@@ -33958,16 +33962,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J134" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; பிராமி</t>
-        </is>
-      </c>
+      <c r="I134" s="9" t="n"/>
+      <c r="J134" s="9" t="n"/>
       <c r="K134" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33975,12 +33971,12 @@
       </c>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -33994,13 +33990,13 @@
       <c r="C135" s="11" t="n"/>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
         </is>
       </c>
       <c r="E135" s="13" t="n"/>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
@@ -34015,10 +34011,14 @@
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J135" s="13" t="n"/>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="J135" s="13" t="inlineStr">
+        <is>
+          <t>நடுகல்</t>
+        </is>
+      </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34026,12 +34026,12 @@
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -34045,18 +34045,22 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
-        </is>
-      </c>
-      <c r="E136" s="9" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -34064,8 +34068,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I136" s="9" t="n"/>
-      <c r="J136" s="9" t="n"/>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+        </is>
+      </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34073,12 +34085,12 @@
       </c>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -34092,53 +34104,320 @@
       <c r="C137" s="11" t="n"/>
       <c r="D137" s="13" t="inlineStr">
         <is>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia (ta)</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Encyclopedia article</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J137" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L137" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
+      <c r="M137" s="14" t="inlineStr">
+        <is>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>WB-0137</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="n"/>
+      <c r="C138" s="7" t="n"/>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="n"/>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>jvpnews.com</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L138" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M138" s="10" t="inlineStr">
+        <is>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>WB-0138</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="n"/>
+      <c r="C139" s="11" t="n"/>
+      <c r="D139" s="13" t="inlineStr">
+        <is>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="n"/>
+      <c r="F139" s="13" t="inlineStr">
+        <is>
+          <t>repo.lib.jfn.ac.lk</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J139" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L139" s="13" t="inlineStr">
+        <is>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M139" s="14" t="inlineStr">
+        <is>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>WB-0139</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="n"/>
+      <c r="C140" s="7" t="n"/>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n"/>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L140" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M140" s="10" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>WB-0140</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="n"/>
+      <c r="C141" s="11" t="n"/>
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="n"/>
+      <c r="F141" s="13" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I141" s="13" t="n"/>
+      <c r="J141" s="13" t="n"/>
+      <c r="K141" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L141" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M141" s="14" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>WB-0141</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="n"/>
+      <c r="C142" s="7" t="n"/>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
           <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
         </is>
       </c>
-      <c r="E137" s="13" t="n"/>
-      <c r="F137" s="13" t="inlineStr">
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="inlineStr">
         <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="G137" s="11" t="inlineStr">
+      <c r="G142" s="7" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="H137" s="11" t="inlineStr">
+      <c r="H142" s="7" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I137" s="13" t="inlineStr">
+      <c r="I142" s="9" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="J137" s="13" t="inlineStr">
+      <c r="J142" s="9" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="K137" s="11" t="inlineStr">
+      <c r="K142" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L137" s="13" t="inlineStr">
+      <c r="L142" s="9" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
-      <c r="M137" s="14" t="inlineStr">
+      <c r="M142" s="10" t="inlineStr">
         <is>
           <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M137"/>
+  <autoFilter ref="A1:M142"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -34276,6 +34555,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34287,7 +34571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N535"/>
+  <dimension ref="A1:N540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -65328,12 +65612,12 @@
       </c>
       <c r="D468" s="7" t="inlineStr">
         <is>
-          <t>2007-12-07</t>
+          <t>2007-12-04</t>
         </is>
       </c>
       <c r="E468" s="9" t="inlineStr">
         <is>
-          <t>தமிழி</t>
+          <t>Kotagama inscription</t>
         </is>
       </c>
       <c r="F468" s="9" t="inlineStr">
@@ -65343,7 +65627,7 @@
       </c>
       <c r="G468" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H468" s="7" t="inlineStr">
@@ -65353,11 +65637,19 @@
       </c>
       <c r="I468" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J468" s="9" t="n"/>
-      <c r="K468" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J468" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K468" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L468" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -65365,12 +65657,12 @@
       </c>
       <c r="M468" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-16 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N468" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%BF</t>
+          <t>https://en.wikipedia.org/wiki/Kotagama_inscription</t>
         </is>
       </c>
     </row>
@@ -65392,12 +65684,12 @@
       </c>
       <c r="D469" s="11" t="inlineStr">
         <is>
-          <t>2007-12-26</t>
+          <t>2007-12-07</t>
         </is>
       </c>
       <c r="E469" s="13" t="inlineStr">
         <is>
-          <t>Naga people (Lanka)</t>
+          <t>தமிழி</t>
         </is>
       </c>
       <c r="F469" s="13" t="inlineStr">
@@ -65407,7 +65699,7 @@
       </c>
       <c r="G469" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H469" s="11" t="inlineStr">
@@ -65417,7 +65709,7 @@
       </c>
       <c r="I469" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J469" s="13" t="n"/>
@@ -65434,7 +65726,7 @@
       </c>
       <c r="N469" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Naga_people_%28Lanka%29</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AE%BF</t>
         </is>
       </c>
     </row>
@@ -65451,17 +65743,17 @@
       </c>
       <c r="C470" s="8" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D470" s="7" t="inlineStr">
         <is>
-          <t>2006-02-15</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="E470" s="9" t="inlineStr">
         <is>
-          <t>Jaffna kingdom</t>
+          <t>Naga people (Lanka)</t>
         </is>
       </c>
       <c r="F470" s="9" t="inlineStr">
@@ -65493,12 +65785,12 @@
       </c>
       <c r="M470" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N470" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Jaffna_kingdom</t>
+          <t>https://en.wikipedia.org/wiki/Naga_people_%28Lanka%29</t>
         </is>
       </c>
     </row>
@@ -65520,12 +65812,12 @@
       </c>
       <c r="D471" s="11" t="inlineStr">
         <is>
-          <t>2006-02-16</t>
+          <t>2006-02-15</t>
         </is>
       </c>
       <c r="E471" s="13" t="inlineStr">
         <is>
-          <t>Sri Lankan Tamils</t>
+          <t>Jaffna kingdom</t>
         </is>
       </c>
       <c r="F471" s="13" t="inlineStr">
@@ -65562,7 +65854,7 @@
       </c>
       <c r="N471" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sri_Lankan_Tamils</t>
+          <t>https://en.wikipedia.org/wiki/Jaffna_kingdom</t>
         </is>
       </c>
     </row>
@@ -65584,12 +65876,12 @@
       </c>
       <c r="D472" s="7" t="inlineStr">
         <is>
-          <t>2006-04-29</t>
+          <t>2006-02-16</t>
         </is>
       </c>
       <c r="E472" s="9" t="inlineStr">
         <is>
-          <t>பொ. பூலோகசிங்கம்</t>
+          <t>Sri Lankan Tamils</t>
         </is>
       </c>
       <c r="F472" s="9" t="inlineStr">
@@ -65599,7 +65891,7 @@
       </c>
       <c r="G472" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H472" s="7" t="inlineStr">
@@ -65609,7 +65901,7 @@
       </c>
       <c r="I472" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J472" s="9" t="n"/>
@@ -65621,12 +65913,12 @@
       </c>
       <c r="M472" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N472" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A._%E0%AE%AA%E0%AF%82%E0%AE%B2%E0%AF%8B%E0%AE%95%E0%AE%9A%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Sri_Lankan_Tamils</t>
         </is>
       </c>
     </row>
@@ -65648,12 +65940,12 @@
       </c>
       <c r="D473" s="11" t="inlineStr">
         <is>
-          <t>2006-08-30</t>
+          <t>2006-04-29</t>
         </is>
       </c>
       <c r="E473" s="13" t="inlineStr">
         <is>
-          <t>Velanai</t>
+          <t>பொ. பூலோகசிங்கம்</t>
         </is>
       </c>
       <c r="F473" s="13" t="inlineStr">
@@ -65663,7 +65955,7 @@
       </c>
       <c r="G473" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H473" s="11" t="inlineStr">
@@ -65673,7 +65965,7 @@
       </c>
       <c r="I473" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J473" s="13" t="n"/>
@@ -65690,7 +65982,7 @@
       </c>
       <c r="N473" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Velanai</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AF%8A._%E0%AE%AA%E0%AF%82%E0%AE%B2%E0%AF%8B%E0%AE%95%E0%AE%9A%E0%AE%BF%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%AE%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -65712,12 +66004,12 @@
       </c>
       <c r="D474" s="7" t="inlineStr">
         <is>
-          <t>2006-10-24</t>
+          <t>2006-08-30</t>
         </is>
       </c>
       <c r="E474" s="9" t="inlineStr">
         <is>
-          <t>நாடுகள் அடிப்படையில் தொல்லியல் களங்களின் பட்டியல்</t>
+          <t>Velanai</t>
         </is>
       </c>
       <c r="F474" s="9" t="inlineStr">
@@ -65727,7 +66019,7 @@
       </c>
       <c r="G474" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H474" s="7" t="inlineStr">
@@ -65737,19 +66029,11 @@
       </c>
       <c r="I474" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J474" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K474" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J474" s="9" t="n"/>
+      <c r="K474" s="9" t="n"/>
       <c r="L474" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -65762,7 +66046,7 @@
       </c>
       <c r="N474" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D_%E0%AE%85%E0%AE%9F%E0%AE%BF%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
+          <t>https://en.wikipedia.org/wiki/Velanai</t>
         </is>
       </c>
     </row>
@@ -65784,12 +66068,12 @@
       </c>
       <c r="D475" s="11" t="inlineStr">
         <is>
-          <t>2006-11-07</t>
+          <t>2006-10-24</t>
         </is>
       </c>
       <c r="E475" s="13" t="inlineStr">
         <is>
-          <t>Tamil-Brahmi</t>
+          <t>நாடுகள் அடிப்படையில் தொல்லியல் களங்களின் பட்டியல்</t>
         </is>
       </c>
       <c r="F475" s="13" t="inlineStr">
@@ -65799,7 +66083,7 @@
       </c>
       <c r="G475" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H475" s="11" t="inlineStr">
@@ -65809,17 +66093,17 @@
       </c>
       <c r="I475" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J475" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K475" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="L475" s="11" t="inlineStr">
@@ -65834,7 +66118,7 @@
       </c>
       <c r="N475" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tamil-Brahmi</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D_%E0%AE%85%E0%AE%9F%E0%AE%BF%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%9F%E0%AF%88%E0%AE%AF%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%A4%E0%AF%8A%E0%AE%B2%E0%AF%8D%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B3%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%B3%E0%AE%BF%E0%AE%A9%E0%AF%8D_%E0%AE%AA%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BF%E0%AE%AF%E0%AE%B2%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -65849,22 +66133,34 @@
           <t>Web Articles</t>
         </is>
       </c>
-      <c r="C476" s="8" t="n"/>
-      <c r="D476" s="7" t="n"/>
+      <c r="C476" s="8" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D476" s="7" t="inlineStr">
+        <is>
+          <t>2006-11-07</t>
+        </is>
+      </c>
       <c r="E476" s="9" t="inlineStr">
         <is>
-          <t>(PDF) Contested Histories, Multi-Religious Space and ... - ResearchGate</t>
-        </is>
-      </c>
-      <c r="F476" s="9" t="n"/>
+          <t>Tamil-Brahmi</t>
+        </is>
+      </c>
+      <c r="F476" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G476" s="9" t="inlineStr">
         <is>
-          <t>researchgate.net</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H476" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I476" s="7" t="inlineStr">
@@ -65872,21 +66168,29 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J476" s="9" t="n"/>
-      <c r="K476" s="9" t="n"/>
+      <c r="J476" s="9" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K476" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="L476" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M476" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N476" s="10" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/publication/335939791_Contested_Histories_Multi-Religious_Space_and_Conflict_A_Case_Study_of_Kantarodai_in_Northern_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Tamil-Brahmi</t>
         </is>
       </c>
     </row>
@@ -65901,22 +66205,34 @@
           <t>Web Articles</t>
         </is>
       </c>
-      <c r="C477" s="12" t="n"/>
-      <c r="D477" s="11" t="n"/>
+      <c r="C477" s="12" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D477" s="11" t="inlineStr">
+        <is>
+          <t>2005-01-07</t>
+        </is>
+      </c>
       <c r="E477" s="13" t="inlineStr">
         <is>
-          <t>(PDF) Contested Histories, Multi-Religious Space and Conflict: A Case ...</t>
-        </is>
-      </c>
-      <c r="F477" s="13" t="n"/>
+          <t>Batticaloa</t>
+        </is>
+      </c>
+      <c r="F477" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G477" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H477" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I477" s="11" t="inlineStr">
@@ -65928,17 +66244,17 @@
       <c r="K477" s="13" t="n"/>
       <c r="L477" s="11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M477" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-16 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N477" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/83422032/Contested_Histories_Multi_Religious_Space_and_Conflict_A_Case_Study_of_Kantarodai_in_Northern_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Batticaloa</t>
         </is>
       </c>
     </row>
@@ -65957,13 +66273,13 @@
       <c r="D478" s="7" t="n"/>
       <c r="E478" s="9" t="inlineStr">
         <is>
-          <t>(PDF) Lifeways of Early Kantharodai, Sri Lanka - ResearchGate</t>
+          <t>'Kantarodai Civilization of Ancient Jaffna' - Sangam</t>
         </is>
       </c>
       <c r="F478" s="9" t="n"/>
       <c r="G478" s="9" t="inlineStr">
         <is>
-          <t>researchgate.net</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="H478" s="7" t="inlineStr">
@@ -65985,12 +66301,12 @@
       </c>
       <c r="M478" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N478" s="10" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/publication/365603730_Lifeways_of_Early_Kantharodai_Sri_Lanka</t>
+          <t>https://sangam.org/kantarodai-civilization-ancient-jaffna/</t>
         </is>
       </c>
     </row>
@@ -66009,13 +66325,13 @@
       <c r="D479" s="11" t="n"/>
       <c r="E479" s="13" t="inlineStr">
         <is>
-          <t>(PDF) Lifeways of Early Kantharodai, Sri Lanka | Academia</t>
+          <t>(PDF) Contested Histories, Multi-Religious Space and ... - ResearchGate</t>
         </is>
       </c>
       <c r="F479" s="13" t="n"/>
       <c r="G479" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>researchgate.net</t>
         </is>
       </c>
       <c r="H479" s="11" t="inlineStr">
@@ -66042,7 +66358,7 @@
       </c>
       <c r="N479" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/123922554/Lifeways_of_Early_Kantharodai_Sri_Lanka</t>
+          <t>https://www.researchgate.net/publication/335939791_Contested_Histories_Multi-Religious_Space_and_Conflict_A_Case_Study_of_Kantarodai_in_Northern_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -66061,18 +66377,18 @@
       <c r="D480" s="7" t="n"/>
       <c r="E480" s="9" t="inlineStr">
         <is>
-          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
+          <t>(PDF) Contested Histories, Multi-Religious Space and Conflict: A Case ...</t>
         </is>
       </c>
       <c r="F480" s="9" t="n"/>
       <c r="G480" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="H480" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I480" s="7" t="inlineStr">
@@ -66080,25 +66396,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J480" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K480" s="9" t="inlineStr">
-        <is>
-          <t>archaeology; East</t>
-        </is>
-      </c>
+      <c r="J480" s="9" t="n"/>
+      <c r="K480" s="9" t="n"/>
       <c r="L480" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M480" s="9" t="n"/>
+      <c r="M480" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N480" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
+          <t>https://www.academia.edu/83422032/Contested_Histories_Multi_Religious_Space_and_Conflict_A_Case_Study_of_Kantarodai_in_Northern_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -66117,13 +66429,13 @@
       <c r="D481" s="11" t="n"/>
       <c r="E481" s="13" t="inlineStr">
         <is>
-          <t>Ancient Coins - Archaeology</t>
+          <t>(PDF) Lifeways of Early Kantharodai, Sri Lanka - ResearchGate</t>
         </is>
       </c>
       <c r="F481" s="13" t="n"/>
       <c r="G481" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>researchgate.net</t>
         </is>
       </c>
       <c r="H481" s="11" t="inlineStr">
@@ -66136,16 +66448,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J481" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K481" s="13" t="inlineStr">
-        <is>
-          <t>archaeology; ancient coins</t>
-        </is>
-      </c>
+      <c r="J481" s="13" t="n"/>
+      <c r="K481" s="13" t="n"/>
       <c r="L481" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -66153,12 +66457,12 @@
       </c>
       <c r="M481" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N481" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/ancient-coins</t>
+          <t>https://www.researchgate.net/publication/365603730_Lifeways_of_Early_Kantharodai_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -66177,13 +66481,13 @@
       <c r="D482" s="7" t="n"/>
       <c r="E482" s="9" t="inlineStr">
         <is>
-          <t>Ancient Coins and Trade Evidence | Lanka Websites</t>
+          <t>(PDF) Lifeways of Early Kantharodai, Sri Lanka | Academia</t>
         </is>
       </c>
       <c r="F482" s="9" t="n"/>
       <c r="G482" s="9" t="inlineStr">
         <is>
-          <t>lankawebsites.com</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="H482" s="7" t="inlineStr">
@@ -66196,16 +66500,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J482" s="9" t="inlineStr">
-        <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K482" s="9" t="inlineStr">
-        <is>
-          <t>ancient coins</t>
-        </is>
-      </c>
+      <c r="J482" s="9" t="n"/>
+      <c r="K482" s="9" t="n"/>
       <c r="L482" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -66213,12 +66509,12 @@
       </c>
       <c r="M482" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N482" s="10" t="inlineStr">
         <is>
-          <t>https://lankawebsites.com/blog/ancient-civilization-archaeology/ancient-coins-and-trade-evidence</t>
+          <t>https://www.academia.edu/123922554/Lifeways_of_Early_Kantharodai_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -66237,18 +66533,18 @@
       <c r="D483" s="11" t="n"/>
       <c r="E483" s="13" t="inlineStr">
         <is>
-          <t>Ancient Pandyan coins unearthed in Mannar | Tamil Guardian</t>
+          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
         </is>
       </c>
       <c r="F483" s="13" t="n"/>
       <c r="G483" s="13" t="inlineStr">
         <is>
-          <t>tamilguardian.com</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H483" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I483" s="11" t="inlineStr">
@@ -66258,23 +66554,23 @@
       </c>
       <c r="J483" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K483" s="13" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K483" s="13" t="inlineStr">
+        <is>
+          <t>archaeology; East</t>
+        </is>
+      </c>
       <c r="L483" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M483" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M483" s="13" t="n"/>
       <c r="N483" s="14" t="inlineStr">
         <is>
-          <t>https://www.tamilguardian.com/content/ancient-pandyan-coins-unearthed-mannar</t>
+          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
         </is>
       </c>
     </row>
@@ -66293,13 +66589,13 @@
       <c r="D484" s="7" t="n"/>
       <c r="E484" s="9" t="inlineStr">
         <is>
-          <t>Archaeological Museum, Jaffna - Wikipedia</t>
+          <t>Ancient Coins - Archaeology</t>
         </is>
       </c>
       <c r="F484" s="9" t="n"/>
       <c r="G484" s="9" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H484" s="7" t="inlineStr">
@@ -66314,12 +66610,12 @@
       </c>
       <c r="J484" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
         </is>
       </c>
       <c r="K484" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>archaeology; ancient coins</t>
         </is>
       </c>
       <c r="L484" s="7" t="inlineStr">
@@ -66329,12 +66625,12 @@
       </c>
       <c r="M484" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N484" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Archaeological_Museum,_Jaffna</t>
+          <t>https://archaeology.gov.lk/index.php/ancient-coins</t>
         </is>
       </c>
     </row>
@@ -66353,13 +66649,13 @@
       <c r="D485" s="11" t="n"/>
       <c r="E485" s="13" t="inlineStr">
         <is>
-          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+          <t>Ancient Coins and Trade Evidence | Lanka Websites</t>
         </is>
       </c>
       <c r="F485" s="13" t="n"/>
       <c r="G485" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>lankawebsites.com</t>
         </is>
       </c>
       <c r="H485" s="11" t="inlineStr">
@@ -66374,12 +66670,12 @@
       </c>
       <c r="J485" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Coins / நாணயம்</t>
         </is>
       </c>
       <c r="K485" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>ancient coins</t>
         </is>
       </c>
       <c r="L485" s="11" t="inlineStr">
@@ -66389,12 +66685,12 @@
       </c>
       <c r="M485" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N485" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
+          <t>https://lankawebsites.com/blog/ancient-civilization-archaeology/ancient-coins-and-trade-evidence</t>
         </is>
       </c>
     </row>
@@ -66413,22 +66709,18 @@
       <c r="D486" s="7" t="n"/>
       <c r="E486" s="9" t="inlineStr">
         <is>
-          <t>Brahmi script</t>
-        </is>
-      </c>
-      <c r="F486" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Ancient Pandyan coins unearthed in Mannar | Tamil Guardian</t>
+        </is>
+      </c>
+      <c r="F486" s="9" t="n"/>
       <c r="G486" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>tamilguardian.com</t>
         </is>
       </c>
       <c r="H486" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I486" s="7" t="inlineStr">
@@ -66438,14 +66730,10 @@
       </c>
       <c r="J486" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K486" s="9" t="inlineStr">
-        <is>
-          <t>brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K486" s="9" t="n"/>
       <c r="L486" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -66453,12 +66741,12 @@
       </c>
       <c r="M486" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N486" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
+          <t>https://www.tamilguardian.com/content/ancient-pandyan-coins-unearthed-mannar</t>
         </is>
       </c>
     </row>
@@ -66477,22 +66765,18 @@
       <c r="D487" s="11" t="n"/>
       <c r="E487" s="13" t="inlineStr">
         <is>
-          <t>Buddhism amongst Tamils in Sri Lanka</t>
-        </is>
-      </c>
-      <c r="F487" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Archaeological Museum, Jaffna - Wikipedia</t>
+        </is>
+      </c>
+      <c r="F487" s="13" t="n"/>
       <c r="G487" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="H487" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I487" s="11" t="inlineStr">
@@ -66500,8 +66784,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J487" s="13" t="n"/>
-      <c r="K487" s="13" t="n"/>
+      <c r="J487" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K487" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L487" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -66509,12 +66801,12 @@
       </c>
       <c r="M487" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N487" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Archaeological_Museum,_Jaffna</t>
         </is>
       </c>
     </row>
@@ -66533,18 +66825,18 @@
       <c r="D488" s="7" t="n"/>
       <c r="E488" s="9" t="inlineStr">
         <is>
-          <t>Buddhist Remains in the Jaffna Peninsula</t>
+          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
         </is>
       </c>
       <c r="F488" s="9" t="n"/>
       <c r="G488" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H488" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I488" s="7" t="inlineStr">
@@ -66554,12 +66846,12 @@
       </c>
       <c r="J488" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K488" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Jaffna</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L488" s="7" t="inlineStr">
@@ -66567,10 +66859,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M488" s="9" t="n"/>
+      <c r="M488" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N488" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna/</t>
+          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
         </is>
       </c>
     </row>
@@ -66589,18 +66885,22 @@
       <c r="D489" s="11" t="n"/>
       <c r="E489" s="13" t="inlineStr">
         <is>
-          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
-        </is>
-      </c>
-      <c r="F489" s="13" t="n"/>
+          <t>Brahmi script</t>
+        </is>
+      </c>
+      <c r="F489" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G489" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H489" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I489" s="11" t="inlineStr">
@@ -66610,12 +66910,12 @@
       </c>
       <c r="J489" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K489" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Pungudutivu</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="L489" s="11" t="inlineStr">
@@ -66623,10 +66923,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M489" s="13" t="n"/>
+      <c r="M489" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N489" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/tikali/</t>
+          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
         </is>
       </c>
     </row>
@@ -66645,7 +66949,7 @@
       <c r="D490" s="7" t="n"/>
       <c r="E490" s="9" t="inlineStr">
         <is>
-          <t>Cankilian Thoppu</t>
+          <t>Buddhism amongst Tamils in Sri Lanka</t>
         </is>
       </c>
       <c r="F490" s="9" t="inlineStr">
@@ -66682,7 +66986,7 @@
       </c>
       <c r="N490" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
+          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -66701,18 +67005,18 @@
       <c r="D491" s="11" t="n"/>
       <c r="E491" s="13" t="inlineStr">
         <is>
-          <t>Coins DB| Home - archaeology.gov.lk</t>
+          <t>Buddhist Remains in the Jaffna Peninsula</t>
         </is>
       </c>
       <c r="F491" s="13" t="n"/>
       <c r="G491" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H491" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I491" s="11" t="inlineStr">
@@ -66722,12 +67026,12 @@
       </c>
       <c r="J491" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K491" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>தொல்லியல்; Jaffna</t>
         </is>
       </c>
       <c r="L491" s="11" t="inlineStr">
@@ -66735,14 +67039,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M491" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M491" s="13" t="n"/>
       <c r="N491" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
+          <t>https://amazinglanka.com/wp/jaffna/</t>
         </is>
       </c>
     </row>
@@ -66761,18 +67061,18 @@
       <c r="D492" s="7" t="n"/>
       <c r="E492" s="9" t="inlineStr">
         <is>
-          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
+          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
         </is>
       </c>
       <c r="F492" s="9" t="n"/>
       <c r="G492" s="9" t="inlineStr">
         <is>
-          <t>dainst.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H492" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I492" s="7" t="inlineStr">
@@ -66780,21 +67080,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J492" s="9" t="n"/>
-      <c r="K492" s="9" t="n"/>
+      <c r="J492" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K492" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Pungudutivu</t>
+        </is>
+      </c>
       <c r="L492" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M492" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M492" s="9" t="n"/>
       <c r="N492" s="10" t="inlineStr">
         <is>
-          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
+          <t>https://amazinglanka.com/wp/tikali/</t>
         </is>
       </c>
     </row>
@@ -66813,18 +67117,22 @@
       <c r="D493" s="11" t="n"/>
       <c r="E493" s="13" t="inlineStr">
         <is>
-          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
-        </is>
-      </c>
-      <c r="F493" s="13" t="n"/>
+          <t>Cankilian Thoppu</t>
+        </is>
+      </c>
+      <c r="F493" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G493" s="13" t="inlineStr">
         <is>
-          <t>elanka.com.au</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H493" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I493" s="11" t="inlineStr">
@@ -66832,16 +67140,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J493" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K493" s="13" t="inlineStr">
-        <is>
-          <t>hero stone</t>
-        </is>
-      </c>
+      <c r="J493" s="13" t="n"/>
+      <c r="K493" s="13" t="n"/>
       <c r="L493" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -66849,12 +67149,12 @@
       </c>
       <c r="M493" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N493" s="14" t="inlineStr">
         <is>
-          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
+          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
         </is>
       </c>
     </row>
@@ -66873,13 +67173,13 @@
       <c r="D494" s="7" t="n"/>
       <c r="E494" s="9" t="inlineStr">
         <is>
-          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
+          <t>Coins DB| Home - archaeology.gov.lk</t>
         </is>
       </c>
       <c r="F494" s="9" t="n"/>
       <c r="G494" s="9" t="inlineStr">
         <is>
-          <t>searchworks.stanford.edu</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H494" s="7" t="inlineStr">
@@ -66892,10 +67192,14 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J494" s="9" t="n"/>
+      <c r="J494" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+        </is>
+      </c>
       <c r="K494" s="9" t="inlineStr">
         <is>
-          <t>hero-stone</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="L494" s="7" t="inlineStr">
@@ -66905,12 +67209,12 @@
       </c>
       <c r="M494" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N494" s="10" t="inlineStr">
         <is>
-          <t>https://searchworks.stanford.edu/view/14451040</t>
+          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
         </is>
       </c>
     </row>
@@ -66929,13 +67233,13 @@
       <c r="D495" s="11" t="n"/>
       <c r="E495" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
+          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
         </is>
       </c>
       <c r="F495" s="13" t="n"/>
       <c r="G495" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>dainst.org</t>
         </is>
       </c>
       <c r="H495" s="11" t="inlineStr">
@@ -66948,16 +67252,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J495" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K495" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="J495" s="13" t="n"/>
+      <c r="K495" s="13" t="n"/>
       <c r="L495" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -66965,12 +67261,12 @@
       </c>
       <c r="M495" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N495" s="14" t="inlineStr">
         <is>
-          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
+          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
         </is>
       </c>
     </row>
@@ -66989,13 +67285,13 @@
       <c r="D496" s="7" t="n"/>
       <c r="E496" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
+          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
         </is>
       </c>
       <c r="F496" s="9" t="n"/>
       <c r="G496" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>elanka.com.au</t>
         </is>
       </c>
       <c r="H496" s="7" t="inlineStr">
@@ -67010,12 +67306,12 @@
       </c>
       <c r="J496" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K496" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="L496" s="7" t="inlineStr">
@@ -67025,12 +67321,12 @@
       </c>
       <c r="M496" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N496" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/?lang=en</t>
+          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
         </is>
       </c>
     </row>
@@ -67049,13 +67345,13 @@
       <c r="D497" s="11" t="n"/>
       <c r="E497" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
+          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
         </is>
       </c>
       <c r="F497" s="13" t="n"/>
       <c r="G497" s="13" t="inlineStr">
         <is>
-          <t>tripadvisor.com</t>
+          <t>searchworks.stanford.edu</t>
         </is>
       </c>
       <c r="H497" s="11" t="inlineStr">
@@ -67068,14 +67364,10 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J497" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="J497" s="13" t="n"/>
       <c r="K497" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>hero-stone</t>
         </is>
       </c>
       <c r="L497" s="11" t="inlineStr">
@@ -67085,12 +67377,12 @@
       </c>
       <c r="M497" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N497" s="14" t="inlineStr">
         <is>
-          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
+          <t>https://searchworks.stanford.edu/view/14451040</t>
         </is>
       </c>
     </row>
@@ -67109,13 +67401,13 @@
       <c r="D498" s="7" t="n"/>
       <c r="E498" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
+          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
         </is>
       </c>
       <c r="F498" s="9" t="n"/>
       <c r="G498" s="9" t="inlineStr">
         <is>
-          <t>jaffna.top</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H498" s="7" t="inlineStr">
@@ -67130,12 +67422,12 @@
       </c>
       <c r="J498" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K498" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L498" s="7" t="inlineStr">
@@ -67145,12 +67437,12 @@
       </c>
       <c r="M498" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N498" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
+          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
         </is>
       </c>
     </row>
@@ -67169,13 +67461,13 @@
       <c r="D499" s="11" t="n"/>
       <c r="E499" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
+          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
         </is>
       </c>
       <c r="F499" s="13" t="n"/>
       <c r="G499" s="13" t="inlineStr">
         <is>
-          <t>srilankatourhelp.org</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H499" s="11" t="inlineStr">
@@ -67190,12 +67482,12 @@
       </c>
       <c r="J499" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K499" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L499" s="11" t="inlineStr">
@@ -67205,12 +67497,12 @@
       </c>
       <c r="M499" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N499" s="14" t="inlineStr">
         <is>
-          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
+          <t>https://www.inscriptions.lk/?lang=en</t>
         </is>
       </c>
     </row>
@@ -67229,13 +67521,13 @@
       <c r="D500" s="7" t="n"/>
       <c r="E500" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | About.lk</t>
+          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
         </is>
       </c>
       <c r="F500" s="9" t="n"/>
       <c r="G500" s="9" t="inlineStr">
         <is>
-          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
+          <t>tripadvisor.com</t>
         </is>
       </c>
       <c r="H500" s="7" t="inlineStr">
@@ -67270,7 +67562,7 @@
       </c>
       <c r="N500" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
         </is>
       </c>
     </row>
@@ -67289,13 +67581,13 @@
       <c r="D501" s="11" t="n"/>
       <c r="E501" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
         </is>
       </c>
       <c r="F501" s="13" t="n"/>
       <c r="G501" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>jaffna.top</t>
         </is>
       </c>
       <c r="H501" s="11" t="inlineStr">
@@ -67330,7 +67622,7 @@
       </c>
       <c r="N501" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
+          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
         </is>
       </c>
     </row>
@@ -67349,13 +67641,13 @@
       <c r="D502" s="7" t="n"/>
       <c r="E502" s="9" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
         </is>
       </c>
       <c r="F502" s="9" t="n"/>
       <c r="G502" s="9" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>srilankatravelpages.com</t>
         </is>
       </c>
       <c r="H502" s="7" t="inlineStr">
@@ -67368,8 +67660,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J502" s="9" t="n"/>
-      <c r="K502" s="9" t="n"/>
+      <c r="J502" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K502" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L502" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -67377,12 +67677,12 @@
       </c>
       <c r="M502" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N502" s="10" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
         </is>
       </c>
     </row>
@@ -67401,13 +67701,13 @@
       <c r="D503" s="11" t="n"/>
       <c r="E503" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
         </is>
       </c>
       <c r="F503" s="13" t="n"/>
       <c r="G503" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>srilankatourhelp.org</t>
         </is>
       </c>
       <c r="H503" s="11" t="inlineStr">
@@ -67420,8 +67720,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J503" s="13" t="n"/>
-      <c r="K503" s="13" t="n"/>
+      <c r="J503" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K503" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L503" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -67429,12 +67737,12 @@
       </c>
       <c r="M503" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N503" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
         </is>
       </c>
     </row>
@@ -67453,13 +67761,13 @@
       <c r="D504" s="7" t="n"/>
       <c r="E504" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Jaffna Archaeological Museum | About.lk</t>
         </is>
       </c>
       <c r="F504" s="9" t="n"/>
       <c r="G504" s="9" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
         </is>
       </c>
       <c r="H504" s="7" t="inlineStr">
@@ -67474,12 +67782,12 @@
       </c>
       <c r="J504" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K504" s="9" t="inlineStr">
         <is>
-          <t>rock art</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L504" s="7" t="inlineStr">
@@ -67489,12 +67797,12 @@
       </c>
       <c r="M504" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N504" s="10" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
         </is>
       </c>
     </row>
@@ -67513,22 +67821,18 @@
       <c r="D505" s="11" t="n"/>
       <c r="E505" s="13" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="F505" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+        </is>
+      </c>
+      <c r="F505" s="13" t="n"/>
       <c r="G505" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H505" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I505" s="11" t="inlineStr">
@@ -67553,12 +67857,12 @@
       </c>
       <c r="M505" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N505" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
         </is>
       </c>
     </row>
@@ -67577,18 +67881,18 @@
       <c r="D506" s="7" t="n"/>
       <c r="E506" s="9" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="F506" s="9" t="n"/>
       <c r="G506" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="H506" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I506" s="7" t="inlineStr">
@@ -67596,25 +67900,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J506" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K506" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; settlement</t>
-        </is>
-      </c>
+      <c r="J506" s="9" t="n"/>
+      <c r="K506" s="9" t="n"/>
       <c r="L506" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M506" s="9" t="n"/>
+      <c r="M506" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N506" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -67633,13 +67933,13 @@
       <c r="D507" s="11" t="n"/>
       <c r="E507" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="F507" s="13" t="n"/>
       <c r="G507" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H507" s="11" t="inlineStr">
@@ -67652,16 +67952,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J507" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K507" s="13" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+      <c r="J507" s="13" t="n"/>
+      <c r="K507" s="13" t="n"/>
       <c r="L507" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -67669,12 +67961,12 @@
       </c>
       <c r="M507" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N507" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -67693,13 +67985,13 @@
       <c r="D508" s="7" t="n"/>
       <c r="E508" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
         </is>
       </c>
       <c r="F508" s="9" t="n"/>
       <c r="G508" s="9" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="H508" s="7" t="inlineStr">
@@ -67714,12 +68006,12 @@
       </c>
       <c r="J508" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K508" s="9" t="inlineStr">
         <is>
-          <t>inscription; brahmi</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L508" s="7" t="inlineStr">
@@ -67729,12 +68021,12 @@
       </c>
       <c r="M508" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N508" s="10" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -67753,18 +68045,22 @@
       <c r="D509" s="11" t="n"/>
       <c r="E509" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
-        </is>
-      </c>
-      <c r="F509" s="13" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="F509" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G509" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H509" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I509" s="11" t="inlineStr">
@@ -67774,10 +68070,14 @@
       </c>
       <c r="J509" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K509" s="13" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K509" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L509" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -67785,12 +68085,12 @@
       </c>
       <c r="M509" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N509" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -67809,18 +68109,18 @@
       <c r="D510" s="7" t="n"/>
       <c r="E510" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="F510" s="9" t="n"/>
       <c r="G510" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H510" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I510" s="7" t="inlineStr">
@@ -67830,12 +68130,12 @@
       </c>
       <c r="J510" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K510" s="9" t="inlineStr">
         <is>
-          <t>rock art</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="L510" s="7" t="inlineStr">
@@ -67843,14 +68143,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M510" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M510" s="9" t="n"/>
       <c r="N510" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -67869,13 +68165,13 @@
       <c r="D511" s="11" t="n"/>
       <c r="E511" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="F511" s="13" t="n"/>
       <c r="G511" s="13" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="H511" s="11" t="inlineStr">
@@ -67890,12 +68186,12 @@
       </c>
       <c r="J511" s="13" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K511" s="13" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L511" s="11" t="inlineStr">
@@ -67905,12 +68201,12 @@
       </c>
       <c r="M511" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N511" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -67929,13 +68225,13 @@
       <c r="D512" s="7" t="n"/>
       <c r="E512" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="F512" s="9" t="n"/>
       <c r="G512" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="H512" s="7" t="inlineStr">
@@ -67950,12 +68246,12 @@
       </c>
       <c r="J512" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K512" s="9" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>inscription; brahmi</t>
         </is>
       </c>
       <c r="L512" s="7" t="inlineStr">
@@ -67965,12 +68261,12 @@
       </c>
       <c r="M512" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N512" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -67989,22 +68285,18 @@
       <c r="D513" s="11" t="n"/>
       <c r="E513" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="F513" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Pandya coinage - Wikipedia</t>
+        </is>
+      </c>
+      <c r="F513" s="13" t="n"/>
       <c r="G513" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="H513" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I513" s="11" t="inlineStr">
@@ -68012,7 +68304,11 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J513" s="13" t="n"/>
+      <c r="J513" s="13" t="inlineStr">
+        <is>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
       <c r="K513" s="13" t="n"/>
       <c r="L513" s="11" t="inlineStr">
         <is>
@@ -68021,12 +68317,12 @@
       </c>
       <c r="M513" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N513" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -68045,13 +68341,13 @@
       <c r="D514" s="7" t="n"/>
       <c r="E514" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F514" s="9" t="n"/>
       <c r="G514" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H514" s="7" t="inlineStr">
@@ -68066,12 +68362,12 @@
       </c>
       <c r="J514" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K514" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L514" s="7" t="inlineStr">
@@ -68081,12 +68377,12 @@
       </c>
       <c r="M514" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N514" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -68105,13 +68401,13 @@
       <c r="D515" s="11" t="n"/>
       <c r="E515" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F515" s="13" t="n"/>
       <c r="G515" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H515" s="11" t="inlineStr">
@@ -68126,12 +68422,12 @@
       </c>
       <c r="J515" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K515" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="L515" s="11" t="inlineStr">
@@ -68141,12 +68437,12 @@
       </c>
       <c r="M515" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N515" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -68165,13 +68461,13 @@
       <c r="D516" s="7" t="n"/>
       <c r="E516" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Sinhalese Hero Stone Analysis</t>
         </is>
       </c>
       <c r="F516" s="9" t="n"/>
       <c r="G516" s="9" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H516" s="7" t="inlineStr">
@@ -68186,12 +68482,12 @@
       </c>
       <c r="J516" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K516" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="L516" s="7" t="inlineStr">
@@ -68201,12 +68497,12 @@
       </c>
       <c r="M516" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N516" s="10" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -68225,18 +68521,22 @@
       <c r="D517" s="11" t="n"/>
       <c r="E517" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
-        </is>
-      </c>
-      <c r="F517" s="13" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="F517" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G517" s="13" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H517" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I517" s="11" t="inlineStr">
@@ -68244,16 +68544,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J517" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K517" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="J517" s="13" t="n"/>
+      <c r="K517" s="13" t="n"/>
       <c r="L517" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68261,12 +68553,12 @@
       </c>
       <c r="M517" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N517" s="14" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -68285,13 +68577,13 @@
       <c r="D518" s="7" t="n"/>
       <c r="E518" s="9" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="F518" s="9" t="n"/>
       <c r="G518" s="9" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="H518" s="7" t="inlineStr">
@@ -68304,8 +68596,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J518" s="9" t="n"/>
-      <c r="K518" s="9" t="n"/>
+      <c r="J518" s="9" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K518" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="L518" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68313,12 +68613,12 @@
       </c>
       <c r="M518" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N518" s="10" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -68337,13 +68637,13 @@
       <c r="D519" s="11" t="n"/>
       <c r="E519" s="13" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="F519" s="13" t="n"/>
       <c r="G519" s="13" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="H519" s="11" t="inlineStr">
@@ -68358,14 +68658,10 @@
       </c>
       <c r="J519" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K519" s="13" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K519" s="13" t="n"/>
       <c r="L519" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68373,12 +68669,12 @@
       </c>
       <c r="M519" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N519" s="14" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -68397,13 +68693,13 @@
       <c r="D520" s="7" t="n"/>
       <c r="E520" s="9" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="F520" s="9" t="n"/>
       <c r="G520" s="9" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H520" s="7" t="inlineStr">
@@ -68418,12 +68714,12 @@
       </c>
       <c r="J520" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K520" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L520" s="7" t="inlineStr">
@@ -68433,12 +68729,12 @@
       </c>
       <c r="M520" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N520" s="10" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -68457,22 +68753,18 @@
       <c r="D521" s="11" t="n"/>
       <c r="E521" s="13" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="F521" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+        </is>
+      </c>
+      <c r="F521" s="13" t="n"/>
       <c r="G521" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="H521" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I521" s="11" t="inlineStr">
@@ -68480,8 +68772,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J521" s="13" t="n"/>
-      <c r="K521" s="13" t="n"/>
+      <c r="J521" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K521" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="L521" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68489,12 +68789,12 @@
       </c>
       <c r="M521" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N521" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -68513,18 +68813,18 @@
       <c r="D522" s="7" t="n"/>
       <c r="E522" s="9" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="F522" s="9" t="n"/>
       <c r="G522" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="H522" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I522" s="7" t="inlineStr">
@@ -68534,12 +68834,12 @@
       </c>
       <c r="J522" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K522" s="9" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L522" s="7" t="inlineStr">
@@ -68547,10 +68847,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M522" s="9" t="n"/>
+      <c r="M522" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N522" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -68569,13 +68873,13 @@
       <c r="D523" s="11" t="n"/>
       <c r="E523" s="13" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="F523" s="13" t="n"/>
       <c r="G523" s="13" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="H523" s="11" t="inlineStr">
@@ -68585,7 +68889,7 @@
       </c>
       <c r="I523" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J523" s="13" t="n"/>
@@ -68602,7 +68906,7 @@
       </c>
       <c r="N523" s="14" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -68621,27 +68925,23 @@
       <c r="D524" s="7" t="n"/>
       <c r="E524" s="9" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F524" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+        </is>
+      </c>
+      <c r="F524" s="9" t="n"/>
       <c r="G524" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="H524" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I524" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J524" s="9" t="inlineStr">
@@ -68651,7 +68951,7 @@
       </c>
       <c r="K524" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="L524" s="7" t="inlineStr">
@@ -68661,12 +68961,12 @@
       </c>
       <c r="M524" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N524" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -68685,13 +68985,13 @@
       <c r="D525" s="11" t="n"/>
       <c r="E525" s="13" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="F525" s="13" t="n"/>
       <c r="G525" s="13" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H525" s="11" t="inlineStr">
@@ -68701,17 +69001,17 @@
       </c>
       <c r="I525" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J525" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K525" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="L525" s="11" t="inlineStr">
@@ -68721,12 +69021,12 @@
       </c>
       <c r="M525" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N525" s="14" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -68745,35 +69045,31 @@
       <c r="D526" s="7" t="n"/>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
-        </is>
-      </c>
-      <c r="F526" s="9" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="F526" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G526" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H526" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I526" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J526" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K526" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J526" s="9" t="n"/>
+      <c r="K526" s="9" t="n"/>
       <c r="L526" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68781,12 +69077,12 @@
       </c>
       <c r="M526" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N526" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -68805,44 +69101,44 @@
       <c r="D527" s="11" t="n"/>
       <c r="E527" s="13" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="F527" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+        </is>
+      </c>
+      <c r="F527" s="13" t="n"/>
       <c r="G527" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H527" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I527" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J527" s="13" t="n"/>
-      <c r="K527" s="13" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J527" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="K527" s="13" t="inlineStr">
+        <is>
+          <t>memorial stone; Vanni</t>
+        </is>
+      </c>
       <c r="L527" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M527" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M527" s="13" t="n"/>
       <c r="N527" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -68861,13 +69157,13 @@
       <c r="D528" s="7" t="n"/>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="F528" s="9" t="n"/>
       <c r="G528" s="9" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H528" s="7" t="inlineStr">
@@ -68880,16 +69176,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J528" s="9" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K528" s="9" t="inlineStr">
-        <is>
-          <t>நடுகல்</t>
-        </is>
-      </c>
+      <c r="J528" s="9" t="n"/>
+      <c r="K528" s="9" t="n"/>
       <c r="L528" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68897,12 +69185,12 @@
       </c>
       <c r="M528" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N528" s="10" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -68921,7 +69209,7 @@
       <c r="D529" s="11" t="n"/>
       <c r="E529" s="13" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F529" s="13" t="inlineStr">
@@ -68951,7 +69239,7 @@
       </c>
       <c r="K529" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L529" s="11" t="inlineStr">
@@ -68966,7 +69254,7 @@
       </c>
       <c r="N529" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -68985,22 +69273,18 @@
       <c r="D530" s="7" t="n"/>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F530" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+        </is>
+      </c>
+      <c r="F530" s="9" t="n"/>
       <c r="G530" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="H530" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I530" s="7" t="inlineStr">
@@ -69010,12 +69294,12 @@
       </c>
       <c r="J530" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="L530" s="7" t="inlineStr">
@@ -69025,12 +69309,12 @@
       </c>
       <c r="M530" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N530" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -69049,13 +69333,13 @@
       <c r="D531" s="11" t="n"/>
       <c r="E531" s="13" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
         </is>
       </c>
       <c r="F531" s="13" t="n"/>
       <c r="G531" s="13" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H531" s="11" t="inlineStr">
@@ -69070,12 +69354,12 @@
       </c>
       <c r="J531" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K531" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="L531" s="11" t="inlineStr">
@@ -69085,12 +69369,12 @@
       </c>
       <c r="M531" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N531" s="14" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -69109,18 +69393,22 @@
       <c r="D532" s="7" t="n"/>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
-        </is>
-      </c>
-      <c r="F532" s="9" t="n"/>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+        </is>
+      </c>
+      <c r="F532" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G532" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H532" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I532" s="7" t="inlineStr">
@@ -69128,16 +69416,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J532" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K532" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; பிராமி</t>
-        </is>
-      </c>
+      <c r="J532" s="9" t="n"/>
+      <c r="K532" s="9" t="n"/>
       <c r="L532" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69145,12 +69425,12 @@
       </c>
       <c r="M532" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N532" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -69169,13 +69449,13 @@
       <c r="D533" s="11" t="n"/>
       <c r="E533" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
         </is>
       </c>
       <c r="F533" s="13" t="n"/>
       <c r="G533" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="H533" s="11" t="inlineStr">
@@ -69190,10 +69470,14 @@
       </c>
       <c r="J533" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K533" s="13" t="n"/>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="K533" s="13" t="inlineStr">
+        <is>
+          <t>நடுகல்</t>
+        </is>
+      </c>
       <c r="L533" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69201,12 +69485,12 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N533" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -69225,18 +69509,22 @@
       <c r="D534" s="7" t="n"/>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
-        </is>
-      </c>
-      <c r="F534" s="9" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="F534" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G534" s="9" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H534" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I534" s="7" t="inlineStr">
@@ -69244,8 +69532,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J534" s="9" t="n"/>
-      <c r="K534" s="9" t="n"/>
+      <c r="J534" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K534" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+        </is>
+      </c>
       <c r="L534" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69253,12 +69549,12 @@
       </c>
       <c r="M534" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N534" s="10" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -69277,53 +69573,345 @@
       <c r="D535" s="11" t="n"/>
       <c r="E535" s="13" t="inlineStr">
         <is>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F535" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
+      <c r="G535" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia (ta)</t>
+        </is>
+      </c>
+      <c r="H535" s="11" t="inlineStr">
+        <is>
+          <t>Encyclopedia article</t>
+        </is>
+      </c>
+      <c r="I535" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J535" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K535" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="L535" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M535" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
+      <c r="N535" s="14" t="inlineStr">
+        <is>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0535</t>
+        </is>
+      </c>
+      <c r="B536" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C536" s="8" t="n"/>
+      <c r="D536" s="7" t="n"/>
+      <c r="E536" s="9" t="inlineStr">
+        <is>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
+        </is>
+      </c>
+      <c r="F536" s="9" t="n"/>
+      <c r="G536" s="9" t="inlineStr">
+        <is>
+          <t>jvpnews.com</t>
+        </is>
+      </c>
+      <c r="H536" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I536" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J536" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K536" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="L536" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M536" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N536" s="10" t="inlineStr">
+        <is>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0536</t>
+        </is>
+      </c>
+      <c r="B537" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C537" s="12" t="n"/>
+      <c r="D537" s="11" t="n"/>
+      <c r="E537" s="13" t="inlineStr">
+        <is>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
+        </is>
+      </c>
+      <c r="F537" s="13" t="n"/>
+      <c r="G537" s="13" t="inlineStr">
+        <is>
+          <t>repo.lib.jfn.ac.lk</t>
+        </is>
+      </c>
+      <c r="H537" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I537" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J537" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K537" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
+      <c r="L537" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M537" s="13" t="inlineStr">
+        <is>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N537" s="14" t="inlineStr">
+        <is>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0537</t>
+        </is>
+      </c>
+      <c r="B538" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C538" s="8" t="n"/>
+      <c r="D538" s="7" t="n"/>
+      <c r="E538" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="F538" s="9" t="n"/>
+      <c r="G538" s="9" t="inlineStr">
+        <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="H538" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I538" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J538" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K538" s="9" t="n"/>
+      <c r="L538" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M538" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N538" s="10" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0538</t>
+        </is>
+      </c>
+      <c r="B539" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C539" s="12" t="n"/>
+      <c r="D539" s="11" t="n"/>
+      <c r="E539" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="F539" s="13" t="n"/>
+      <c r="G539" s="13" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="H539" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I539" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J539" s="13" t="n"/>
+      <c r="K539" s="13" t="n"/>
+      <c r="L539" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M539" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N539" s="14" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0539</t>
+        </is>
+      </c>
+      <c r="B540" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C540" s="8" t="n"/>
+      <c r="D540" s="7" t="n"/>
+      <c r="E540" s="9" t="inlineStr">
+        <is>
           <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
         </is>
       </c>
-      <c r="F535" s="13" t="n"/>
-      <c r="G535" s="13" t="inlineStr">
+      <c r="F540" s="9" t="n"/>
+      <c r="G540" s="9" t="inlineStr">
         <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="H535" s="11" t="inlineStr">
+      <c r="H540" s="7" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="I535" s="11" t="inlineStr">
+      <c r="I540" s="7" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J535" s="13" t="inlineStr">
+      <c r="J540" s="9" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="K535" s="13" t="inlineStr">
+      <c r="K540" s="9" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="L535" s="11" t="inlineStr">
+      <c r="L540" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M535" s="13" t="inlineStr">
+      <c r="M540" s="9" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
-      <c r="N535" s="14" t="inlineStr">
+      <c r="N540" s="10" t="inlineStr">
         <is>
           <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N535"/>
+  <autoFilter ref="A1:N540"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -69859,6 +70447,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N533" r:id="rId532"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N534" r:id="rId533"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N540" r:id="rId539"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Papers'!$A$1:$M$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspaper Articles'!$A$1:$M$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Magazines &amp; Journals'!$A$1:$M$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$540</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$543</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-16. Counts below are live formulas over the 'All Records' sheet.</t>
+          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-17. Counts below are live formulas over the 'All Records' sheet.</t>
         </is>
       </c>
     </row>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$540,A6)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$543,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$540,A6,'All Records'!$L$2:$L$540,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$543,A6,'All Records'!$L$2:$L$543,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$540,A7)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$543,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$540,A7,'All Records'!$L$2:$L$540,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$543,A7,'All Records'!$L$2:$L$543,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$540,A8)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$543,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$540,A8,'All Records'!$L$2:$L$540,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$543,A8,'All Records'!$L$2:$L$543,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$540,A9)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$543,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$540,A9,'All Records'!$L$2:$L$540,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$543,A9,'All Records'!$L$2:$L$543,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$540,A10)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$543,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$540,A10,'All Records'!$L$2:$L$540,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$543,A10,'All Records'!$L$2:$L$543,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$543,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$543,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$543,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$543,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$543,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$540,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$543,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -787,23 +787,23 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="G23" s="4">
@@ -818,23 +818,23 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="G24" s="4">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="G25" s="4">
@@ -880,23 +880,23 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="G26" s="4">
@@ -911,23 +911,23 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="G27" s="4">
@@ -942,23 +942,23 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$540="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$540,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$543="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$543,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="G28" s="4">
@@ -26144,7 +26144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32557,13 +32557,13 @@
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Jaffna Archeology Tour - Journe Experiences</t>
         </is>
       </c>
       <c r="E108" s="9" t="n"/>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>journesrilanka.com</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -32585,12 +32585,12 @@
       </c>
       <c r="L108" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
         </is>
       </c>
     </row>
@@ -32604,13 +32604,13 @@
       <c r="C109" s="11" t="n"/>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="E109" s="13" t="n"/>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -32632,12 +32632,12 @@
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M109" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -32651,13 +32651,13 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="E110" s="9" t="n"/>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -32670,16 +32670,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J110" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="I110" s="9" t="n"/>
+      <c r="J110" s="9" t="n"/>
       <c r="K110" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32692,7 +32684,7 @@
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -32706,22 +32698,18 @@
       <c r="C111" s="11" t="n"/>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="E111" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="n"/>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -32731,12 +32719,12 @@
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J111" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
@@ -32746,12 +32734,12 @@
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M111" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -32765,18 +32753,22 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -32791,7 +32783,7 @@
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr">
@@ -32799,10 +32791,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L112" s="9" t="n"/>
+      <c r="L112" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -32816,18 +32812,18 @@
       <c r="C113" s="11" t="n"/>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="E113" s="13" t="n"/>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -32842,7 +32838,7 @@
       </c>
       <c r="J113" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
@@ -32850,14 +32846,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L113" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L113" s="13" t="n"/>
       <c r="M113" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -32871,13 +32863,13 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="E114" s="9" t="n"/>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -32892,12 +32884,12 @@
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>inscription; brahmi</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K114" s="7" t="inlineStr">
@@ -32907,12 +32899,12 @@
       </c>
       <c r="L114" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -32926,13 +32918,13 @@
       <c r="C115" s="11" t="n"/>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="E115" s="13" t="n"/>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
@@ -32958,12 +32950,12 @@
       </c>
       <c r="L115" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M115" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -32977,13 +32969,13 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="E116" s="9" t="n"/>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -32998,12 +32990,12 @@
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>rock art</t>
+          <t>inscription; brahmi</t>
         </is>
       </c>
       <c r="K116" s="7" t="inlineStr">
@@ -33013,12 +33005,12 @@
       </c>
       <c r="L116" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -33032,13 +33024,13 @@
       <c r="C117" s="11" t="n"/>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="E117" s="13" t="n"/>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
@@ -33053,14 +33045,10 @@
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J117" s="13" t="inlineStr">
-        <is>
-          <t>rock painting</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J117" s="13" t="n"/>
       <c r="K117" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33068,12 +33056,12 @@
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M117" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -33087,13 +33075,13 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
@@ -33108,12 +33096,12 @@
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K118" s="7" t="inlineStr">
@@ -33123,12 +33111,12 @@
       </c>
       <c r="L118" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -33142,22 +33130,18 @@
       <c r="C119" s="11" t="n"/>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="E119" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="n"/>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
@@ -33165,8 +33149,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I119" s="13" t="n"/>
-      <c r="J119" s="13" t="n"/>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>Rock art / பாறை ஓவியம்</t>
+        </is>
+      </c>
+      <c r="J119" s="13" t="inlineStr">
+        <is>
+          <t>rock painting</t>
+        </is>
+      </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33174,12 +33166,12 @@
       </c>
       <c r="L119" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M119" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -33193,13 +33185,13 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sinhalese Hero Stone Analysis</t>
         </is>
       </c>
       <c r="E120" s="9" t="n"/>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -33214,12 +33206,12 @@
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr">
@@ -33229,12 +33221,12 @@
       </c>
       <c r="L120" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -33248,18 +33240,22 @@
       <c r="C121" s="11" t="n"/>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
-        </is>
-      </c>
-      <c r="E121" s="13" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -33267,11 +33263,7 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
+      <c r="I121" s="13" t="n"/>
       <c r="J121" s="13" t="n"/>
       <c r="K121" s="11" t="inlineStr">
         <is>
@@ -33280,12 +33272,12 @@
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M121" s="14" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -33299,13 +33291,13 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="E122" s="9" t="n"/>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -33320,12 +33312,12 @@
       </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="K122" s="7" t="inlineStr">
@@ -33340,7 +33332,7 @@
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -33354,13 +33346,13 @@
       <c r="C123" s="11" t="n"/>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="E123" s="13" t="n"/>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
@@ -33375,14 +33367,10 @@
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J123" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J123" s="13" t="n"/>
       <c r="K123" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33390,12 +33378,12 @@
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M123" s="14" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -33409,13 +33397,13 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="E124" s="9" t="n"/>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -33430,12 +33418,12 @@
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K124" s="7" t="inlineStr">
@@ -33445,12 +33433,12 @@
       </c>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -33464,13 +33452,13 @@
       <c r="C125" s="11" t="n"/>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="E125" s="13" t="n"/>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
@@ -33483,8 +33471,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I125" s="13" t="n"/>
-      <c r="J125" s="13" t="n"/>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J125" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="K125" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33492,12 +33488,12 @@
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M125" s="14" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -33511,13 +33507,13 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="E126" s="9" t="n"/>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
@@ -33537,7 +33533,7 @@
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K126" s="7" t="inlineStr">
@@ -33552,7 +33548,7 @@
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -33566,13 +33562,13 @@
       <c r="C127" s="11" t="n"/>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="E127" s="13" t="n"/>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
@@ -33602,12 +33598,12 @@
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -33621,22 +33617,18 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="n"/>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -33653,12 +33645,12 @@
       </c>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -33672,18 +33664,18 @@
       <c r="C129" s="11" t="n"/>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
         </is>
       </c>
       <c r="E129" s="13" t="n"/>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -33693,12 +33685,12 @@
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J129" s="13" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="K129" s="11" t="inlineStr">
@@ -33706,10 +33698,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L129" s="13" t="n"/>
+      <c r="L129" s="13" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -33723,13 +33719,13 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="E130" s="9" t="n"/>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -33739,11 +33735,19 @@
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I130" s="9" t="n"/>
-      <c r="J130" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33751,12 +33755,12 @@
       </c>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -33770,7 +33774,7 @@
       <c r="C131" s="11" t="n"/>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+          <t>Vallipuram</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
@@ -33780,7 +33784,7 @@
       </c>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -33790,19 +33794,11 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J131" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I131" s="13" t="n"/>
+      <c r="J131" s="13" t="n"/>
       <c r="K131" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33815,7 +33811,7 @@
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -33829,33 +33825,33 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
         </is>
       </c>
       <c r="E132" s="9" t="n"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="K132" s="7" t="inlineStr">
@@ -33863,14 +33859,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L132" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L132" s="9" t="n"/>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -33884,13 +33876,13 @@
       <c r="C133" s="11" t="n"/>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="E133" s="13" t="n"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
@@ -33903,16 +33895,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J133" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="I133" s="13" t="n"/>
+      <c r="J133" s="13" t="n"/>
       <c r="K133" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33920,12 +33904,12 @@
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -33939,7 +33923,7 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -33962,8 +33946,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I134" s="9" t="n"/>
-      <c r="J134" s="9" t="n"/>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33976,7 +33968,7 @@
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -33990,13 +33982,13 @@
       <c r="C135" s="11" t="n"/>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
         </is>
       </c>
       <c r="E135" s="13" t="n"/>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
@@ -34011,12 +34003,12 @@
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J135" s="13" t="inlineStr">
         <is>
-          <t>நடுகல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="K135" s="11" t="inlineStr">
@@ -34026,12 +34018,12 @@
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -34045,22 +34037,18 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
-        </is>
-      </c>
-      <c r="E136" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="n"/>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -34070,12 +34058,12 @@
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr">
@@ -34085,12 +34073,12 @@
       </c>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -34104,7 +34092,7 @@
       <c r="C137" s="11" t="n"/>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
@@ -34127,16 +34115,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J137" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I137" s="13" t="n"/>
+      <c r="J137" s="13" t="n"/>
       <c r="K137" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34149,7 +34129,7 @@
       </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -34163,13 +34143,13 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
         </is>
       </c>
       <c r="E138" s="9" t="n"/>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
@@ -34184,12 +34164,12 @@
       </c>
       <c r="I138" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="K138" s="7" t="inlineStr">
@@ -34199,12 +34179,12 @@
       </c>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -34218,18 +34198,22 @@
       <c r="C139" s="11" t="n"/>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
-        </is>
-      </c>
-      <c r="E139" s="13" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -34239,12 +34223,12 @@
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J139" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="K139" s="11" t="inlineStr">
@@ -34254,12 +34238,12 @@
       </c>
       <c r="L139" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M139" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -34273,18 +34257,22 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
-        </is>
-      </c>
-      <c r="E140" s="9" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -34294,10 +34282,14 @@
       </c>
       <c r="I140" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J140" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K140" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34305,12 +34297,12 @@
       </c>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -34324,13 +34316,13 @@
       <c r="C141" s="11" t="n"/>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="E141" s="13" t="n"/>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
@@ -34343,8 +34335,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I141" s="13" t="n"/>
-      <c r="J141" s="13" t="n"/>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J141" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K141" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34352,12 +34352,12 @@
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M141" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -34371,53 +34371,206 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="E142" s="9" t="n"/>
       <c r="F142" s="9" t="inlineStr">
         <is>
+          <t>repo.lib.jfn.ac.lk</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
+      <c r="K142" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L142" s="9" t="inlineStr">
+        <is>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M142" s="10" t="inlineStr">
+        <is>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>WB-0142</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="n"/>
+      <c r="C143" s="11" t="n"/>
+      <c r="D143" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="n"/>
+      <c r="F143" s="13" t="inlineStr">
+        <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J143" s="13" t="n"/>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L143" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M143" s="14" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>WB-0143</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="n"/>
+      <c r="C144" s="7" t="n"/>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I144" s="9" t="n"/>
+      <c r="J144" s="9" t="n"/>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L144" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M144" s="10" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>WB-0144</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="n"/>
+      <c r="C145" s="11" t="n"/>
+      <c r="D145" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="n"/>
+      <c r="F145" s="13" t="inlineStr">
+        <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="G142" s="7" t="inlineStr">
+      <c r="G145" s="11" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="H142" s="7" t="inlineStr">
+      <c r="H145" s="11" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I142" s="9" t="inlineStr">
+      <c r="I145" s="13" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="J142" s="9" t="inlineStr">
+      <c r="J145" s="13" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="K142" s="7" t="inlineStr">
+      <c r="K145" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L142" s="9" t="inlineStr">
+      <c r="L145" s="13" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
-      <c r="M142" s="10" t="inlineStr">
+      <c r="M145" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M142"/>
+  <autoFilter ref="A1:M145"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -34560,6 +34713,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34571,7 +34727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N540"/>
+  <dimension ref="A1:N543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -67881,13 +68037,13 @@
       <c r="D506" s="7" t="n"/>
       <c r="E506" s="9" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Jaffna Archeology Tour - Journe Experiences</t>
         </is>
       </c>
       <c r="F506" s="9" t="n"/>
       <c r="G506" s="9" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>journesrilanka.com</t>
         </is>
       </c>
       <c r="H506" s="7" t="inlineStr">
@@ -67909,12 +68065,12 @@
       </c>
       <c r="M506" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N506" s="10" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
         </is>
       </c>
     </row>
@@ -67933,13 +68089,13 @@
       <c r="D507" s="11" t="n"/>
       <c r="E507" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="F507" s="13" t="n"/>
       <c r="G507" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="H507" s="11" t="inlineStr">
@@ -67961,12 +68117,12 @@
       </c>
       <c r="M507" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N507" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -67985,13 +68141,13 @@
       <c r="D508" s="7" t="n"/>
       <c r="E508" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="F508" s="9" t="n"/>
       <c r="G508" s="9" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H508" s="7" t="inlineStr">
@@ -68004,16 +68160,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J508" s="9" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K508" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="J508" s="9" t="n"/>
+      <c r="K508" s="9" t="n"/>
       <c r="L508" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68026,7 +68174,7 @@
       </c>
       <c r="N508" s="10" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -68045,22 +68193,18 @@
       <c r="D509" s="11" t="n"/>
       <c r="E509" s="13" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="F509" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+        </is>
+      </c>
+      <c r="F509" s="13" t="n"/>
       <c r="G509" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="H509" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I509" s="11" t="inlineStr">
@@ -68070,12 +68214,12 @@
       </c>
       <c r="J509" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K509" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L509" s="11" t="inlineStr">
@@ -68085,12 +68229,12 @@
       </c>
       <c r="M509" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N509" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -68109,18 +68253,22 @@
       <c r="D510" s="7" t="n"/>
       <c r="E510" s="9" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="F510" s="9" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="F510" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G510" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H510" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I510" s="7" t="inlineStr">
@@ -68135,7 +68283,7 @@
       </c>
       <c r="K510" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L510" s="7" t="inlineStr">
@@ -68143,10 +68291,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M510" s="9" t="n"/>
+      <c r="M510" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N510" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -68165,18 +68317,18 @@
       <c r="D511" s="11" t="n"/>
       <c r="E511" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="F511" s="13" t="n"/>
       <c r="G511" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H511" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I511" s="11" t="inlineStr">
@@ -68191,7 +68343,7 @@
       </c>
       <c r="K511" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="L511" s="11" t="inlineStr">
@@ -68199,14 +68351,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M511" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M511" s="13" t="n"/>
       <c r="N511" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -68225,13 +68373,13 @@
       <c r="D512" s="7" t="n"/>
       <c r="E512" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="F512" s="9" t="n"/>
       <c r="G512" s="9" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="H512" s="7" t="inlineStr">
@@ -68246,12 +68394,12 @@
       </c>
       <c r="J512" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K512" s="9" t="inlineStr">
         <is>
-          <t>inscription; brahmi</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L512" s="7" t="inlineStr">
@@ -68261,12 +68409,12 @@
       </c>
       <c r="M512" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N512" s="10" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -68285,13 +68433,13 @@
       <c r="D513" s="11" t="n"/>
       <c r="E513" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="F513" s="13" t="n"/>
       <c r="G513" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H513" s="11" t="inlineStr">
@@ -68317,12 +68465,12 @@
       </c>
       <c r="M513" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N513" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -68341,13 +68489,13 @@
       <c r="D514" s="7" t="n"/>
       <c r="E514" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="F514" s="9" t="n"/>
       <c r="G514" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="H514" s="7" t="inlineStr">
@@ -68362,12 +68510,12 @@
       </c>
       <c r="J514" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K514" s="9" t="inlineStr">
         <is>
-          <t>rock art</t>
+          <t>inscription; brahmi</t>
         </is>
       </c>
       <c r="L514" s="7" t="inlineStr">
@@ -68377,12 +68525,12 @@
       </c>
       <c r="M514" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N514" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -68401,13 +68549,13 @@
       <c r="D515" s="11" t="n"/>
       <c r="E515" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="F515" s="13" t="n"/>
       <c r="G515" s="13" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="H515" s="11" t="inlineStr">
@@ -68422,14 +68570,10 @@
       </c>
       <c r="J515" s="13" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K515" s="13" t="inlineStr">
-        <is>
-          <t>rock painting</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K515" s="13" t="n"/>
       <c r="L515" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68437,12 +68581,12 @@
       </c>
       <c r="M515" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N515" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -68461,13 +68605,13 @@
       <c r="D516" s="7" t="n"/>
       <c r="E516" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F516" s="9" t="n"/>
       <c r="G516" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H516" s="7" t="inlineStr">
@@ -68482,12 +68626,12 @@
       </c>
       <c r="J516" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K516" s="9" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L516" s="7" t="inlineStr">
@@ -68497,12 +68641,12 @@
       </c>
       <c r="M516" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N516" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -68521,22 +68665,18 @@
       <c r="D517" s="11" t="n"/>
       <c r="E517" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="F517" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+        </is>
+      </c>
+      <c r="F517" s="13" t="n"/>
       <c r="G517" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H517" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I517" s="11" t="inlineStr">
@@ -68544,8 +68684,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J517" s="13" t="n"/>
-      <c r="K517" s="13" t="n"/>
+      <c r="J517" s="13" t="inlineStr">
+        <is>
+          <t>Rock art / பாறை ஓவியம்</t>
+        </is>
+      </c>
+      <c r="K517" s="13" t="inlineStr">
+        <is>
+          <t>rock painting</t>
+        </is>
+      </c>
       <c r="L517" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68553,12 +68701,12 @@
       </c>
       <c r="M517" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N517" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -68577,13 +68725,13 @@
       <c r="D518" s="7" t="n"/>
       <c r="E518" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sinhalese Hero Stone Analysis</t>
         </is>
       </c>
       <c r="F518" s="9" t="n"/>
       <c r="G518" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H518" s="7" t="inlineStr">
@@ -68598,12 +68746,12 @@
       </c>
       <c r="J518" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K518" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="L518" s="7" t="inlineStr">
@@ -68613,12 +68761,12 @@
       </c>
       <c r="M518" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N518" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -68637,18 +68785,22 @@
       <c r="D519" s="11" t="n"/>
       <c r="E519" s="13" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
-        </is>
-      </c>
-      <c r="F519" s="13" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="F519" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G519" s="13" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H519" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I519" s="11" t="inlineStr">
@@ -68656,11 +68808,7 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J519" s="13" t="inlineStr">
-        <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
+      <c r="J519" s="13" t="n"/>
       <c r="K519" s="13" t="n"/>
       <c r="L519" s="11" t="inlineStr">
         <is>
@@ -68669,12 +68817,12 @@
       </c>
       <c r="M519" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N519" s="14" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -68693,13 +68841,13 @@
       <c r="D520" s="7" t="n"/>
       <c r="E520" s="9" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="F520" s="9" t="n"/>
       <c r="G520" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="H520" s="7" t="inlineStr">
@@ -68714,12 +68862,12 @@
       </c>
       <c r="J520" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K520" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="L520" s="7" t="inlineStr">
@@ -68734,7 +68882,7 @@
       </c>
       <c r="N520" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -68753,13 +68901,13 @@
       <c r="D521" s="11" t="n"/>
       <c r="E521" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="F521" s="13" t="n"/>
       <c r="G521" s="13" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="H521" s="11" t="inlineStr">
@@ -68774,14 +68922,10 @@
       </c>
       <c r="J521" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K521" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K521" s="13" t="n"/>
       <c r="L521" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68789,12 +68933,12 @@
       </c>
       <c r="M521" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N521" s="14" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -68813,13 +68957,13 @@
       <c r="D522" s="7" t="n"/>
       <c r="E522" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="F522" s="9" t="n"/>
       <c r="G522" s="9" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H522" s="7" t="inlineStr">
@@ -68834,12 +68978,12 @@
       </c>
       <c r="J522" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K522" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L522" s="7" t="inlineStr">
@@ -68849,12 +68993,12 @@
       </c>
       <c r="M522" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N522" s="10" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -68873,13 +69017,13 @@
       <c r="D523" s="11" t="n"/>
       <c r="E523" s="13" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="F523" s="13" t="n"/>
       <c r="G523" s="13" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="H523" s="11" t="inlineStr">
@@ -68892,8 +69036,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J523" s="13" t="n"/>
-      <c r="K523" s="13" t="n"/>
+      <c r="J523" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K523" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="L523" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68901,12 +69053,12 @@
       </c>
       <c r="M523" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N523" s="14" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -68925,13 +69077,13 @@
       <c r="D524" s="7" t="n"/>
       <c r="E524" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="F524" s="9" t="n"/>
       <c r="G524" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="H524" s="7" t="inlineStr">
@@ -68951,7 +69103,7 @@
       </c>
       <c r="K524" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L524" s="7" t="inlineStr">
@@ -68966,7 +69118,7 @@
       </c>
       <c r="N524" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -68985,13 +69137,13 @@
       <c r="D525" s="11" t="n"/>
       <c r="E525" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="F525" s="13" t="n"/>
       <c r="G525" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="H525" s="11" t="inlineStr">
@@ -69021,12 +69173,12 @@
       </c>
       <c r="M525" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N525" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -69045,22 +69197,18 @@
       <c r="D526" s="7" t="n"/>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="F526" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+        </is>
+      </c>
+      <c r="F526" s="9" t="n"/>
       <c r="G526" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="H526" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I526" s="7" t="inlineStr">
@@ -69077,12 +69225,12 @@
       </c>
       <c r="M526" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N526" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -69101,18 +69249,18 @@
       <c r="D527" s="11" t="n"/>
       <c r="E527" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
         </is>
       </c>
       <c r="F527" s="13" t="n"/>
       <c r="G527" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="H527" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I527" s="11" t="inlineStr">
@@ -69122,12 +69270,12 @@
       </c>
       <c r="J527" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K527" s="13" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="L527" s="11" t="inlineStr">
@@ -69135,10 +69283,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M527" s="13" t="n"/>
+      <c r="M527" s="13" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N527" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -69157,13 +69309,13 @@
       <c r="D528" s="7" t="n"/>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="F528" s="9" t="n"/>
       <c r="G528" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H528" s="7" t="inlineStr">
@@ -69173,11 +69325,19 @@
       </c>
       <c r="I528" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J528" s="9" t="n"/>
-      <c r="K528" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J528" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K528" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L528" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69185,12 +69345,12 @@
       </c>
       <c r="M528" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N528" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -69209,7 +69369,7 @@
       <c r="D529" s="11" t="n"/>
       <c r="E529" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+          <t>Vallipuram</t>
         </is>
       </c>
       <c r="F529" s="13" t="inlineStr">
@@ -69219,7 +69379,7 @@
       </c>
       <c r="G529" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H529" s="11" t="inlineStr">
@@ -69229,19 +69389,11 @@
       </c>
       <c r="I529" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J529" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K529" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J529" s="13" t="n"/>
+      <c r="K529" s="13" t="n"/>
       <c r="L529" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69254,7 +69406,7 @@
       </c>
       <c r="N529" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -69273,33 +69425,33 @@
       <c r="D530" s="7" t="n"/>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
         </is>
       </c>
       <c r="F530" s="9" t="n"/>
       <c r="G530" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H530" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I530" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J530" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="L530" s="7" t="inlineStr">
@@ -69307,14 +69459,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M530" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M530" s="9" t="n"/>
       <c r="N530" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -69333,13 +69481,13 @@
       <c r="D531" s="11" t="n"/>
       <c r="E531" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="F531" s="13" t="n"/>
       <c r="G531" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H531" s="11" t="inlineStr">
@@ -69352,16 +69500,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J531" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K531" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="J531" s="13" t="n"/>
+      <c r="K531" s="13" t="n"/>
       <c r="L531" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69369,12 +69509,12 @@
       </c>
       <c r="M531" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N531" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -69393,7 +69533,7 @@
       <c r="D532" s="7" t="n"/>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F532" s="9" t="inlineStr">
@@ -69416,8 +69556,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J532" s="9" t="n"/>
-      <c r="K532" s="9" t="n"/>
+      <c r="J532" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K532" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L532" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69430,7 +69578,7 @@
       </c>
       <c r="N532" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -69449,13 +69597,13 @@
       <c r="D533" s="11" t="n"/>
       <c r="E533" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
         </is>
       </c>
       <c r="F533" s="13" t="n"/>
       <c r="G533" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="H533" s="11" t="inlineStr">
@@ -69470,12 +69618,12 @@
       </c>
       <c r="J533" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K533" s="13" t="inlineStr">
         <is>
-          <t>நடுகல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="L533" s="11" t="inlineStr">
@@ -69485,12 +69633,12 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N533" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -69509,22 +69657,18 @@
       <c r="D534" s="7" t="n"/>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
-        </is>
-      </c>
-      <c r="F534" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="F534" s="9" t="n"/>
       <c r="G534" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H534" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I534" s="7" t="inlineStr">
@@ -69534,12 +69678,12 @@
       </c>
       <c r="J534" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K534" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="L534" s="7" t="inlineStr">
@@ -69549,12 +69693,12 @@
       </c>
       <c r="M534" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N534" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -69573,7 +69717,7 @@
       <c r="D535" s="11" t="n"/>
       <c r="E535" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="F535" s="13" t="inlineStr">
@@ -69596,16 +69740,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J535" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K535" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J535" s="13" t="n"/>
+      <c r="K535" s="13" t="n"/>
       <c r="L535" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69618,7 +69754,7 @@
       </c>
       <c r="N535" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -69637,13 +69773,13 @@
       <c r="D536" s="7" t="n"/>
       <c r="E536" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
         </is>
       </c>
       <c r="F536" s="9" t="n"/>
       <c r="G536" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="H536" s="7" t="inlineStr">
@@ -69658,12 +69794,12 @@
       </c>
       <c r="J536" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K536" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="L536" s="7" t="inlineStr">
@@ -69673,12 +69809,12 @@
       </c>
       <c r="M536" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N536" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -69697,18 +69833,22 @@
       <c r="D537" s="11" t="n"/>
       <c r="E537" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
-        </is>
-      </c>
-      <c r="F537" s="13" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="F537" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G537" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H537" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I537" s="11" t="inlineStr">
@@ -69718,12 +69858,12 @@
       </c>
       <c r="J537" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K537" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="L537" s="11" t="inlineStr">
@@ -69733,12 +69873,12 @@
       </c>
       <c r="M537" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N537" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -69757,18 +69897,22 @@
       <c r="D538" s="7" t="n"/>
       <c r="E538" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
-        </is>
-      </c>
-      <c r="F538" s="9" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F538" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G538" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H538" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I538" s="7" t="inlineStr">
@@ -69778,10 +69922,14 @@
       </c>
       <c r="J538" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K538" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K538" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L538" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69789,12 +69937,12 @@
       </c>
       <c r="M538" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N538" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -69813,13 +69961,13 @@
       <c r="D539" s="11" t="n"/>
       <c r="E539" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="F539" s="13" t="n"/>
       <c r="G539" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="H539" s="11" t="inlineStr">
@@ -69832,8 +69980,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J539" s="13" t="n"/>
-      <c r="K539" s="13" t="n"/>
+      <c r="J539" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K539" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L539" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69841,12 +69997,12 @@
       </c>
       <c r="M539" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N539" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -69865,53 +70021,221 @@
       <c r="D540" s="7" t="n"/>
       <c r="E540" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="F540" s="9" t="n"/>
       <c r="G540" s="9" t="inlineStr">
         <is>
+          <t>repo.lib.jfn.ac.lk</t>
+        </is>
+      </c>
+      <c r="H540" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I540" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J540" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K540" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
+      <c r="L540" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M540" s="9" t="inlineStr">
+        <is>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N540" s="10" t="inlineStr">
+        <is>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0540</t>
+        </is>
+      </c>
+      <c r="B541" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C541" s="12" t="n"/>
+      <c r="D541" s="11" t="n"/>
+      <c r="E541" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="F541" s="13" t="n"/>
+      <c r="G541" s="13" t="inlineStr">
+        <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="H541" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I541" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J541" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K541" s="13" t="n"/>
+      <c r="L541" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M541" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N541" s="14" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0541</t>
+        </is>
+      </c>
+      <c r="B542" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C542" s="8" t="n"/>
+      <c r="D542" s="7" t="n"/>
+      <c r="E542" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="F542" s="9" t="n"/>
+      <c r="G542" s="9" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="H542" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I542" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J542" s="9" t="n"/>
+      <c r="K542" s="9" t="n"/>
+      <c r="L542" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M542" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N542" s="10" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0542</t>
+        </is>
+      </c>
+      <c r="B543" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C543" s="12" t="n"/>
+      <c r="D543" s="11" t="n"/>
+      <c r="E543" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="F543" s="13" t="n"/>
+      <c r="G543" s="13" t="inlineStr">
+        <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="H540" s="7" t="inlineStr">
+      <c r="H543" s="11" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="I540" s="7" t="inlineStr">
+      <c r="I543" s="11" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J540" s="9" t="inlineStr">
+      <c r="J543" s="13" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="K540" s="9" t="inlineStr">
+      <c r="K543" s="13" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="L540" s="7" t="inlineStr">
+      <c r="L543" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M540" s="9" t="inlineStr">
+      <c r="M543" s="13" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
-      <c r="N540" s="10" t="inlineStr">
+      <c r="N543" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N540"/>
+  <autoFilter ref="A1:N543"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -70452,6 +70776,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N538" r:id="rId537"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N539" r:id="rId538"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N543" r:id="rId542"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Papers'!$A$1:$M$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspaper Articles'!$A$1:$M$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Magazines &amp; Journals'!$A$1:$M$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$550</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$553</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-19. Counts below are live formulas over the 'All Records' sheet.</t>
+          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-20. Counts below are live formulas over the 'All Records' sheet.</t>
         </is>
       </c>
     </row>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$550,A6)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$553,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$550,A6,'All Records'!$L$2:$L$550,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$553,A6,'All Records'!$L$2:$L$553,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$550,A7)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$553,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$550,A7,'All Records'!$L$2:$L$550,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$553,A7,'All Records'!$L$2:$L$553,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$550,A8)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$553,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$550,A8,'All Records'!$L$2:$L$550,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$553,A8,'All Records'!$L$2:$L$553,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$550,A9)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$553,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$550,A9,'All Records'!$L$2:$L$550,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$553,A9,'All Records'!$L$2:$L$553,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$550,A10)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$553,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$550,A10,'All Records'!$L$2:$L$550,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$553,A10,'All Records'!$L$2:$L$553,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$550,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$553,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$550,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$553,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$550,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$553,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$550,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$553,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$550,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$553,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$550,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$553,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -787,23 +787,23 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="G23" s="4">
@@ -818,23 +818,23 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="G24" s="4">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="G25" s="4">
@@ -880,23 +880,23 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="G26" s="4">
@@ -911,23 +911,23 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="G27" s="4">
@@ -942,23 +942,23 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$550="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$550,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$553="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$553,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="G28" s="4">
@@ -26272,7 +26272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -33619,13 +33619,13 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="E126" s="9" t="n"/>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
@@ -33640,12 +33640,12 @@
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K126" s="7" t="inlineStr">
@@ -33655,12 +33655,12 @@
       </c>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -33674,13 +33674,13 @@
       <c r="C127" s="11" t="n"/>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="E127" s="13" t="n"/>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
@@ -33710,12 +33710,12 @@
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -33729,13 +33729,13 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="E128" s="9" t="n"/>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
@@ -33750,10 +33750,14 @@
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J128" s="9" t="n"/>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33761,12 +33765,12 @@
       </c>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -33780,13 +33784,13 @@
       <c r="C129" s="11" t="n"/>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="E129" s="13" t="n"/>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr">
@@ -33801,14 +33805,10 @@
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J129" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J129" s="13" t="n"/>
       <c r="K129" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33816,12 +33816,12 @@
       </c>
       <c r="L129" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -33835,13 +33835,13 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="E130" s="9" t="n"/>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -33856,12 +33856,12 @@
       </c>
       <c r="I130" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K130" s="7" t="inlineStr">
@@ -33871,12 +33871,12 @@
       </c>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -33890,13 +33890,13 @@
       <c r="C131" s="11" t="n"/>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="E131" s="13" t="n"/>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -33926,12 +33926,12 @@
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -33945,13 +33945,13 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="E132" s="9" t="n"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -33971,7 +33971,7 @@
       </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K132" s="7" t="inlineStr">
@@ -33981,12 +33981,12 @@
       </c>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -34000,13 +34000,13 @@
       <c r="C133" s="11" t="n"/>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="E133" s="13" t="n"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
@@ -34019,8 +34019,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I133" s="13" t="n"/>
-      <c r="J133" s="13" t="n"/>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J133" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="K133" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34028,12 +34036,12 @@
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -34047,13 +34055,13 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="E134" s="9" t="n"/>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
@@ -34083,12 +34091,12 @@
       </c>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -34102,13 +34110,13 @@
       <c r="C135" s="11" t="n"/>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="E135" s="13" t="n"/>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
@@ -34121,16 +34129,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J135" s="13" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="I135" s="13" t="n"/>
+      <c r="J135" s="13" t="n"/>
       <c r="K135" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34138,12 +34138,12 @@
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -34157,22 +34157,18 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="E136" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="n"/>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -34180,8 +34176,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I136" s="9" t="n"/>
-      <c r="J136" s="9" t="n"/>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34189,12 +34193,12 @@
       </c>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -34208,18 +34212,18 @@
       <c r="C137" s="11" t="n"/>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="E137" s="13" t="n"/>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -34229,12 +34233,12 @@
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J137" s="13" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="K137" s="11" t="inlineStr">
@@ -34242,10 +34246,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L137" s="13" t="n"/>
+      <c r="L137" s="13" t="inlineStr">
+        <is>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -34259,23 +34267,27 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
-        </is>
-      </c>
-      <c r="E138" s="9" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I138" s="9" t="n"/>
@@ -34287,12 +34299,12 @@
       </c>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -34306,37 +34318,33 @@
       <c r="C139" s="11" t="n"/>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E139" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="n"/>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J139" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="K139" s="11" t="inlineStr">
@@ -34344,14 +34352,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L139" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L139" s="13" t="n"/>
       <c r="M139" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -34365,13 +34369,13 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="E140" s="9" t="n"/>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -34384,16 +34388,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I140" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J140" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
-        </is>
-      </c>
+      <c r="I140" s="9" t="n"/>
+      <c r="J140" s="9" t="n"/>
       <c r="K140" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34401,12 +34397,12 @@
       </c>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -34420,18 +34416,22 @@
       <c r="C141" s="11" t="n"/>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
-        </is>
-      </c>
-      <c r="E141" s="13" t="n"/>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J141" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K141" s="11" t="inlineStr">
@@ -34456,12 +34456,12 @@
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M141" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -34475,22 +34475,18 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="n"/>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
@@ -34498,8 +34494,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I142" s="9" t="n"/>
-      <c r="J142" s="9" t="n"/>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+        </is>
+      </c>
       <c r="K142" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34507,12 +34511,12 @@
       </c>
       <c r="L142" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -34526,13 +34530,13 @@
       <c r="C143" s="11" t="n"/>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
         </is>
       </c>
       <c r="E143" s="13" t="n"/>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
@@ -34547,12 +34551,12 @@
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J143" s="13" t="inlineStr">
         <is>
-          <t>நடுகல்</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="K143" s="11" t="inlineStr">
@@ -34562,12 +34566,12 @@
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M143" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -34581,7 +34585,7 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
@@ -34604,16 +34608,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I144" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J144" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+      <c r="I144" s="9" t="n"/>
+      <c r="J144" s="9" t="n"/>
       <c r="K144" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34626,7 +34622,7 @@
       </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -34640,22 +34636,18 @@
       <c r="C145" s="11" t="n"/>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E145" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="n"/>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
@@ -34665,12 +34657,12 @@
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J145" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="K145" s="11" t="inlineStr">
@@ -34680,12 +34672,12 @@
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M145" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -34699,18 +34691,22 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
-        </is>
-      </c>
-      <c r="E146" s="9" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
@@ -34725,7 +34721,7 @@
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="K146" s="7" t="inlineStr">
@@ -34735,12 +34731,12 @@
       </c>
       <c r="L146" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -34754,18 +34750,22 @@
       <c r="C147" s="11" t="n"/>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
-        </is>
-      </c>
-      <c r="E147" s="13" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -34775,12 +34775,12 @@
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J147" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K147" s="11" t="inlineStr">
@@ -34790,12 +34790,12 @@
       </c>
       <c r="L147" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M147" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -34809,13 +34809,13 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="E148" s="9" t="n"/>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
@@ -34830,10 +34830,14 @@
       </c>
       <c r="I148" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J148" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K148" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34841,12 +34845,12 @@
       </c>
       <c r="L148" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -34860,13 +34864,13 @@
       <c r="C149" s="11" t="n"/>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="E149" s="13" t="n"/>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr">
@@ -34879,8 +34883,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I149" s="13" t="n"/>
-      <c r="J149" s="13" t="n"/>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J149" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
       <c r="K149" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34888,12 +34900,12 @@
       </c>
       <c r="L149" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M149" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -34907,53 +34919,206 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="E150" s="9" t="n"/>
       <c r="F150" s="9" t="inlineStr">
         <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n"/>
+      <c r="K150" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L150" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M150" s="10" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>WB-0150</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="n"/>
+      <c r="C151" s="11" t="n"/>
+      <c r="D151" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="E151" s="13" t="n"/>
+      <c r="F151" s="13" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I151" s="13" t="n"/>
+      <c r="J151" s="13" t="n"/>
+      <c r="K151" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L151" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M151" s="14" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>WB-0151</t>
+        </is>
+      </c>
+      <c r="B152" s="8" t="n"/>
+      <c r="C152" s="7" t="n"/>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>jvpnews.com</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L152" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>WB-0152</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="n"/>
+      <c r="C153" s="11" t="n"/>
+      <c r="D153" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="E153" s="13" t="n"/>
+      <c r="F153" s="13" t="inlineStr">
+        <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="G150" s="7" t="inlineStr">
+      <c r="G153" s="11" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="H150" s="7" t="inlineStr">
+      <c r="H153" s="11" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I150" s="9" t="inlineStr">
+      <c r="I153" s="13" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="J150" s="9" t="inlineStr">
+      <c r="J153" s="13" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="K150" s="7" t="inlineStr">
+      <c r="K153" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L150" s="9" t="inlineStr">
+      <c r="L153" s="13" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
-      <c r="M150" s="10" t="inlineStr">
+      <c r="M153" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M150"/>
+  <autoFilter ref="A1:M153"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -35104,6 +35269,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId152"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35115,7 +35283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N550"/>
+  <dimension ref="A1:N553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -69585,13 +69753,13 @@
       <c r="D526" s="7" t="n"/>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="F526" s="9" t="n"/>
       <c r="G526" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H526" s="7" t="inlineStr">
@@ -69606,12 +69774,12 @@
       </c>
       <c r="J526" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K526" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L526" s="7" t="inlineStr">
@@ -69621,12 +69789,12 @@
       </c>
       <c r="M526" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N526" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -69645,13 +69813,13 @@
       <c r="D527" s="11" t="n"/>
       <c r="E527" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="F527" s="13" t="n"/>
       <c r="G527" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="H527" s="11" t="inlineStr">
@@ -69681,12 +69849,12 @@
       </c>
       <c r="M527" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N527" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -69705,13 +69873,13 @@
       <c r="D528" s="7" t="n"/>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="F528" s="9" t="n"/>
       <c r="G528" s="9" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="H528" s="7" t="inlineStr">
@@ -69726,10 +69894,14 @@
       </c>
       <c r="J528" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K528" s="9" t="n"/>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K528" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="L528" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69737,12 +69909,12 @@
       </c>
       <c r="M528" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N528" s="10" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -69761,13 +69933,13 @@
       <c r="D529" s="11" t="n"/>
       <c r="E529" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="F529" s="13" t="n"/>
       <c r="G529" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="H529" s="11" t="inlineStr">
@@ -69782,14 +69954,10 @@
       </c>
       <c r="J529" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K529" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K529" s="13" t="n"/>
       <c r="L529" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69797,12 +69965,12 @@
       </c>
       <c r="M529" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N529" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -69821,13 +69989,13 @@
       <c r="D530" s="7" t="n"/>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="F530" s="9" t="n"/>
       <c r="G530" s="9" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H530" s="7" t="inlineStr">
@@ -69842,12 +70010,12 @@
       </c>
       <c r="J530" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L530" s="7" t="inlineStr">
@@ -69857,12 +70025,12 @@
       </c>
       <c r="M530" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N530" s="10" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -69881,13 +70049,13 @@
       <c r="D531" s="11" t="n"/>
       <c r="E531" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="F531" s="13" t="n"/>
       <c r="G531" s="13" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="H531" s="11" t="inlineStr">
@@ -69917,12 +70085,12 @@
       </c>
       <c r="M531" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N531" s="14" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -69941,13 +70109,13 @@
       <c r="D532" s="7" t="n"/>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="F532" s="9" t="n"/>
       <c r="G532" s="9" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="H532" s="7" t="inlineStr">
@@ -69967,7 +70135,7 @@
       </c>
       <c r="K532" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L532" s="7" t="inlineStr">
@@ -69977,12 +70145,12 @@
       </c>
       <c r="M532" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N532" s="10" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -70001,13 +70169,13 @@
       <c r="D533" s="11" t="n"/>
       <c r="E533" s="13" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="F533" s="13" t="n"/>
       <c r="G533" s="13" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="H533" s="11" t="inlineStr">
@@ -70020,8 +70188,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J533" s="13" t="n"/>
-      <c r="K533" s="13" t="n"/>
+      <c r="J533" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K533" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="L533" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70029,12 +70205,12 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N533" s="14" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -70053,13 +70229,13 @@
       <c r="D534" s="7" t="n"/>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="F534" s="9" t="n"/>
       <c r="G534" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="H534" s="7" t="inlineStr">
@@ -70089,12 +70265,12 @@
       </c>
       <c r="M534" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N534" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -70113,13 +70289,13 @@
       <c r="D535" s="11" t="n"/>
       <c r="E535" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="F535" s="13" t="n"/>
       <c r="G535" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="H535" s="11" t="inlineStr">
@@ -70132,16 +70308,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J535" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K535" s="13" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="J535" s="13" t="n"/>
+      <c r="K535" s="13" t="n"/>
       <c r="L535" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70149,12 +70317,12 @@
       </c>
       <c r="M535" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N535" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -70173,22 +70341,18 @@
       <c r="D536" s="7" t="n"/>
       <c r="E536" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="F536" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+        </is>
+      </c>
+      <c r="F536" s="9" t="n"/>
       <c r="G536" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="H536" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I536" s="7" t="inlineStr">
@@ -70196,8 +70360,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J536" s="9" t="n"/>
-      <c r="K536" s="9" t="n"/>
+      <c r="J536" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K536" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L536" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70205,12 +70377,12 @@
       </c>
       <c r="M536" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N536" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -70229,18 +70401,18 @@
       <c r="D537" s="11" t="n"/>
       <c r="E537" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="F537" s="13" t="n"/>
       <c r="G537" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H537" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I537" s="11" t="inlineStr">
@@ -70250,12 +70422,12 @@
       </c>
       <c r="J537" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K537" s="13" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="L537" s="11" t="inlineStr">
@@ -70263,10 +70435,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M537" s="13" t="n"/>
+      <c r="M537" s="13" t="inlineStr">
+        <is>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N537" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -70285,23 +70461,27 @@
       <c r="D538" s="7" t="n"/>
       <c r="E538" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
-        </is>
-      </c>
-      <c r="F538" s="9" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="F538" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G538" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H538" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I538" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J538" s="9" t="n"/>
@@ -70313,12 +70493,12 @@
       </c>
       <c r="M538" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N538" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -70337,37 +70517,33 @@
       <c r="D539" s="11" t="n"/>
       <c r="E539" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F539" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+        </is>
+      </c>
+      <c r="F539" s="13" t="n"/>
       <c r="G539" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H539" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I539" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J539" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K539" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="L539" s="11" t="inlineStr">
@@ -70375,14 +70551,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M539" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M539" s="13" t="n"/>
       <c r="N539" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -70401,13 +70573,13 @@
       <c r="D540" s="7" t="n"/>
       <c r="E540" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="F540" s="9" t="n"/>
       <c r="G540" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H540" s="7" t="inlineStr">
@@ -70420,16 +70592,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J540" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K540" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
-        </is>
-      </c>
+      <c r="J540" s="9" t="n"/>
+      <c r="K540" s="9" t="n"/>
       <c r="L540" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70437,12 +70601,12 @@
       </c>
       <c r="M540" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N540" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -70461,18 +70625,22 @@
       <c r="D541" s="11" t="n"/>
       <c r="E541" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
-        </is>
-      </c>
-      <c r="F541" s="13" t="n"/>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F541" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G541" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H541" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I541" s="11" t="inlineStr">
@@ -70482,12 +70650,12 @@
       </c>
       <c r="J541" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K541" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L541" s="11" t="inlineStr">
@@ -70497,12 +70665,12 @@
       </c>
       <c r="M541" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N541" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -70521,22 +70689,18 @@
       <c r="D542" s="7" t="n"/>
       <c r="E542" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="F542" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+        </is>
+      </c>
+      <c r="F542" s="9" t="n"/>
       <c r="G542" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="H542" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I542" s="7" t="inlineStr">
@@ -70544,8 +70708,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J542" s="9" t="n"/>
-      <c r="K542" s="9" t="n"/>
+      <c r="J542" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K542" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+        </is>
+      </c>
       <c r="L542" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70553,12 +70725,12 @@
       </c>
       <c r="M542" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N542" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -70577,13 +70749,13 @@
       <c r="D543" s="11" t="n"/>
       <c r="E543" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
         </is>
       </c>
       <c r="F543" s="13" t="n"/>
       <c r="G543" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H543" s="11" t="inlineStr">
@@ -70598,12 +70770,12 @@
       </c>
       <c r="J543" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K543" s="13" t="inlineStr">
         <is>
-          <t>நடுகல்</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="L543" s="11" t="inlineStr">
@@ -70613,12 +70785,12 @@
       </c>
       <c r="M543" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N543" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -70637,7 +70809,7 @@
       <c r="D544" s="7" t="n"/>
       <c r="E544" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="F544" s="9" t="inlineStr">
@@ -70660,16 +70832,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J544" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K544" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+      <c r="J544" s="9" t="n"/>
+      <c r="K544" s="9" t="n"/>
       <c r="L544" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70682,7 +70846,7 @@
       </c>
       <c r="N544" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -70701,22 +70865,18 @@
       <c r="D545" s="11" t="n"/>
       <c r="E545" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F545" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+        </is>
+      </c>
+      <c r="F545" s="13" t="n"/>
       <c r="G545" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="H545" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I545" s="11" t="inlineStr">
@@ -70726,12 +70886,12 @@
       </c>
       <c r="J545" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K545" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="L545" s="11" t="inlineStr">
@@ -70741,12 +70901,12 @@
       </c>
       <c r="M545" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N545" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -70765,18 +70925,22 @@
       <c r="D546" s="7" t="n"/>
       <c r="E546" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
-        </is>
-      </c>
-      <c r="F546" s="9" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="F546" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G546" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H546" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I546" s="7" t="inlineStr">
@@ -70791,7 +70955,7 @@
       </c>
       <c r="K546" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="L546" s="7" t="inlineStr">
@@ -70801,12 +70965,12 @@
       </c>
       <c r="M546" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N546" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -70825,18 +70989,22 @@
       <c r="D547" s="11" t="n"/>
       <c r="E547" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
-        </is>
-      </c>
-      <c r="F547" s="13" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F547" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G547" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H547" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I547" s="11" t="inlineStr">
@@ -70846,12 +71014,12 @@
       </c>
       <c r="J547" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K547" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L547" s="11" t="inlineStr">
@@ -70861,12 +71029,12 @@
       </c>
       <c r="M547" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N547" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -70885,13 +71053,13 @@
       <c r="D548" s="7" t="n"/>
       <c r="E548" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="F548" s="9" t="n"/>
       <c r="G548" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="H548" s="7" t="inlineStr">
@@ -70906,10 +71074,14 @@
       </c>
       <c r="J548" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K548" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K548" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L548" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70917,12 +71089,12 @@
       </c>
       <c r="M548" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N548" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -70941,13 +71113,13 @@
       <c r="D549" s="11" t="n"/>
       <c r="E549" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="F549" s="13" t="n"/>
       <c r="G549" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H549" s="11" t="inlineStr">
@@ -70960,8 +71132,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J549" s="13" t="n"/>
-      <c r="K549" s="13" t="n"/>
+      <c r="J549" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K549" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
       <c r="L549" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70969,12 +71149,12 @@
       </c>
       <c r="M549" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N549" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -70993,53 +71173,221 @@
       <c r="D550" s="7" t="n"/>
       <c r="E550" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="F550" s="9" t="n"/>
       <c r="G550" s="9" t="inlineStr">
         <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="H550" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I550" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J550" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K550" s="9" t="n"/>
+      <c r="L550" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M550" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N550" s="10" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0550</t>
+        </is>
+      </c>
+      <c r="B551" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C551" s="12" t="n"/>
+      <c r="D551" s="11" t="n"/>
+      <c r="E551" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="F551" s="13" t="n"/>
+      <c r="G551" s="13" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="H551" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I551" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J551" s="13" t="n"/>
+      <c r="K551" s="13" t="n"/>
+      <c r="L551" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M551" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N551" s="14" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0551</t>
+        </is>
+      </c>
+      <c r="B552" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C552" s="8" t="n"/>
+      <c r="D552" s="7" t="n"/>
+      <c r="E552" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+        </is>
+      </c>
+      <c r="F552" s="9" t="n"/>
+      <c r="G552" s="9" t="inlineStr">
+        <is>
+          <t>jvpnews.com</t>
+        </is>
+      </c>
+      <c r="H552" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I552" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J552" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K552" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="L552" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M552" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N552" s="10" t="inlineStr">
+        <is>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0552</t>
+        </is>
+      </c>
+      <c r="B553" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C553" s="12" t="n"/>
+      <c r="D553" s="11" t="n"/>
+      <c r="E553" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="F553" s="13" t="n"/>
+      <c r="G553" s="13" t="inlineStr">
+        <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="H550" s="7" t="inlineStr">
+      <c r="H553" s="11" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="I550" s="7" t="inlineStr">
+      <c r="I553" s="11" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J550" s="9" t="inlineStr">
+      <c r="J553" s="13" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="K550" s="9" t="inlineStr">
+      <c r="K553" s="13" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="L550" s="7" t="inlineStr">
+      <c r="L553" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M550" s="9" t="inlineStr">
+      <c r="M553" s="13" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
-      <c r="N550" s="10" t="inlineStr">
+      <c r="N553" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N550"/>
+  <autoFilter ref="A1:N553"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -71590,6 +71938,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N548" r:id="rId547"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N549" r:id="rId548"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N553" r:id="rId552"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Papers'!$A$1:$M$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspaper Articles'!$A$1:$M$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Magazines &amp; Journals'!$A$1:$M$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$566</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$570</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-24. Counts below are live formulas over the 'All Records' sheet.</t>
+          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-25. Counts below are live formulas over the 'All Records' sheet.</t>
         </is>
       </c>
     </row>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$566,A6)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$570,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$566,A6,'All Records'!$L$2:$L$566,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$570,A6,'All Records'!$L$2:$L$570,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$566,A7)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$570,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$566,A7,'All Records'!$L$2:$L$566,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$570,A7,'All Records'!$L$2:$L$570,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$566,A8)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$570,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$566,A8,'All Records'!$L$2:$L$566,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$570,A8,'All Records'!$L$2:$L$570,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$566,A9)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$570,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$566,A9,'All Records'!$L$2:$L$566,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$570,A9,'All Records'!$L$2:$L$570,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$566,A10)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$570,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$566,A10,'All Records'!$L$2:$L$566,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$570,A10,'All Records'!$L$2:$L$570,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$566,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$566,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$566,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$566,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$566,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$566,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -787,23 +787,23 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="G23" s="4">
@@ -818,23 +818,23 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="G24" s="4">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="G25" s="4">
@@ -880,23 +880,23 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="G26" s="4">
@@ -911,23 +911,23 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="G27" s="4">
@@ -942,23 +942,23 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$566="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$566,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="G28" s="4">
@@ -26336,7 +26336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -31858,18 +31858,18 @@
       <c r="C91" s="11" t="n"/>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
+          <t>About: Tamil inscriptions in Sri Lanka - DBpedia Association</t>
         </is>
       </c>
       <c r="E91" s="13" t="n"/>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>dbpedia.org</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -31879,12 +31879,12 @@
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J91" s="13" t="inlineStr">
         <is>
-          <t>archaeology; East</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
@@ -31892,10 +31892,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L91" s="13" t="n"/>
+      <c r="L91" s="13" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-25 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M91" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
+          <t>https://dbpedia.org/page/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -31909,18 +31913,18 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Ancient Coins - Archaeology</t>
+          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
         </is>
       </c>
       <c r="E92" s="9" t="n"/>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -31930,12 +31934,12 @@
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>archaeology; ancient coins</t>
+          <t>archaeology; East</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
@@ -31943,14 +31947,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L92" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L92" s="9" t="n"/>
       <c r="M92" s="10" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/ancient-coins</t>
+          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
         </is>
       </c>
     </row>
@@ -31964,13 +31964,13 @@
       <c r="C93" s="11" t="n"/>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>Ancient Coins and Trade Evidence | Lanka Websites</t>
+          <t>Ancient Coins - Archaeology</t>
         </is>
       </c>
       <c r="E93" s="13" t="n"/>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>lankawebsites.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -31985,12 +31985,12 @@
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
         </is>
       </c>
       <c r="J93" s="13" t="inlineStr">
         <is>
-          <t>ancient coins</t>
+          <t>archaeology; ancient coins</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
@@ -32005,7 +32005,7 @@
       </c>
       <c r="M93" s="14" t="inlineStr">
         <is>
-          <t>https://lankawebsites.com/blog/ancient-civilization-archaeology/ancient-coins-and-trade-evidence</t>
+          <t>https://archaeology.gov.lk/index.php/ancient-coins</t>
         </is>
       </c>
     </row>
@@ -32019,13 +32019,13 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Ancient Kadurugoda Viharaya — Grokipedia</t>
+          <t>Ancient Coins and Trade Evidence | Lanka Websites</t>
         </is>
       </c>
       <c r="E94" s="9" t="n"/>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>lankawebsites.com</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
@@ -32038,8 +32038,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I94" s="9" t="n"/>
-      <c r="J94" s="9" t="n"/>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>ancient coins</t>
+        </is>
+      </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32047,12 +32055,12 @@
       </c>
       <c r="L94" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/ancient_kadurugoda_viharaya</t>
+          <t>https://lankawebsites.com/blog/ancient-civilization-archaeology/ancient-coins-and-trade-evidence</t>
         </is>
       </c>
     </row>
@@ -32066,13 +32074,13 @@
       <c r="C95" s="11" t="n"/>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Ancient Pandyan coins unearthed in Mannar | Tamil Guardian</t>
+          <t>Ancient Kadurugoda Viharaya — Grokipedia</t>
         </is>
       </c>
       <c r="E95" s="13" t="n"/>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>tamilguardian.com</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -32085,11 +32093,7 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
+      <c r="I95" s="13" t="n"/>
       <c r="J95" s="13" t="n"/>
       <c r="K95" s="11" t="inlineStr">
         <is>
@@ -32098,12 +32102,12 @@
       </c>
       <c r="L95" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M95" s="14" t="inlineStr">
         <is>
-          <t>https://www.tamilguardian.com/content/ancient-pandyan-coins-unearthed-mannar</t>
+          <t>https://grokipedia.com/page/ancient_kadurugoda_viharaya</t>
         </is>
       </c>
     </row>
@@ -32117,13 +32121,13 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Archaeological Museum of Jaffna - Tales of Ceylon</t>
+          <t>Ancient Pandyan coins unearthed in Mannar | Tamil Guardian</t>
         </is>
       </c>
       <c r="E96" s="9" t="n"/>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>talesofceylon.com</t>
+          <t>tamilguardian.com</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
@@ -32138,14 +32142,10 @@
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n"/>
       <c r="K96" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32153,12 +32153,12 @@
       </c>
       <c r="L96" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
-          <t>https://www.talesofceylon.com/destinations/jaffna/attractions-in-jaffna/archaeological-museum-of-jaffna/</t>
+          <t>https://www.tamilguardian.com/content/ancient-pandyan-coins-unearthed-mannar</t>
         </is>
       </c>
     </row>
@@ -32172,13 +32172,13 @@
       <c r="C97" s="11" t="n"/>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Archaeological Museum, Jaffna - Wikipedia</t>
+          <t>Archaeological Museum of Jaffna - Tales of Ceylon</t>
         </is>
       </c>
       <c r="E97" s="13" t="n"/>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>talesofceylon.com</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -32208,12 +32208,12 @@
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
         </is>
       </c>
       <c r="M97" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Archaeological_Museum,_Jaffna</t>
+          <t>https://www.talesofceylon.com/destinations/jaffna/attractions-in-jaffna/archaeological-museum-of-jaffna/</t>
         </is>
       </c>
     </row>
@@ -32227,13 +32227,13 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+          <t>Archaeological Museum, Jaffna - Wikipedia</t>
         </is>
       </c>
       <c r="E98" s="9" t="n"/>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
@@ -32263,12 +32263,12 @@
       </c>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
+          <t>https://en.wikipedia.org/wiki/Archaeological_Museum,_Jaffna</t>
         </is>
       </c>
     </row>
@@ -32282,22 +32282,18 @@
       <c r="C99" s="11" t="n"/>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>Brahmi script</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="n"/>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
@@ -32307,12 +32303,12 @@
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J99" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr">
@@ -32322,12 +32318,12 @@
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M99" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
+          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
         </is>
       </c>
     </row>
@@ -32341,7 +32337,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Buddhism amongst Tamils in Sri Lanka</t>
+          <t>Brahmi script</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -32364,8 +32360,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I100" s="9" t="n"/>
-      <c r="J100" s="9" t="n"/>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32373,12 +32377,12 @@
       </c>
       <c r="L100" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
         </is>
       </c>
     </row>
@@ -32392,18 +32396,22 @@
       <c r="C101" s="11" t="n"/>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Buddhist Remains in the Jaffna Peninsula</t>
-        </is>
-      </c>
-      <c r="E101" s="13" t="n"/>
+          <t>Buddhism amongst Tamils in Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
@@ -32411,25 +32419,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J101" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; Jaffna</t>
-        </is>
-      </c>
+      <c r="I101" s="13" t="n"/>
+      <c r="J101" s="13" t="n"/>
       <c r="K101" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L101" s="13" t="n"/>
+      <c r="L101" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M101" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna/</t>
+          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -32443,7 +32447,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+          <t>Buddhist Remains in the Jaffna Peninsula</t>
         </is>
       </c>
       <c r="E102" s="9" t="n"/>
@@ -32469,7 +32473,7 @@
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Pungudutivu</t>
+          <t>தொல்லியல்; Jaffna</t>
         </is>
       </c>
       <c r="K102" s="7" t="inlineStr">
@@ -32480,7 +32484,7 @@
       <c r="L102" s="9" t="n"/>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/tikali/</t>
+          <t>https://amazinglanka.com/wp/jaffna/</t>
         </is>
       </c>
     </row>
@@ -32494,22 +32498,18 @@
       <c r="C103" s="11" t="n"/>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>Cankilian Thoppu</t>
-        </is>
-      </c>
-      <c r="E103" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="n"/>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -32517,21 +32517,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I103" s="13" t="n"/>
-      <c r="J103" s="13" t="n"/>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J103" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Pungudutivu</t>
+        </is>
+      </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L103" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L103" s="13" t="n"/>
       <c r="M103" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
+          <t>https://amazinglanka.com/wp/tikali/</t>
         </is>
       </c>
     </row>
@@ -32545,18 +32549,22 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Coins DB| Home - archaeology.gov.lk</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="n"/>
+          <t>Cankilian Thoppu</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -32564,16 +32572,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J104" s="9" t="inlineStr">
-        <is>
-          <t>archaeology</t>
-        </is>
-      </c>
+      <c r="I104" s="9" t="n"/>
+      <c r="J104" s="9" t="n"/>
       <c r="K104" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32581,12 +32581,12 @@
       </c>
       <c r="L104" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
+          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
         </is>
       </c>
     </row>
@@ -32600,13 +32600,13 @@
       <c r="C105" s="11" t="n"/>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
+          <t>Coins DB| Home - archaeology.gov.lk</t>
         </is>
       </c>
       <c r="E105" s="13" t="n"/>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>dainst.org</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
@@ -32619,8 +32619,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I105" s="13" t="n"/>
-      <c r="J105" s="13" t="n"/>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J105" s="13" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="K105" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32628,12 +32636,12 @@
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M105" s="14" t="inlineStr">
         <is>
-          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
+          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
         </is>
       </c>
     </row>
@@ -32647,13 +32655,13 @@
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
+          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
         </is>
       </c>
       <c r="E106" s="9" t="n"/>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>elanka.com.au</t>
+          <t>dainst.org</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -32666,16 +32674,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I106" s="9" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="inlineStr">
-        <is>
-          <t>hero stone</t>
-        </is>
-      </c>
+      <c r="I106" s="9" t="n"/>
+      <c r="J106" s="9" t="n"/>
       <c r="K106" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32683,12 +32683,12 @@
       </c>
       <c r="L106" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
-          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
+          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
         </is>
       </c>
     </row>
@@ -32702,13 +32702,13 @@
       <c r="C107" s="11" t="n"/>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
+          <t>Epigraphy of Tamil Brahmi Script - தமிழ்-பிராமி - கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="E107" s="13" t="n"/>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>searchworks.stanford.edu</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -32718,13 +32718,17 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I107" s="13" t="n"/>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
       <c r="J107" s="13" t="inlineStr">
         <is>
-          <t>hero-stone</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி; epigraphy; brahmi</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr">
@@ -32734,12 +32738,12 @@
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="M107" s="14" t="inlineStr">
         <is>
-          <t>https://searchworks.stanford.edu/view/14451040</t>
+          <t>https://www.scribd.com/document/397330115/Epigraphy-of-Tamil-Brahmi-Script-%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4-%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%AE%E0%AE%BF-%E0%AE%95%E0%AE%B2-%E0%AE%B5%E0%AF%86%E0%AE%9F-%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3</t>
         </is>
       </c>
     </row>
@@ -32753,13 +32757,13 @@
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
+          <t>Glimpses of the Eelam Tamil Heritage - நூலகம்</t>
         </is>
       </c>
       <c r="E108" s="9" t="n"/>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -32769,19 +32773,15 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J108" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n"/>
       <c r="K108" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32789,12 +32789,12 @@
       </c>
       <c r="L108" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
+          <t>https://noolaham.org/wiki/index.php/Glimpses_of_the_Eelam_Tamil_Heritage</t>
         </is>
       </c>
     </row>
@@ -32808,13 +32808,13 @@
       <c r="C109" s="11" t="n"/>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
+          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
         </is>
       </c>
       <c r="E109" s="13" t="n"/>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>elanka.com.au</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -32829,12 +32829,12 @@
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J109" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr">
@@ -32844,12 +32844,12 @@
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M109" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/?lang=en</t>
+          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
         </is>
       </c>
     </row>
@@ -32863,13 +32863,13 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum</t>
+          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
         </is>
       </c>
       <c r="E110" s="9" t="n"/>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>lonelyplanet.com</t>
+          <t>searchworks.stanford.edu</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -32882,14 +32882,10 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="I110" s="9" t="n"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>hero-stone</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr">
@@ -32899,12 +32895,12 @@
       </c>
       <c r="L110" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
+          <t>https://searchworks.stanford.edu/view/14451040</t>
         </is>
       </c>
     </row>
@@ -32918,13 +32914,13 @@
       <c r="C111" s="11" t="n"/>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
+          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
         </is>
       </c>
       <c r="E111" s="13" t="n"/>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>tripadvisor.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
@@ -32939,12 +32935,12 @@
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J111" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
@@ -32954,12 +32950,12 @@
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M111" s="14" t="inlineStr">
         <is>
-          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
+          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
         </is>
       </c>
     </row>
@@ -32973,13 +32969,13 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
+          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
         </is>
       </c>
       <c r="E112" s="9" t="n"/>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>jaffna.top</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -32994,12 +32990,12 @@
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr">
@@ -33009,12 +33005,12 @@
       </c>
       <c r="L112" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
+          <t>https://www.inscriptions.lk/?lang=en</t>
         </is>
       </c>
     </row>
@@ -33028,13 +33024,13 @@
       <c r="C113" s="11" t="n"/>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
+          <t>Jaffna Archaeological Museum</t>
         </is>
       </c>
       <c r="E113" s="13" t="n"/>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>srilankatravelpages.com</t>
+          <t>lonelyplanet.com</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
@@ -33064,12 +33060,12 @@
       </c>
       <c r="L113" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
       <c r="M113" s="14" t="inlineStr">
         <is>
-          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
+          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
         </is>
       </c>
     </row>
@@ -33083,13 +33079,13 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
+          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
         </is>
       </c>
       <c r="E114" s="9" t="n"/>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>srilankatourhelp.org</t>
+          <t>tripadvisor.com</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -33124,7 +33120,7 @@
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
         </is>
       </c>
     </row>
@@ -33138,13 +33134,13 @@
       <c r="C115" s="11" t="n"/>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | About.lk</t>
+          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
         </is>
       </c>
       <c r="E115" s="13" t="n"/>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
+          <t>jaffna.top</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
@@ -33179,7 +33175,7 @@
       </c>
       <c r="M115" s="14" t="inlineStr">
         <is>
-          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
+          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
         </is>
       </c>
     </row>
@@ -33193,13 +33189,13 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
         </is>
       </c>
       <c r="E116" s="9" t="n"/>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>srilankatravelpages.com</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -33229,12 +33225,12 @@
       </c>
       <c r="L116" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
+          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
         </is>
       </c>
     </row>
@@ -33248,13 +33244,13 @@
       <c r="C117" s="11" t="n"/>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
+          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
         </is>
       </c>
       <c r="E117" s="13" t="n"/>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>i-discoverasia.com</t>
+          <t>srilankatourhelp.org</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
@@ -33274,7 +33270,7 @@
       </c>
       <c r="J117" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
@@ -33284,12 +33280,12 @@
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M117" s="14" t="inlineStr">
         <is>
-          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
+          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
         </is>
       </c>
     </row>
@@ -33303,13 +33299,13 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archeology Tour - Journe Experiences</t>
+          <t>Jaffna Archaeological Museum | About.lk</t>
         </is>
       </c>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>journesrilanka.com</t>
+          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
@@ -33322,8 +33318,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I118" s="9" t="n"/>
-      <c r="J118" s="9" t="n"/>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33331,12 +33335,12 @@
       </c>
       <c r="L118" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
+          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
         </is>
       </c>
     </row>
@@ -33350,13 +33354,13 @@
       <c r="C119" s="11" t="n"/>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
+          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
         </is>
       </c>
       <c r="E119" s="13" t="n"/>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>lanka-excursions-holidays.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
@@ -33369,8 +33373,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I119" s="13" t="n"/>
-      <c r="J119" s="13" t="n"/>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J119" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33378,12 +33390,12 @@
       </c>
       <c r="L119" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M119" s="14" t="inlineStr">
         <is>
-          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
+          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
         </is>
       </c>
     </row>
@@ -33397,13 +33409,13 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
         </is>
       </c>
       <c r="E120" s="9" t="n"/>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>i-discoverasia.com</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -33416,8 +33428,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I120" s="9" t="n"/>
-      <c r="J120" s="9" t="n"/>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33425,12 +33445,12 @@
       </c>
       <c r="L120" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -33444,13 +33464,13 @@
       <c r="C121" s="11" t="n"/>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Jaffna Archeology Tour - Journe Experiences</t>
         </is>
       </c>
       <c r="E121" s="13" t="n"/>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>journesrilanka.com</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr">
@@ -33472,12 +33492,12 @@
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M121" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
         </is>
       </c>
     </row>
@@ -33491,13 +33511,13 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
         </is>
       </c>
       <c r="E122" s="9" t="n"/>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>lanka-excursions-holidays.com</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -33510,16 +33530,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I122" s="9" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J122" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="I122" s="9" t="n"/>
+      <c r="J122" s="9" t="n"/>
       <c r="K122" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33527,12 +33539,12 @@
       </c>
       <c r="L122" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
         </is>
       </c>
     </row>
@@ -33546,22 +33558,18 @@
       <c r="C123" s="11" t="n"/>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="E123" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="n"/>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
@@ -33569,16 +33577,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J123" s="13" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+      <c r="I123" s="13" t="n"/>
+      <c r="J123" s="13" t="n"/>
       <c r="K123" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33586,12 +33586,12 @@
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M123" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -33605,18 +33605,18 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="E124" s="9" t="n"/>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -33624,25 +33624,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I124" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J124" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; settlement</t>
-        </is>
-      </c>
+      <c r="I124" s="9" t="n"/>
+      <c r="J124" s="9" t="n"/>
       <c r="K124" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L124" s="9" t="n"/>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -33656,13 +33652,13 @@
       <c r="C125" s="11" t="n"/>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>Museums - Archaeology</t>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
         </is>
       </c>
       <c r="E125" s="13" t="n"/>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
@@ -33677,12 +33673,12 @@
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J125" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K125" s="11" t="inlineStr">
@@ -33692,12 +33688,12 @@
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M125" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -33711,18 +33707,22 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -33747,12 +33747,12 @@
       </c>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -33766,18 +33766,18 @@
       <c r="C127" s="11" t="n"/>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="E127" s="13" t="n"/>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
@@ -33787,23 +33787,23 @@
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J127" s="13" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J127" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; settlement</t>
+        </is>
+      </c>
       <c r="K127" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L127" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L127" s="13" t="n"/>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -33817,13 +33817,13 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>Museums - Archaeology</t>
         </is>
       </c>
       <c r="E128" s="9" t="n"/>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
@@ -33838,12 +33838,12 @@
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>inscription; brahmi</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="K128" s="7" t="inlineStr">
@@ -33853,12 +33853,12 @@
       </c>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
         </is>
       </c>
     </row>
@@ -33872,13 +33872,13 @@
       <c r="C129" s="11" t="n"/>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="E129" s="13" t="n"/>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk:8080</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr">
@@ -33893,12 +33893,12 @@
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J129" s="13" t="inlineStr">
         <is>
-          <t>inscription; brahmi</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K129" s="11" t="inlineStr">
@@ -33908,12 +33908,12 @@
       </c>
       <c r="L129" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -33927,13 +33927,13 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="E130" s="9" t="n"/>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -33959,12 +33959,12 @@
       </c>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -33978,13 +33978,13 @@
       <c r="C131" s="11" t="n"/>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="E131" s="13" t="n"/>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -33999,12 +33999,12 @@
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J131" s="13" t="inlineStr">
         <is>
-          <t>rock art</t>
+          <t>inscription; brahmi</t>
         </is>
       </c>
       <c r="K131" s="11" t="inlineStr">
@@ -34014,12 +34014,12 @@
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -34033,13 +34033,13 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
         </is>
       </c>
       <c r="E132" s="9" t="n"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>repo.lib.jfn.ac.lk:8080</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>inscription; brahmi</t>
         </is>
       </c>
       <c r="K132" s="7" t="inlineStr">
@@ -34069,12 +34069,12 @@
       </c>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
         </is>
       </c>
     </row>
@@ -34088,13 +34088,13 @@
       <c r="C133" s="11" t="n"/>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="E133" s="13" t="n"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
@@ -34109,14 +34109,10 @@
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J133" s="13" t="inlineStr">
-        <is>
-          <t>hero stone</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J133" s="13" t="n"/>
       <c r="K133" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34124,12 +34120,12 @@
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -34143,22 +34139,18 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="E134" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="n"/>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
@@ -34166,8 +34158,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I134" s="9" t="n"/>
-      <c r="J134" s="9" t="n"/>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>Rock art / பாறை ஓவியம்</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>rock art</t>
+        </is>
+      </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34175,12 +34175,12 @@
       </c>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -34194,13 +34194,13 @@
       <c r="C135" s="11" t="n"/>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>Sri Lanka Inscriptions</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E135" s="13" t="n"/>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
@@ -34215,12 +34215,12 @@
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J135" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="K135" s="11" t="inlineStr">
@@ -34230,12 +34230,12 @@
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -34249,13 +34249,13 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sinhalese Hero Stone Analysis</t>
         </is>
       </c>
       <c r="E136" s="9" t="n"/>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
@@ -34270,12 +34270,12 @@
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr">
@@ -34285,12 +34285,12 @@
       </c>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -34304,18 +34304,22 @@
       <c r="C137" s="11" t="n"/>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
-        </is>
-      </c>
-      <c r="E137" s="13" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -34323,16 +34327,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J137" s="13" t="inlineStr">
-        <is>
-          <t>brahmi</t>
-        </is>
-      </c>
+      <c r="I137" s="13" t="n"/>
+      <c r="J137" s="13" t="n"/>
       <c r="K137" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34340,12 +34336,12 @@
       </c>
       <c r="L137" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -34359,13 +34355,13 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="E138" s="9" t="n"/>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
@@ -34380,10 +34376,14 @@
       </c>
       <c r="I138" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J138" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34391,12 +34391,12 @@
       </c>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -34410,13 +34410,13 @@
       <c r="C139" s="11" t="n"/>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="E139" s="13" t="n"/>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
@@ -34431,12 +34431,12 @@
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J139" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="K139" s="11" t="inlineStr">
@@ -34451,7 +34451,7 @@
       </c>
       <c r="M139" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -34465,13 +34465,13 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="E140" s="9" t="n"/>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>en.bharatpedia.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -34486,12 +34486,12 @@
       </c>
       <c r="I140" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="K140" s="7" t="inlineStr">
@@ -34501,12 +34501,12 @@
       </c>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -34520,13 +34520,13 @@
       <c r="C141" s="11" t="n"/>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="E141" s="13" t="n"/>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
@@ -34541,14 +34541,10 @@
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J141" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J141" s="13" t="n"/>
       <c r="K141" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34556,12 +34552,12 @@
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M141" s="14" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -34575,13 +34571,13 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="E142" s="9" t="n"/>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
@@ -34596,12 +34592,12 @@
       </c>
       <c r="I142" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K142" s="7" t="inlineStr">
@@ -34611,12 +34607,12 @@
       </c>
       <c r="L142" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -34630,13 +34626,13 @@
       <c r="C143" s="11" t="n"/>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="E143" s="13" t="n"/>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
@@ -34656,7 +34652,7 @@
       </c>
       <c r="J143" s="13" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K143" s="11" t="inlineStr">
@@ -34666,12 +34662,12 @@
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M143" s="14" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -34685,13 +34681,13 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="E144" s="9" t="n"/>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
@@ -34704,8 +34700,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I144" s="9" t="n"/>
-      <c r="J144" s="9" t="n"/>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="K144" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34713,12 +34717,12 @@
       </c>
       <c r="L144" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -34732,13 +34736,13 @@
       <c r="C145" s="11" t="n"/>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="E145" s="13" t="n"/>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>cambridge.org</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
@@ -34751,8 +34755,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I145" s="13" t="n"/>
-      <c r="J145" s="13" t="n"/>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J145" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="K145" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34760,12 +34772,12 @@
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M145" s="14" t="inlineStr">
         <is>
-          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -34779,13 +34791,13 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="E146" s="9" t="n"/>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -34815,12 +34827,12 @@
       </c>
       <c r="L146" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -34834,13 +34846,13 @@
       <c r="C147" s="11" t="n"/>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="E147" s="13" t="n"/>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
@@ -34853,16 +34865,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I147" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J147" s="13" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="I147" s="13" t="n"/>
+      <c r="J147" s="13" t="n"/>
       <c r="K147" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34870,12 +34874,12 @@
       </c>
       <c r="L147" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M147" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -34889,22 +34893,18 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="n"/>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>cambridge.org</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
@@ -34921,12 +34921,12 @@
       </c>
       <c r="L148" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
         </is>
       </c>
     </row>
@@ -34940,18 +34940,18 @@
       <c r="C149" s="11" t="n"/>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
         </is>
       </c>
       <c r="E149" s="13" t="n"/>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
@@ -34961,12 +34961,12 @@
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J149" s="13" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="K149" s="11" t="inlineStr">
@@ -34974,10 +34974,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L149" s="13" t="n"/>
+      <c r="L149" s="13" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M149" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -34991,13 +34995,13 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="E150" s="9" t="n"/>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
@@ -35007,11 +35011,19 @@
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I150" s="9" t="n"/>
-      <c r="J150" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35019,12 +35031,12 @@
       </c>
       <c r="L150" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M150" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -35038,7 +35050,7 @@
       <c r="C151" s="11" t="n"/>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+          <t>Vallipuram</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
@@ -35048,7 +35060,7 @@
       </c>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr">
@@ -35058,19 +35070,11 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J151" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I151" s="13" t="n"/>
+      <c r="J151" s="13" t="n"/>
       <c r="K151" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35083,7 +35087,7 @@
       </c>
       <c r="M151" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -35097,33 +35101,33 @@
       <c r="C152" s="7" t="n"/>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
         </is>
       </c>
       <c r="E152" s="9" t="n"/>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I152" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr">
@@ -35131,14 +35135,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L152" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L152" s="9" t="n"/>
       <c r="M152" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -35152,13 +35152,13 @@
       <c r="C153" s="11" t="n"/>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="E153" s="13" t="n"/>
       <c r="F153" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr">
@@ -35171,16 +35171,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J153" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="I153" s="13" t="n"/>
+      <c r="J153" s="13" t="n"/>
       <c r="K153" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35188,12 +35180,12 @@
       </c>
       <c r="L153" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M153" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -35207,7 +35199,7 @@
       <c r="C154" s="7" t="n"/>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
@@ -35230,8 +35222,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I154" s="9" t="n"/>
-      <c r="J154" s="9" t="n"/>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K154" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35244,7 +35244,7 @@
       </c>
       <c r="M154" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -35258,13 +35258,13 @@
       <c r="C155" s="11" t="n"/>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
         </is>
       </c>
       <c r="E155" s="13" t="n"/>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr">
@@ -35279,12 +35279,12 @@
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J155" s="13" t="inlineStr">
         <is>
-          <t>நடுகல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="K155" s="11" t="inlineStr">
@@ -35294,12 +35294,12 @@
       </c>
       <c r="L155" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M155" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -35313,22 +35313,18 @@
       <c r="C156" s="7" t="n"/>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
-        </is>
-      </c>
-      <c r="E156" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="n"/>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -35338,12 +35334,12 @@
       </c>
       <c r="I156" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J156" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="K156" s="7" t="inlineStr">
@@ -35353,12 +35349,12 @@
       </c>
       <c r="L156" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M156" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -35372,7 +35368,7 @@
       <c r="C157" s="11" t="n"/>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
@@ -35395,16 +35391,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J157" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I157" s="13" t="n"/>
+      <c r="J157" s="13" t="n"/>
       <c r="K157" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35417,7 +35405,7 @@
       </c>
       <c r="M157" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -35431,13 +35419,13 @@
       <c r="C158" s="7" t="n"/>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
         </is>
       </c>
       <c r="E158" s="9" t="n"/>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
@@ -35452,12 +35440,12 @@
       </c>
       <c r="I158" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="K158" s="7" t="inlineStr">
@@ -35467,12 +35455,12 @@
       </c>
       <c r="L158" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M158" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -35486,18 +35474,22 @@
       <c r="C159" s="11" t="n"/>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
-        </is>
-      </c>
-      <c r="E159" s="13" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F159" s="13" t="inlineStr">
         <is>
-          <t>ezhunaonline.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
@@ -35507,10 +35499,14 @@
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J159" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J159" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+        </is>
+      </c>
       <c r="K159" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35518,12 +35514,12 @@
       </c>
       <c r="L159" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M159" s="14" t="inlineStr">
         <is>
-          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -35537,18 +35533,22 @@
       <c r="C160" s="7" t="n"/>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
-        </is>
-      </c>
-      <c r="E160" s="9" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
@@ -35558,12 +35558,12 @@
       </c>
       <c r="I160" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J160" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K160" s="7" t="inlineStr">
@@ -35573,12 +35573,12 @@
       </c>
       <c r="L160" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M160" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -35592,13 +35592,13 @@
       <c r="C161" s="11" t="n"/>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="E161" s="13" t="n"/>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr">
@@ -35613,10 +35613,14 @@
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J161" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J161" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K161" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35624,12 +35628,12 @@
       </c>
       <c r="L161" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M161" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -35643,13 +35647,13 @@
       <c r="C162" s="7" t="n"/>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
         </is>
       </c>
       <c r="E162" s="9" t="n"/>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>ezhunaonline.com</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
@@ -35662,7 +35666,11 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I162" s="9" t="n"/>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
       <c r="J162" s="9" t="n"/>
       <c r="K162" s="7" t="inlineStr">
         <is>
@@ -35671,12 +35679,12 @@
       </c>
       <c r="L162" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
         </is>
       </c>
     </row>
@@ -35690,13 +35698,13 @@
       <c r="C163" s="11" t="n"/>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
         </is>
       </c>
       <c r="E163" s="13" t="n"/>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>ta.wikipedia.org</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr">
@@ -35711,12 +35719,12 @@
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J163" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="K163" s="11" t="inlineStr">
@@ -35726,12 +35734,12 @@
       </c>
       <c r="L163" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="M163" s="14" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -35745,13 +35753,13 @@
       <c r="C164" s="7" t="n"/>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="E164" s="9" t="n"/>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>shritharan.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
@@ -35766,12 +35774,12 @@
       </c>
       <c r="I164" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு; பிராமி</t>
         </is>
       </c>
       <c r="K164" s="7" t="inlineStr">
@@ -35781,12 +35789,12 @@
       </c>
       <c r="L164" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M164" s="10" t="inlineStr">
         <is>
-          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -35800,53 +35808,261 @@
       <c r="C165" s="11" t="n"/>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="E165" s="13" t="n"/>
       <c r="F165" s="13" t="inlineStr">
         <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H165" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J165" s="13" t="n"/>
+      <c r="K165" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L165" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M165" s="14" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>WB-0165</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="n"/>
+      <c r="C166" s="7" t="n"/>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I166" s="9" t="n"/>
+      <c r="J166" s="9" t="n"/>
+      <c r="K166" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L166" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M166" s="10" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>WB-0166</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="n"/>
+      <c r="C167" s="11" t="n"/>
+      <c r="D167" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+        </is>
+      </c>
+      <c r="E167" s="13" t="n"/>
+      <c r="F167" s="13" t="inlineStr">
+        <is>
+          <t>jvpnews.com</t>
+        </is>
+      </c>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H167" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J167" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K167" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L167" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M167" s="14" t="inlineStr">
+        <is>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>WB-0167</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="n"/>
+      <c r="C168" s="7" t="n"/>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="E168" s="9" t="n"/>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="G165" s="11" t="inlineStr">
+      <c r="G168" s="7" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="H165" s="11" t="inlineStr">
+      <c r="H168" s="7" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I165" s="13" t="inlineStr">
+      <c r="I168" s="9" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="J165" s="13" t="inlineStr">
+      <c r="J168" s="9" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="K165" s="11" t="inlineStr">
+      <c r="K168" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L165" s="13" t="inlineStr">
+      <c r="L168" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M168" s="10" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>WB-0168</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="n"/>
+      <c r="C169" s="11" t="n"/>
+      <c r="D169" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+        </is>
+      </c>
+      <c r="E169" s="13" t="n"/>
+      <c r="F169" s="13" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H169" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J169" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K169" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L169" s="13" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
-      <c r="M165" s="14" t="inlineStr">
+      <c r="M169" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/jaffna-anaikotta-archaeological-exhibition-begins/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M165"/>
+  <autoFilter ref="A1:M169"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -36012,6 +36228,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId168"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36023,7 +36243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N566"/>
+  <dimension ref="A1:N570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -68561,18 +68781,18 @@
       <c r="D492" s="7" t="n"/>
       <c r="E492" s="9" t="inlineStr">
         <is>
-          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
+          <t>About: Tamil inscriptions in Sri Lanka - DBpedia Association</t>
         </is>
       </c>
       <c r="F492" s="9" t="n"/>
       <c r="G492" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>dbpedia.org</t>
         </is>
       </c>
       <c r="H492" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I492" s="7" t="inlineStr">
@@ -68582,12 +68802,12 @@
       </c>
       <c r="J492" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K492" s="9" t="inlineStr">
         <is>
-          <t>archaeology; East</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L492" s="7" t="inlineStr">
@@ -68595,10 +68815,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M492" s="9" t="n"/>
+      <c r="M492" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-25 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N492" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
+          <t>https://dbpedia.org/page/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -68617,18 +68841,18 @@
       <c r="D493" s="11" t="n"/>
       <c r="E493" s="13" t="inlineStr">
         <is>
-          <t>Ancient Coins - Archaeology</t>
+          <t>Ancient Buddhist Shrines in Batticaloa and Ampara Districts</t>
         </is>
       </c>
       <c r="F493" s="13" t="n"/>
       <c r="G493" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H493" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I493" s="11" t="inlineStr">
@@ -68638,12 +68862,12 @@
       </c>
       <c r="J493" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K493" s="13" t="inlineStr">
         <is>
-          <t>archaeology; ancient coins</t>
+          <t>archaeology; East</t>
         </is>
       </c>
       <c r="L493" s="11" t="inlineStr">
@@ -68651,14 +68875,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M493" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M493" s="13" t="n"/>
       <c r="N493" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/ancient-coins</t>
+          <t>https://amazinglanka.com/wp/buddhist-shrines-in-batticaloa-and-ampara/</t>
         </is>
       </c>
     </row>
@@ -68677,13 +68897,13 @@
       <c r="D494" s="7" t="n"/>
       <c r="E494" s="9" t="inlineStr">
         <is>
-          <t>Ancient Coins and Trade Evidence | Lanka Websites</t>
+          <t>Ancient Coins - Archaeology</t>
         </is>
       </c>
       <c r="F494" s="9" t="n"/>
       <c r="G494" s="9" t="inlineStr">
         <is>
-          <t>lankawebsites.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H494" s="7" t="inlineStr">
@@ -68698,12 +68918,12 @@
       </c>
       <c r="J494" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
         </is>
       </c>
       <c r="K494" s="9" t="inlineStr">
         <is>
-          <t>ancient coins</t>
+          <t>archaeology; ancient coins</t>
         </is>
       </c>
       <c r="L494" s="7" t="inlineStr">
@@ -68718,7 +68938,7 @@
       </c>
       <c r="N494" s="10" t="inlineStr">
         <is>
-          <t>https://lankawebsites.com/blog/ancient-civilization-archaeology/ancient-coins-and-trade-evidence</t>
+          <t>https://archaeology.gov.lk/index.php/ancient-coins</t>
         </is>
       </c>
     </row>
@@ -68737,13 +68957,13 @@
       <c r="D495" s="11" t="n"/>
       <c r="E495" s="13" t="inlineStr">
         <is>
-          <t>Ancient Kadurugoda Viharaya — Grokipedia</t>
+          <t>Ancient Coins and Trade Evidence | Lanka Websites</t>
         </is>
       </c>
       <c r="F495" s="13" t="n"/>
       <c r="G495" s="13" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>lankawebsites.com</t>
         </is>
       </c>
       <c r="H495" s="11" t="inlineStr">
@@ -68756,8 +68976,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J495" s="13" t="n"/>
-      <c r="K495" s="13" t="n"/>
+      <c r="J495" s="13" t="inlineStr">
+        <is>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K495" s="13" t="inlineStr">
+        <is>
+          <t>ancient coins</t>
+        </is>
+      </c>
       <c r="L495" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68765,12 +68993,12 @@
       </c>
       <c r="M495" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N495" s="14" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/ancient_kadurugoda_viharaya</t>
+          <t>https://lankawebsites.com/blog/ancient-civilization-archaeology/ancient-coins-and-trade-evidence</t>
         </is>
       </c>
     </row>
@@ -68789,13 +69017,13 @@
       <c r="D496" s="7" t="n"/>
       <c r="E496" s="9" t="inlineStr">
         <is>
-          <t>Ancient Pandyan coins unearthed in Mannar | Tamil Guardian</t>
+          <t>Ancient Kadurugoda Viharaya — Grokipedia</t>
         </is>
       </c>
       <c r="F496" s="9" t="n"/>
       <c r="G496" s="9" t="inlineStr">
         <is>
-          <t>tamilguardian.com</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="H496" s="7" t="inlineStr">
@@ -68808,11 +69036,7 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J496" s="9" t="inlineStr">
-        <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
+      <c r="J496" s="9" t="n"/>
       <c r="K496" s="9" t="n"/>
       <c r="L496" s="7" t="inlineStr">
         <is>
@@ -68821,12 +69045,12 @@
       </c>
       <c r="M496" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N496" s="10" t="inlineStr">
         <is>
-          <t>https://www.tamilguardian.com/content/ancient-pandyan-coins-unearthed-mannar</t>
+          <t>https://grokipedia.com/page/ancient_kadurugoda_viharaya</t>
         </is>
       </c>
     </row>
@@ -68845,13 +69069,13 @@
       <c r="D497" s="11" t="n"/>
       <c r="E497" s="13" t="inlineStr">
         <is>
-          <t>Archaeological Museum of Jaffna - Tales of Ceylon</t>
+          <t>Ancient Pandyan coins unearthed in Mannar | Tamil Guardian</t>
         </is>
       </c>
       <c r="F497" s="13" t="n"/>
       <c r="G497" s="13" t="inlineStr">
         <is>
-          <t>talesofceylon.com</t>
+          <t>tamilguardian.com</t>
         </is>
       </c>
       <c r="H497" s="11" t="inlineStr">
@@ -68866,14 +69090,10 @@
       </c>
       <c r="J497" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K497" s="13" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K497" s="13" t="n"/>
       <c r="L497" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -68881,12 +69101,12 @@
       </c>
       <c r="M497" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N497" s="14" t="inlineStr">
         <is>
-          <t>https://www.talesofceylon.com/destinations/jaffna/attractions-in-jaffna/archaeological-museum-of-jaffna/</t>
+          <t>https://www.tamilguardian.com/content/ancient-pandyan-coins-unearthed-mannar</t>
         </is>
       </c>
     </row>
@@ -68905,13 +69125,13 @@
       <c r="D498" s="7" t="n"/>
       <c r="E498" s="9" t="inlineStr">
         <is>
-          <t>Archaeological Museum, Jaffna - Wikipedia</t>
+          <t>Archaeological Museum of Jaffna - Tales of Ceylon</t>
         </is>
       </c>
       <c r="F498" s="9" t="n"/>
       <c r="G498" s="9" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>talesofceylon.com</t>
         </is>
       </c>
       <c r="H498" s="7" t="inlineStr">
@@ -68941,12 +69161,12 @@
       </c>
       <c r="M498" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
         </is>
       </c>
       <c r="N498" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Archaeological_Museum,_Jaffna</t>
+          <t>https://www.talesofceylon.com/destinations/jaffna/attractions-in-jaffna/archaeological-museum-of-jaffna/</t>
         </is>
       </c>
     </row>
@@ -68965,13 +69185,13 @@
       <c r="D499" s="11" t="n"/>
       <c r="E499" s="13" t="inlineStr">
         <is>
-          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+          <t>Archaeological Museum, Jaffna - Wikipedia</t>
         </is>
       </c>
       <c r="F499" s="13" t="n"/>
       <c r="G499" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="H499" s="11" t="inlineStr">
@@ -68986,12 +69206,12 @@
       </c>
       <c r="J499" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K499" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L499" s="11" t="inlineStr">
@@ -69001,12 +69221,12 @@
       </c>
       <c r="M499" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N499" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
+          <t>https://en.wikipedia.org/wiki/Archaeological_Museum,_Jaffna</t>
         </is>
       </c>
     </row>
@@ -69025,22 +69245,18 @@
       <c r="D500" s="7" t="n"/>
       <c r="E500" s="9" t="inlineStr">
         <is>
-          <t>Brahmi script</t>
-        </is>
-      </c>
-      <c r="F500" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+        </is>
+      </c>
+      <c r="F500" s="9" t="n"/>
       <c r="G500" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H500" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I500" s="7" t="inlineStr">
@@ -69050,12 +69266,12 @@
       </c>
       <c r="J500" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K500" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L500" s="7" t="inlineStr">
@@ -69065,12 +69281,12 @@
       </c>
       <c r="M500" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N500" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
+          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
         </is>
       </c>
     </row>
@@ -69089,7 +69305,7 @@
       <c r="D501" s="11" t="n"/>
       <c r="E501" s="13" t="inlineStr">
         <is>
-          <t>Buddhism amongst Tamils in Sri Lanka</t>
+          <t>Brahmi script</t>
         </is>
       </c>
       <c r="F501" s="13" t="inlineStr">
@@ -69112,8 +69328,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J501" s="13" t="n"/>
-      <c r="K501" s="13" t="n"/>
+      <c r="J501" s="13" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K501" s="13" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="L501" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69121,12 +69345,12 @@
       </c>
       <c r="M501" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N501" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
         </is>
       </c>
     </row>
@@ -69145,18 +69369,22 @@
       <c r="D502" s="7" t="n"/>
       <c r="E502" s="9" t="inlineStr">
         <is>
-          <t>Buddhist Remains in the Jaffna Peninsula</t>
-        </is>
-      </c>
-      <c r="F502" s="9" t="n"/>
+          <t>Buddhism amongst Tamils in Sri Lanka</t>
+        </is>
+      </c>
+      <c r="F502" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G502" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H502" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I502" s="7" t="inlineStr">
@@ -69164,25 +69392,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J502" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K502" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; Jaffna</t>
-        </is>
-      </c>
+      <c r="J502" s="9" t="n"/>
+      <c r="K502" s="9" t="n"/>
       <c r="L502" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M502" s="9" t="n"/>
+      <c r="M502" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N502" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna/</t>
+          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -69201,7 +69425,7 @@
       <c r="D503" s="11" t="n"/>
       <c r="E503" s="13" t="inlineStr">
         <is>
-          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+          <t>Buddhist Remains in the Jaffna Peninsula</t>
         </is>
       </c>
       <c r="F503" s="13" t="n"/>
@@ -69227,7 +69451,7 @@
       </c>
       <c r="K503" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Pungudutivu</t>
+          <t>தொல்லியல்; Jaffna</t>
         </is>
       </c>
       <c r="L503" s="11" t="inlineStr">
@@ -69238,7 +69462,7 @@
       <c r="M503" s="13" t="n"/>
       <c r="N503" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/tikali/</t>
+          <t>https://amazinglanka.com/wp/jaffna/</t>
         </is>
       </c>
     </row>
@@ -69257,22 +69481,18 @@
       <c r="D504" s="7" t="n"/>
       <c r="E504" s="9" t="inlineStr">
         <is>
-          <t>Cankilian Thoppu</t>
-        </is>
-      </c>
-      <c r="F504" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+        </is>
+      </c>
+      <c r="F504" s="9" t="n"/>
       <c r="G504" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H504" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I504" s="7" t="inlineStr">
@@ -69280,21 +69500,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J504" s="9" t="n"/>
-      <c r="K504" s="9" t="n"/>
+      <c r="J504" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K504" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Pungudutivu</t>
+        </is>
+      </c>
       <c r="L504" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M504" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M504" s="9" t="n"/>
       <c r="N504" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
+          <t>https://amazinglanka.com/wp/tikali/</t>
         </is>
       </c>
     </row>
@@ -69313,18 +69537,22 @@
       <c r="D505" s="11" t="n"/>
       <c r="E505" s="13" t="inlineStr">
         <is>
-          <t>Coins DB| Home - archaeology.gov.lk</t>
-        </is>
-      </c>
-      <c r="F505" s="13" t="n"/>
+          <t>Cankilian Thoppu</t>
+        </is>
+      </c>
+      <c r="F505" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G505" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H505" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I505" s="11" t="inlineStr">
@@ -69332,16 +69560,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J505" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K505" s="13" t="inlineStr">
-        <is>
-          <t>archaeology</t>
-        </is>
-      </c>
+      <c r="J505" s="13" t="n"/>
+      <c r="K505" s="13" t="n"/>
       <c r="L505" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69349,12 +69569,12 @@
       </c>
       <c r="M505" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N505" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
+          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
         </is>
       </c>
     </row>
@@ -69373,13 +69593,13 @@
       <c r="D506" s="7" t="n"/>
       <c r="E506" s="9" t="inlineStr">
         <is>
-          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
+          <t>Coins DB| Home - archaeology.gov.lk</t>
         </is>
       </c>
       <c r="F506" s="9" t="n"/>
       <c r="G506" s="9" t="inlineStr">
         <is>
-          <t>dainst.org</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H506" s="7" t="inlineStr">
@@ -69392,8 +69612,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J506" s="9" t="n"/>
-      <c r="K506" s="9" t="n"/>
+      <c r="J506" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K506" s="9" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="L506" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69401,12 +69629,12 @@
       </c>
       <c r="M506" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N506" s="10" t="inlineStr">
         <is>
-          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
+          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
         </is>
       </c>
     </row>
@@ -69425,13 +69653,13 @@
       <c r="D507" s="11" t="n"/>
       <c r="E507" s="13" t="inlineStr">
         <is>
-          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
+          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
         </is>
       </c>
       <c r="F507" s="13" t="n"/>
       <c r="G507" s="13" t="inlineStr">
         <is>
-          <t>elanka.com.au</t>
+          <t>dainst.org</t>
         </is>
       </c>
       <c r="H507" s="11" t="inlineStr">
@@ -69444,16 +69672,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J507" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K507" s="13" t="inlineStr">
-        <is>
-          <t>hero stone</t>
-        </is>
-      </c>
+      <c r="J507" s="13" t="n"/>
+      <c r="K507" s="13" t="n"/>
       <c r="L507" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69461,12 +69681,12 @@
       </c>
       <c r="M507" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N507" s="14" t="inlineStr">
         <is>
-          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
+          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
         </is>
       </c>
     </row>
@@ -69485,13 +69705,13 @@
       <c r="D508" s="7" t="n"/>
       <c r="E508" s="9" t="inlineStr">
         <is>
-          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
+          <t>Epigraphy of Tamil Brahmi Script - தமிழ்-பிராமி - கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="F508" s="9" t="n"/>
       <c r="G508" s="9" t="inlineStr">
         <is>
-          <t>searchworks.stanford.edu</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H508" s="7" t="inlineStr">
@@ -69501,13 +69721,17 @@
       </c>
       <c r="I508" s="7" t="inlineStr">
         <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="J508" s="9" t="n"/>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J508" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
       <c r="K508" s="9" t="inlineStr">
         <is>
-          <t>hero-stone</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி; epigraphy; brahmi</t>
         </is>
       </c>
       <c r="L508" s="7" t="inlineStr">
@@ -69517,12 +69741,12 @@
       </c>
       <c r="M508" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="N508" s="10" t="inlineStr">
         <is>
-          <t>https://searchworks.stanford.edu/view/14451040</t>
+          <t>https://www.scribd.com/document/397330115/Epigraphy-of-Tamil-Brahmi-Script-%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4-%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%AE%E0%AE%BF-%E0%AE%95%E0%AE%B2-%E0%AE%B5%E0%AF%86%E0%AE%9F-%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3</t>
         </is>
       </c>
     </row>
@@ -69541,13 +69765,13 @@
       <c r="D509" s="11" t="n"/>
       <c r="E509" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
+          <t>Glimpses of the Eelam Tamil Heritage - நூலகம்</t>
         </is>
       </c>
       <c r="F509" s="13" t="n"/>
       <c r="G509" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H509" s="11" t="inlineStr">
@@ -69557,19 +69781,15 @@
       </c>
       <c r="I509" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J509" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K509" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K509" s="13" t="n"/>
       <c r="L509" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69577,12 +69797,12 @@
       </c>
       <c r="M509" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="N509" s="14" t="inlineStr">
         <is>
-          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
+          <t>https://noolaham.org/wiki/index.php/Glimpses_of_the_Eelam_Tamil_Heritage</t>
         </is>
       </c>
     </row>
@@ -69601,13 +69821,13 @@
       <c r="D510" s="7" t="n"/>
       <c r="E510" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
+          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
         </is>
       </c>
       <c r="F510" s="9" t="n"/>
       <c r="G510" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>elanka.com.au</t>
         </is>
       </c>
       <c r="H510" s="7" t="inlineStr">
@@ -69622,12 +69842,12 @@
       </c>
       <c r="J510" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K510" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="L510" s="7" t="inlineStr">
@@ -69637,12 +69857,12 @@
       </c>
       <c r="M510" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N510" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/?lang=en</t>
+          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
         </is>
       </c>
     </row>
@@ -69661,13 +69881,13 @@
       <c r="D511" s="11" t="n"/>
       <c r="E511" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum</t>
+          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
         </is>
       </c>
       <c r="F511" s="13" t="n"/>
       <c r="G511" s="13" t="inlineStr">
         <is>
-          <t>lonelyplanet.com</t>
+          <t>searchworks.stanford.edu</t>
         </is>
       </c>
       <c r="H511" s="11" t="inlineStr">
@@ -69680,14 +69900,10 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J511" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="J511" s="13" t="n"/>
       <c r="K511" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>hero-stone</t>
         </is>
       </c>
       <c r="L511" s="11" t="inlineStr">
@@ -69697,12 +69913,12 @@
       </c>
       <c r="M511" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N511" s="14" t="inlineStr">
         <is>
-          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
+          <t>https://searchworks.stanford.edu/view/14451040</t>
         </is>
       </c>
     </row>
@@ -69721,13 +69937,13 @@
       <c r="D512" s="7" t="n"/>
       <c r="E512" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
+          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
         </is>
       </c>
       <c r="F512" s="9" t="n"/>
       <c r="G512" s="9" t="inlineStr">
         <is>
-          <t>tripadvisor.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H512" s="7" t="inlineStr">
@@ -69742,12 +69958,12 @@
       </c>
       <c r="J512" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K512" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L512" s="7" t="inlineStr">
@@ -69757,12 +69973,12 @@
       </c>
       <c r="M512" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N512" s="10" t="inlineStr">
         <is>
-          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
+          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
         </is>
       </c>
     </row>
@@ -69781,13 +69997,13 @@
       <c r="D513" s="11" t="n"/>
       <c r="E513" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
+          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
         </is>
       </c>
       <c r="F513" s="13" t="n"/>
       <c r="G513" s="13" t="inlineStr">
         <is>
-          <t>jaffna.top</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H513" s="11" t="inlineStr">
@@ -69802,12 +70018,12 @@
       </c>
       <c r="J513" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K513" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L513" s="11" t="inlineStr">
@@ -69817,12 +70033,12 @@
       </c>
       <c r="M513" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N513" s="14" t="inlineStr">
         <is>
-          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
+          <t>https://www.inscriptions.lk/?lang=en</t>
         </is>
       </c>
     </row>
@@ -69841,13 +70057,13 @@
       <c r="D514" s="7" t="n"/>
       <c r="E514" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
+          <t>Jaffna Archaeological Museum</t>
         </is>
       </c>
       <c r="F514" s="9" t="n"/>
       <c r="G514" s="9" t="inlineStr">
         <is>
-          <t>srilankatravelpages.com</t>
+          <t>lonelyplanet.com</t>
         </is>
       </c>
       <c r="H514" s="7" t="inlineStr">
@@ -69877,12 +70093,12 @@
       </c>
       <c r="M514" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
       <c r="N514" s="10" t="inlineStr">
         <is>
-          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
+          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
         </is>
       </c>
     </row>
@@ -69901,13 +70117,13 @@
       <c r="D515" s="11" t="n"/>
       <c r="E515" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
+          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
         </is>
       </c>
       <c r="F515" s="13" t="n"/>
       <c r="G515" s="13" t="inlineStr">
         <is>
-          <t>srilankatourhelp.org</t>
+          <t>tripadvisor.com</t>
         </is>
       </c>
       <c r="H515" s="11" t="inlineStr">
@@ -69942,7 +70158,7 @@
       </c>
       <c r="N515" s="14" t="inlineStr">
         <is>
-          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
         </is>
       </c>
     </row>
@@ -69961,13 +70177,13 @@
       <c r="D516" s="7" t="n"/>
       <c r="E516" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | About.lk</t>
+          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
         </is>
       </c>
       <c r="F516" s="9" t="n"/>
       <c r="G516" s="9" t="inlineStr">
         <is>
-          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
+          <t>jaffna.top</t>
         </is>
       </c>
       <c r="H516" s="7" t="inlineStr">
@@ -70002,7 +70218,7 @@
       </c>
       <c r="N516" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
+          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
         </is>
       </c>
     </row>
@@ -70021,13 +70237,13 @@
       <c r="D517" s="11" t="n"/>
       <c r="E517" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
         </is>
       </c>
       <c r="F517" s="13" t="n"/>
       <c r="G517" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>srilankatravelpages.com</t>
         </is>
       </c>
       <c r="H517" s="11" t="inlineStr">
@@ -70057,12 +70273,12 @@
       </c>
       <c r="M517" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N517" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
+          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
         </is>
       </c>
     </row>
@@ -70081,13 +70297,13 @@
       <c r="D518" s="7" t="n"/>
       <c r="E518" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
+          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
         </is>
       </c>
       <c r="F518" s="9" t="n"/>
       <c r="G518" s="9" t="inlineStr">
         <is>
-          <t>i-discoverasia.com</t>
+          <t>srilankatourhelp.org</t>
         </is>
       </c>
       <c r="H518" s="7" t="inlineStr">
@@ -70107,7 +70323,7 @@
       </c>
       <c r="K518" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L518" s="7" t="inlineStr">
@@ -70117,12 +70333,12 @@
       </c>
       <c r="M518" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N518" s="10" t="inlineStr">
         <is>
-          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
+          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
         </is>
       </c>
     </row>
@@ -70141,13 +70357,13 @@
       <c r="D519" s="11" t="n"/>
       <c r="E519" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archeology Tour - Journe Experiences</t>
+          <t>Jaffna Archaeological Museum | About.lk</t>
         </is>
       </c>
       <c r="F519" s="13" t="n"/>
       <c r="G519" s="13" t="inlineStr">
         <is>
-          <t>journesrilanka.com</t>
+          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
         </is>
       </c>
       <c r="H519" s="11" t="inlineStr">
@@ -70160,8 +70376,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J519" s="13" t="n"/>
-      <c r="K519" s="13" t="n"/>
+      <c r="J519" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K519" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L519" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70169,12 +70393,12 @@
       </c>
       <c r="M519" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N519" s="14" t="inlineStr">
         <is>
-          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
+          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
         </is>
       </c>
     </row>
@@ -70193,13 +70417,13 @@
       <c r="D520" s="7" t="n"/>
       <c r="E520" s="9" t="inlineStr">
         <is>
-          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
+          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
         </is>
       </c>
       <c r="F520" s="9" t="n"/>
       <c r="G520" s="9" t="inlineStr">
         <is>
-          <t>lanka-excursions-holidays.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H520" s="7" t="inlineStr">
@@ -70212,8 +70436,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J520" s="9" t="n"/>
-      <c r="K520" s="9" t="n"/>
+      <c r="J520" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K520" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L520" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70221,12 +70453,12 @@
       </c>
       <c r="M520" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N520" s="10" t="inlineStr">
         <is>
-          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
+          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
         </is>
       </c>
     </row>
@@ -70245,13 +70477,13 @@
       <c r="D521" s="11" t="n"/>
       <c r="E521" s="13" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
         </is>
       </c>
       <c r="F521" s="13" t="n"/>
       <c r="G521" s="13" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>i-discoverasia.com</t>
         </is>
       </c>
       <c r="H521" s="11" t="inlineStr">
@@ -70264,8 +70496,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J521" s="13" t="n"/>
-      <c r="K521" s="13" t="n"/>
+      <c r="J521" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K521" s="13" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="L521" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70273,12 +70513,12 @@
       </c>
       <c r="M521" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
         </is>
       </c>
       <c r="N521" s="14" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -70297,13 +70537,13 @@
       <c r="D522" s="7" t="n"/>
       <c r="E522" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Jaffna Archeology Tour - Journe Experiences</t>
         </is>
       </c>
       <c r="F522" s="9" t="n"/>
       <c r="G522" s="9" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>journesrilanka.com</t>
         </is>
       </c>
       <c r="H522" s="7" t="inlineStr">
@@ -70325,12 +70565,12 @@
       </c>
       <c r="M522" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N522" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
         </is>
       </c>
     </row>
@@ -70349,13 +70589,13 @@
       <c r="D523" s="11" t="n"/>
       <c r="E523" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
         </is>
       </c>
       <c r="F523" s="13" t="n"/>
       <c r="G523" s="13" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>lanka-excursions-holidays.com</t>
         </is>
       </c>
       <c r="H523" s="11" t="inlineStr">
@@ -70368,16 +70608,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J523" s="13" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K523" s="13" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="J523" s="13" t="n"/>
+      <c r="K523" s="13" t="n"/>
       <c r="L523" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70385,12 +70617,12 @@
       </c>
       <c r="M523" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N523" s="14" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
         </is>
       </c>
     </row>
@@ -70409,22 +70641,18 @@
       <c r="D524" s="7" t="n"/>
       <c r="E524" s="9" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="F524" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+        </is>
+      </c>
+      <c r="F524" s="9" t="n"/>
       <c r="G524" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="H524" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I524" s="7" t="inlineStr">
@@ -70432,16 +70660,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J524" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K524" s="9" t="inlineStr">
-        <is>
-          <t>archaeological</t>
-        </is>
-      </c>
+      <c r="J524" s="9" t="n"/>
+      <c r="K524" s="9" t="n"/>
       <c r="L524" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70449,12 +70669,12 @@
       </c>
       <c r="M524" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N524" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -70473,18 +70693,18 @@
       <c r="D525" s="11" t="n"/>
       <c r="E525" s="13" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="F525" s="13" t="n"/>
       <c r="G525" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H525" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I525" s="11" t="inlineStr">
@@ -70492,25 +70712,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J525" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K525" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; settlement</t>
-        </is>
-      </c>
+      <c r="J525" s="13" t="n"/>
+      <c r="K525" s="13" t="n"/>
       <c r="L525" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M525" s="13" t="n"/>
+      <c r="M525" s="13" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N525" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -70529,13 +70745,13 @@
       <c r="D526" s="7" t="n"/>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>Museums - Archaeology</t>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
         </is>
       </c>
       <c r="F526" s="9" t="n"/>
       <c r="G526" s="9" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="H526" s="7" t="inlineStr">
@@ -70550,12 +70766,12 @@
       </c>
       <c r="J526" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K526" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L526" s="7" t="inlineStr">
@@ -70565,12 +70781,12 @@
       </c>
       <c r="M526" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N526" s="10" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -70589,18 +70805,22 @@
       <c r="D527" s="11" t="n"/>
       <c r="E527" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
-        </is>
-      </c>
-      <c r="F527" s="13" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="F527" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G527" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H527" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I527" s="11" t="inlineStr">
@@ -70625,12 +70845,12 @@
       </c>
       <c r="M527" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N527" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -70649,18 +70869,18 @@
       <c r="D528" s="7" t="n"/>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="F528" s="9" t="n"/>
       <c r="G528" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H528" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I528" s="7" t="inlineStr">
@@ -70670,23 +70890,23 @@
       </c>
       <c r="J528" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K528" s="9" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K528" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; settlement</t>
+        </is>
+      </c>
       <c r="L528" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M528" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M528" s="9" t="n"/>
       <c r="N528" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -70705,13 +70925,13 @@
       <c r="D529" s="11" t="n"/>
       <c r="E529" s="13" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>Museums - Archaeology</t>
         </is>
       </c>
       <c r="F529" s="13" t="n"/>
       <c r="G529" s="13" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H529" s="11" t="inlineStr">
@@ -70726,12 +70946,12 @@
       </c>
       <c r="J529" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K529" s="13" t="inlineStr">
         <is>
-          <t>inscription; brahmi</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="L529" s="11" t="inlineStr">
@@ -70741,12 +70961,12 @@
       </c>
       <c r="M529" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N529" s="14" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
         </is>
       </c>
     </row>
@@ -70765,13 +70985,13 @@
       <c r="D530" s="7" t="n"/>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="F530" s="9" t="n"/>
       <c r="G530" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk:8080</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="H530" s="7" t="inlineStr">
@@ -70786,12 +71006,12 @@
       </c>
       <c r="J530" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>inscription; brahmi</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L530" s="7" t="inlineStr">
@@ -70801,12 +71021,12 @@
       </c>
       <c r="M530" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N530" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -70825,13 +71045,13 @@
       <c r="D531" s="11" t="n"/>
       <c r="E531" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="F531" s="13" t="n"/>
       <c r="G531" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H531" s="11" t="inlineStr">
@@ -70857,12 +71077,12 @@
       </c>
       <c r="M531" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N531" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -70881,13 +71101,13 @@
       <c r="D532" s="7" t="n"/>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="F532" s="9" t="n"/>
       <c r="G532" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="H532" s="7" t="inlineStr">
@@ -70902,12 +71122,12 @@
       </c>
       <c r="J532" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K532" s="9" t="inlineStr">
         <is>
-          <t>rock art</t>
+          <t>inscription; brahmi</t>
         </is>
       </c>
       <c r="L532" s="7" t="inlineStr">
@@ -70917,12 +71137,12 @@
       </c>
       <c r="M532" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N532" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -70941,13 +71161,13 @@
       <c r="D533" s="11" t="n"/>
       <c r="E533" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
         </is>
       </c>
       <c r="F533" s="13" t="n"/>
       <c r="G533" s="13" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>repo.lib.jfn.ac.lk:8080</t>
         </is>
       </c>
       <c r="H533" s="11" t="inlineStr">
@@ -70962,12 +71182,12 @@
       </c>
       <c r="J533" s="13" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K533" s="13" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>inscription; brahmi</t>
         </is>
       </c>
       <c r="L533" s="11" t="inlineStr">
@@ -70977,12 +71197,12 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N533" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
         </is>
       </c>
     </row>
@@ -71001,13 +71221,13 @@
       <c r="D534" s="7" t="n"/>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="F534" s="9" t="n"/>
       <c r="G534" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="H534" s="7" t="inlineStr">
@@ -71022,14 +71242,10 @@
       </c>
       <c r="J534" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K534" s="9" t="inlineStr">
-        <is>
-          <t>hero stone</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K534" s="9" t="n"/>
       <c r="L534" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71037,12 +71253,12 @@
       </c>
       <c r="M534" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N534" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -71061,22 +71277,18 @@
       <c r="D535" s="11" t="n"/>
       <c r="E535" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="F535" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+        </is>
+      </c>
+      <c r="F535" s="13" t="n"/>
       <c r="G535" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H535" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I535" s="11" t="inlineStr">
@@ -71084,8 +71296,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J535" s="13" t="n"/>
-      <c r="K535" s="13" t="n"/>
+      <c r="J535" s="13" t="inlineStr">
+        <is>
+          <t>Rock art / பாறை ஓவியம்</t>
+        </is>
+      </c>
+      <c r="K535" s="13" t="inlineStr">
+        <is>
+          <t>rock art</t>
+        </is>
+      </c>
       <c r="L535" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71093,12 +71313,12 @@
       </c>
       <c r="M535" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N535" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -71117,13 +71337,13 @@
       <c r="D536" s="7" t="n"/>
       <c r="E536" s="9" t="inlineStr">
         <is>
-          <t>Sri Lanka Inscriptions</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F536" s="9" t="n"/>
       <c r="G536" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H536" s="7" t="inlineStr">
@@ -71138,12 +71358,12 @@
       </c>
       <c r="J536" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K536" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="L536" s="7" t="inlineStr">
@@ -71153,12 +71373,12 @@
       </c>
       <c r="M536" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N536" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -71177,13 +71397,13 @@
       <c r="D537" s="11" t="n"/>
       <c r="E537" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sinhalese Hero Stone Analysis</t>
         </is>
       </c>
       <c r="F537" s="13" t="n"/>
       <c r="G537" s="13" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H537" s="11" t="inlineStr">
@@ -71198,12 +71418,12 @@
       </c>
       <c r="J537" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K537" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="L537" s="11" t="inlineStr">
@@ -71213,12 +71433,12 @@
       </c>
       <c r="M537" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N537" s="14" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -71237,18 +71457,22 @@
       <c r="D538" s="7" t="n"/>
       <c r="E538" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
-        </is>
-      </c>
-      <c r="F538" s="9" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="F538" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G538" s="9" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H538" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I538" s="7" t="inlineStr">
@@ -71256,16 +71480,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J538" s="9" t="inlineStr">
-        <is>
-          <t>Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K538" s="9" t="inlineStr">
-        <is>
-          <t>brahmi</t>
-        </is>
-      </c>
+      <c r="J538" s="9" t="n"/>
+      <c r="K538" s="9" t="n"/>
       <c r="L538" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71273,12 +71489,12 @@
       </c>
       <c r="M538" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N538" s="10" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -71297,13 +71513,13 @@
       <c r="D539" s="11" t="n"/>
       <c r="E539" s="13" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="F539" s="13" t="n"/>
       <c r="G539" s="13" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H539" s="11" t="inlineStr">
@@ -71318,10 +71534,14 @@
       </c>
       <c r="J539" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K539" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K539" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="L539" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71329,12 +71549,12 @@
       </c>
       <c r="M539" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N539" s="14" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -71353,13 +71573,13 @@
       <c r="D540" s="7" t="n"/>
       <c r="E540" s="9" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="F540" s="9" t="n"/>
       <c r="G540" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="H540" s="7" t="inlineStr">
@@ -71374,12 +71594,12 @@
       </c>
       <c r="J540" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K540" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="L540" s="7" t="inlineStr">
@@ -71394,7 +71614,7 @@
       </c>
       <c r="N540" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -71413,13 +71633,13 @@
       <c r="D541" s="11" t="n"/>
       <c r="E541" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="F541" s="13" t="n"/>
       <c r="G541" s="13" t="inlineStr">
         <is>
-          <t>en.bharatpedia.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="H541" s="11" t="inlineStr">
@@ -71434,12 +71654,12 @@
       </c>
       <c r="J541" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K541" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>brahmi</t>
         </is>
       </c>
       <c r="L541" s="11" t="inlineStr">
@@ -71449,12 +71669,12 @@
       </c>
       <c r="M541" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N541" s="14" t="inlineStr">
         <is>
-          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -71473,13 +71693,13 @@
       <c r="D542" s="7" t="n"/>
       <c r="E542" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="F542" s="9" t="n"/>
       <c r="G542" s="9" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="H542" s="7" t="inlineStr">
@@ -71494,14 +71714,10 @@
       </c>
       <c r="J542" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K542" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K542" s="9" t="n"/>
       <c r="L542" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71509,12 +71725,12 @@
       </c>
       <c r="M542" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N542" s="10" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -71533,13 +71749,13 @@
       <c r="D543" s="11" t="n"/>
       <c r="E543" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="F543" s="13" t="n"/>
       <c r="G543" s="13" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H543" s="11" t="inlineStr">
@@ -71554,12 +71770,12 @@
       </c>
       <c r="J543" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K543" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L543" s="11" t="inlineStr">
@@ -71569,12 +71785,12 @@
       </c>
       <c r="M543" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N543" s="14" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -71593,13 +71809,13 @@
       <c r="D544" s="7" t="n"/>
       <c r="E544" s="9" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="F544" s="9" t="n"/>
       <c r="G544" s="9" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="H544" s="7" t="inlineStr">
@@ -71619,7 +71835,7 @@
       </c>
       <c r="K544" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L544" s="7" t="inlineStr">
@@ -71629,12 +71845,12 @@
       </c>
       <c r="M544" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N544" s="10" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -71653,13 +71869,13 @@
       <c r="D545" s="11" t="n"/>
       <c r="E545" s="13" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="F545" s="13" t="n"/>
       <c r="G545" s="13" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="H545" s="11" t="inlineStr">
@@ -71672,8 +71888,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J545" s="13" t="n"/>
-      <c r="K545" s="13" t="n"/>
+      <c r="J545" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K545" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="L545" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71681,12 +71905,12 @@
       </c>
       <c r="M545" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N545" s="14" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -71705,13 +71929,13 @@
       <c r="D546" s="7" t="n"/>
       <c r="E546" s="9" t="inlineStr">
         <is>
-          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="F546" s="9" t="n"/>
       <c r="G546" s="9" t="inlineStr">
         <is>
-          <t>cambridge.org</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="H546" s="7" t="inlineStr">
@@ -71724,8 +71948,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J546" s="9" t="n"/>
-      <c r="K546" s="9" t="n"/>
+      <c r="J546" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K546" s="9" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="L546" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71733,12 +71965,12 @@
       </c>
       <c r="M546" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N546" s="10" t="inlineStr">
         <is>
-          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -71757,13 +71989,13 @@
       <c r="D547" s="11" t="n"/>
       <c r="E547" s="13" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="F547" s="13" t="n"/>
       <c r="G547" s="13" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="H547" s="11" t="inlineStr">
@@ -71793,12 +72025,12 @@
       </c>
       <c r="M547" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N547" s="14" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -71817,13 +72049,13 @@
       <c r="D548" s="7" t="n"/>
       <c r="E548" s="9" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="F548" s="9" t="n"/>
       <c r="G548" s="9" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="H548" s="7" t="inlineStr">
@@ -71836,16 +72068,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J548" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K548" s="9" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="J548" s="9" t="n"/>
+      <c r="K548" s="9" t="n"/>
       <c r="L548" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71853,12 +72077,12 @@
       </c>
       <c r="M548" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N548" s="10" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -71877,22 +72101,18 @@
       <c r="D549" s="11" t="n"/>
       <c r="E549" s="13" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="F549" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+        </is>
+      </c>
+      <c r="F549" s="13" t="n"/>
       <c r="G549" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>cambridge.org</t>
         </is>
       </c>
       <c r="H549" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I549" s="11" t="inlineStr">
@@ -71909,12 +72129,12 @@
       </c>
       <c r="M549" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N549" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
         </is>
       </c>
     </row>
@@ -71933,18 +72153,18 @@
       <c r="D550" s="7" t="n"/>
       <c r="E550" s="9" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
         </is>
       </c>
       <c r="F550" s="9" t="n"/>
       <c r="G550" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="H550" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I550" s="7" t="inlineStr">
@@ -71954,12 +72174,12 @@
       </c>
       <c r="J550" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K550" s="9" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="L550" s="7" t="inlineStr">
@@ -71967,10 +72187,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M550" s="9" t="n"/>
+      <c r="M550" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N550" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -71989,13 +72213,13 @@
       <c r="D551" s="11" t="n"/>
       <c r="E551" s="13" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="F551" s="13" t="n"/>
       <c r="G551" s="13" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H551" s="11" t="inlineStr">
@@ -72005,11 +72229,19 @@
       </c>
       <c r="I551" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J551" s="13" t="n"/>
-      <c r="K551" s="13" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J551" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K551" s="13" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L551" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72017,12 +72249,12 @@
       </c>
       <c r="M551" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N551" s="14" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -72041,7 +72273,7 @@
       <c r="D552" s="7" t="n"/>
       <c r="E552" s="9" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+          <t>Vallipuram</t>
         </is>
       </c>
       <c r="F552" s="9" t="inlineStr">
@@ -72051,7 +72283,7 @@
       </c>
       <c r="G552" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H552" s="7" t="inlineStr">
@@ -72061,19 +72293,11 @@
       </c>
       <c r="I552" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J552" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K552" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J552" s="9" t="n"/>
+      <c r="K552" s="9" t="n"/>
       <c r="L552" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72086,7 +72310,7 @@
       </c>
       <c r="N552" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -72105,33 +72329,33 @@
       <c r="D553" s="11" t="n"/>
       <c r="E553" s="13" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
         </is>
       </c>
       <c r="F553" s="13" t="n"/>
       <c r="G553" s="13" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H553" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I553" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J553" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K553" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="L553" s="11" t="inlineStr">
@@ -72139,14 +72363,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M553" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M553" s="13" t="n"/>
       <c r="N553" s="14" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -72165,13 +72385,13 @@
       <c r="D554" s="7" t="n"/>
       <c r="E554" s="9" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="F554" s="9" t="n"/>
       <c r="G554" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H554" s="7" t="inlineStr">
@@ -72184,16 +72404,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J554" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K554" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="J554" s="9" t="n"/>
+      <c r="K554" s="9" t="n"/>
       <c r="L554" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72201,12 +72413,12 @@
       </c>
       <c r="M554" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N554" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -72225,7 +72437,7 @@
       <c r="D555" s="11" t="n"/>
       <c r="E555" s="13" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
         </is>
       </c>
       <c r="F555" s="13" t="inlineStr">
@@ -72248,8 +72460,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J555" s="13" t="n"/>
-      <c r="K555" s="13" t="n"/>
+      <c r="J555" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K555" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L555" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72262,7 +72482,7 @@
       </c>
       <c r="N555" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -72281,13 +72501,13 @@
       <c r="D556" s="7" t="n"/>
       <c r="E556" s="9" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
         </is>
       </c>
       <c r="F556" s="9" t="n"/>
       <c r="G556" s="9" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="H556" s="7" t="inlineStr">
@@ -72302,12 +72522,12 @@
       </c>
       <c r="J556" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K556" s="9" t="inlineStr">
         <is>
-          <t>நடுகல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="L556" s="7" t="inlineStr">
@@ -72317,12 +72537,12 @@
       </c>
       <c r="M556" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N556" s="10" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -72341,22 +72561,18 @@
       <c r="D557" s="11" t="n"/>
       <c r="E557" s="13" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
-        </is>
-      </c>
-      <c r="F557" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="F557" s="13" t="n"/>
       <c r="G557" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H557" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I557" s="11" t="inlineStr">
@@ -72366,12 +72582,12 @@
       </c>
       <c r="J557" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K557" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="L557" s="11" t="inlineStr">
@@ -72381,12 +72597,12 @@
       </c>
       <c r="M557" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N557" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72621,7 @@
       <c r="D558" s="7" t="n"/>
       <c r="E558" s="9" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="F558" s="9" t="inlineStr">
@@ -72428,16 +72644,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J558" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K558" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J558" s="9" t="n"/>
+      <c r="K558" s="9" t="n"/>
       <c r="L558" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72450,7 +72658,7 @@
       </c>
       <c r="N558" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -72469,13 +72677,13 @@
       <c r="D559" s="11" t="n"/>
       <c r="E559" s="13" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
         </is>
       </c>
       <c r="F559" s="13" t="n"/>
       <c r="G559" s="13" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="H559" s="11" t="inlineStr">
@@ -72490,12 +72698,12 @@
       </c>
       <c r="J559" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K559" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="L559" s="11" t="inlineStr">
@@ -72505,12 +72713,12 @@
       </c>
       <c r="M559" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N559" s="14" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -72529,18 +72737,22 @@
       <c r="D560" s="7" t="n"/>
       <c r="E560" s="9" t="inlineStr">
         <is>
-          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
-        </is>
-      </c>
-      <c r="F560" s="9" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="F560" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G560" s="9" t="inlineStr">
         <is>
-          <t>ezhunaonline.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H560" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I560" s="7" t="inlineStr">
@@ -72550,10 +72762,14 @@
       </c>
       <c r="J560" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K560" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K560" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+        </is>
+      </c>
       <c r="L560" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72561,12 +72777,12 @@
       </c>
       <c r="M560" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N560" s="10" t="inlineStr">
         <is>
-          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -72585,18 +72801,22 @@
       <c r="D561" s="11" t="n"/>
       <c r="E561" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
-        </is>
-      </c>
-      <c r="F561" s="13" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F561" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G561" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H561" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I561" s="11" t="inlineStr">
@@ -72606,12 +72826,12 @@
       </c>
       <c r="J561" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K561" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L561" s="11" t="inlineStr">
@@ -72621,12 +72841,12 @@
       </c>
       <c r="M561" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N561" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -72645,13 +72865,13 @@
       <c r="D562" s="7" t="n"/>
       <c r="E562" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="F562" s="9" t="n"/>
       <c r="G562" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="H562" s="7" t="inlineStr">
@@ -72666,10 +72886,14 @@
       </c>
       <c r="J562" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K562" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K562" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L562" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72677,12 +72901,12 @@
       </c>
       <c r="M562" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N562" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -72701,13 +72925,13 @@
       <c r="D563" s="11" t="n"/>
       <c r="E563" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
         </is>
       </c>
       <c r="F563" s="13" t="n"/>
       <c r="G563" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>ezhunaonline.com</t>
         </is>
       </c>
       <c r="H563" s="11" t="inlineStr">
@@ -72720,7 +72944,11 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J563" s="13" t="n"/>
+      <c r="J563" s="13" t="inlineStr">
+        <is>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
       <c r="K563" s="13" t="n"/>
       <c r="L563" s="11" t="inlineStr">
         <is>
@@ -72729,12 +72957,12 @@
       </c>
       <c r="M563" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N563" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
         </is>
       </c>
     </row>
@@ -72753,13 +72981,13 @@
       <c r="D564" s="7" t="n"/>
       <c r="E564" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
         </is>
       </c>
       <c r="F564" s="9" t="n"/>
       <c r="G564" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>ta.wikipedia.org</t>
         </is>
       </c>
       <c r="H564" s="7" t="inlineStr">
@@ -72774,12 +73002,12 @@
       </c>
       <c r="J564" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K564" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="L564" s="7" t="inlineStr">
@@ -72789,12 +73017,12 @@
       </c>
       <c r="M564" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="N564" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -72813,13 +73041,13 @@
       <c r="D565" s="11" t="n"/>
       <c r="E565" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="F565" s="13" t="n"/>
       <c r="G565" s="13" t="inlineStr">
         <is>
-          <t>shritharan.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H565" s="11" t="inlineStr">
@@ -72834,12 +73062,12 @@
       </c>
       <c r="J565" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K565" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு; பிராமி</t>
         </is>
       </c>
       <c r="L565" s="11" t="inlineStr">
@@ -72849,12 +73077,12 @@
       </c>
       <c r="M565" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N565" s="14" t="inlineStr">
         <is>
-          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -72873,53 +73101,281 @@
       <c r="D566" s="7" t="n"/>
       <c r="E566" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="F566" s="9" t="n"/>
       <c r="G566" s="9" t="inlineStr">
         <is>
+          <t>telibrary.com</t>
+        </is>
+      </c>
+      <c r="H566" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I566" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J566" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K566" s="9" t="n"/>
+      <c r="L566" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M566" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N566" s="10" t="inlineStr">
+        <is>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0566</t>
+        </is>
+      </c>
+      <c r="B567" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C567" s="12" t="n"/>
+      <c r="D567" s="11" t="n"/>
+      <c r="E567" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+        </is>
+      </c>
+      <c r="F567" s="13" t="n"/>
+      <c r="G567" s="13" t="inlineStr">
+        <is>
+          <t>treasurehouseofjaffna.com</t>
+        </is>
+      </c>
+      <c r="H567" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I567" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J567" s="13" t="n"/>
+      <c r="K567" s="13" t="n"/>
+      <c r="L567" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M567" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N567" s="14" t="inlineStr">
+        <is>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0567</t>
+        </is>
+      </c>
+      <c r="B568" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C568" s="8" t="n"/>
+      <c r="D568" s="7" t="n"/>
+      <c r="E568" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+        </is>
+      </c>
+      <c r="F568" s="9" t="n"/>
+      <c r="G568" s="9" t="inlineStr">
+        <is>
+          <t>jvpnews.com</t>
+        </is>
+      </c>
+      <c r="H568" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I568" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J568" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K568" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="L568" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M568" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N568" s="10" t="inlineStr">
+        <is>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0568</t>
+        </is>
+      </c>
+      <c r="B569" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C569" s="12" t="n"/>
+      <c r="D569" s="11" t="n"/>
+      <c r="E569" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="F569" s="13" t="n"/>
+      <c r="G569" s="13" t="inlineStr">
+        <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="H566" s="7" t="inlineStr">
+      <c r="H569" s="11" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="I566" s="7" t="inlineStr">
+      <c r="I569" s="11" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J566" s="9" t="inlineStr">
+      <c r="J569" s="13" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="K566" s="9" t="inlineStr">
+      <c r="K569" s="13" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="L566" s="7" t="inlineStr">
+      <c r="L569" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M566" s="9" t="inlineStr">
+      <c r="M569" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N569" s="14" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0569</t>
+        </is>
+      </c>
+      <c r="B570" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C570" s="8" t="n"/>
+      <c r="D570" s="7" t="n"/>
+      <c r="E570" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+        </is>
+      </c>
+      <c r="F570" s="9" t="n"/>
+      <c r="G570" s="9" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="H570" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I570" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J570" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K570" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="L570" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M570" s="9" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
-      <c r="N566" s="10" t="inlineStr">
+      <c r="N570" s="10" t="inlineStr">
         <is>
           <t>https://shritharan.com/jaffna-anaikotta-archaeological-exhibition-begins/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N566"/>
+  <autoFilter ref="A1:N570"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -73486,6 +73942,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N564" r:id="rId563"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N565" r:id="rId564"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N570" r:id="rId569"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Papers'!$A$1:$M$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspaper Articles'!$A$1:$M$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Magazines &amp; Journals'!$A$1:$M$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$169</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$570</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$572</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-25. Counts below are live formulas over the 'All Records' sheet.</t>
+          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-26. Counts below are live formulas over the 'All Records' sheet.</t>
         </is>
       </c>
     </row>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$570,A6)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$572,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$570,A6,'All Records'!$L$2:$L$570,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$572,A6,'All Records'!$L$2:$L$572,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$570,A7)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$572,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$570,A7,'All Records'!$L$2:$L$570,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$572,A7,'All Records'!$L$2:$L$572,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$570,A8)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$572,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$570,A8,'All Records'!$L$2:$L$570,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$572,A8,'All Records'!$L$2:$L$572,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$570,A9)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$572,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$570,A9,'All Records'!$L$2:$L$570,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$572,A9,'All Records'!$L$2:$L$572,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$570,A10)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$572,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$570,A10,'All Records'!$L$2:$L$570,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$572,A10,'All Records'!$L$2:$L$572,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$570,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -787,23 +787,23 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="G23" s="4">
@@ -818,23 +818,23 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="G24" s="4">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="G25" s="4">
@@ -880,23 +880,23 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="G26" s="4">
@@ -911,23 +911,23 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="G27" s="4">
@@ -942,23 +942,23 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$570="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$570,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="G28" s="4">
@@ -26336,7 +26336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32808,13 +32808,13 @@
       <c r="C109" s="11" t="n"/>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
+          <t>Hero Stonebridge MS Welding Rod 6013 G12 - Stockpile</t>
         </is>
       </c>
       <c r="E109" s="13" t="n"/>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>elanka.com.au</t>
+          <t>stockpile.lk</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -32844,12 +32844,12 @@
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="M109" s="14" t="inlineStr">
         <is>
-          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
+          <t>https://stockpile.lk/welding-rod-6013-g12-kg.html</t>
         </is>
       </c>
     </row>
@@ -32863,13 +32863,13 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
+          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
         </is>
       </c>
       <c r="E110" s="9" t="n"/>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>searchworks.stanford.edu</t>
+          <t>elanka.com.au</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -32882,10 +32882,14 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I110" s="9" t="n"/>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>hero-stone</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr">
@@ -32900,7 +32904,7 @@
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>https://searchworks.stanford.edu/view/14451040</t>
+          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
         </is>
       </c>
     </row>
@@ -32914,13 +32918,13 @@
       <c r="C111" s="11" t="n"/>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
+          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
         </is>
       </c>
       <c r="E111" s="13" t="n"/>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>searchworks.stanford.edu</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
@@ -32933,14 +32937,10 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I111" s="13" t="n"/>
       <c r="J111" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero-stone</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
@@ -32950,12 +32950,12 @@
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M111" s="14" t="inlineStr">
         <is>
-          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
+          <t>https://searchworks.stanford.edu/view/14451040</t>
         </is>
       </c>
     </row>
@@ -32969,7 +32969,7 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
+          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
         </is>
       </c>
       <c r="E112" s="9" t="n"/>
@@ -33010,7 +33010,7 @@
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/?lang=en</t>
+          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
         </is>
       </c>
     </row>
@@ -33024,13 +33024,13 @@
       <c r="C113" s="11" t="n"/>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum</t>
+          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
         </is>
       </c>
       <c r="E113" s="13" t="n"/>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>lonelyplanet.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
@@ -33045,12 +33045,12 @@
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J113" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
@@ -33060,12 +33060,12 @@
       </c>
       <c r="L113" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M113" s="14" t="inlineStr">
         <is>
-          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
+          <t>https://www.inscriptions.lk/?lang=en</t>
         </is>
       </c>
     </row>
@@ -33079,13 +33079,13 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
+          <t>Jaffna Archaeological Museum</t>
         </is>
       </c>
       <c r="E114" s="9" t="n"/>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>tripadvisor.com</t>
+          <t>lonelyplanet.com</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -33115,12 +33115,12 @@
       </c>
       <c r="L114" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
+          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
         </is>
       </c>
     </row>
@@ -33134,13 +33134,13 @@
       <c r="C115" s="11" t="n"/>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
+          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
         </is>
       </c>
       <c r="E115" s="13" t="n"/>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>jaffna.top</t>
+          <t>tripadvisor.com</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
@@ -33175,7 +33175,7 @@
       </c>
       <c r="M115" s="14" t="inlineStr">
         <is>
-          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
         </is>
       </c>
     </row>
@@ -33189,13 +33189,13 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
+          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
         </is>
       </c>
       <c r="E116" s="9" t="n"/>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>srilankatravelpages.com</t>
+          <t>jaffna.top</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -33225,12 +33225,12 @@
       </c>
       <c r="L116" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
+          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
         </is>
       </c>
     </row>
@@ -33244,13 +33244,13 @@
       <c r="C117" s="11" t="n"/>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
+          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
         </is>
       </c>
       <c r="E117" s="13" t="n"/>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>srilankatourhelp.org</t>
+          <t>srilankatravelpages.com</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M117" s="14" t="inlineStr">
         <is>
-          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
+          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
         </is>
       </c>
     </row>
@@ -33299,13 +33299,13 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | About.lk</t>
+          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
         </is>
       </c>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
+          <t>srilankatourhelp.org</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
@@ -33340,7 +33340,7 @@
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
+          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
         </is>
       </c>
     </row>
@@ -33354,13 +33354,13 @@
       <c r="C119" s="11" t="n"/>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum | About.lk</t>
         </is>
       </c>
       <c r="E119" s="13" t="n"/>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
@@ -33395,7 +33395,7 @@
       </c>
       <c r="M119" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
+          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
         </is>
       </c>
     </row>
@@ -33409,13 +33409,13 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
+          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
         </is>
       </c>
       <c r="E120" s="9" t="n"/>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>i-discoverasia.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -33435,7 +33435,7 @@
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr">
@@ -33445,12 +33445,12 @@
       </c>
       <c r="L120" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
+          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
         </is>
       </c>
     </row>
@@ -33464,13 +33464,13 @@
       <c r="C121" s="11" t="n"/>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archeology Tour - Journe Experiences</t>
+          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
         </is>
       </c>
       <c r="E121" s="13" t="n"/>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>journesrilanka.com</t>
+          <t>i-discoverasia.com</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr">
@@ -33483,8 +33483,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I121" s="13" t="n"/>
-      <c r="J121" s="13" t="n"/>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J121" s="13" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33492,12 +33500,12 @@
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
         </is>
       </c>
       <c r="M121" s="14" t="inlineStr">
         <is>
-          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
+          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -33511,13 +33519,13 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
+          <t>Jaffna Archeology Tour - Journe Experiences</t>
         </is>
       </c>
       <c r="E122" s="9" t="n"/>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>lanka-excursions-holidays.com</t>
+          <t>journesrilanka.com</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -33539,12 +33547,12 @@
       </c>
       <c r="L122" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
+          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
         </is>
       </c>
     </row>
@@ -33558,13 +33566,13 @@
       <c r="C123" s="11" t="n"/>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
         </is>
       </c>
       <c r="E123" s="13" t="n"/>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>lanka-excursions-holidays.com</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
@@ -33586,12 +33594,12 @@
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M123" s="14" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
         </is>
       </c>
     </row>
@@ -33605,13 +33613,13 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="E124" s="9" t="n"/>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -33633,12 +33641,12 @@
       </c>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -33652,13 +33660,13 @@
       <c r="C125" s="11" t="n"/>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="E125" s="13" t="n"/>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
@@ -33671,16 +33679,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J125" s="13" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="I125" s="13" t="n"/>
+      <c r="J125" s="13" t="n"/>
       <c r="K125" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33693,7 +33693,7 @@
       </c>
       <c r="M125" s="14" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -33707,22 +33707,18 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="n"/>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -33732,12 +33728,12 @@
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K126" s="7" t="inlineStr">
@@ -33747,12 +33743,12 @@
       </c>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -33766,18 +33762,22 @@
       <c r="C127" s="11" t="n"/>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="E127" s="13" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
@@ -33792,7 +33792,7 @@
       </c>
       <c r="J127" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K127" s="11" t="inlineStr">
@@ -33800,10 +33800,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L127" s="13" t="n"/>
+      <c r="L127" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -33817,18 +33821,18 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Museums - Archaeology</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="E128" s="9" t="n"/>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -33843,7 +33847,7 @@
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="K128" s="7" t="inlineStr">
@@ -33851,14 +33855,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L128" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L128" s="9" t="n"/>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -33872,13 +33872,13 @@
       <c r="C129" s="11" t="n"/>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Museums - Archaeology</t>
         </is>
       </c>
       <c r="E129" s="13" t="n"/>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr">
@@ -33898,7 +33898,7 @@
       </c>
       <c r="J129" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="K129" s="11" t="inlineStr">
@@ -33908,12 +33908,12 @@
       </c>
       <c r="L129" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
         </is>
       </c>
     </row>
@@ -33927,13 +33927,13 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="E130" s="9" t="n"/>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -33948,10 +33948,14 @@
       </c>
       <c r="I130" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J130" s="9" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33959,12 +33963,12 @@
       </c>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -33978,13 +33982,13 @@
       <c r="C131" s="11" t="n"/>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="E131" s="13" t="n"/>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -33999,14 +34003,10 @@
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J131" s="13" t="inlineStr">
-        <is>
-          <t>inscription; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J131" s="13" t="n"/>
       <c r="K131" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34014,12 +34014,12 @@
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -34033,13 +34033,13 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="E132" s="9" t="n"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk:8080</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -34069,12 +34069,12 @@
       </c>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -34088,13 +34088,13 @@
       <c r="C133" s="11" t="n"/>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
         </is>
       </c>
       <c r="E133" s="13" t="n"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk:8080</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
@@ -34109,10 +34109,14 @@
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J133" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J133" s="13" t="inlineStr">
+        <is>
+          <t>inscription; brahmi</t>
+        </is>
+      </c>
       <c r="K133" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34120,12 +34124,12 @@
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
         </is>
       </c>
     </row>
@@ -34139,13 +34143,13 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="E134" s="9" t="n"/>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
@@ -34160,14 +34164,10 @@
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J134" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n"/>
       <c r="K134" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34175,12 +34175,12 @@
       </c>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -34194,7 +34194,7 @@
       <c r="C135" s="11" t="n"/>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E135" s="13" t="n"/>
@@ -34220,7 +34220,7 @@
       </c>
       <c r="J135" s="13" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K135" s="11" t="inlineStr">
@@ -34235,7 +34235,7 @@
       </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -34249,13 +34249,13 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E136" s="9" t="n"/>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
@@ -34270,12 +34270,12 @@
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr">
@@ -34285,12 +34285,12 @@
       </c>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -34304,22 +34304,18 @@
       <c r="C137" s="11" t="n"/>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="E137" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Sinhalese Hero Stone Analysis</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="n"/>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -34327,8 +34323,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I137" s="13" t="n"/>
-      <c r="J137" s="13" t="n"/>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="J137" s="13" t="inlineStr">
+        <is>
+          <t>hero stone</t>
+        </is>
+      </c>
       <c r="K137" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34336,12 +34340,12 @@
       </c>
       <c r="L137" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -34355,18 +34359,22 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Sri Lanka Inscriptions</t>
-        </is>
-      </c>
-      <c r="E138" s="9" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -34374,16 +34382,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J138" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="I138" s="9" t="n"/>
+      <c r="J138" s="9" t="n"/>
       <c r="K138" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34391,12 +34391,12 @@
       </c>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -34410,13 +34410,13 @@
       <c r="C139" s="11" t="n"/>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="E139" s="13" t="n"/>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
@@ -34431,12 +34431,12 @@
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J139" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K139" s="11" t="inlineStr">
@@ -34446,12 +34446,12 @@
       </c>
       <c r="L139" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M139" s="14" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -34465,13 +34465,13 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="E140" s="9" t="n"/>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -34501,12 +34501,12 @@
       </c>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -34520,13 +34520,13 @@
       <c r="C141" s="11" t="n"/>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="E141" s="13" t="n"/>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
@@ -34541,10 +34541,14 @@
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J141" s="13" t="n"/>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J141" s="13" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="K141" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34552,12 +34556,12 @@
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M141" s="14" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -34571,13 +34575,13 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="E142" s="9" t="n"/>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
@@ -34592,14 +34596,10 @@
       </c>
       <c r="I142" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J142" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n"/>
       <c r="K142" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34607,12 +34607,12 @@
       </c>
       <c r="L142" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -34626,13 +34626,13 @@
       <c r="C143" s="11" t="n"/>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
+          <t>Tamil Identity in Vanni Monuments</t>
         </is>
       </c>
       <c r="E143" s="13" t="n"/>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>en.bharatpedia.org</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
@@ -34647,14 +34647,10 @@
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J143" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J143" s="13" t="n"/>
       <c r="K143" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34662,12 +34658,12 @@
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="M143" s="14" t="inlineStr">
         <is>
-          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/933772684/MC-13</t>
         </is>
       </c>
     </row>
@@ -34681,13 +34677,13 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="E144" s="9" t="n"/>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
@@ -34702,12 +34698,12 @@
       </c>
       <c r="I144" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K144" s="7" t="inlineStr">
@@ -34717,12 +34713,12 @@
       </c>
       <c r="L144" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -34736,13 +34732,13 @@
       <c r="C145" s="11" t="n"/>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="E145" s="13" t="n"/>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
@@ -34772,12 +34768,12 @@
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M145" s="14" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -34791,13 +34787,13 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="E146" s="9" t="n"/>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -34817,7 +34813,7 @@
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K146" s="7" t="inlineStr">
@@ -34827,12 +34823,12 @@
       </c>
       <c r="L146" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -34846,13 +34842,13 @@
       <c r="C147" s="11" t="n"/>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="E147" s="13" t="n"/>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
@@ -34865,8 +34861,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I147" s="13" t="n"/>
-      <c r="J147" s="13" t="n"/>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J147" s="13" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="K147" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34874,12 +34878,12 @@
       </c>
       <c r="L147" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M147" s="14" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -34893,13 +34897,13 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="E148" s="9" t="n"/>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>cambridge.org</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
@@ -34912,8 +34916,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I148" s="9" t="n"/>
-      <c r="J148" s="9" t="n"/>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K148" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34921,12 +34933,12 @@
       </c>
       <c r="L148" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
-          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -34940,13 +34952,13 @@
       <c r="C149" s="11" t="n"/>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="E149" s="13" t="n"/>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr">
@@ -34959,16 +34971,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J149" s="13" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="I149" s="13" t="n"/>
+      <c r="J149" s="13" t="n"/>
       <c r="K149" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34976,12 +34980,12 @@
       </c>
       <c r="L149" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M149" s="14" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -34995,13 +34999,13 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
         </is>
       </c>
       <c r="E150" s="9" t="n"/>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>cambridge.org</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
@@ -35014,16 +35018,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I150" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J150" s="9" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="I150" s="9" t="n"/>
+      <c r="J150" s="9" t="n"/>
       <c r="K150" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35031,12 +35027,12 @@
       </c>
       <c r="L150" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M150" s="10" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
         </is>
       </c>
     </row>
@@ -35050,22 +35046,18 @@
       <c r="C151" s="11" t="n"/>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="E151" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+        </is>
+      </c>
+      <c r="E151" s="13" t="n"/>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
@@ -35073,8 +35065,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I151" s="13" t="n"/>
-      <c r="J151" s="13" t="n"/>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J151" s="13" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K151" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35082,12 +35082,12 @@
       </c>
       <c r="L151" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M151" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -35101,18 +35101,18 @@
       <c r="C152" s="7" t="n"/>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="E152" s="9" t="n"/>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
@@ -35122,12 +35122,12 @@
       </c>
       <c r="I152" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr">
@@ -35135,10 +35135,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L152" s="9" t="n"/>
+      <c r="L152" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="M152" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -35152,23 +35156,27 @@
       <c r="C153" s="11" t="n"/>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
-        </is>
-      </c>
-      <c r="E153" s="13" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="E153" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F153" s="13" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I153" s="13" t="n"/>
@@ -35180,12 +35188,12 @@
       </c>
       <c r="L153" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M153" s="14" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -35199,37 +35207,33 @@
       <c r="C154" s="7" t="n"/>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="n"/>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I154" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J154" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="K154" s="7" t="inlineStr">
@@ -35237,14 +35241,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L154" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L154" s="9" t="n"/>
       <c r="M154" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -35258,13 +35258,13 @@
       <c r="C155" s="11" t="n"/>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="E155" s="13" t="n"/>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr">
@@ -35277,16 +35277,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J155" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
-        </is>
-      </c>
+      <c r="I155" s="13" t="n"/>
+      <c r="J155" s="13" t="n"/>
       <c r="K155" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35294,12 +35286,12 @@
       </c>
       <c r="L155" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M155" s="14" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -35313,18 +35305,22 @@
       <c r="C156" s="7" t="n"/>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
-        </is>
-      </c>
-      <c r="E156" s="9" t="n"/>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -35334,12 +35330,12 @@
       </c>
       <c r="I156" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J156" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K156" s="7" t="inlineStr">
@@ -35349,12 +35345,12 @@
       </c>
       <c r="L156" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M156" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -35368,22 +35364,18 @@
       <c r="C157" s="11" t="n"/>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="E157" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="n"/>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -35391,8 +35383,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I157" s="13" t="n"/>
-      <c r="J157" s="13" t="n"/>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J157" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+        </is>
+      </c>
       <c r="K157" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35400,12 +35400,12 @@
       </c>
       <c r="L157" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M157" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -35419,13 +35419,13 @@
       <c r="C158" s="7" t="n"/>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
         </is>
       </c>
       <c r="E158" s="9" t="n"/>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
@@ -35440,12 +35440,12 @@
       </c>
       <c r="I158" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>நடுகல்</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="K158" s="7" t="inlineStr">
@@ -35455,12 +35455,12 @@
       </c>
       <c r="L158" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M158" s="10" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -35474,7 +35474,7 @@
       <c r="C159" s="11" t="n"/>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
@@ -35497,16 +35497,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J159" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+      <c r="I159" s="13" t="n"/>
+      <c r="J159" s="13" t="n"/>
       <c r="K159" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35519,7 +35511,7 @@
       </c>
       <c r="M159" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -35533,22 +35525,18 @@
       <c r="C160" s="7" t="n"/>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E160" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="n"/>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
@@ -35558,12 +35546,12 @@
       </c>
       <c r="I160" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J160" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="K160" s="7" t="inlineStr">
@@ -35573,12 +35561,12 @@
       </c>
       <c r="L160" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M160" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -35592,18 +35580,22 @@
       <c r="C161" s="11" t="n"/>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
-        </is>
-      </c>
-      <c r="E161" s="13" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
@@ -35618,7 +35610,7 @@
       </c>
       <c r="J161" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="K161" s="11" t="inlineStr">
@@ -35628,12 +35620,12 @@
       </c>
       <c r="L161" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M161" s="14" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -35647,18 +35639,22 @@
       <c r="C162" s="7" t="n"/>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
-        </is>
-      </c>
-      <c r="E162" s="9" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>ezhunaonline.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -35668,10 +35664,14 @@
       </c>
       <c r="I162" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J162" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K162" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35679,12 +35679,12 @@
       </c>
       <c r="L162" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
-          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -35698,13 +35698,13 @@
       <c r="C163" s="11" t="n"/>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="E163" s="13" t="n"/>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>ta.wikipedia.org</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr">
@@ -35724,7 +35724,7 @@
       </c>
       <c r="J163" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K163" s="11" t="inlineStr">
@@ -35734,12 +35734,12 @@
       </c>
       <c r="L163" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M163" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -35753,13 +35753,13 @@
       <c r="C164" s="7" t="n"/>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
+          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
         </is>
       </c>
       <c r="E164" s="9" t="n"/>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>ezhunaonline.com</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
@@ -35774,14 +35774,10 @@
       </c>
       <c r="I164" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J164" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; பிராமி</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n"/>
       <c r="K164" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35789,12 +35785,12 @@
       </c>
       <c r="L164" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M164" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
         </is>
       </c>
     </row>
@@ -35808,13 +35804,13 @@
       <c r="C165" s="11" t="n"/>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
         </is>
       </c>
       <c r="E165" s="13" t="n"/>
       <c r="F165" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>ta.wikipedia.org</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr">
@@ -35829,10 +35825,14 @@
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J165" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J165" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+        </is>
+      </c>
       <c r="K165" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35840,12 +35840,12 @@
       </c>
       <c r="L165" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="M165" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -35859,13 +35859,13 @@
       <c r="C166" s="7" t="n"/>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="E166" s="9" t="n"/>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
@@ -35878,8 +35878,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I166" s="9" t="n"/>
-      <c r="J166" s="9" t="n"/>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
       <c r="K166" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35887,12 +35895,12 @@
       </c>
       <c r="L166" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M166" s="10" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -35906,13 +35914,13 @@
       <c r="C167" s="11" t="n"/>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="E167" s="13" t="n"/>
       <c r="F167" s="13" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr">
@@ -35930,11 +35938,7 @@
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="J167" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="J167" s="13" t="n"/>
       <c r="K167" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35942,12 +35946,12 @@
       </c>
       <c r="L167" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
       <c r="M167" s="14" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
         </is>
       </c>
     </row>
@@ -35961,13 +35965,13 @@
       <c r="C168" s="7" t="n"/>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
         </is>
       </c>
       <c r="E168" s="9" t="n"/>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>shritharan.com</t>
+          <t>treasurehouseofjaffna.com</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
@@ -35980,16 +35984,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I168" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J168" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="I168" s="9" t="n"/>
+      <c r="J168" s="9" t="n"/>
       <c r="K168" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -36002,7 +35998,7 @@
       </c>
       <c r="M168" s="10" t="inlineStr">
         <is>
-          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
         </is>
       </c>
     </row>
@@ -36016,53 +36012,163 @@
       <c r="C169" s="11" t="n"/>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
         </is>
       </c>
       <c r="E169" s="13" t="n"/>
       <c r="F169" s="13" t="inlineStr">
         <is>
+          <t>jvpnews.com</t>
+        </is>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H169" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J169" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K169" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L169" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M169" s="14" t="inlineStr">
+        <is>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>WB-0169</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="n"/>
+      <c r="C170" s="7" t="n"/>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="n"/>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="G169" s="11" t="inlineStr">
+      <c r="G170" s="7" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="H169" s="11" t="inlineStr">
+      <c r="H170" s="7" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I169" s="13" t="inlineStr">
+      <c r="I170" s="9" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="J169" s="13" t="inlineStr">
+      <c r="J170" s="9" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="K169" s="11" t="inlineStr">
+      <c r="K170" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L169" s="13" t="inlineStr">
+      <c r="L170" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M170" s="10" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>WB-0170</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="n"/>
+      <c r="C171" s="11" t="n"/>
+      <c r="D171" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+        </is>
+      </c>
+      <c r="E171" s="13" t="n"/>
+      <c r="F171" s="13" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H171" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J171" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K171" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L171" s="13" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
-      <c r="M169" s="14" t="inlineStr">
+      <c r="M171" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/jaffna-anaikotta-archaeological-exhibition-begins/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M169"/>
+  <autoFilter ref="A1:M171"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -36232,6 +36338,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36243,7 +36351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N570"/>
+  <dimension ref="A1:N572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -69821,13 +69929,13 @@
       <c r="D510" s="7" t="n"/>
       <c r="E510" s="9" t="inlineStr">
         <is>
-          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
+          <t>Hero Stonebridge MS Welding Rod 6013 G12 - Stockpile</t>
         </is>
       </c>
       <c r="F510" s="9" t="n"/>
       <c r="G510" s="9" t="inlineStr">
         <is>
-          <t>elanka.com.au</t>
+          <t>stockpile.lk</t>
         </is>
       </c>
       <c r="H510" s="7" t="inlineStr">
@@ -69857,12 +69965,12 @@
       </c>
       <c r="M510" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="N510" s="10" t="inlineStr">
         <is>
-          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
+          <t>https://stockpile.lk/welding-rod-6013-g12-kg.html</t>
         </is>
       </c>
     </row>
@@ -69881,13 +69989,13 @@
       <c r="D511" s="11" t="n"/>
       <c r="E511" s="13" t="inlineStr">
         <is>
-          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
+          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
         </is>
       </c>
       <c r="F511" s="13" t="n"/>
       <c r="G511" s="13" t="inlineStr">
         <is>
-          <t>searchworks.stanford.edu</t>
+          <t>elanka.com.au</t>
         </is>
       </c>
       <c r="H511" s="11" t="inlineStr">
@@ -69900,10 +70008,14 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J511" s="13" t="n"/>
+      <c r="J511" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
       <c r="K511" s="13" t="inlineStr">
         <is>
-          <t>hero-stone</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="L511" s="11" t="inlineStr">
@@ -69918,7 +70030,7 @@
       </c>
       <c r="N511" s="14" t="inlineStr">
         <is>
-          <t>https://searchworks.stanford.edu/view/14451040</t>
+          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
         </is>
       </c>
     </row>
@@ -69937,13 +70049,13 @@
       <c r="D512" s="7" t="n"/>
       <c r="E512" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
+          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
         </is>
       </c>
       <c r="F512" s="9" t="n"/>
       <c r="G512" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>searchworks.stanford.edu</t>
         </is>
       </c>
       <c r="H512" s="7" t="inlineStr">
@@ -69956,14 +70068,10 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J512" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J512" s="9" t="n"/>
       <c r="K512" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero-stone</t>
         </is>
       </c>
       <c r="L512" s="7" t="inlineStr">
@@ -69973,12 +70081,12 @@
       </c>
       <c r="M512" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N512" s="10" t="inlineStr">
         <is>
-          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
+          <t>https://searchworks.stanford.edu/view/14451040</t>
         </is>
       </c>
     </row>
@@ -69997,7 +70105,7 @@
       <c r="D513" s="11" t="n"/>
       <c r="E513" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
+          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
         </is>
       </c>
       <c r="F513" s="13" t="n"/>
@@ -70038,7 +70146,7 @@
       </c>
       <c r="N513" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/?lang=en</t>
+          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
         </is>
       </c>
     </row>
@@ -70057,13 +70165,13 @@
       <c r="D514" s="7" t="n"/>
       <c r="E514" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum</t>
+          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
         </is>
       </c>
       <c r="F514" s="9" t="n"/>
       <c r="G514" s="9" t="inlineStr">
         <is>
-          <t>lonelyplanet.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H514" s="7" t="inlineStr">
@@ -70078,12 +70186,12 @@
       </c>
       <c r="J514" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K514" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L514" s="7" t="inlineStr">
@@ -70093,12 +70201,12 @@
       </c>
       <c r="M514" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N514" s="10" t="inlineStr">
         <is>
-          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
+          <t>https://www.inscriptions.lk/?lang=en</t>
         </is>
       </c>
     </row>
@@ -70117,13 +70225,13 @@
       <c r="D515" s="11" t="n"/>
       <c r="E515" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
+          <t>Jaffna Archaeological Museum</t>
         </is>
       </c>
       <c r="F515" s="13" t="n"/>
       <c r="G515" s="13" t="inlineStr">
         <is>
-          <t>tripadvisor.com</t>
+          <t>lonelyplanet.com</t>
         </is>
       </c>
       <c r="H515" s="11" t="inlineStr">
@@ -70153,12 +70261,12 @@
       </c>
       <c r="M515" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
       <c r="N515" s="14" t="inlineStr">
         <is>
-          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
+          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
         </is>
       </c>
     </row>
@@ -70177,13 +70285,13 @@
       <c r="D516" s="7" t="n"/>
       <c r="E516" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
+          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
         </is>
       </c>
       <c r="F516" s="9" t="n"/>
       <c r="G516" s="9" t="inlineStr">
         <is>
-          <t>jaffna.top</t>
+          <t>tripadvisor.com</t>
         </is>
       </c>
       <c r="H516" s="7" t="inlineStr">
@@ -70218,7 +70326,7 @@
       </c>
       <c r="N516" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
         </is>
       </c>
     </row>
@@ -70237,13 +70345,13 @@
       <c r="D517" s="11" t="n"/>
       <c r="E517" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
+          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
         </is>
       </c>
       <c r="F517" s="13" t="n"/>
       <c r="G517" s="13" t="inlineStr">
         <is>
-          <t>srilankatravelpages.com</t>
+          <t>jaffna.top</t>
         </is>
       </c>
       <c r="H517" s="11" t="inlineStr">
@@ -70273,12 +70381,12 @@
       </c>
       <c r="M517" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N517" s="14" t="inlineStr">
         <is>
-          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
+          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
         </is>
       </c>
     </row>
@@ -70297,13 +70405,13 @@
       <c r="D518" s="7" t="n"/>
       <c r="E518" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
+          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
         </is>
       </c>
       <c r="F518" s="9" t="n"/>
       <c r="G518" s="9" t="inlineStr">
         <is>
-          <t>srilankatourhelp.org</t>
+          <t>srilankatravelpages.com</t>
         </is>
       </c>
       <c r="H518" s="7" t="inlineStr">
@@ -70333,12 +70441,12 @@
       </c>
       <c r="M518" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N518" s="10" t="inlineStr">
         <is>
-          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
+          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
         </is>
       </c>
     </row>
@@ -70357,13 +70465,13 @@
       <c r="D519" s="11" t="n"/>
       <c r="E519" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | About.lk</t>
+          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
         </is>
       </c>
       <c r="F519" s="13" t="n"/>
       <c r="G519" s="13" t="inlineStr">
         <is>
-          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
+          <t>srilankatourhelp.org</t>
         </is>
       </c>
       <c r="H519" s="11" t="inlineStr">
@@ -70398,7 +70506,7 @@
       </c>
       <c r="N519" s="14" t="inlineStr">
         <is>
-          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
+          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
         </is>
       </c>
     </row>
@@ -70417,13 +70525,13 @@
       <c r="D520" s="7" t="n"/>
       <c r="E520" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum | About.lk</t>
         </is>
       </c>
       <c r="F520" s="9" t="n"/>
       <c r="G520" s="9" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
         </is>
       </c>
       <c r="H520" s="7" t="inlineStr">
@@ -70458,7 +70566,7 @@
       </c>
       <c r="N520" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
+          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
         </is>
       </c>
     </row>
@@ -70477,13 +70585,13 @@
       <c r="D521" s="11" t="n"/>
       <c r="E521" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
+          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
         </is>
       </c>
       <c r="F521" s="13" t="n"/>
       <c r="G521" s="13" t="inlineStr">
         <is>
-          <t>i-discoverasia.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H521" s="11" t="inlineStr">
@@ -70503,7 +70611,7 @@
       </c>
       <c r="K521" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L521" s="11" t="inlineStr">
@@ -70513,12 +70621,12 @@
       </c>
       <c r="M521" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N521" s="14" t="inlineStr">
         <is>
-          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
+          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
         </is>
       </c>
     </row>
@@ -70537,13 +70645,13 @@
       <c r="D522" s="7" t="n"/>
       <c r="E522" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archeology Tour - Journe Experiences</t>
+          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
         </is>
       </c>
       <c r="F522" s="9" t="n"/>
       <c r="G522" s="9" t="inlineStr">
         <is>
-          <t>journesrilanka.com</t>
+          <t>i-discoverasia.com</t>
         </is>
       </c>
       <c r="H522" s="7" t="inlineStr">
@@ -70556,8 +70664,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J522" s="9" t="n"/>
-      <c r="K522" s="9" t="n"/>
+      <c r="J522" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K522" s="9" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="L522" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70565,12 +70681,12 @@
       </c>
       <c r="M522" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
         </is>
       </c>
       <c r="N522" s="10" t="inlineStr">
         <is>
-          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
+          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -70589,13 +70705,13 @@
       <c r="D523" s="11" t="n"/>
       <c r="E523" s="13" t="inlineStr">
         <is>
-          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
+          <t>Jaffna Archeology Tour - Journe Experiences</t>
         </is>
       </c>
       <c r="F523" s="13" t="n"/>
       <c r="G523" s="13" t="inlineStr">
         <is>
-          <t>lanka-excursions-holidays.com</t>
+          <t>journesrilanka.com</t>
         </is>
       </c>
       <c r="H523" s="11" t="inlineStr">
@@ -70617,12 +70733,12 @@
       </c>
       <c r="M523" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N523" s="14" t="inlineStr">
         <is>
-          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
+          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
         </is>
       </c>
     </row>
@@ -70641,13 +70757,13 @@
       <c r="D524" s="7" t="n"/>
       <c r="E524" s="9" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
         </is>
       </c>
       <c r="F524" s="9" t="n"/>
       <c r="G524" s="9" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>lanka-excursions-holidays.com</t>
         </is>
       </c>
       <c r="H524" s="7" t="inlineStr">
@@ -70669,12 +70785,12 @@
       </c>
       <c r="M524" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N524" s="10" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
         </is>
       </c>
     </row>
@@ -70693,13 +70809,13 @@
       <c r="D525" s="11" t="n"/>
       <c r="E525" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="F525" s="13" t="n"/>
       <c r="G525" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="H525" s="11" t="inlineStr">
@@ -70721,12 +70837,12 @@
       </c>
       <c r="M525" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N525" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -70745,13 +70861,13 @@
       <c r="D526" s="7" t="n"/>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="F526" s="9" t="n"/>
       <c r="G526" s="9" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H526" s="7" t="inlineStr">
@@ -70764,16 +70880,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J526" s="9" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K526" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="J526" s="9" t="n"/>
+      <c r="K526" s="9" t="n"/>
       <c r="L526" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70786,7 +70894,7 @@
       </c>
       <c r="N526" s="10" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -70805,22 +70913,18 @@
       <c r="D527" s="11" t="n"/>
       <c r="E527" s="13" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="F527" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+        </is>
+      </c>
+      <c r="F527" s="13" t="n"/>
       <c r="G527" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="H527" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I527" s="11" t="inlineStr">
@@ -70830,12 +70934,12 @@
       </c>
       <c r="J527" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K527" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L527" s="11" t="inlineStr">
@@ -70845,12 +70949,12 @@
       </c>
       <c r="M527" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N527" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -70869,18 +70973,22 @@
       <c r="D528" s="7" t="n"/>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="F528" s="9" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="F528" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G528" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H528" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I528" s="7" t="inlineStr">
@@ -70895,7 +71003,7 @@
       </c>
       <c r="K528" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L528" s="7" t="inlineStr">
@@ -70903,10 +71011,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M528" s="9" t="n"/>
+      <c r="M528" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N528" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -70925,18 +71037,18 @@
       <c r="D529" s="11" t="n"/>
       <c r="E529" s="13" t="inlineStr">
         <is>
-          <t>Museums - Archaeology</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="F529" s="13" t="n"/>
       <c r="G529" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H529" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I529" s="11" t="inlineStr">
@@ -70951,7 +71063,7 @@
       </c>
       <c r="K529" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="L529" s="11" t="inlineStr">
@@ -70959,14 +71071,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M529" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M529" s="13" t="n"/>
       <c r="N529" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -70985,13 +71093,13 @@
       <c r="D530" s="7" t="n"/>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Museums - Archaeology</t>
         </is>
       </c>
       <c r="F530" s="9" t="n"/>
       <c r="G530" s="9" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H530" s="7" t="inlineStr">
@@ -71011,7 +71119,7 @@
       </c>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="L530" s="7" t="inlineStr">
@@ -71021,12 +71129,12 @@
       </c>
       <c r="M530" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N530" s="10" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
         </is>
       </c>
     </row>
@@ -71045,13 +71153,13 @@
       <c r="D531" s="11" t="n"/>
       <c r="E531" s="13" t="inlineStr">
         <is>
-          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="F531" s="13" t="n"/>
       <c r="G531" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="H531" s="11" t="inlineStr">
@@ -71066,10 +71174,14 @@
       </c>
       <c r="J531" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K531" s="13" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K531" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L531" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71077,12 +71189,12 @@
       </c>
       <c r="M531" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N531" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -71101,13 +71213,13 @@
       <c r="D532" s="7" t="n"/>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="F532" s="9" t="n"/>
       <c r="G532" s="9" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H532" s="7" t="inlineStr">
@@ -71122,14 +71234,10 @@
       </c>
       <c r="J532" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K532" s="9" t="inlineStr">
-        <is>
-          <t>inscription; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K532" s="9" t="n"/>
       <c r="L532" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71137,12 +71245,12 @@
       </c>
       <c r="M532" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N532" s="10" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -71161,13 +71269,13 @@
       <c r="D533" s="11" t="n"/>
       <c r="E533" s="13" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="F533" s="13" t="n"/>
       <c r="G533" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk:8080</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="H533" s="11" t="inlineStr">
@@ -71197,12 +71305,12 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N533" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -71221,13 +71329,13 @@
       <c r="D534" s="7" t="n"/>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
         </is>
       </c>
       <c r="F534" s="9" t="n"/>
       <c r="G534" s="9" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk:8080</t>
         </is>
       </c>
       <c r="H534" s="7" t="inlineStr">
@@ -71242,10 +71350,14 @@
       </c>
       <c r="J534" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K534" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K534" s="9" t="inlineStr">
+        <is>
+          <t>inscription; brahmi</t>
+        </is>
+      </c>
       <c r="L534" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71253,12 +71365,12 @@
       </c>
       <c r="M534" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N534" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
         </is>
       </c>
     </row>
@@ -71277,13 +71389,13 @@
       <c r="D535" s="11" t="n"/>
       <c r="E535" s="13" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="F535" s="13" t="n"/>
       <c r="G535" s="13" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="H535" s="11" t="inlineStr">
@@ -71298,14 +71410,10 @@
       </c>
       <c r="J535" s="13" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K535" s="13" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K535" s="13" t="n"/>
       <c r="L535" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71313,12 +71421,12 @@
       </c>
       <c r="M535" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N535" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -71337,7 +71445,7 @@
       <c r="D536" s="7" t="n"/>
       <c r="E536" s="9" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F536" s="9" t="n"/>
@@ -71363,7 +71471,7 @@
       </c>
       <c r="K536" s="9" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L536" s="7" t="inlineStr">
@@ -71378,7 +71486,7 @@
       </c>
       <c r="N536" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -71397,13 +71505,13 @@
       <c r="D537" s="11" t="n"/>
       <c r="E537" s="13" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F537" s="13" t="n"/>
       <c r="G537" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H537" s="11" t="inlineStr">
@@ -71418,12 +71526,12 @@
       </c>
       <c r="J537" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K537" s="13" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="L537" s="11" t="inlineStr">
@@ -71433,12 +71541,12 @@
       </c>
       <c r="M537" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N537" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -71457,22 +71565,18 @@
       <c r="D538" s="7" t="n"/>
       <c r="E538" s="9" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="F538" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Sinhalese Hero Stone Analysis</t>
+        </is>
+      </c>
+      <c r="F538" s="9" t="n"/>
       <c r="G538" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H538" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I538" s="7" t="inlineStr">
@@ -71480,8 +71584,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J538" s="9" t="n"/>
-      <c r="K538" s="9" t="n"/>
+      <c r="J538" s="9" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="K538" s="9" t="inlineStr">
+        <is>
+          <t>hero stone</t>
+        </is>
+      </c>
       <c r="L538" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71489,12 +71601,12 @@
       </c>
       <c r="M538" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N538" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -71513,18 +71625,22 @@
       <c r="D539" s="11" t="n"/>
       <c r="E539" s="13" t="inlineStr">
         <is>
-          <t>Sri Lanka Inscriptions</t>
-        </is>
-      </c>
-      <c r="F539" s="13" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="F539" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G539" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H539" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I539" s="11" t="inlineStr">
@@ -71532,16 +71648,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J539" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K539" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="J539" s="13" t="n"/>
+      <c r="K539" s="13" t="n"/>
       <c r="L539" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71549,12 +71657,12 @@
       </c>
       <c r="M539" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N539" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -71573,13 +71681,13 @@
       <c r="D540" s="7" t="n"/>
       <c r="E540" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="F540" s="9" t="n"/>
       <c r="G540" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H540" s="7" t="inlineStr">
@@ -71594,12 +71702,12 @@
       </c>
       <c r="J540" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K540" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L540" s="7" t="inlineStr">
@@ -71609,12 +71717,12 @@
       </c>
       <c r="M540" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N540" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -71633,13 +71741,13 @@
       <c r="D541" s="11" t="n"/>
       <c r="E541" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="F541" s="13" t="n"/>
       <c r="G541" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="H541" s="11" t="inlineStr">
@@ -71669,12 +71777,12 @@
       </c>
       <c r="M541" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N541" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -71693,13 +71801,13 @@
       <c r="D542" s="7" t="n"/>
       <c r="E542" s="9" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="F542" s="9" t="n"/>
       <c r="G542" s="9" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="H542" s="7" t="inlineStr">
@@ -71714,10 +71822,14 @@
       </c>
       <c r="J542" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K542" s="9" t="n"/>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K542" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="L542" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71725,12 +71837,12 @@
       </c>
       <c r="M542" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N542" s="10" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -71749,13 +71861,13 @@
       <c r="D543" s="11" t="n"/>
       <c r="E543" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="F543" s="13" t="n"/>
       <c r="G543" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="H543" s="11" t="inlineStr">
@@ -71770,14 +71882,10 @@
       </c>
       <c r="J543" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K543" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K543" s="13" t="n"/>
       <c r="L543" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71785,12 +71893,12 @@
       </c>
       <c r="M543" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N543" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -71809,13 +71917,13 @@
       <c r="D544" s="7" t="n"/>
       <c r="E544" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
+          <t>Tamil Identity in Vanni Monuments</t>
         </is>
       </c>
       <c r="F544" s="9" t="n"/>
       <c r="G544" s="9" t="inlineStr">
         <is>
-          <t>en.bharatpedia.org</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H544" s="7" t="inlineStr">
@@ -71830,14 +71938,10 @@
       </c>
       <c r="J544" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K544" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K544" s="9" t="n"/>
       <c r="L544" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71845,12 +71949,12 @@
       </c>
       <c r="M544" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="N544" s="10" t="inlineStr">
         <is>
-          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/933772684/MC-13</t>
         </is>
       </c>
     </row>
@@ -71869,13 +71973,13 @@
       <c r="D545" s="11" t="n"/>
       <c r="E545" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="F545" s="13" t="n"/>
       <c r="G545" s="13" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H545" s="11" t="inlineStr">
@@ -71890,12 +71994,12 @@
       </c>
       <c r="J545" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K545" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L545" s="11" t="inlineStr">
@@ -71905,12 +72009,12 @@
       </c>
       <c r="M545" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N545" s="14" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -71929,13 +72033,13 @@
       <c r="D546" s="7" t="n"/>
       <c r="E546" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="F546" s="9" t="n"/>
       <c r="G546" s="9" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="H546" s="7" t="inlineStr">
@@ -71965,12 +72069,12 @@
       </c>
       <c r="M546" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N546" s="10" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -71989,13 +72093,13 @@
       <c r="D547" s="11" t="n"/>
       <c r="E547" s="13" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="F547" s="13" t="n"/>
       <c r="G547" s="13" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="H547" s="11" t="inlineStr">
@@ -72015,7 +72119,7 @@
       </c>
       <c r="K547" s="13" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L547" s="11" t="inlineStr">
@@ -72025,12 +72129,12 @@
       </c>
       <c r="M547" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N547" s="14" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -72049,13 +72153,13 @@
       <c r="D548" s="7" t="n"/>
       <c r="E548" s="9" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="F548" s="9" t="n"/>
       <c r="G548" s="9" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="H548" s="7" t="inlineStr">
@@ -72068,8 +72172,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J548" s="9" t="n"/>
-      <c r="K548" s="9" t="n"/>
+      <c r="J548" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K548" s="9" t="inlineStr">
+        <is>
+          <t>inscription; inscriptions</t>
+        </is>
+      </c>
       <c r="L548" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72077,12 +72189,12 @@
       </c>
       <c r="M548" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N548" s="10" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -72101,13 +72213,13 @@
       <c r="D549" s="11" t="n"/>
       <c r="E549" s="13" t="inlineStr">
         <is>
-          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="F549" s="13" t="n"/>
       <c r="G549" s="13" t="inlineStr">
         <is>
-          <t>cambridge.org</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="H549" s="11" t="inlineStr">
@@ -72120,8 +72232,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J549" s="13" t="n"/>
-      <c r="K549" s="13" t="n"/>
+      <c r="J549" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K549" s="13" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L549" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72129,12 +72249,12 @@
       </c>
       <c r="M549" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N549" s="14" t="inlineStr">
         <is>
-          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -72153,13 +72273,13 @@
       <c r="D550" s="7" t="n"/>
       <c r="E550" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="F550" s="9" t="n"/>
       <c r="G550" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="H550" s="7" t="inlineStr">
@@ -72172,16 +72292,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J550" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K550" s="9" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="J550" s="9" t="n"/>
+      <c r="K550" s="9" t="n"/>
       <c r="L550" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72189,12 +72301,12 @@
       </c>
       <c r="M550" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N550" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -72213,13 +72325,13 @@
       <c r="D551" s="11" t="n"/>
       <c r="E551" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
         </is>
       </c>
       <c r="F551" s="13" t="n"/>
       <c r="G551" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>cambridge.org</t>
         </is>
       </c>
       <c r="H551" s="11" t="inlineStr">
@@ -72232,16 +72344,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J551" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K551" s="13" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="J551" s="13" t="n"/>
+      <c r="K551" s="13" t="n"/>
       <c r="L551" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72249,12 +72353,12 @@
       </c>
       <c r="M551" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N551" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
         </is>
       </c>
     </row>
@@ -72273,22 +72377,18 @@
       <c r="D552" s="7" t="n"/>
       <c r="E552" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="F552" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+        </is>
+      </c>
+      <c r="F552" s="9" t="n"/>
       <c r="G552" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="H552" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I552" s="7" t="inlineStr">
@@ -72296,8 +72396,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J552" s="9" t="n"/>
-      <c r="K552" s="9" t="n"/>
+      <c r="J552" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K552" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L552" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72305,12 +72413,12 @@
       </c>
       <c r="M552" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N552" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -72329,18 +72437,18 @@
       <c r="D553" s="11" t="n"/>
       <c r="E553" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
         </is>
       </c>
       <c r="F553" s="13" t="n"/>
       <c r="G553" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H553" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I553" s="11" t="inlineStr">
@@ -72350,12 +72458,12 @@
       </c>
       <c r="J553" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K553" s="13" t="inlineStr">
         <is>
-          <t>memorial stone; Vanni</t>
+          <t>inscription</t>
         </is>
       </c>
       <c r="L553" s="11" t="inlineStr">
@@ -72363,10 +72471,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M553" s="13" t="n"/>
+      <c r="M553" s="13" t="inlineStr">
+        <is>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+        </is>
+      </c>
       <c r="N553" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -72385,23 +72497,27 @@
       <c r="D554" s="7" t="n"/>
       <c r="E554" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
-        </is>
-      </c>
-      <c r="F554" s="9" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="F554" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G554" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H554" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I554" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J554" s="9" t="n"/>
@@ -72413,12 +72529,12 @@
       </c>
       <c r="M554" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N554" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -72437,37 +72553,33 @@
       <c r="D555" s="11" t="n"/>
       <c r="E555" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F555" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
+        </is>
+      </c>
+      <c r="F555" s="13" t="n"/>
       <c r="G555" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H555" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I555" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J555" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K555" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>memorial stone; Vanni</t>
         </is>
       </c>
       <c r="L555" s="11" t="inlineStr">
@@ -72475,14 +72587,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M555" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M555" s="13" t="n"/>
       <c r="N555" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -72501,13 +72609,13 @@
       <c r="D556" s="7" t="n"/>
       <c r="E556" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
         </is>
       </c>
       <c r="F556" s="9" t="n"/>
       <c r="G556" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H556" s="7" t="inlineStr">
@@ -72520,16 +72628,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J556" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K556" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
-        </is>
-      </c>
+      <c r="J556" s="9" t="n"/>
+      <c r="K556" s="9" t="n"/>
       <c r="L556" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72537,12 +72637,12 @@
       </c>
       <c r="M556" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N556" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -72561,18 +72661,22 @@
       <c r="D557" s="11" t="n"/>
       <c r="E557" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
-        </is>
-      </c>
-      <c r="F557" s="13" t="n"/>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F557" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G557" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H557" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I557" s="11" t="inlineStr">
@@ -72582,12 +72686,12 @@
       </c>
       <c r="J557" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K557" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L557" s="11" t="inlineStr">
@@ -72597,12 +72701,12 @@
       </c>
       <c r="M557" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N557" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -72621,22 +72725,18 @@
       <c r="D558" s="7" t="n"/>
       <c r="E558" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="F558" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
+        </is>
+      </c>
+      <c r="F558" s="9" t="n"/>
       <c r="G558" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="H558" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I558" s="7" t="inlineStr">
@@ -72644,8 +72744,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J558" s="9" t="n"/>
-      <c r="K558" s="9" t="n"/>
+      <c r="J558" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K558" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+        </is>
+      </c>
       <c r="L558" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72653,12 +72761,12 @@
       </c>
       <c r="M558" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N558" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -72677,13 +72785,13 @@
       <c r="D559" s="11" t="n"/>
       <c r="E559" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
         </is>
       </c>
       <c r="F559" s="13" t="n"/>
       <c r="G559" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H559" s="11" t="inlineStr">
@@ -72698,12 +72806,12 @@
       </c>
       <c r="J559" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K559" s="13" t="inlineStr">
         <is>
-          <t>நடுகல்</t>
+          <t>தொல்லியல்</t>
         </is>
       </c>
       <c r="L559" s="11" t="inlineStr">
@@ -72713,12 +72821,12 @@
       </c>
       <c r="M559" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N559" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -72737,7 +72845,7 @@
       <c r="D560" s="7" t="n"/>
       <c r="E560" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
         </is>
       </c>
       <c r="F560" s="9" t="inlineStr">
@@ -72760,16 +72868,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J560" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K560" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+      <c r="J560" s="9" t="n"/>
+      <c r="K560" s="9" t="n"/>
       <c r="L560" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72782,7 +72882,7 @@
       </c>
       <c r="N560" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -72801,22 +72901,18 @@
       <c r="D561" s="11" t="n"/>
       <c r="E561" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F561" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+        </is>
+      </c>
+      <c r="F561" s="13" t="n"/>
       <c r="G561" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="H561" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I561" s="11" t="inlineStr">
@@ -72826,12 +72922,12 @@
       </c>
       <c r="J561" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K561" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="L561" s="11" t="inlineStr">
@@ -72841,12 +72937,12 @@
       </c>
       <c r="M561" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N561" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -72865,18 +72961,22 @@
       <c r="D562" s="7" t="n"/>
       <c r="E562" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
-        </is>
-      </c>
-      <c r="F562" s="9" t="n"/>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
+        </is>
+      </c>
+      <c r="F562" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G562" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H562" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I562" s="7" t="inlineStr">
@@ -72891,7 +72991,7 @@
       </c>
       <c r="K562" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="L562" s="7" t="inlineStr">
@@ -72901,12 +73001,12 @@
       </c>
       <c r="M562" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N562" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -72925,18 +73025,22 @@
       <c r="D563" s="11" t="n"/>
       <c r="E563" s="13" t="inlineStr">
         <is>
-          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
-        </is>
-      </c>
-      <c r="F563" s="13" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F563" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G563" s="13" t="inlineStr">
         <is>
-          <t>ezhunaonline.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H563" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I563" s="11" t="inlineStr">
@@ -72946,10 +73050,14 @@
       </c>
       <c r="J563" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K563" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K563" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L563" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72957,12 +73065,12 @@
       </c>
       <c r="M563" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N563" s="14" t="inlineStr">
         <is>
-          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -72981,13 +73089,13 @@
       <c r="D564" s="7" t="n"/>
       <c r="E564" s="9" t="inlineStr">
         <is>
-          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="F564" s="9" t="n"/>
       <c r="G564" s="9" t="inlineStr">
         <is>
-          <t>ta.wikipedia.org</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="H564" s="7" t="inlineStr">
@@ -73007,7 +73115,7 @@
       </c>
       <c r="K564" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L564" s="7" t="inlineStr">
@@ -73017,12 +73125,12 @@
       </c>
       <c r="M564" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N564" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -73041,13 +73149,13 @@
       <c r="D565" s="11" t="n"/>
       <c r="E565" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
+          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
         </is>
       </c>
       <c r="F565" s="13" t="n"/>
       <c r="G565" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>ezhunaonline.com</t>
         </is>
       </c>
       <c r="H565" s="11" t="inlineStr">
@@ -73062,14 +73170,10 @@
       </c>
       <c r="J565" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K565" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; பிராமி</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K565" s="13" t="n"/>
       <c r="L565" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73077,12 +73181,12 @@
       </c>
       <c r="M565" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N565" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
         </is>
       </c>
     </row>
@@ -73101,13 +73205,13 @@
       <c r="D566" s="7" t="n"/>
       <c r="E566" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
         </is>
       </c>
       <c r="F566" s="9" t="n"/>
       <c r="G566" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>ta.wikipedia.org</t>
         </is>
       </c>
       <c r="H566" s="7" t="inlineStr">
@@ -73122,10 +73226,14 @@
       </c>
       <c r="J566" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K566" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K566" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+        </is>
+      </c>
       <c r="L566" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73133,12 +73241,12 @@
       </c>
       <c r="M566" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="N566" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -73157,13 +73265,13 @@
       <c r="D567" s="11" t="n"/>
       <c r="E567" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="F567" s="13" t="n"/>
       <c r="G567" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H567" s="11" t="inlineStr">
@@ -73176,8 +73284,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J567" s="13" t="n"/>
-      <c r="K567" s="13" t="n"/>
+      <c r="J567" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K567" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
       <c r="L567" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73185,12 +73301,12 @@
       </c>
       <c r="M567" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N567" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -73209,13 +73325,13 @@
       <c r="D568" s="7" t="n"/>
       <c r="E568" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="F568" s="9" t="n"/>
       <c r="G568" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H568" s="7" t="inlineStr">
@@ -73233,11 +73349,7 @@
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="K568" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="K568" s="9" t="n"/>
       <c r="L568" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73245,12 +73357,12 @@
       </c>
       <c r="M568" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
       <c r="N568" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
         </is>
       </c>
     </row>
@@ -73269,13 +73381,13 @@
       <c r="D569" s="11" t="n"/>
       <c r="E569" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
         </is>
       </c>
       <c r="F569" s="13" t="n"/>
       <c r="G569" s="13" t="inlineStr">
         <is>
-          <t>shritharan.com</t>
+          <t>treasurehouseofjaffna.com</t>
         </is>
       </c>
       <c r="H569" s="11" t="inlineStr">
@@ -73288,16 +73400,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J569" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K569" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="J569" s="13" t="n"/>
+      <c r="K569" s="13" t="n"/>
       <c r="L569" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73310,7 +73414,7 @@
       </c>
       <c r="N569" s="14" t="inlineStr">
         <is>
-          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
         </is>
       </c>
     </row>
@@ -73329,53 +73433,173 @@
       <c r="D570" s="7" t="n"/>
       <c r="E570" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
         </is>
       </c>
       <c r="F570" s="9" t="n"/>
       <c r="G570" s="9" t="inlineStr">
         <is>
+          <t>jvpnews.com</t>
+        </is>
+      </c>
+      <c r="H570" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I570" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J570" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K570" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="L570" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M570" s="9" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N570" s="10" t="inlineStr">
+        <is>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0570</t>
+        </is>
+      </c>
+      <c r="B571" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C571" s="12" t="n"/>
+      <c r="D571" s="11" t="n"/>
+      <c r="E571" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+        </is>
+      </c>
+      <c r="F571" s="13" t="n"/>
+      <c r="G571" s="13" t="inlineStr">
+        <is>
           <t>shritharan.com</t>
         </is>
       </c>
-      <c r="H570" s="7" t="inlineStr">
+      <c r="H571" s="11" t="inlineStr">
         <is>
           <t>Web page</t>
         </is>
       </c>
-      <c r="I570" s="7" t="inlineStr">
+      <c r="I571" s="11" t="inlineStr">
         <is>
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J570" s="9" t="inlineStr">
+      <c r="J571" s="13" t="inlineStr">
         <is>
           <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
-      <c r="K570" s="9" t="inlineStr">
+      <c r="K571" s="13" t="inlineStr">
         <is>
           <t>தொல்லியல்</t>
         </is>
       </c>
-      <c r="L570" s="7" t="inlineStr">
+      <c r="L571" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M570" s="9" t="inlineStr">
+      <c r="M571" s="13" t="inlineStr">
+        <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N571" s="14" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0571</t>
+        </is>
+      </c>
+      <c r="B572" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C572" s="8" t="n"/>
+      <c r="D572" s="7" t="n"/>
+      <c r="E572" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+        </is>
+      </c>
+      <c r="F572" s="9" t="n"/>
+      <c r="G572" s="9" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="H572" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I572" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J572" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K572" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="L572" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M572" s="9" t="inlineStr">
         <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
-      <c r="N570" s="10" t="inlineStr">
+      <c r="N572" s="10" t="inlineStr">
         <is>
           <t>https://shritharan.com/jaffna-anaikotta-archaeological-exhibition-begins/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N570"/>
+  <autoFilter ref="A1:N572"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -73946,6 +74170,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N568" r:id="rId567"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N569" r:id="rId568"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N572" r:id="rId571"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Papers'!$A$1:$M$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspaper Articles'!$A$1:$M$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Magazines &amp; Journals'!$A$1:$M$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$572</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$573</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-26. Counts below are live formulas over the 'All Records' sheet.</t>
+          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-27. Counts below are live formulas over the 'All Records' sheet.</t>
         </is>
       </c>
     </row>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$572,A6)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$573,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$572,A6,'All Records'!$L$2:$L$572,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$573,A6,'All Records'!$L$2:$L$573,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$572,A7)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$573,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$572,A7,'All Records'!$L$2:$L$572,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$573,A7,'All Records'!$L$2:$L$573,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$572,A8)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$573,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$572,A8,'All Records'!$L$2:$L$572,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$573,A8,'All Records'!$L$2:$L$573,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$572,A9)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$573,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$572,A9,'All Records'!$L$2:$L$572,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$573,A9,'All Records'!$L$2:$L$573,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$572,A10)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$573,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$572,A10,'All Records'!$L$2:$L$572,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$573,A10,'All Records'!$L$2:$L$573,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$573,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$573,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$573,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$573,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$573,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$572,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$573,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -787,23 +787,23 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="G23" s="4">
@@ -818,23 +818,23 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="G24" s="4">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="G25" s="4">
@@ -880,23 +880,23 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="G26" s="4">
@@ -911,23 +911,23 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="G27" s="4">
@@ -942,23 +942,23 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$572="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$572,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$573="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$573,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="G28" s="4">
@@ -26336,7 +26336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32282,13 +32282,13 @@
       <c r="C99" s="11" t="n"/>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+          <t>Archaeology - Department of History</t>
         </is>
       </c>
       <c r="E99" s="13" t="n"/>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>his.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -32303,12 +32303,12 @@
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="J99" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr">
@@ -32318,12 +32318,12 @@
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-27 (ddg); review.</t>
         </is>
       </c>
       <c r="M99" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
+          <t>https://www.his.jfn.ac.lk/index.php/students/field-report/archaeology/</t>
         </is>
       </c>
     </row>
@@ -32337,22 +32337,18 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Brahmi script</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="n"/>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -32362,12 +32358,12 @@
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K100" s="7" t="inlineStr">
@@ -32377,12 +32373,12 @@
       </c>
       <c r="L100" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
+          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
         </is>
       </c>
     </row>
@@ -32396,7 +32392,7 @@
       <c r="C101" s="11" t="n"/>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Buddhism amongst Tamils in Sri Lanka</t>
+          <t>Brahmi script</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
@@ -32419,8 +32415,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I101" s="13" t="n"/>
-      <c r="J101" s="13" t="n"/>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J101" s="13" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32428,12 +32432,12 @@
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M101" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
         </is>
       </c>
     </row>
@@ -32447,18 +32451,22 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Buddhist Remains in the Jaffna Peninsula</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="n"/>
+          <t>Buddhism amongst Tamils in Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -32466,25 +32474,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J102" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; Jaffna</t>
-        </is>
-      </c>
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="n"/>
       <c r="K102" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L102" s="9" t="n"/>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna/</t>
+          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -32498,7 +32502,7 @@
       <c r="C103" s="11" t="n"/>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+          <t>Buddhist Remains in the Jaffna Peninsula</t>
         </is>
       </c>
       <c r="E103" s="13" t="n"/>
@@ -32524,7 +32528,7 @@
       </c>
       <c r="J103" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Pungudutivu</t>
+          <t>தொல்லியல்; Jaffna</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr">
@@ -32535,7 +32539,7 @@
       <c r="L103" s="13" t="n"/>
       <c r="M103" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/tikali/</t>
+          <t>https://amazinglanka.com/wp/jaffna/</t>
         </is>
       </c>
     </row>
@@ -32549,22 +32553,18 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Cankilian Thoppu</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="n"/>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -32572,21 +32572,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I104" s="9" t="n"/>
-      <c r="J104" s="9" t="n"/>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Pungudutivu</t>
+        </is>
+      </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L104" s="9" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="L104" s="9" t="n"/>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
+          <t>https://amazinglanka.com/wp/tikali/</t>
         </is>
       </c>
     </row>
@@ -32600,18 +32604,22 @@
       <c r="C105" s="11" t="n"/>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>Coins DB| Home - archaeology.gov.lk</t>
-        </is>
-      </c>
-      <c r="E105" s="13" t="n"/>
+          <t>Cankilian Thoppu</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -32619,16 +32627,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J105" s="13" t="inlineStr">
-        <is>
-          <t>archaeology</t>
-        </is>
-      </c>
+      <c r="I105" s="13" t="n"/>
+      <c r="J105" s="13" t="n"/>
       <c r="K105" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32636,12 +32636,12 @@
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M105" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
+          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
         </is>
       </c>
     </row>
@@ -32655,13 +32655,13 @@
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
+          <t>Coins DB| Home - archaeology.gov.lk</t>
         </is>
       </c>
       <c r="E106" s="9" t="n"/>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>dainst.org</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -32674,8 +32674,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I106" s="9" t="n"/>
-      <c r="J106" s="9" t="n"/>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32683,12 +32691,12 @@
       </c>
       <c r="L106" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
-          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
+          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
         </is>
       </c>
     </row>
@@ -32702,13 +32710,13 @@
       <c r="C107" s="11" t="n"/>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>Epigraphy of Tamil Brahmi Script - தமிழ்-பிராமி - கல்வெட்டுகள்</t>
+          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
         </is>
       </c>
       <c r="E107" s="13" t="n"/>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>dainst.org</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -32718,19 +32726,11 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J107" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி; epigraphy; brahmi</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="n"/>
+      <c r="J107" s="13" t="n"/>
       <c r="K107" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32738,12 +32738,12 @@
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M107" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/397330115/Epigraphy-of-Tamil-Brahmi-Script-%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4-%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%AE%E0%AE%BF-%E0%AE%95%E0%AE%B2-%E0%AE%B5%E0%AF%86%E0%AE%9F-%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3</t>
+          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
         </is>
       </c>
     </row>
@@ -32757,13 +32757,13 @@
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Glimpses of the Eelam Tamil Heritage - நூலகம்</t>
+          <t>Epigraphy of Tamil Brahmi Script - தமிழ்-பிராமி - கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="E108" s="9" t="n"/>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -32778,10 +32778,14 @@
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J108" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி; epigraphy; brahmi</t>
+        </is>
+      </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32789,12 +32793,12 @@
       </c>
       <c r="L108" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Glimpses_of_the_Eelam_Tamil_Heritage</t>
+          <t>https://www.scribd.com/document/397330115/Epigraphy-of-Tamil-Brahmi-Script-%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4-%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%AE%E0%AE%BF-%E0%AE%95%E0%AE%B2-%E0%AE%B5%E0%AF%86%E0%AE%9F-%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3</t>
         </is>
       </c>
     </row>
@@ -32808,13 +32812,13 @@
       <c r="C109" s="11" t="n"/>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>Hero Stonebridge MS Welding Rod 6013 G12 - Stockpile</t>
+          <t>Glimpses of the Eelam Tamil Heritage - நூலகம்</t>
         </is>
       </c>
       <c r="E109" s="13" t="n"/>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>stockpile.lk</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -32824,19 +32828,15 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J109" s="13" t="inlineStr">
-        <is>
-          <t>hero stone</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J109" s="13" t="n"/>
       <c r="K109" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -32844,12 +32844,12 @@
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-26 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="M109" s="14" t="inlineStr">
         <is>
-          <t>https://stockpile.lk/welding-rod-6013-g12-kg.html</t>
+          <t>https://noolaham.org/wiki/index.php/Glimpses_of_the_Eelam_Tamil_Heritage</t>
         </is>
       </c>
     </row>
@@ -32863,13 +32863,13 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
+          <t>Hero Stonebridge MS Welding Rod 6013 G12 - Stockpile</t>
         </is>
       </c>
       <c r="E110" s="9" t="n"/>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>elanka.com.au</t>
+          <t>stockpile.lk</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -32899,12 +32899,12 @@
       </c>
       <c r="L110" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
+          <t>https://stockpile.lk/welding-rod-6013-g12-kg.html</t>
         </is>
       </c>
     </row>
@@ -32918,13 +32918,13 @@
       <c r="C111" s="11" t="n"/>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
+          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
         </is>
       </c>
       <c r="E111" s="13" t="n"/>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>searchworks.stanford.edu</t>
+          <t>elanka.com.au</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
@@ -32937,10 +32937,14 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I111" s="13" t="n"/>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
       <c r="J111" s="13" t="inlineStr">
         <is>
-          <t>hero-stone</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
@@ -32955,7 +32959,7 @@
       </c>
       <c r="M111" s="14" t="inlineStr">
         <is>
-          <t>https://searchworks.stanford.edu/view/14451040</t>
+          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
         </is>
       </c>
     </row>
@@ -32969,13 +32973,13 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
+          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
         </is>
       </c>
       <c r="E112" s="9" t="n"/>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>searchworks.stanford.edu</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -32988,14 +32992,10 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I112" s="9" t="n"/>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero-stone</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr">
@@ -33005,12 +33005,12 @@
       </c>
       <c r="L112" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
+          <t>https://searchworks.stanford.edu/view/14451040</t>
         </is>
       </c>
     </row>
@@ -33024,7 +33024,7 @@
       <c r="C113" s="11" t="n"/>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
+          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
         </is>
       </c>
       <c r="E113" s="13" t="n"/>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="M113" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/?lang=en</t>
+          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
         </is>
       </c>
     </row>
@@ -33079,13 +33079,13 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum</t>
+          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
         </is>
       </c>
       <c r="E114" s="9" t="n"/>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>lonelyplanet.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -33100,12 +33100,12 @@
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K114" s="7" t="inlineStr">
@@ -33115,12 +33115,12 @@
       </c>
       <c r="L114" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
+          <t>https://www.inscriptions.lk/?lang=en</t>
         </is>
       </c>
     </row>
@@ -33134,13 +33134,13 @@
       <c r="C115" s="11" t="n"/>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
+          <t>Jaffna Archaeological Museum</t>
         </is>
       </c>
       <c r="E115" s="13" t="n"/>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>tripadvisor.com</t>
+          <t>lonelyplanet.com</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
@@ -33170,12 +33170,12 @@
       </c>
       <c r="L115" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
       <c r="M115" s="14" t="inlineStr">
         <is>
-          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
+          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
         </is>
       </c>
     </row>
@@ -33189,13 +33189,13 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
+          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
         </is>
       </c>
       <c r="E116" s="9" t="n"/>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>jaffna.top</t>
+          <t>tripadvisor.com</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
         </is>
       </c>
     </row>
@@ -33244,13 +33244,13 @@
       <c r="C117" s="11" t="n"/>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
+          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
         </is>
       </c>
       <c r="E117" s="13" t="n"/>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>srilankatravelpages.com</t>
+          <t>jaffna.top</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M117" s="14" t="inlineStr">
         <is>
-          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
+          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
         </is>
       </c>
     </row>
@@ -33299,13 +33299,13 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
+          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
         </is>
       </c>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>srilankatourhelp.org</t>
+          <t>srilankatravelpages.com</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
@@ -33335,12 +33335,12 @@
       </c>
       <c r="L118" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
+          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
         </is>
       </c>
     </row>
@@ -33354,13 +33354,13 @@
       <c r="C119" s="11" t="n"/>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | About.lk</t>
+          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
         </is>
       </c>
       <c r="E119" s="13" t="n"/>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
+          <t>srilankatourhelp.org</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
@@ -33395,7 +33395,7 @@
       </c>
       <c r="M119" s="14" t="inlineStr">
         <is>
-          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
+          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
         </is>
       </c>
     </row>
@@ -33409,13 +33409,13 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum | About.lk</t>
         </is>
       </c>
       <c r="E120" s="9" t="n"/>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -33450,7 +33450,7 @@
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
+          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
         </is>
       </c>
     </row>
@@ -33464,13 +33464,13 @@
       <c r="C121" s="11" t="n"/>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
+          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
         </is>
       </c>
       <c r="E121" s="13" t="n"/>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>i-discoverasia.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr">
@@ -33490,7 +33490,7 @@
       </c>
       <c r="J121" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K121" s="11" t="inlineStr">
@@ -33500,12 +33500,12 @@
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M121" s="14" t="inlineStr">
         <is>
-          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
+          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
         </is>
       </c>
     </row>
@@ -33519,13 +33519,13 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archeology Tour - Journe Experiences</t>
+          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
         </is>
       </c>
       <c r="E122" s="9" t="n"/>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>journesrilanka.com</t>
+          <t>i-discoverasia.com</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -33538,8 +33538,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I122" s="9" t="n"/>
-      <c r="J122" s="9" t="n"/>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33547,12 +33555,12 @@
       </c>
       <c r="L122" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
+          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -33566,13 +33574,13 @@
       <c r="C123" s="11" t="n"/>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
+          <t>Jaffna Archeology Tour - Journe Experiences</t>
         </is>
       </c>
       <c r="E123" s="13" t="n"/>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>lanka-excursions-holidays.com</t>
+          <t>journesrilanka.com</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
@@ -33594,12 +33602,12 @@
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M123" s="14" t="inlineStr">
         <is>
-          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
+          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
         </is>
       </c>
     </row>
@@ -33613,13 +33621,13 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
         </is>
       </c>
       <c r="E124" s="9" t="n"/>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>lanka-excursions-holidays.com</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -33641,12 +33649,12 @@
       </c>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
         </is>
       </c>
     </row>
@@ -33660,13 +33668,13 @@
       <c r="C125" s="11" t="n"/>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="E125" s="13" t="n"/>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
@@ -33688,12 +33696,12 @@
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M125" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -33707,13 +33715,13 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="E126" s="9" t="n"/>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
@@ -33726,16 +33734,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J126" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="I126" s="9" t="n"/>
+      <c r="J126" s="9" t="n"/>
       <c r="K126" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33748,7 +33748,7 @@
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -33762,22 +33762,18 @@
       <c r="C127" s="11" t="n"/>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="E127" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="n"/>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
@@ -33787,12 +33783,12 @@
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J127" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K127" s="11" t="inlineStr">
@@ -33802,12 +33798,12 @@
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -33821,18 +33817,22 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -33847,7 +33847,7 @@
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K128" s="7" t="inlineStr">
@@ -33855,10 +33855,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L128" s="9" t="n"/>
+      <c r="L128" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -33872,18 +33876,18 @@
       <c r="C129" s="11" t="n"/>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>Museums - Archaeology</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="E129" s="13" t="n"/>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -33898,7 +33902,7 @@
       </c>
       <c r="J129" s="13" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="K129" s="11" t="inlineStr">
@@ -33906,14 +33910,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L129" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L129" s="13" t="n"/>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -33927,13 +33927,13 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Museums - Archaeology</t>
         </is>
       </c>
       <c r="E130" s="9" t="n"/>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -33953,7 +33953,7 @@
       </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="K130" s="7" t="inlineStr">
@@ -33963,12 +33963,12 @@
       </c>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
         </is>
       </c>
     </row>
@@ -33982,13 +33982,13 @@
       <c r="C131" s="11" t="n"/>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="E131" s="13" t="n"/>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -34003,10 +34003,14 @@
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J131" s="13" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J131" s="13" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K131" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34014,12 +34018,12 @@
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -34033,13 +34037,13 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="E132" s="9" t="n"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -34054,14 +34058,10 @@
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J132" s="9" t="inlineStr">
-        <is>
-          <t>inscription; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n"/>
       <c r="K132" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34069,12 +34069,12 @@
       </c>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -34088,13 +34088,13 @@
       <c r="C133" s="11" t="n"/>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="E133" s="13" t="n"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk:8080</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
@@ -34124,12 +34124,12 @@
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -34143,13 +34143,13 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
         </is>
       </c>
       <c r="E134" s="9" t="n"/>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk:8080</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
@@ -34164,10 +34164,14 @@
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J134" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>inscription; brahmi</t>
+        </is>
+      </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34175,12 +34179,12 @@
       </c>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
         </is>
       </c>
     </row>
@@ -34194,13 +34198,13 @@
       <c r="C135" s="11" t="n"/>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="E135" s="13" t="n"/>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
@@ -34215,14 +34219,10 @@
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J135" s="13" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J135" s="13" t="n"/>
       <c r="K135" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34230,12 +34230,12 @@
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -34249,7 +34249,7 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E136" s="9" t="n"/>
@@ -34275,7 +34275,7 @@
       </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -34304,13 +34304,13 @@
       <c r="C137" s="11" t="n"/>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E137" s="13" t="n"/>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr">
@@ -34325,12 +34325,12 @@
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J137" s="13" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="K137" s="11" t="inlineStr">
@@ -34340,12 +34340,12 @@
       </c>
       <c r="L137" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -34359,22 +34359,18 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="E138" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Sinhalese Hero Stone Analysis</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="n"/>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -34382,8 +34378,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I138" s="9" t="n"/>
-      <c r="J138" s="9" t="n"/>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>hero stone</t>
+        </is>
+      </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34391,12 +34395,12 @@
       </c>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -34410,18 +34414,22 @@
       <c r="C139" s="11" t="n"/>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>Sri Lanka Inscriptions</t>
-        </is>
-      </c>
-      <c r="E139" s="13" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -34429,16 +34437,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J139" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="I139" s="13" t="n"/>
+      <c r="J139" s="13" t="n"/>
       <c r="K139" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34446,12 +34446,12 @@
       </c>
       <c r="L139" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M139" s="14" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -34465,13 +34465,13 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="E140" s="9" t="n"/>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -34486,12 +34486,12 @@
       </c>
       <c r="I140" s="9" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K140" s="7" t="inlineStr">
@@ -34501,12 +34501,12 @@
       </c>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -34520,13 +34520,13 @@
       <c r="C141" s="11" t="n"/>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="E141" s="13" t="n"/>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
@@ -34556,12 +34556,12 @@
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M141" s="14" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -34575,13 +34575,13 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="E142" s="9" t="n"/>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
@@ -34596,10 +34596,14 @@
       </c>
       <c r="I142" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J142" s="9" t="n"/>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="K142" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34607,12 +34611,12 @@
       </c>
       <c r="L142" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -34626,13 +34630,13 @@
       <c r="C143" s="11" t="n"/>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>Tamil Identity in Vanni Monuments</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="E143" s="13" t="n"/>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
@@ -34647,7 +34651,7 @@
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Coins / நாணயம்</t>
         </is>
       </c>
       <c r="J143" s="13" t="n"/>
@@ -34658,12 +34662,12 @@
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M143" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/933772684/MC-13</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -34677,7 +34681,7 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Identity in Vanni Monuments</t>
         </is>
       </c>
       <c r="E144" s="9" t="n"/>
@@ -34698,14 +34702,10 @@
       </c>
       <c r="I144" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J144" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions; brahmi</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n"/>
       <c r="K144" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34713,12 +34713,12 @@
       </c>
       <c r="L144" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.scribd.com/document/933772684/MC-13</t>
         </is>
       </c>
     </row>
@@ -34732,13 +34732,13 @@
       <c r="C145" s="11" t="n"/>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="E145" s="13" t="n"/>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>en.bharatpedia.org</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
@@ -34753,12 +34753,12 @@
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J145" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K145" s="11" t="inlineStr">
@@ -34768,12 +34768,12 @@
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M145" s="14" t="inlineStr">
         <is>
-          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -34787,13 +34787,13 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="E146" s="9" t="n"/>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -34823,12 +34823,12 @@
       </c>
       <c r="L146" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -34842,13 +34842,13 @@
       <c r="C147" s="11" t="n"/>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="E147" s="13" t="n"/>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
@@ -34883,7 +34883,7 @@
       </c>
       <c r="M147" s="14" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -34897,13 +34897,13 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="E148" s="9" t="n"/>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
@@ -34923,7 +34923,7 @@
       </c>
       <c r="J148" s="9" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K148" s="7" t="inlineStr">
@@ -34933,12 +34933,12 @@
       </c>
       <c r="L148" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -34952,13 +34952,13 @@
       <c r="C149" s="11" t="n"/>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="E149" s="13" t="n"/>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr">
@@ -34971,8 +34971,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I149" s="13" t="n"/>
-      <c r="J149" s="13" t="n"/>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J149" s="13" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K149" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34980,12 +34988,12 @@
       </c>
       <c r="L149" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M149" s="14" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -34999,13 +35007,13 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="E150" s="9" t="n"/>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>cambridge.org</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
@@ -35027,12 +35035,12 @@
       </c>
       <c r="L150" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M150" s="10" t="inlineStr">
         <is>
-          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -35046,13 +35054,13 @@
       <c r="C151" s="11" t="n"/>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
         </is>
       </c>
       <c r="E151" s="13" t="n"/>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>cambridge.org</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr">
@@ -35065,16 +35073,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J151" s="13" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="I151" s="13" t="n"/>
+      <c r="J151" s="13" t="n"/>
       <c r="K151" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35082,12 +35082,12 @@
       </c>
       <c r="L151" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M151" s="14" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
         </is>
       </c>
     </row>
@@ -35101,13 +35101,13 @@
       <c r="C152" s="7" t="n"/>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
         </is>
       </c>
       <c r="E152" s="9" t="n"/>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
@@ -35137,12 +35137,12 @@
       </c>
       <c r="L152" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M152" s="10" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -35156,22 +35156,18 @@
       <c r="C153" s="11" t="n"/>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="E153" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+        </is>
+      </c>
+      <c r="E153" s="13" t="n"/>
       <c r="F153" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
@@ -35179,8 +35175,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I153" s="13" t="n"/>
-      <c r="J153" s="13" t="n"/>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J153" s="13" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K153" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35188,12 +35192,12 @@
       </c>
       <c r="L153" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M153" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -35207,18 +35211,22 @@
       <c r="C154" s="7" t="n"/>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -35226,25 +35234,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I154" s="9" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J154" s="9" t="inlineStr">
-        <is>
-          <t>memorial stone; Vanni</t>
-        </is>
-      </c>
+      <c r="I154" s="9" t="n"/>
+      <c r="J154" s="9" t="n"/>
       <c r="K154" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L154" s="9" t="n"/>
+      <c r="L154" s="9" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M154" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -35258,40 +35262,44 @@
       <c r="C155" s="11" t="n"/>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
         </is>
       </c>
       <c r="E155" s="13" t="n"/>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I155" s="13" t="n"/>
-      <c r="J155" s="13" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="J155" s="13" t="inlineStr">
+        <is>
+          <t>memorial stone; Vanni</t>
+        </is>
+      </c>
       <c r="K155" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L155" s="13" t="inlineStr">
-        <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L155" s="13" t="n"/>
       <c r="M155" s="14" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -35305,22 +35313,18 @@
       <c r="C156" s="7" t="n"/>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E156" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="n"/>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -35328,16 +35332,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I156" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J156" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I156" s="9" t="n"/>
+      <c r="J156" s="9" t="n"/>
       <c r="K156" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35345,12 +35341,12 @@
       </c>
       <c r="L156" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M156" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -35364,18 +35360,22 @@
       <c r="C157" s="11" t="n"/>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
-        </is>
-      </c>
-      <c r="E157" s="13" t="n"/>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -35385,12 +35385,12 @@
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J157" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K157" s="11" t="inlineStr">
@@ -35400,12 +35400,12 @@
       </c>
       <c r="L157" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M157" s="14" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -35419,13 +35419,13 @@
       <c r="C158" s="7" t="n"/>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
         </is>
       </c>
       <c r="E158" s="9" t="n"/>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
@@ -35440,12 +35440,12 @@
       </c>
       <c r="I158" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="K158" s="7" t="inlineStr">
@@ -35455,12 +35455,12 @@
       </c>
       <c r="L158" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M158" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -35474,22 +35474,18 @@
       <c r="C159" s="11" t="n"/>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="E159" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="n"/>
       <c r="F159" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
@@ -35497,8 +35493,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I159" s="13" t="n"/>
-      <c r="J159" s="13" t="n"/>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J159" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
       <c r="K159" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35506,12 +35510,12 @@
       </c>
       <c r="L159" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M159" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -35525,18 +35529,22 @@
       <c r="C160" s="7" t="n"/>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
-        </is>
-      </c>
-      <c r="E160" s="9" t="n"/>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
@@ -35544,16 +35552,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I160" s="9" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J160" s="9" t="inlineStr">
-        <is>
-          <t>நடுகல்</t>
-        </is>
-      </c>
+      <c r="I160" s="9" t="n"/>
+      <c r="J160" s="9" t="n"/>
       <c r="K160" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35561,12 +35561,12 @@
       </c>
       <c r="L160" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M160" s="10" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -35580,22 +35580,18 @@
       <c r="C161" s="11" t="n"/>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
-        </is>
-      </c>
-      <c r="E161" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="n"/>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
@@ -35605,12 +35601,12 @@
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J161" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="K161" s="11" t="inlineStr">
@@ -35620,12 +35616,12 @@
       </c>
       <c r="L161" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M161" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -35639,7 +35635,7 @@
       <c r="C162" s="7" t="n"/>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
@@ -35669,7 +35665,7 @@
       </c>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="K162" s="7" t="inlineStr">
@@ -35684,7 +35680,7 @@
       </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -35698,18 +35694,22 @@
       <c r="C163" s="11" t="n"/>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
-        </is>
-      </c>
-      <c r="E163" s="13" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E163" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
@@ -35734,12 +35734,12 @@
       </c>
       <c r="L163" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M163" s="14" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -35753,13 +35753,13 @@
       <c r="C164" s="7" t="n"/>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="E164" s="9" t="n"/>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>ezhunaonline.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
@@ -35774,10 +35774,14 @@
       </c>
       <c r="I164" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J164" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K164" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35785,12 +35789,12 @@
       </c>
       <c r="L164" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M164" s="10" t="inlineStr">
         <is>
-          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -35804,13 +35808,13 @@
       <c r="C165" s="11" t="n"/>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
+          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
         </is>
       </c>
       <c r="E165" s="13" t="n"/>
       <c r="F165" s="13" t="inlineStr">
         <is>
-          <t>ta.wikipedia.org</t>
+          <t>ezhunaonline.com</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr">
@@ -35825,14 +35829,10 @@
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J165" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J165" s="13" t="n"/>
       <c r="K165" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35840,12 +35840,12 @@
       </c>
       <c r="L165" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M165" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
         </is>
       </c>
     </row>
@@ -35859,13 +35859,13 @@
       <c r="C166" s="7" t="n"/>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
+          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
         </is>
       </c>
       <c r="E166" s="9" t="n"/>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>ta.wikipedia.org</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
@@ -35880,12 +35880,12 @@
       </c>
       <c r="I166" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J166" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="K166" s="7" t="inlineStr">
@@ -35895,12 +35895,12 @@
       </c>
       <c r="L166" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="M166" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -35914,13 +35914,13 @@
       <c r="C167" s="11" t="n"/>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="E167" s="13" t="n"/>
       <c r="F167" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr">
@@ -35935,10 +35935,14 @@
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J167" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J167" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
       <c r="K167" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35946,12 +35950,12 @@
       </c>
       <c r="L167" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M167" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -35965,13 +35969,13 @@
       <c r="C168" s="7" t="n"/>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="E168" s="9" t="n"/>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
@@ -35984,7 +35988,11 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I168" s="9" t="n"/>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
       <c r="J168" s="9" t="n"/>
       <c r="K168" s="7" t="inlineStr">
         <is>
@@ -35998,7 +36006,7 @@
       </c>
       <c r="M168" s="10" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
         </is>
       </c>
     </row>
@@ -36012,13 +36020,13 @@
       <c r="C169" s="11" t="n"/>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
         </is>
       </c>
       <c r="E169" s="13" t="n"/>
       <c r="F169" s="13" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>treasurehouseofjaffna.com</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr">
@@ -36031,16 +36039,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J169" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="I169" s="13" t="n"/>
+      <c r="J169" s="13" t="n"/>
       <c r="K169" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -36048,12 +36048,12 @@
       </c>
       <c r="L169" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
       <c r="M169" s="14" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
         </is>
       </c>
     </row>
@@ -36067,13 +36067,13 @@
       <c r="C170" s="7" t="n"/>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
         </is>
       </c>
       <c r="E170" s="9" t="n"/>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>shritharan.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
@@ -36103,12 +36103,12 @@
       </c>
       <c r="L170" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M170" s="10" t="inlineStr">
         <is>
-          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
         </is>
       </c>
     </row>
@@ -36122,7 +36122,7 @@
       <c r="C171" s="11" t="n"/>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
         </is>
       </c>
       <c r="E171" s="13" t="n"/>
@@ -36158,17 +36158,72 @@
       </c>
       <c r="L171" s="13" t="inlineStr">
         <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M171" s="14" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>WB-0171</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="n"/>
+      <c r="C172" s="7" t="n"/>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+        </is>
+      </c>
+      <c r="E172" s="9" t="n"/>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K172" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L172" s="9" t="inlineStr">
+        <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
-      <c r="M171" s="14" t="inlineStr">
+      <c r="M172" s="10" t="inlineStr">
         <is>
           <t>https://shritharan.com/jaffna-anaikotta-archaeological-exhibition-begins/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M171"/>
+  <autoFilter ref="A1:M172"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -36340,6 +36395,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId171"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36351,7 +36407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N572"/>
+  <dimension ref="A1:N573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -69353,13 +69409,13 @@
       <c r="D500" s="7" t="n"/>
       <c r="E500" s="9" t="inlineStr">
         <is>
-          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+          <t>Archaeology - Department of History</t>
         </is>
       </c>
       <c r="F500" s="9" t="n"/>
       <c r="G500" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>his.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H500" s="7" t="inlineStr">
@@ -69374,12 +69430,12 @@
       </c>
       <c r="J500" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Archaeology / தொல்லியல்</t>
         </is>
       </c>
       <c r="K500" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions; brahmi</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="L500" s="7" t="inlineStr">
@@ -69389,12 +69445,12 @@
       </c>
       <c r="M500" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-27 (ddg); review.</t>
         </is>
       </c>
       <c r="N500" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
+          <t>https://www.his.jfn.ac.lk/index.php/students/field-report/archaeology/</t>
         </is>
       </c>
     </row>
@@ -69413,22 +69469,18 @@
       <c r="D501" s="11" t="n"/>
       <c r="E501" s="13" t="inlineStr">
         <is>
-          <t>Brahmi script</t>
-        </is>
-      </c>
-      <c r="F501" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Brahmi alphabet Inscriptions of Sri Lanka</t>
+        </is>
+      </c>
+      <c r="F501" s="13" t="n"/>
       <c r="G501" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H501" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I501" s="11" t="inlineStr">
@@ -69438,12 +69490,12 @@
       </c>
       <c r="J501" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K501" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L501" s="11" t="inlineStr">
@@ -69453,12 +69505,12 @@
       </c>
       <c r="M501" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N501" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
+          <t>https://www.inscriptions.lk/brahmi-alphabet/?lang=en</t>
         </is>
       </c>
     </row>
@@ -69477,7 +69529,7 @@
       <c r="D502" s="7" t="n"/>
       <c r="E502" s="9" t="inlineStr">
         <is>
-          <t>Buddhism amongst Tamils in Sri Lanka</t>
+          <t>Brahmi script</t>
         </is>
       </c>
       <c r="F502" s="9" t="inlineStr">
@@ -69500,8 +69552,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J502" s="9" t="n"/>
-      <c r="K502" s="9" t="n"/>
+      <c r="J502" s="9" t="inlineStr">
+        <is>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K502" s="9" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="L502" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69509,12 +69569,12 @@
       </c>
       <c r="M502" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-15 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N502" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
+          <t>https://en.wikipedia.org/wiki/Brahmi_script</t>
         </is>
       </c>
     </row>
@@ -69533,18 +69593,22 @@
       <c r="D503" s="11" t="n"/>
       <c r="E503" s="13" t="inlineStr">
         <is>
-          <t>Buddhist Remains in the Jaffna Peninsula</t>
-        </is>
-      </c>
-      <c r="F503" s="13" t="n"/>
+          <t>Buddhism amongst Tamils in Sri Lanka</t>
+        </is>
+      </c>
+      <c r="F503" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G503" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H503" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I503" s="11" t="inlineStr">
@@ -69552,25 +69616,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J503" s="13" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K503" s="13" t="inlineStr">
-        <is>
-          <t>தொல்லியல்; Jaffna</t>
-        </is>
-      </c>
+      <c r="J503" s="13" t="n"/>
+      <c r="K503" s="13" t="n"/>
       <c r="L503" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M503" s="13" t="n"/>
+      <c r="M503" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N503" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna/</t>
+          <t>https://en.wikipedia.org/wiki/Buddhism_amongst_Tamils_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -69589,7 +69649,7 @@
       <c r="D504" s="7" t="n"/>
       <c r="E504" s="9" t="inlineStr">
         <is>
-          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+          <t>Buddhist Remains in the Jaffna Peninsula</t>
         </is>
       </c>
       <c r="F504" s="9" t="n"/>
@@ -69615,7 +69675,7 @@
       </c>
       <c r="K504" s="9" t="inlineStr">
         <is>
-          <t>தொல்லியல்; Pungudutivu</t>
+          <t>தொல்லியல்; Jaffna</t>
         </is>
       </c>
       <c r="L504" s="7" t="inlineStr">
@@ -69626,7 +69686,7 @@
       <c r="M504" s="9" t="n"/>
       <c r="N504" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/tikali/</t>
+          <t>https://amazinglanka.com/wp/jaffna/</t>
         </is>
       </c>
     </row>
@@ -69645,22 +69705,18 @@
       <c r="D505" s="11" t="n"/>
       <c r="E505" s="13" t="inlineStr">
         <is>
-          <t>Cankilian Thoppu</t>
-        </is>
-      </c>
-      <c r="F505" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Buddhist Ruins at Tikali in Pungudutivu Island in Jaffna</t>
+        </is>
+      </c>
+      <c r="F505" s="13" t="n"/>
       <c r="G505" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H505" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I505" s="11" t="inlineStr">
@@ -69668,21 +69724,25 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J505" s="13" t="n"/>
-      <c r="K505" s="13" t="n"/>
+      <c r="J505" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K505" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்; Pungudutivu</t>
+        </is>
+      </c>
       <c r="L505" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M505" s="13" t="inlineStr">
-        <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
-        </is>
-      </c>
+      <c r="M505" s="13" t="n"/>
       <c r="N505" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
+          <t>https://amazinglanka.com/wp/tikali/</t>
         </is>
       </c>
     </row>
@@ -69701,18 +69761,22 @@
       <c r="D506" s="7" t="n"/>
       <c r="E506" s="9" t="inlineStr">
         <is>
-          <t>Coins DB| Home - archaeology.gov.lk</t>
-        </is>
-      </c>
-      <c r="F506" s="9" t="n"/>
+          <t>Cankilian Thoppu</t>
+        </is>
+      </c>
+      <c r="F506" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G506" s="9" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H506" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I506" s="7" t="inlineStr">
@@ -69720,16 +69784,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J506" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K506" s="9" t="inlineStr">
-        <is>
-          <t>archaeology</t>
-        </is>
-      </c>
+      <c r="J506" s="9" t="n"/>
+      <c r="K506" s="9" t="n"/>
       <c r="L506" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69737,12 +69793,12 @@
       </c>
       <c r="M506" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N506" s="10" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
+          <t>https://en.wikipedia.org/wiki/Cankilian_Thoppu</t>
         </is>
       </c>
     </row>
@@ -69761,13 +69817,13 @@
       <c r="D507" s="11" t="n"/>
       <c r="E507" s="13" t="inlineStr">
         <is>
-          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
+          <t>Coins DB| Home - archaeology.gov.lk</t>
         </is>
       </c>
       <c r="F507" s="13" t="n"/>
       <c r="G507" s="13" t="inlineStr">
         <is>
-          <t>dainst.org</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H507" s="11" t="inlineStr">
@@ -69780,8 +69836,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J507" s="13" t="n"/>
-      <c r="K507" s="13" t="n"/>
+      <c r="J507" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்; Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K507" s="13" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="L507" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69789,12 +69853,12 @@
       </c>
       <c r="M507" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N507" s="14" t="inlineStr">
         <is>
-          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
+          <t>https://archaeology.gov.lk/coins/query/adsearch.php?lang=en</t>
         </is>
       </c>
     </row>
@@ -69813,13 +69877,13 @@
       <c r="D508" s="7" t="n"/>
       <c r="E508" s="9" t="inlineStr">
         <is>
-          <t>Epigraphy of Tamil Brahmi Script - தமிழ்-பிராமி - கல்வெட்டுகள்</t>
+          <t>DAI - «Exploring Ancient Kantarodai»: season 2026</t>
         </is>
       </c>
       <c r="F508" s="9" t="n"/>
       <c r="G508" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>dainst.org</t>
         </is>
       </c>
       <c r="H508" s="7" t="inlineStr">
@@ -69829,19 +69893,11 @@
       </c>
       <c r="I508" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J508" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K508" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி; epigraphy; brahmi</t>
-        </is>
-      </c>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J508" s="9" t="n"/>
+      <c r="K508" s="9" t="n"/>
       <c r="L508" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69849,12 +69905,12 @@
       </c>
       <c r="M508" s="9" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N508" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/397330115/Epigraphy-of-Tamil-Brahmi-Script-%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4-%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%AE%E0%AE%BF-%E0%AE%95%E0%AE%B2-%E0%AE%B5%E0%AF%86%E0%AE%9F-%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3</t>
+          <t>https://www.dainst.org/en/newsroom/exploring-ancient-kantarodai-season-2026/918</t>
         </is>
       </c>
     </row>
@@ -69873,13 +69929,13 @@
       <c r="D509" s="11" t="n"/>
       <c r="E509" s="13" t="inlineStr">
         <is>
-          <t>Glimpses of the Eelam Tamil Heritage - நூலகம்</t>
+          <t>Epigraphy of Tamil Brahmi Script - தமிழ்-பிராமி - கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="F509" s="13" t="n"/>
       <c r="G509" s="13" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H509" s="11" t="inlineStr">
@@ -69894,10 +69950,14 @@
       </c>
       <c r="J509" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K509" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K509" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி; epigraphy; brahmi</t>
+        </is>
+      </c>
       <c r="L509" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69905,12 +69965,12 @@
       </c>
       <c r="M509" s="13" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="N509" s="14" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Glimpses_of_the_Eelam_Tamil_Heritage</t>
+          <t>https://www.scribd.com/document/397330115/Epigraphy-of-Tamil-Brahmi-Script-%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4-%E0%AE%AA%E0%AE%BF%E0%AE%B0%E0%AE%BE%E0%AE%AE%E0%AE%BF-%E0%AE%95%E0%AE%B2-%E0%AE%B5%E0%AF%86%E0%AE%9F-%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3</t>
         </is>
       </c>
     </row>
@@ -69929,13 +69989,13 @@
       <c r="D510" s="7" t="n"/>
       <c r="E510" s="9" t="inlineStr">
         <is>
-          <t>Hero Stonebridge MS Welding Rod 6013 G12 - Stockpile</t>
+          <t>Glimpses of the Eelam Tamil Heritage - நூலகம்</t>
         </is>
       </c>
       <c r="F510" s="9" t="n"/>
       <c r="G510" s="9" t="inlineStr">
         <is>
-          <t>stockpile.lk</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H510" s="7" t="inlineStr">
@@ -69945,19 +70005,15 @@
       </c>
       <c r="I510" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="J510" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K510" s="9" t="inlineStr">
-        <is>
-          <t>hero stone</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K510" s="9" t="n"/>
       <c r="L510" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -69965,12 +70021,12 @@
       </c>
       <c r="M510" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-26 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="N510" s="10" t="inlineStr">
         <is>
-          <t>https://stockpile.lk/welding-rod-6013-g12-kg.html</t>
+          <t>https://noolaham.org/wiki/index.php/Glimpses_of_the_Eelam_Tamil_Heritage</t>
         </is>
       </c>
     </row>
@@ -69989,13 +70045,13 @@
       <c r="D511" s="11" t="n"/>
       <c r="E511" s="13" t="inlineStr">
         <is>
-          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
+          <t>Hero Stonebridge MS Welding Rod 6013 G12 - Stockpile</t>
         </is>
       </c>
       <c r="F511" s="13" t="n"/>
       <c r="G511" s="13" t="inlineStr">
         <is>
-          <t>elanka.com.au</t>
+          <t>stockpile.lk</t>
         </is>
       </c>
       <c r="H511" s="11" t="inlineStr">
@@ -70025,12 +70081,12 @@
       </c>
       <c r="M511" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="N511" s="14" t="inlineStr">
         <is>
-          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
+          <t>https://stockpile.lk/welding-rod-6013-g12-kg.html</t>
         </is>
       </c>
     </row>
@@ -70049,13 +70105,13 @@
       <c r="D512" s="7" t="n"/>
       <c r="E512" s="9" t="inlineStr">
         <is>
-          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
+          <t>Hero Stones in Sri Lanka's Past-by Ama H.Vanniarachchy</t>
         </is>
       </c>
       <c r="F512" s="9" t="n"/>
       <c r="G512" s="9" t="inlineStr">
         <is>
-          <t>searchworks.stanford.edu</t>
+          <t>elanka.com.au</t>
         </is>
       </c>
       <c r="H512" s="7" t="inlineStr">
@@ -70068,10 +70124,14 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J512" s="9" t="n"/>
+      <c r="J512" s="9" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
       <c r="K512" s="9" t="inlineStr">
         <is>
-          <t>hero-stone</t>
+          <t>hero stone</t>
         </is>
       </c>
       <c r="L512" s="7" t="inlineStr">
@@ -70086,7 +70146,7 @@
       </c>
       <c r="N512" s="10" t="inlineStr">
         <is>
-          <t>https://searchworks.stanford.edu/view/14451040</t>
+          <t>https://www.elanka.com.au/hero-stones-in-sri-lankas-past-by-ama-h-vanniarachchy/</t>
         </is>
       </c>
     </row>
@@ -70105,13 +70165,13 @@
       <c r="D513" s="11" t="n"/>
       <c r="E513" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
+          <t>Hero-stone at Anurādhapura and other essays - SearchWorks catalog</t>
         </is>
       </c>
       <c r="F513" s="13" t="n"/>
       <c r="G513" s="13" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>searchworks.stanford.edu</t>
         </is>
       </c>
       <c r="H513" s="11" t="inlineStr">
@@ -70124,14 +70184,10 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J513" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J513" s="13" t="n"/>
       <c r="K513" s="13" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>hero-stone</t>
         </is>
       </c>
       <c r="L513" s="11" t="inlineStr">
@@ -70141,12 +70197,12 @@
       </c>
       <c r="M513" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N513" s="14" t="inlineStr">
         <is>
-          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
+          <t>https://searchworks.stanford.edu/view/14451040</t>
         </is>
       </c>
     </row>
@@ -70165,7 +70221,7 @@
       <c r="D514" s="7" t="n"/>
       <c r="E514" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
+          <t>Inscriptions of Ceylon - Volume I Hiṭṭāragama-hīnna 1160 Sri Lanka ...</t>
         </is>
       </c>
       <c r="F514" s="9" t="n"/>
@@ -70206,7 +70262,7 @@
       </c>
       <c r="N514" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/?lang=en</t>
+          <t>https://inscriptions.lk/db/VInscriptionsView/1220?language=en-US</t>
         </is>
       </c>
     </row>
@@ -70225,13 +70281,13 @@
       <c r="D515" s="11" t="n"/>
       <c r="E515" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum</t>
+          <t>Inscriptions of Sri Lanka Online Database with Estampage</t>
         </is>
       </c>
       <c r="F515" s="13" t="n"/>
       <c r="G515" s="13" t="inlineStr">
         <is>
-          <t>lonelyplanet.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H515" s="11" t="inlineStr">
@@ -70246,12 +70302,12 @@
       </c>
       <c r="J515" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K515" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L515" s="11" t="inlineStr">
@@ -70261,12 +70317,12 @@
       </c>
       <c r="M515" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N515" s="14" t="inlineStr">
         <is>
-          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
+          <t>https://www.inscriptions.lk/?lang=en</t>
         </is>
       </c>
     </row>
@@ -70285,13 +70341,13 @@
       <c r="D516" s="7" t="n"/>
       <c r="E516" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
+          <t>Jaffna Archaeological Museum</t>
         </is>
       </c>
       <c r="F516" s="9" t="n"/>
       <c r="G516" s="9" t="inlineStr">
         <is>
-          <t>tripadvisor.com</t>
+          <t>lonelyplanet.com</t>
         </is>
       </c>
       <c r="H516" s="7" t="inlineStr">
@@ -70321,12 +70377,12 @@
       </c>
       <c r="M516" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
       <c r="N516" s="10" t="inlineStr">
         <is>
-          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
+          <t>https://www.lonelyplanet.com/points-of-interest/jaffna-archaeological-museum/1195363</t>
         </is>
       </c>
     </row>
@@ -70345,13 +70401,13 @@
       <c r="D517" s="11" t="n"/>
       <c r="E517" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
+          <t>Jaffna Archaeological Museum - All You SHOULD Know Before ... - Tripadvisor</t>
         </is>
       </c>
       <c r="F517" s="13" t="n"/>
       <c r="G517" s="13" t="inlineStr">
         <is>
-          <t>jaffna.top</t>
+          <t>tripadvisor.com</t>
         </is>
       </c>
       <c r="H517" s="11" t="inlineStr">
@@ -70386,7 +70442,7 @@
       </c>
       <c r="N517" s="14" t="inlineStr">
         <is>
-          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
+          <t>https://www.tripadvisor.com/Attraction_Review-g304135-d8865728-Reviews-Jaffna_Archaeological_Museum-Jaffna_Northern_Province.html</t>
         </is>
       </c>
     </row>
@@ -70405,13 +70461,13 @@
       <c r="D518" s="7" t="n"/>
       <c r="E518" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
+          <t>Jaffna Archaeological Museum - History &amp; Heritage of Jaffna</t>
         </is>
       </c>
       <c r="F518" s="9" t="n"/>
       <c r="G518" s="9" t="inlineStr">
         <is>
-          <t>srilankatravelpages.com</t>
+          <t>jaffna.top</t>
         </is>
       </c>
       <c r="H518" s="7" t="inlineStr">
@@ -70441,12 +70497,12 @@
       </c>
       <c r="M518" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N518" s="10" t="inlineStr">
         <is>
-          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
+          <t>https://jaffna.top/jaffna-archaeological-museum-nallur/</t>
         </is>
       </c>
     </row>
@@ -70465,13 +70521,13 @@
       <c r="D519" s="11" t="n"/>
       <c r="E519" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
+          <t>Jaffna Archaeological Museum - Sri Lanka Travel Pages</t>
         </is>
       </c>
       <c r="F519" s="13" t="n"/>
       <c r="G519" s="13" t="inlineStr">
         <is>
-          <t>srilankatourhelp.org</t>
+          <t>srilankatravelpages.com</t>
         </is>
       </c>
       <c r="H519" s="11" t="inlineStr">
@@ -70501,12 +70557,12 @@
       </c>
       <c r="M519" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N519" s="14" t="inlineStr">
         <is>
-          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
+          <t>https://srilankatravelpages.com/listing/jaffna-archaeological-museum/</t>
         </is>
       </c>
     </row>
@@ -70525,13 +70581,13 @@
       <c r="D520" s="7" t="n"/>
       <c r="E520" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | About.lk</t>
+          <t>Jaffna Archaeological Museum Travel Guide 2026 - Sri Lanka Tour Help</t>
         </is>
       </c>
       <c r="F520" s="9" t="n"/>
       <c r="G520" s="9" t="inlineStr">
         <is>
-          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
+          <t>srilankatourhelp.org</t>
         </is>
       </c>
       <c r="H520" s="7" t="inlineStr">
@@ -70566,7 +70622,7 @@
       </c>
       <c r="N520" s="10" t="inlineStr">
         <is>
-          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
+          <t>https://srilankatourhelp.org/articles/explore-rich-heritage-jaffna-archaeological-museum</t>
         </is>
       </c>
     </row>
@@ -70585,13 +70641,13 @@
       <c r="D521" s="11" t="n"/>
       <c r="E521" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
+          <t>Jaffna Archaeological Museum | About.lk</t>
         </is>
       </c>
       <c r="F521" s="13" t="n"/>
       <c r="G521" s="13" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>jaffna-archaeological-museum-sri-lanka.about.lk</t>
         </is>
       </c>
       <c r="H521" s="11" t="inlineStr">
@@ -70626,7 +70682,7 @@
       </c>
       <c r="N521" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
+          <t>https://jaffna-archaeological-museum-sri-lanka.about.lk/</t>
         </is>
       </c>
     </row>
@@ -70645,13 +70701,13 @@
       <c r="D522" s="7" t="n"/>
       <c r="E522" s="9" t="inlineStr">
         <is>
-          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
+          <t>Jaffna Archaeological Museum | AmazingLanka.com</t>
         </is>
       </c>
       <c r="F522" s="9" t="n"/>
       <c r="G522" s="9" t="inlineStr">
         <is>
-          <t>i-discoverasia.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H522" s="7" t="inlineStr">
@@ -70671,7 +70727,7 @@
       </c>
       <c r="K522" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L522" s="7" t="inlineStr">
@@ -70681,12 +70737,12 @@
       </c>
       <c r="M522" s="9" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N522" s="10" t="inlineStr">
         <is>
-          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
+          <t>https://amazinglanka.com/wp/jaffna-museum/</t>
         </is>
       </c>
     </row>
@@ -70705,13 +70761,13 @@
       <c r="D523" s="11" t="n"/>
       <c r="E523" s="13" t="inlineStr">
         <is>
-          <t>Jaffna Archeology Tour - Journe Experiences</t>
+          <t>Jaffna Archaeology Museum - iDiscover Maps</t>
         </is>
       </c>
       <c r="F523" s="13" t="n"/>
       <c r="G523" s="13" t="inlineStr">
         <is>
-          <t>journesrilanka.com</t>
+          <t>i-discoverasia.com</t>
         </is>
       </c>
       <c r="H523" s="11" t="inlineStr">
@@ -70724,8 +70780,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J523" s="13" t="n"/>
-      <c r="K523" s="13" t="n"/>
+      <c r="J523" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K523" s="13" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
       <c r="L523" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70733,12 +70797,12 @@
       </c>
       <c r="M523" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-22 (ddg); review.</t>
         </is>
       </c>
       <c r="N523" s="14" t="inlineStr">
         <is>
-          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
+          <t>https://i-discoverasia.com/walks/jaffna-university-city-walk-sri-lanka/locations/jaffna-archaeological-museum-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -70757,13 +70821,13 @@
       <c r="D524" s="7" t="n"/>
       <c r="E524" s="9" t="inlineStr">
         <is>
-          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
+          <t>Jaffna Archeology Tour - Journe Experiences</t>
         </is>
       </c>
       <c r="F524" s="9" t="n"/>
       <c r="G524" s="9" t="inlineStr">
         <is>
-          <t>lanka-excursions-holidays.com</t>
+          <t>journesrilanka.com</t>
         </is>
       </c>
       <c r="H524" s="7" t="inlineStr">
@@ -70785,12 +70849,12 @@
       </c>
       <c r="M524" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N524" s="10" t="inlineStr">
         <is>
-          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
+          <t>https://journesrilanka.com/trips/jaffna-archeology-tour/</t>
         </is>
       </c>
     </row>
@@ -70809,13 +70873,13 @@
       <c r="D525" s="11" t="n"/>
       <c r="E525" s="13" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
         </is>
       </c>
       <c r="F525" s="13" t="n"/>
       <c r="G525" s="13" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>lanka-excursions-holidays.com</t>
         </is>
       </c>
       <c r="H525" s="11" t="inlineStr">
@@ -70837,12 +70901,12 @@
       </c>
       <c r="M525" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N525" s="14" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
         </is>
       </c>
     </row>
@@ -70861,13 +70925,13 @@
       <c r="D526" s="7" t="n"/>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="F526" s="9" t="n"/>
       <c r="G526" s="9" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="H526" s="7" t="inlineStr">
@@ -70889,12 +70953,12 @@
       </c>
       <c r="M526" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N526" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -70913,13 +70977,13 @@
       <c r="D527" s="11" t="n"/>
       <c r="E527" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="F527" s="13" t="n"/>
       <c r="G527" s="13" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H527" s="11" t="inlineStr">
@@ -70932,16 +70996,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J527" s="13" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K527" s="13" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="J527" s="13" t="n"/>
+      <c r="K527" s="13" t="n"/>
       <c r="L527" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -70954,7 +71010,7 @@
       </c>
       <c r="N527" s="14" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -70973,22 +71029,18 @@
       <c r="D528" s="7" t="n"/>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="F528" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+        </is>
+      </c>
+      <c r="F528" s="9" t="n"/>
       <c r="G528" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="H528" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I528" s="7" t="inlineStr">
@@ -70998,12 +71050,12 @@
       </c>
       <c r="J528" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K528" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L528" s="7" t="inlineStr">
@@ -71013,12 +71065,12 @@
       </c>
       <c r="M528" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N528" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -71037,18 +71089,22 @@
       <c r="D529" s="11" t="n"/>
       <c r="E529" s="13" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="F529" s="13" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="F529" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G529" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H529" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I529" s="11" t="inlineStr">
@@ -71063,7 +71119,7 @@
       </c>
       <c r="K529" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L529" s="11" t="inlineStr">
@@ -71071,10 +71127,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M529" s="13" t="n"/>
+      <c r="M529" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N529" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -71093,18 +71153,18 @@
       <c r="D530" s="7" t="n"/>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>Museums - Archaeology</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="F530" s="9" t="n"/>
       <c r="G530" s="9" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H530" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I530" s="7" t="inlineStr">
@@ -71119,7 +71179,7 @@
       </c>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="L530" s="7" t="inlineStr">
@@ -71127,14 +71187,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M530" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M530" s="9" t="n"/>
       <c r="N530" s="10" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -71153,13 +71209,13 @@
       <c r="D531" s="11" t="n"/>
       <c r="E531" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Museums - Archaeology</t>
         </is>
       </c>
       <c r="F531" s="13" t="n"/>
       <c r="G531" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H531" s="11" t="inlineStr">
@@ -71179,7 +71235,7 @@
       </c>
       <c r="K531" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="L531" s="11" t="inlineStr">
@@ -71189,12 +71245,12 @@
       </c>
       <c r="M531" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N531" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
         </is>
       </c>
     </row>
@@ -71213,13 +71269,13 @@
       <c r="D532" s="7" t="n"/>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="F532" s="9" t="n"/>
       <c r="G532" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="H532" s="7" t="inlineStr">
@@ -71234,10 +71290,14 @@
       </c>
       <c r="J532" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K532" s="9" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K532" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L532" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71245,12 +71305,12 @@
       </c>
       <c r="M532" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N532" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -71269,13 +71329,13 @@
       <c r="D533" s="11" t="n"/>
       <c r="E533" s="13" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="F533" s="13" t="n"/>
       <c r="G533" s="13" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H533" s="11" t="inlineStr">
@@ -71290,14 +71350,10 @@
       </c>
       <c r="J533" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K533" s="13" t="inlineStr">
-        <is>
-          <t>inscription; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K533" s="13" t="n"/>
       <c r="L533" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71305,12 +71361,12 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N533" s="14" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -71329,13 +71385,13 @@
       <c r="D534" s="7" t="n"/>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="F534" s="9" t="n"/>
       <c r="G534" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk:8080</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="H534" s="7" t="inlineStr">
@@ -71365,12 +71421,12 @@
       </c>
       <c r="M534" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N534" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -71389,13 +71445,13 @@
       <c r="D535" s="11" t="n"/>
       <c r="E535" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
         </is>
       </c>
       <c r="F535" s="13" t="n"/>
       <c r="G535" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk:8080</t>
         </is>
       </c>
       <c r="H535" s="11" t="inlineStr">
@@ -71410,10 +71466,14 @@
       </c>
       <c r="J535" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K535" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K535" s="13" t="inlineStr">
+        <is>
+          <t>inscription; brahmi</t>
+        </is>
+      </c>
       <c r="L535" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71421,12 +71481,12 @@
       </c>
       <c r="M535" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N535" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
         </is>
       </c>
     </row>
@@ -71445,13 +71505,13 @@
       <c r="D536" s="7" t="n"/>
       <c r="E536" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="F536" s="9" t="n"/>
       <c r="G536" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="H536" s="7" t="inlineStr">
@@ -71466,14 +71526,10 @@
       </c>
       <c r="J536" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K536" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K536" s="9" t="n"/>
       <c r="L536" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71481,12 +71537,12 @@
       </c>
       <c r="M536" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N536" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -71505,7 +71561,7 @@
       <c r="D537" s="11" t="n"/>
       <c r="E537" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F537" s="13" t="n"/>
@@ -71531,7 +71587,7 @@
       </c>
       <c r="K537" s="13" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L537" s="11" t="inlineStr">
@@ -71546,7 +71602,7 @@
       </c>
       <c r="N537" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -71565,13 +71621,13 @@
       <c r="D538" s="7" t="n"/>
       <c r="E538" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F538" s="9" t="n"/>
       <c r="G538" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H538" s="7" t="inlineStr">
@@ -71586,12 +71642,12 @@
       </c>
       <c r="J538" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K538" s="9" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="L538" s="7" t="inlineStr">
@@ -71601,12 +71657,12 @@
       </c>
       <c r="M538" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N538" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -71625,22 +71681,18 @@
       <c r="D539" s="11" t="n"/>
       <c r="E539" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="F539" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Sinhalese Hero Stone Analysis</t>
+        </is>
+      </c>
+      <c r="F539" s="13" t="n"/>
       <c r="G539" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H539" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I539" s="11" t="inlineStr">
@@ -71648,8 +71700,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J539" s="13" t="n"/>
-      <c r="K539" s="13" t="n"/>
+      <c r="J539" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="K539" s="13" t="inlineStr">
+        <is>
+          <t>hero stone</t>
+        </is>
+      </c>
       <c r="L539" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71657,12 +71717,12 @@
       </c>
       <c r="M539" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N539" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -71681,18 +71741,22 @@
       <c r="D540" s="7" t="n"/>
       <c r="E540" s="9" t="inlineStr">
         <is>
-          <t>Sri Lanka Inscriptions</t>
-        </is>
-      </c>
-      <c r="F540" s="9" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="F540" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G540" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H540" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I540" s="7" t="inlineStr">
@@ -71700,16 +71764,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J540" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K540" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="J540" s="9" t="n"/>
+      <c r="K540" s="9" t="n"/>
       <c r="L540" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71717,12 +71773,12 @@
       </c>
       <c r="M540" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N540" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -71741,13 +71797,13 @@
       <c r="D541" s="11" t="n"/>
       <c r="E541" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="F541" s="13" t="n"/>
       <c r="G541" s="13" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H541" s="11" t="inlineStr">
@@ -71762,12 +71818,12 @@
       </c>
       <c r="J541" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K541" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L541" s="11" t="inlineStr">
@@ -71777,12 +71833,12 @@
       </c>
       <c r="M541" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N541" s="14" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -71801,13 +71857,13 @@
       <c r="D542" s="7" t="n"/>
       <c r="E542" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="F542" s="9" t="n"/>
       <c r="G542" s="9" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="H542" s="7" t="inlineStr">
@@ -71837,12 +71893,12 @@
       </c>
       <c r="M542" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N542" s="10" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -71861,13 +71917,13 @@
       <c r="D543" s="11" t="n"/>
       <c r="E543" s="13" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="F543" s="13" t="n"/>
       <c r="G543" s="13" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="H543" s="11" t="inlineStr">
@@ -71882,10 +71938,14 @@
       </c>
       <c r="J543" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K543" s="13" t="n"/>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K543" s="13" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="L543" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71893,12 +71953,12 @@
       </c>
       <c r="M543" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N543" s="14" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -71917,13 +71977,13 @@
       <c r="D544" s="7" t="n"/>
       <c r="E544" s="9" t="inlineStr">
         <is>
-          <t>Tamil Identity in Vanni Monuments</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="F544" s="9" t="n"/>
       <c r="G544" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="H544" s="7" t="inlineStr">
@@ -71938,7 +71998,7 @@
       </c>
       <c r="J544" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Coins / நாணயம்</t>
         </is>
       </c>
       <c r="K544" s="9" t="n"/>
@@ -71949,12 +72009,12 @@
       </c>
       <c r="M544" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N544" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/933772684/MC-13</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -71973,7 +72033,7 @@
       <c r="D545" s="11" t="n"/>
       <c r="E545" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Identity in Vanni Monuments</t>
         </is>
       </c>
       <c r="F545" s="13" t="n"/>
@@ -71994,14 +72054,10 @@
       </c>
       <c r="J545" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K545" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions; brahmi</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K545" s="13" t="n"/>
       <c r="L545" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72009,12 +72065,12 @@
       </c>
       <c r="M545" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="N545" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.scribd.com/document/933772684/MC-13</t>
         </is>
       </c>
     </row>
@@ -72033,13 +72089,13 @@
       <c r="D546" s="7" t="n"/>
       <c r="E546" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="F546" s="9" t="n"/>
       <c r="G546" s="9" t="inlineStr">
         <is>
-          <t>en.bharatpedia.org</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H546" s="7" t="inlineStr">
@@ -72054,12 +72110,12 @@
       </c>
       <c r="J546" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K546" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L546" s="7" t="inlineStr">
@@ -72069,12 +72125,12 @@
       </c>
       <c r="M546" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N546" s="10" t="inlineStr">
         <is>
-          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -72093,13 +72149,13 @@
       <c r="D547" s="11" t="n"/>
       <c r="E547" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="F547" s="13" t="n"/>
       <c r="G547" s="13" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="H547" s="11" t="inlineStr">
@@ -72129,12 +72185,12 @@
       </c>
       <c r="M547" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N547" s="14" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -72153,13 +72209,13 @@
       <c r="D548" s="7" t="n"/>
       <c r="E548" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="F548" s="9" t="n"/>
       <c r="G548" s="9" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="H548" s="7" t="inlineStr">
@@ -72194,7 +72250,7 @@
       </c>
       <c r="N548" s="10" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -72213,13 +72269,13 @@
       <c r="D549" s="11" t="n"/>
       <c r="E549" s="13" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="F549" s="13" t="n"/>
       <c r="G549" s="13" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="H549" s="11" t="inlineStr">
@@ -72239,7 +72295,7 @@
       </c>
       <c r="K549" s="13" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L549" s="11" t="inlineStr">
@@ -72249,12 +72305,12 @@
       </c>
       <c r="M549" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N549" s="14" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -72273,13 +72329,13 @@
       <c r="D550" s="7" t="n"/>
       <c r="E550" s="9" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="F550" s="9" t="n"/>
       <c r="G550" s="9" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="H550" s="7" t="inlineStr">
@@ -72292,8 +72348,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J550" s="9" t="n"/>
-      <c r="K550" s="9" t="n"/>
+      <c r="J550" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K550" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L550" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72301,12 +72365,12 @@
       </c>
       <c r="M550" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N550" s="10" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -72325,13 +72389,13 @@
       <c r="D551" s="11" t="n"/>
       <c r="E551" s="13" t="inlineStr">
         <is>
-          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="F551" s="13" t="n"/>
       <c r="G551" s="13" t="inlineStr">
         <is>
-          <t>cambridge.org</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="H551" s="11" t="inlineStr">
@@ -72353,12 +72417,12 @@
       </c>
       <c r="M551" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N551" s="14" t="inlineStr">
         <is>
-          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -72377,13 +72441,13 @@
       <c r="D552" s="7" t="n"/>
       <c r="E552" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
         </is>
       </c>
       <c r="F552" s="9" t="n"/>
       <c r="G552" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>cambridge.org</t>
         </is>
       </c>
       <c r="H552" s="7" t="inlineStr">
@@ -72396,16 +72460,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J552" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K552" s="9" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="J552" s="9" t="n"/>
+      <c r="K552" s="9" t="n"/>
       <c r="L552" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72413,12 +72469,12 @@
       </c>
       <c r="M552" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N552" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
         </is>
       </c>
     </row>
@@ -72437,13 +72493,13 @@
       <c r="D553" s="11" t="n"/>
       <c r="E553" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
         </is>
       </c>
       <c r="F553" s="13" t="n"/>
       <c r="G553" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="H553" s="11" t="inlineStr">
@@ -72473,12 +72529,12 @@
       </c>
       <c r="M553" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N553" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -72497,22 +72553,18 @@
       <c r="D554" s="7" t="n"/>
       <c r="E554" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="F554" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+        </is>
+      </c>
+      <c r="F554" s="9" t="n"/>
       <c r="G554" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H554" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I554" s="7" t="inlineStr">
@@ -72520,8 +72572,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J554" s="9" t="n"/>
-      <c r="K554" s="9" t="n"/>
+      <c r="J554" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K554" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L554" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72529,12 +72589,12 @@
       </c>
       <c r="M554" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N554" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -72553,18 +72613,22 @@
       <c r="D555" s="11" t="n"/>
       <c r="E555" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
-        </is>
-      </c>
-      <c r="F555" s="13" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="F555" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G555" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H555" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I555" s="11" t="inlineStr">
@@ -72572,25 +72636,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J555" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K555" s="13" t="inlineStr">
-        <is>
-          <t>memorial stone; Vanni</t>
-        </is>
-      </c>
+      <c r="J555" s="13" t="n"/>
+      <c r="K555" s="13" t="n"/>
       <c r="L555" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M555" s="13" t="n"/>
+      <c r="M555" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N555" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -72609,40 +72669,44 @@
       <c r="D556" s="7" t="n"/>
       <c r="E556" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
         </is>
       </c>
       <c r="F556" s="9" t="n"/>
       <c r="G556" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H556" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I556" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J556" s="9" t="n"/>
-      <c r="K556" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J556" s="9" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="K556" s="9" t="inlineStr">
+        <is>
+          <t>memorial stone; Vanni</t>
+        </is>
+      </c>
       <c r="L556" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M556" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M556" s="9" t="n"/>
       <c r="N556" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -72661,22 +72725,18 @@
       <c r="D557" s="11" t="n"/>
       <c r="E557" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F557" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+        </is>
+      </c>
+      <c r="F557" s="13" t="n"/>
       <c r="G557" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H557" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I557" s="11" t="inlineStr">
@@ -72684,16 +72744,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J557" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K557" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J557" s="13" t="n"/>
+      <c r="K557" s="13" t="n"/>
       <c r="L557" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72701,12 +72753,12 @@
       </c>
       <c r="M557" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N557" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -72725,18 +72777,22 @@
       <c r="D558" s="7" t="n"/>
       <c r="E558" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
-        </is>
-      </c>
-      <c r="F558" s="9" t="n"/>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F558" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G558" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H558" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I558" s="7" t="inlineStr">
@@ -72746,12 +72802,12 @@
       </c>
       <c r="J558" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K558" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L558" s="7" t="inlineStr">
@@ -72761,12 +72817,12 @@
       </c>
       <c r="M558" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N558" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -72785,13 +72841,13 @@
       <c r="D559" s="11" t="n"/>
       <c r="E559" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
         </is>
       </c>
       <c r="F559" s="13" t="n"/>
       <c r="G559" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="H559" s="11" t="inlineStr">
@@ -72806,12 +72862,12 @@
       </c>
       <c r="J559" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K559" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="L559" s="11" t="inlineStr">
@@ -72821,12 +72877,12 @@
       </c>
       <c r="M559" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N559" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -72845,22 +72901,18 @@
       <c r="D560" s="7" t="n"/>
       <c r="E560" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="F560" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="F560" s="9" t="n"/>
       <c r="G560" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H560" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I560" s="7" t="inlineStr">
@@ -72868,8 +72920,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J560" s="9" t="n"/>
-      <c r="K560" s="9" t="n"/>
+      <c r="J560" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K560" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
       <c r="L560" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72877,12 +72937,12 @@
       </c>
       <c r="M560" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N560" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -72901,18 +72961,22 @@
       <c r="D561" s="11" t="n"/>
       <c r="E561" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
-        </is>
-      </c>
-      <c r="F561" s="13" t="n"/>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+        </is>
+      </c>
+      <c r="F561" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G561" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H561" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I561" s="11" t="inlineStr">
@@ -72920,16 +72984,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J561" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K561" s="13" t="inlineStr">
-        <is>
-          <t>நடுகல்</t>
-        </is>
-      </c>
+      <c r="J561" s="13" t="n"/>
+      <c r="K561" s="13" t="n"/>
       <c r="L561" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72937,12 +72993,12 @@
       </c>
       <c r="M561" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N561" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -72961,22 +73017,18 @@
       <c r="D562" s="7" t="n"/>
       <c r="E562" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
-        </is>
-      </c>
-      <c r="F562" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+        </is>
+      </c>
+      <c r="F562" s="9" t="n"/>
       <c r="G562" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="H562" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I562" s="7" t="inlineStr">
@@ -72986,12 +73038,12 @@
       </c>
       <c r="J562" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K562" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="L562" s="7" t="inlineStr">
@@ -73001,12 +73053,12 @@
       </c>
       <c r="M562" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N562" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -73025,7 +73077,7 @@
       <c r="D563" s="11" t="n"/>
       <c r="E563" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="F563" s="13" t="inlineStr">
@@ -73055,7 +73107,7 @@
       </c>
       <c r="K563" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="L563" s="11" t="inlineStr">
@@ -73070,7 +73122,7 @@
       </c>
       <c r="N563" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -73089,18 +73141,22 @@
       <c r="D564" s="7" t="n"/>
       <c r="E564" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
-        </is>
-      </c>
-      <c r="F564" s="9" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F564" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G564" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H564" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I564" s="7" t="inlineStr">
@@ -73125,12 +73181,12 @@
       </c>
       <c r="M564" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N564" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -73149,13 +73205,13 @@
       <c r="D565" s="11" t="n"/>
       <c r="E565" s="13" t="inlineStr">
         <is>
-          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="F565" s="13" t="n"/>
       <c r="G565" s="13" t="inlineStr">
         <is>
-          <t>ezhunaonline.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="H565" s="11" t="inlineStr">
@@ -73170,10 +73226,14 @@
       </c>
       <c r="J565" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K565" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K565" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L565" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73181,12 +73241,12 @@
       </c>
       <c r="M565" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N565" s="14" t="inlineStr">
         <is>
-          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -73205,13 +73265,13 @@
       <c r="D566" s="7" t="n"/>
       <c r="E566" s="9" t="inlineStr">
         <is>
-          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
+          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
         </is>
       </c>
       <c r="F566" s="9" t="n"/>
       <c r="G566" s="9" t="inlineStr">
         <is>
-          <t>ta.wikipedia.org</t>
+          <t>ezhunaonline.com</t>
         </is>
       </c>
       <c r="H566" s="7" t="inlineStr">
@@ -73226,14 +73286,10 @@
       </c>
       <c r="J566" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K566" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K566" s="9" t="n"/>
       <c r="L566" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73241,12 +73297,12 @@
       </c>
       <c r="M566" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N566" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
         </is>
       </c>
     </row>
@@ -73265,13 +73321,13 @@
       <c r="D567" s="11" t="n"/>
       <c r="E567" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
+          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
         </is>
       </c>
       <c r="F567" s="13" t="n"/>
       <c r="G567" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>ta.wikipedia.org</t>
         </is>
       </c>
       <c r="H567" s="11" t="inlineStr">
@@ -73286,12 +73342,12 @@
       </c>
       <c r="J567" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K567" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="L567" s="11" t="inlineStr">
@@ -73301,12 +73357,12 @@
       </c>
       <c r="M567" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="N567" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -73325,13 +73381,13 @@
       <c r="D568" s="7" t="n"/>
       <c r="E568" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="F568" s="9" t="n"/>
       <c r="G568" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H568" s="7" t="inlineStr">
@@ -73346,10 +73402,14 @@
       </c>
       <c r="J568" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K568" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K568" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
       <c r="L568" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73357,12 +73417,12 @@
       </c>
       <c r="M568" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N568" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -73381,13 +73441,13 @@
       <c r="D569" s="11" t="n"/>
       <c r="E569" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="F569" s="13" t="n"/>
       <c r="G569" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H569" s="11" t="inlineStr">
@@ -73400,7 +73460,11 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J569" s="13" t="n"/>
+      <c r="J569" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
       <c r="K569" s="13" t="n"/>
       <c r="L569" s="11" t="inlineStr">
         <is>
@@ -73414,7 +73478,7 @@
       </c>
       <c r="N569" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
         </is>
       </c>
     </row>
@@ -73433,13 +73497,13 @@
       <c r="D570" s="7" t="n"/>
       <c r="E570" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
         </is>
       </c>
       <c r="F570" s="9" t="n"/>
       <c r="G570" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>treasurehouseofjaffna.com</t>
         </is>
       </c>
       <c r="H570" s="7" t="inlineStr">
@@ -73452,16 +73516,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J570" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K570" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="J570" s="9" t="n"/>
+      <c r="K570" s="9" t="n"/>
       <c r="L570" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73469,12 +73525,12 @@
       </c>
       <c r="M570" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
       <c r="N570" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
         </is>
       </c>
     </row>
@@ -73493,13 +73549,13 @@
       <c r="D571" s="11" t="n"/>
       <c r="E571" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
         </is>
       </c>
       <c r="F571" s="13" t="n"/>
       <c r="G571" s="13" t="inlineStr">
         <is>
-          <t>shritharan.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="H571" s="11" t="inlineStr">
@@ -73529,12 +73585,12 @@
       </c>
       <c r="M571" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N571" s="14" t="inlineStr">
         <is>
-          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
         </is>
       </c>
     </row>
@@ -73553,7 +73609,7 @@
       <c r="D572" s="7" t="n"/>
       <c r="E572" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
         </is>
       </c>
       <c r="F572" s="9" t="n"/>
@@ -73589,17 +73645,77 @@
       </c>
       <c r="M572" s="9" t="inlineStr">
         <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N572" s="10" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0572</t>
+        </is>
+      </c>
+      <c r="B573" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C573" s="12" t="n"/>
+      <c r="D573" s="11" t="n"/>
+      <c r="E573" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+        </is>
+      </c>
+      <c r="F573" s="13" t="n"/>
+      <c r="G573" s="13" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="H573" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I573" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J573" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K573" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="L573" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M573" s="13" t="inlineStr">
+        <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
-      <c r="N572" s="10" t="inlineStr">
+      <c r="N573" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/jaffna-anaikotta-archaeological-exhibition-begins/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N572"/>
+  <autoFilter ref="A1:N573"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -74172,6 +74288,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N570" r:id="rId569"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N571" r:id="rId570"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N573" r:id="rId572"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-27. Counts below are live formulas over the 'All Records' sheet.</t>
+          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-28. Counts below are live formulas over the 'All Records' sheet.</t>
         </is>
       </c>
     </row>

--- a/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
+++ b/output/SriLanka_Tamil_Inscriptions_Bibliography.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Papers'!$A$1:$M$160</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspaper Articles'!$A$1:$M$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Magazines &amp; Journals'!$A$1:$M$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$172</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$574</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Web Articles'!$A$1:$M$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'All Records'!$A$1:$N$576</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-29. Counts below are live formulas over the 'All Records' sheet.</t>
+          <t>Books, research papers, newspaper and magazine articles, 1996-2026 (plus key earlier references). Compiled 2026-10-30. Counts below are live formulas over the 'All Records' sheet.</t>
         </is>
       </c>
     </row>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$574,A6)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$576,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$574,A6,'All Records'!$L$2:$L$574,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$576,A6,'All Records'!$L$2:$L$576,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$574,A7)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$576,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$574,A7,'All Records'!$L$2:$L$574,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$576,A7,'All Records'!$L$2:$L$576,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$574,A8)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$576,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$574,A8,'All Records'!$L$2:$L$574,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$576,A8,'All Records'!$L$2:$L$576,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$574,A9)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$576,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$574,A9,'All Records'!$L$2:$L$574,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$576,A9,'All Records'!$L$2:$L$576,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF('All Records'!$B$2:$B$574,A10)</f>
+        <f>COUNTIF('All Records'!$B$2:$B$576,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS('All Records'!$B$2:$B$574,A10,'All Records'!$L$2:$L$574,"Yes")</f>
+        <f>COUNTIFS('All Records'!$B$2:$B$576,A10,'All Records'!$L$2:$L$576,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$574,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$576,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$574,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$576,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$574,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$576,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$574,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$576,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$574,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$576,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('All Records'!$J$2:$J$574,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF('All Records'!$J$2:$J$576,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -787,23 +787,23 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2000))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=1996)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2000))</f>
         <v/>
       </c>
       <c r="G23" s="4">
@@ -818,23 +818,23 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="C24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="D24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2005))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2001)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2005))</f>
         <v/>
       </c>
       <c r="G24" s="4">
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="C25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="D25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2010))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2006)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2010))</f>
         <v/>
       </c>
       <c r="G25" s="4">
@@ -880,23 +880,23 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="C26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="D26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2015))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2011)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2015))</f>
         <v/>
       </c>
       <c r="G26" s="4">
@@ -911,23 +911,23 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="C27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="D27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2020))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2016)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2020))</f>
         <v/>
       </c>
       <c r="G27" s="4">
@@ -942,23 +942,23 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Books")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Research Papers")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Newspaper Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Magazines/Journals")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUMPRODUCT(('All Records'!$B$2:$B$574="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$574,4)),0)&lt;=2026))</f>
+        <f>SUMPRODUCT(('All Records'!$B$2:$B$576="Web Articles")*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&gt;=2021)*(IFERROR(VALUE(LEFT('All Records'!$C$2:$C$576,4)),0)&lt;=2026))</f>
         <v/>
       </c>
       <c r="G28" s="4">
@@ -26396,7 +26396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -33681,13 +33681,13 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
+          <t>Jaffna Peninsula - Durham University</t>
         </is>
       </c>
       <c r="E124" s="9" t="n"/>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>lanka-excursions-holidays.com</t>
+          <t>durham.ac.uk</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -33709,12 +33709,12 @@
       </c>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-30 (ddg); review.</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
+          <t>https://www.durham.ac.uk/departments/academic/archaeology/research/archaeology-research-projects/jaffna-peninsula/</t>
         </is>
       </c>
     </row>
@@ -33728,13 +33728,13 @@
       <c r="C125" s="11" t="n"/>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
         </is>
       </c>
       <c r="E125" s="13" t="n"/>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>lanka-excursions-holidays.com</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
@@ -33756,12 +33756,12 @@
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M125" s="14" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
         </is>
       </c>
     </row>
@@ -33775,13 +33775,13 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="E126" s="9" t="n"/>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
@@ -33803,12 +33803,12 @@
       </c>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -33822,13 +33822,13 @@
       <c r="C127" s="11" t="n"/>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="E127" s="13" t="n"/>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
@@ -33841,16 +33841,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J127" s="13" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="I127" s="13" t="n"/>
+      <c r="J127" s="13" t="n"/>
       <c r="K127" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33863,7 +33855,7 @@
       </c>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -33877,22 +33869,18 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="n"/>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -33902,12 +33890,12 @@
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K128" s="7" t="inlineStr">
@@ -33917,12 +33905,12 @@
       </c>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -33936,18 +33924,22 @@
       <c r="C129" s="11" t="n"/>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="E129" s="13" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -33962,7 +33954,7 @@
       </c>
       <c r="J129" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="K129" s="11" t="inlineStr">
@@ -33970,10 +33962,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L129" s="13" t="n"/>
+      <c r="L129" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -33987,18 +33983,18 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Museums - Archaeology</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="E130" s="9" t="n"/>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -34013,7 +34009,7 @@
       </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="K130" s="7" t="inlineStr">
@@ -34021,14 +34017,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L130" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L130" s="9" t="n"/>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -34042,13 +34034,13 @@
       <c r="C131" s="11" t="n"/>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Museums - Archaeology</t>
         </is>
       </c>
       <c r="E131" s="13" t="n"/>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -34068,7 +34060,7 @@
       </c>
       <c r="J131" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="K131" s="11" t="inlineStr">
@@ -34078,12 +34070,12 @@
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
         </is>
       </c>
     </row>
@@ -34097,13 +34089,13 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="E132" s="9" t="n"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -34118,10 +34110,14 @@
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J132" s="9" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34129,12 +34125,12 @@
       </c>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -34148,13 +34144,13 @@
       <c r="C133" s="11" t="n"/>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="E133" s="13" t="n"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
@@ -34169,14 +34165,10 @@
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J133" s="13" t="inlineStr">
-        <is>
-          <t>inscription; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J133" s="13" t="n"/>
       <c r="K133" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34184,12 +34176,12 @@
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -34203,13 +34195,13 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="E134" s="9" t="n"/>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk:8080</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
@@ -34239,12 +34231,12 @@
       </c>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -34258,13 +34250,13 @@
       <c r="C135" s="11" t="n"/>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
         </is>
       </c>
       <c r="E135" s="13" t="n"/>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk:8080</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
@@ -34279,10 +34271,14 @@
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J135" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J135" s="13" t="inlineStr">
+        <is>
+          <t>inscription; brahmi</t>
+        </is>
+      </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34290,12 +34286,12 @@
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
         </is>
       </c>
     </row>
@@ -34309,13 +34305,13 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="E136" s="9" t="n"/>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
@@ -34330,14 +34326,10 @@
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="J136" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n"/>
       <c r="K136" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34345,12 +34337,12 @@
       </c>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -34364,7 +34356,7 @@
       <c r="C137" s="11" t="n"/>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E137" s="13" t="n"/>
@@ -34390,7 +34382,7 @@
       </c>
       <c r="J137" s="13" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="K137" s="11" t="inlineStr">
@@ -34405,7 +34397,7 @@
       </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -34419,13 +34411,13 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="E138" s="9" t="n"/>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
@@ -34440,12 +34432,12 @@
       </c>
       <c r="I138" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="K138" s="7" t="inlineStr">
@@ -34455,12 +34447,12 @@
       </c>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -34474,22 +34466,18 @@
       <c r="C139" s="11" t="n"/>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="E139" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Sinhalese Hero Stone Analysis</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="n"/>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -34497,8 +34485,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I139" s="13" t="n"/>
-      <c r="J139" s="13" t="n"/>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="J139" s="13" t="inlineStr">
+        <is>
+          <t>hero stone</t>
+        </is>
+      </c>
       <c r="K139" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34506,12 +34502,12 @@
       </c>
       <c r="L139" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M139" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -34525,18 +34521,22 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Sri Lanka Inscriptions</t>
-        </is>
-      </c>
-      <c r="E140" s="9" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -34544,16 +34544,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I140" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J140" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="I140" s="9" t="n"/>
+      <c r="J140" s="9" t="n"/>
       <c r="K140" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34561,12 +34553,12 @@
       </c>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -34580,13 +34572,13 @@
       <c r="C141" s="11" t="n"/>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="E141" s="13" t="n"/>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
@@ -34601,12 +34593,12 @@
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J141" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K141" s="11" t="inlineStr">
@@ -34616,12 +34608,12 @@
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M141" s="14" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -34635,13 +34627,13 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="E142" s="9" t="n"/>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
@@ -34671,12 +34663,12 @@
       </c>
       <c r="L142" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -34690,13 +34682,13 @@
       <c r="C143" s="11" t="n"/>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="E143" s="13" t="n"/>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
@@ -34711,10 +34703,14 @@
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J143" s="13" t="n"/>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J143" s="13" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="K143" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34722,12 +34718,12 @@
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="M143" s="14" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -34741,13 +34737,13 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Tamil Identity in Vanni Monuments</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="E144" s="9" t="n"/>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
@@ -34762,7 +34758,7 @@
       </c>
       <c r="I144" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Coins / நாணயம்</t>
         </is>
       </c>
       <c r="J144" s="9" t="n"/>
@@ -34773,12 +34769,12 @@
       </c>
       <c r="L144" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/933772684/MC-13</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34788,7 @@
       <c r="C145" s="11" t="n"/>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Identity in Vanni Monuments</t>
         </is>
       </c>
       <c r="E145" s="13" t="n"/>
@@ -34813,14 +34809,10 @@
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="J145" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions; brahmi</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J145" s="13" t="n"/>
       <c r="K145" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -34828,12 +34820,12 @@
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="M145" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.scribd.com/document/933772684/MC-13</t>
         </is>
       </c>
     </row>
@@ -34847,13 +34839,13 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="E146" s="9" t="n"/>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>en.bharatpedia.org</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -34868,12 +34860,12 @@
       </c>
       <c r="I146" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="K146" s="7" t="inlineStr">
@@ -34883,12 +34875,12 @@
       </c>
       <c r="L146" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
-          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -34902,13 +34894,13 @@
       <c r="C147" s="11" t="n"/>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="E147" s="13" t="n"/>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
@@ -34938,12 +34930,12 @@
       </c>
       <c r="L147" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M147" s="14" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -34957,13 +34949,13 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="E148" s="9" t="n"/>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
@@ -34998,7 +34990,7 @@
       </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -35012,13 +35004,13 @@
       <c r="C149" s="11" t="n"/>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="E149" s="13" t="n"/>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr">
@@ -35038,7 +35030,7 @@
       </c>
       <c r="J149" s="13" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="K149" s="11" t="inlineStr">
@@ -35048,12 +35040,12 @@
       </c>
       <c r="L149" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M149" s="14" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -35067,13 +35059,13 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="E150" s="9" t="n"/>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
@@ -35086,8 +35078,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I150" s="9" t="n"/>
-      <c r="J150" s="9" t="n"/>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35095,12 +35095,12 @@
       </c>
       <c r="L150" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="M150" s="10" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -35114,13 +35114,13 @@
       <c r="C151" s="11" t="n"/>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="E151" s="13" t="n"/>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>cambridge.org</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr">
@@ -35142,12 +35142,12 @@
       </c>
       <c r="L151" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M151" s="14" t="inlineStr">
         <is>
-          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -35161,13 +35161,13 @@
       <c r="C152" s="7" t="n"/>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
         </is>
       </c>
       <c r="E152" s="9" t="n"/>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>cambridge.org</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
@@ -35180,16 +35180,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I152" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J152" s="9" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="I152" s="9" t="n"/>
+      <c r="J152" s="9" t="n"/>
       <c r="K152" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35197,12 +35189,12 @@
       </c>
       <c r="L152" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M152" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
         </is>
       </c>
     </row>
@@ -35216,13 +35208,13 @@
       <c r="C153" s="11" t="n"/>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
         </is>
       </c>
       <c r="E153" s="13" t="n"/>
       <c r="F153" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr">
@@ -35252,12 +35244,12 @@
       </c>
       <c r="L153" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M153" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -35271,22 +35263,18 @@
       <c r="C154" s="7" t="n"/>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="n"/>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -35294,8 +35282,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I154" s="9" t="n"/>
-      <c r="J154" s="9" t="n"/>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="K154" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35303,12 +35299,12 @@
       </c>
       <c r="L154" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M154" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -35322,18 +35318,22 @@
       <c r="C155" s="11" t="n"/>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
-        </is>
-      </c>
-      <c r="E155" s="13" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
@@ -35341,25 +35341,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J155" s="13" t="inlineStr">
-        <is>
-          <t>memorial stone; Vanni</t>
-        </is>
-      </c>
+      <c r="I155" s="13" t="n"/>
+      <c r="J155" s="13" t="n"/>
       <c r="K155" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L155" s="13" t="n"/>
+      <c r="L155" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="M155" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -35373,40 +35369,44 @@
       <c r="C156" s="7" t="n"/>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
         </is>
       </c>
       <c r="E156" s="9" t="n"/>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="I156" s="9" t="n"/>
-      <c r="J156" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>memorial stone; Vanni</t>
+        </is>
+      </c>
       <c r="K156" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L156" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="L156" s="9" t="n"/>
       <c r="M156" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -35420,22 +35420,18 @@
       <c r="C157" s="11" t="n"/>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="E157" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="n"/>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -35443,16 +35439,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J157" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="I157" s="13" t="n"/>
+      <c r="J157" s="13" t="n"/>
       <c r="K157" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35460,12 +35448,12 @@
       </c>
       <c r="L157" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M157" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -35479,18 +35467,22 @@
       <c r="C158" s="7" t="n"/>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
-        </is>
-      </c>
-      <c r="E158" s="9" t="n"/>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
@@ -35500,12 +35492,12 @@
       </c>
       <c r="I158" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="K158" s="7" t="inlineStr">
@@ -35515,12 +35507,12 @@
       </c>
       <c r="L158" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M158" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -35534,13 +35526,13 @@
       <c r="C159" s="11" t="n"/>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
         </is>
       </c>
       <c r="E159" s="13" t="n"/>
       <c r="F159" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr">
@@ -35555,12 +35547,12 @@
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="J159" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="K159" s="11" t="inlineStr">
@@ -35570,12 +35562,12 @@
       </c>
       <c r="L159" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M159" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -35589,22 +35581,18 @@
       <c r="C160" s="7" t="n"/>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="E160" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="n"/>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
@@ -35612,8 +35600,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I160" s="9" t="n"/>
-      <c r="J160" s="9" t="n"/>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
       <c r="K160" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35621,12 +35617,12 @@
       </c>
       <c r="L160" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M160" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -35640,18 +35636,22 @@
       <c r="C161" s="11" t="n"/>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
-        </is>
-      </c>
-      <c r="E161" s="13" t="n"/>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
@@ -35659,16 +35659,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I161" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="J161" s="13" t="inlineStr">
-        <is>
-          <t>நடுகல்</t>
-        </is>
-      </c>
+      <c r="I161" s="13" t="n"/>
+      <c r="J161" s="13" t="n"/>
       <c r="K161" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35676,12 +35668,12 @@
       </c>
       <c r="L161" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M161" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -35695,22 +35687,18 @@
       <c r="C162" s="7" t="n"/>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
-        </is>
-      </c>
-      <c r="E162" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="n"/>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -35720,12 +35708,12 @@
       </c>
       <c r="I162" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="K162" s="7" t="inlineStr">
@@ -35735,12 +35723,12 @@
       </c>
       <c r="L162" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -35754,7 +35742,7 @@
       <c r="C163" s="11" t="n"/>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
@@ -35784,7 +35772,7 @@
       </c>
       <c r="J163" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="K163" s="11" t="inlineStr">
@@ -35799,7 +35787,7 @@
       </c>
       <c r="M163" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -35813,18 +35801,22 @@
       <c r="C164" s="7" t="n"/>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
-        </is>
-      </c>
-      <c r="E164" s="9" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
@@ -35849,12 +35841,12 @@
       </c>
       <c r="L164" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="M164" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -35868,13 +35860,13 @@
       <c r="C165" s="11" t="n"/>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="E165" s="13" t="n"/>
       <c r="F165" s="13" t="inlineStr">
         <is>
-          <t>ezhunaonline.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr">
@@ -35889,10 +35881,14 @@
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="J165" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="J165" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="K165" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35900,12 +35896,12 @@
       </c>
       <c r="L165" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M165" s="14" t="inlineStr">
         <is>
-          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -35919,13 +35915,13 @@
       <c r="C166" s="7" t="n"/>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
+          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
         </is>
       </c>
       <c r="E166" s="9" t="n"/>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>ta.wikipedia.org</t>
+          <t>ezhunaonline.com</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
@@ -35940,14 +35936,10 @@
       </c>
       <c r="I166" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="J166" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n"/>
       <c r="K166" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -35955,12 +35947,12 @@
       </c>
       <c r="L166" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="M166" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
         </is>
       </c>
     </row>
@@ -35974,13 +35966,13 @@
       <c r="C167" s="11" t="n"/>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
+          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
         </is>
       </c>
       <c r="E167" s="13" t="n"/>
       <c r="F167" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>ta.wikipedia.org</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr">
@@ -35995,12 +35987,12 @@
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="J167" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="K167" s="11" t="inlineStr">
@@ -36010,12 +36002,12 @@
       </c>
       <c r="L167" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="M167" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -36029,13 +36021,13 @@
       <c r="C168" s="7" t="n"/>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="E168" s="9" t="n"/>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
@@ -36050,10 +36042,14 @@
       </c>
       <c r="I168" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J168" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
       <c r="K168" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -36061,12 +36057,12 @@
       </c>
       <c r="L168" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="M168" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -36080,13 +36076,13 @@
       <c r="C169" s="11" t="n"/>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="E169" s="13" t="n"/>
       <c r="F169" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr">
@@ -36099,7 +36095,11 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I169" s="13" t="n"/>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
       <c r="J169" s="13" t="n"/>
       <c r="K169" s="11" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
       </c>
       <c r="M169" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
         </is>
       </c>
     </row>
@@ -36127,13 +36127,13 @@
       <c r="C170" s="7" t="n"/>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
         </is>
       </c>
       <c r="E170" s="9" t="n"/>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>treasurehouseofjaffna.com</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
@@ -36146,16 +36146,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="I170" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="J170" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="I170" s="9" t="n"/>
+      <c r="J170" s="9" t="n"/>
       <c r="K170" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -36163,12 +36155,12 @@
       </c>
       <c r="L170" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
       <c r="M170" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
         </is>
       </c>
     </row>
@@ -36182,13 +36174,13 @@
       <c r="C171" s="11" t="n"/>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
         </is>
       </c>
       <c r="E171" s="13" t="n"/>
       <c r="F171" s="13" t="inlineStr">
         <is>
-          <t>shritharan.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr">
@@ -36218,12 +36210,12 @@
       </c>
       <c r="L171" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="M171" s="14" t="inlineStr">
         <is>
-          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
         </is>
       </c>
     </row>
@@ -36237,7 +36229,7 @@
       <c r="C172" s="7" t="n"/>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
         </is>
       </c>
       <c r="E172" s="9" t="n"/>
@@ -36273,17 +36265,119 @@
       </c>
       <c r="L172" s="9" t="inlineStr">
         <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M172" s="10" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>WB-0172</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="n"/>
+      <c r="C173" s="11" t="n"/>
+      <c r="D173" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+        </is>
+      </c>
+      <c r="E173" s="13" t="n"/>
+      <c r="F173" s="13" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H173" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="J173" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K173" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L173" s="13" t="inlineStr">
+        <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
-      <c r="M172" s="10" t="inlineStr">
+      <c r="M173" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/jaffna-anaikotta-archaeological-exhibition-begins/</t>
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>WB-0173</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="n"/>
+      <c r="C174" s="7" t="n"/>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>வன்னி (மரம்) - தமிழ் விக்கிப்பீடியா</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="n"/>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>ta.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I174" s="9" t="n"/>
+      <c r="J174" s="9" t="n"/>
+      <c r="K174" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L174" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-30 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="M174" s="10" t="inlineStr">
+        <is>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AE%A9%E0%AF%8D%E0%AE%A9%E0%AE%BF_(%E0%AE%AE%E0%AE%B0%E0%AE%AE%E0%AF%8D)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M172"/>
+  <autoFilter ref="A1:M174"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -36456,6 +36550,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId173"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36467,7 +36563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N574"/>
+  <dimension ref="A1:N576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -70997,13 +71093,13 @@
       <c r="D526" s="7" t="n"/>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
+          <t>Jaffna Peninsula - Durham University</t>
         </is>
       </c>
       <c r="F526" s="9" t="n"/>
       <c r="G526" s="9" t="inlineStr">
         <is>
-          <t>lanka-excursions-holidays.com</t>
+          <t>durham.ac.uk</t>
         </is>
       </c>
       <c r="H526" s="7" t="inlineStr">
@@ -71025,12 +71121,12 @@
       </c>
       <c r="M526" s="9" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-30 (ddg); review.</t>
         </is>
       </c>
       <c r="N526" s="10" t="inlineStr">
         <is>
-          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
+          <t>https://www.durham.ac.uk/departments/academic/archaeology/research/archaeology-research-projects/jaffna-peninsula/</t>
         </is>
       </c>
     </row>
@@ -71049,13 +71145,13 @@
       <c r="D527" s="11" t="n"/>
       <c r="E527" s="13" t="inlineStr">
         <is>
-          <t>Kantharodai in Jaffna - Atlas Obscura</t>
+          <t>Kandarodai alias Kadurugoda near Jaffna - LANKA EXCURSIONS HOLIDAYS</t>
         </is>
       </c>
       <c r="F527" s="13" t="n"/>
       <c r="G527" s="13" t="inlineStr">
         <is>
-          <t>atlasobscura.com</t>
+          <t>lanka-excursions-holidays.com</t>
         </is>
       </c>
       <c r="H527" s="11" t="inlineStr">
@@ -71077,12 +71173,12 @@
       </c>
       <c r="M527" s="13" t="inlineStr">
         <is>
-          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N527" s="14" t="inlineStr">
         <is>
-          <t>https://www.atlasobscura.com/places/kantharodai</t>
+          <t>https://www.lanka-excursions-holidays.com/kandarodai.html</t>
         </is>
       </c>
     </row>
@@ -71101,13 +71197,13 @@
       <c r="D528" s="7" t="n"/>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
+          <t>Kantharodai in Jaffna - Atlas Obscura</t>
         </is>
       </c>
       <c r="F528" s="9" t="n"/>
       <c r="G528" s="9" t="inlineStr">
         <is>
-          <t>amazinglanka.com</t>
+          <t>atlasobscura.com</t>
         </is>
       </c>
       <c r="H528" s="7" t="inlineStr">
@@ -71129,12 +71225,12 @@
       </c>
       <c r="M528" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Kantarodai archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N528" s="10" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/kurullangala/</t>
+          <t>https://www.atlasobscura.com/places/kantharodai</t>
         </is>
       </c>
     </row>
@@ -71153,13 +71249,13 @@
       <c r="D529" s="11" t="n"/>
       <c r="E529" s="13" t="inlineStr">
         <is>
-          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+          <t>Kurullangala Prehistoric Cave Art Site at ... - AmazingLanka.com</t>
         </is>
       </c>
       <c r="F529" s="13" t="n"/>
       <c r="G529" s="13" t="inlineStr">
         <is>
-          <t>asianartnewspaper.com</t>
+          <t>amazinglanka.com</t>
         </is>
       </c>
       <c r="H529" s="11" t="inlineStr">
@@ -71172,16 +71268,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J529" s="13" t="inlineStr">
-        <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K529" s="13" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+      <c r="J529" s="13" t="n"/>
+      <c r="K529" s="13" t="n"/>
       <c r="L529" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71194,7 +71282,7 @@
       </c>
       <c r="N529" s="14" t="inlineStr">
         <is>
-          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
+          <t>https://amazinglanka.com/wp/kurullangala/</t>
         </is>
       </c>
     </row>
@@ -71213,22 +71301,18 @@
       <c r="D530" s="7" t="n"/>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>List of Archaeological Protected Monuments in Jaffna District</t>
-        </is>
-      </c>
-      <c r="F530" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Kurullangala Rock Art: A Mystery - Asian Art Newspaper</t>
+        </is>
+      </c>
+      <c r="F530" s="9" t="n"/>
       <c r="G530" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>asianartnewspaper.com</t>
         </is>
       </c>
       <c r="H530" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I530" s="7" t="inlineStr">
@@ -71238,12 +71322,12 @@
       </c>
       <c r="J530" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L530" s="7" t="inlineStr">
@@ -71253,12 +71337,12 @@
       </c>
       <c r="M530" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N530" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
+          <t>https://asianartnewspaper.com/the-mysterious-rock-art-of-kurullangala/</t>
         </is>
       </c>
     </row>
@@ -71277,18 +71361,22 @@
       <c r="D531" s="11" t="n"/>
       <c r="E531" s="13" t="inlineStr">
         <is>
-          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
-        </is>
-      </c>
-      <c r="F531" s="13" t="n"/>
+          <t>List of Archaeological Protected Monuments in Jaffna District</t>
+        </is>
+      </c>
+      <c r="F531" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G531" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H531" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I531" s="11" t="inlineStr">
@@ -71303,7 +71391,7 @@
       </c>
       <c r="K531" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்; settlement</t>
+          <t>archaeological</t>
         </is>
       </c>
       <c r="L531" s="11" t="inlineStr">
@@ -71311,10 +71399,14 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M531" s="13" t="n"/>
+      <c r="M531" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N531" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_Archaeological_Protected_Monuments_in_Jaffna_District</t>
         </is>
       </c>
     </row>
@@ -71333,18 +71425,18 @@
       <c r="D532" s="7" t="n"/>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>Museums - Archaeology</t>
+          <t>Manniththalai Sand Bar Ancient Settlement and Archaeological Sites</t>
         </is>
       </c>
       <c r="F532" s="9" t="n"/>
       <c r="G532" s="9" t="inlineStr">
         <is>
-          <t>archaeology.gov.lk</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H532" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I532" s="7" t="inlineStr">
@@ -71359,7 +71451,7 @@
       </c>
       <c r="K532" s="9" t="inlineStr">
         <is>
-          <t>archaeology</t>
+          <t>தொல்லியல்; settlement</t>
         </is>
       </c>
       <c r="L532" s="7" t="inlineStr">
@@ -71367,14 +71459,10 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M532" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M532" s="9" t="n"/>
       <c r="N532" s="10" t="inlineStr">
         <is>
-          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
+          <t>https://amazinglanka.com/wp/manniththalai-settlements/</t>
         </is>
       </c>
     </row>
@@ -71393,13 +71481,13 @@
       <c r="D533" s="11" t="n"/>
       <c r="E533" s="13" t="inlineStr">
         <is>
-          <t>New Archaeological Evidence - Tamil Diplomat</t>
+          <t>Museums - Archaeology</t>
         </is>
       </c>
       <c r="F533" s="13" t="n"/>
       <c r="G533" s="13" t="inlineStr">
         <is>
-          <t>tamildiplomat.com</t>
+          <t>archaeology.gov.lk</t>
         </is>
       </c>
       <c r="H533" s="11" t="inlineStr">
@@ -71419,7 +71507,7 @@
       </c>
       <c r="K533" s="13" t="inlineStr">
         <is>
-          <t>archaeological</t>
+          <t>archaeology</t>
         </is>
       </c>
       <c r="L533" s="11" t="inlineStr">
@@ -71429,12 +71517,12 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N533" s="14" t="inlineStr">
         <is>
-          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
+          <t>https://archaeology.gov.lk/index.php/about/sections/museums</t>
         </is>
       </c>
     </row>
@@ -71453,13 +71541,13 @@
       <c r="D534" s="7" t="n"/>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
+          <t>New Archaeological Evidence - Tamil Diplomat</t>
         </is>
       </c>
       <c r="F534" s="9" t="n"/>
       <c r="G534" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>tamildiplomat.com</t>
         </is>
       </c>
       <c r="H534" s="7" t="inlineStr">
@@ -71474,10 +71562,14 @@
       </c>
       <c r="J534" s="9" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K534" s="9" t="n"/>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K534" s="9" t="inlineStr">
+        <is>
+          <t>archaeological</t>
+        </is>
+      </c>
       <c r="L534" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71485,12 +71577,12 @@
       </c>
       <c r="M534" s="9" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N534" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
+          <t>https://tamildiplomat.com/new-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -71509,13 +71601,13 @@
       <c r="D535" s="11" t="n"/>
       <c r="E535" s="13" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
+          <t>PDF Historical Significance of Recent Discovery of Tamils' Coins of the ...</t>
         </is>
       </c>
       <c r="F535" s="13" t="n"/>
       <c r="G535" s="13" t="inlineStr">
         <is>
-          <t>tamilwritersguild.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H535" s="11" t="inlineStr">
@@ -71530,14 +71622,10 @@
       </c>
       <c r="J535" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K535" s="13" t="inlineStr">
-        <is>
-          <t>inscription; brahmi</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K535" s="13" t="n"/>
       <c r="L535" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71545,12 +71633,12 @@
       </c>
       <c r="M535" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N535" s="14" t="inlineStr">
         <is>
-          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/bitstream/handle/123456789/9724/Historical%20Significance%20of%20Recent%20Discovery%20of%20Tamils%27%20Coins%20of%20the%20Period%20before%202000%20Years%20in%20Sri%20Lanka..pdf?sequence=1</t>
         </is>
       </c>
     </row>
@@ -71569,13 +71657,13 @@
       <c r="D536" s="7" t="n"/>
       <c r="E536" s="9" t="inlineStr">
         <is>
-          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago,</t>
         </is>
       </c>
       <c r="F536" s="9" t="n"/>
       <c r="G536" s="9" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk:8080</t>
+          <t>tamilwritersguild.com</t>
         </is>
       </c>
       <c r="H536" s="7" t="inlineStr">
@@ -71605,12 +71693,12 @@
       </c>
       <c r="M536" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N536" s="10" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
+          <t>https://tamilwritersguild.com/Tamil%20Brahmi%20Inscription%20Belonging%20to%2022_240119_110151.pdf</t>
         </is>
       </c>
     </row>
@@ -71629,13 +71717,13 @@
       <c r="D537" s="11" t="n"/>
       <c r="E537" s="13" t="inlineStr">
         <is>
-          <t>Pandya coinage - Wikipedia</t>
+          <t>PDF Tamil Brahmi Inscription Belonging to 2200 years ago, Discovered by ...</t>
         </is>
       </c>
       <c r="F537" s="13" t="n"/>
       <c r="G537" s="13" t="inlineStr">
         <is>
-          <t>en.wikipedia.org</t>
+          <t>repo.lib.jfn.ac.lk:8080</t>
         </is>
       </c>
       <c r="H537" s="11" t="inlineStr">
@@ -71650,10 +71738,14 @@
       </c>
       <c r="J537" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K537" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K537" s="13" t="inlineStr">
+        <is>
+          <t>inscription; brahmi</t>
+        </is>
+      </c>
       <c r="L537" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71661,12 +71753,12 @@
       </c>
       <c r="M537" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N537" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
+          <t>http://repo.lib.jfn.ac.lk:8080/ujrr/bitstream/123456789/865/2/JUICE2014-Tamil%20Brahmi%20Inscription%20Belonging%20to%202200%20years%20ago%2C.pdf</t>
         </is>
       </c>
     </row>
@@ -71685,13 +71777,13 @@
       <c r="D538" s="7" t="n"/>
       <c r="E538" s="9" t="inlineStr">
         <is>
-          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
+          <t>Pandya coinage - Wikipedia</t>
         </is>
       </c>
       <c r="F538" s="9" t="n"/>
       <c r="G538" s="9" t="inlineStr">
         <is>
-          <t>bradshawfoundation.com</t>
+          <t>en.wikipedia.org</t>
         </is>
       </c>
       <c r="H538" s="7" t="inlineStr">
@@ -71706,14 +71798,10 @@
       </c>
       <c r="J538" s="9" t="inlineStr">
         <is>
-          <t>Rock art / பாறை ஓவியம்</t>
-        </is>
-      </c>
-      <c r="K538" s="9" t="inlineStr">
-        <is>
-          <t>rock art</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K538" s="9" t="n"/>
       <c r="L538" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71721,12 +71809,12 @@
       </c>
       <c r="M538" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N538" s="10" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
+          <t>https://en.wikipedia.org/wiki/Pandya_coinage</t>
         </is>
       </c>
     </row>
@@ -71745,7 +71833,7 @@
       <c r="D539" s="11" t="n"/>
       <c r="E539" s="13" t="inlineStr">
         <is>
-          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
+          <t>Rock Art Gallery of Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F539" s="13" t="n"/>
@@ -71771,7 +71859,7 @@
       </c>
       <c r="K539" s="13" t="inlineStr">
         <is>
-          <t>rock painting</t>
+          <t>rock art</t>
         </is>
       </c>
       <c r="L539" s="11" t="inlineStr">
@@ -71786,7 +71874,7 @@
       </c>
       <c r="N539" s="14" t="inlineStr">
         <is>
-          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/gallery/index.php</t>
         </is>
       </c>
     </row>
@@ -71805,13 +71893,13 @@
       <c r="D540" s="7" t="n"/>
       <c r="E540" s="9" t="inlineStr">
         <is>
-          <t>Sinhalese Hero Stone Analysis</t>
+          <t>Rock Paintings and Engraving Sites in Sri Lanka - Bradshaw Foundation</t>
         </is>
       </c>
       <c r="F540" s="9" t="n"/>
       <c r="G540" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>bradshawfoundation.com</t>
         </is>
       </c>
       <c r="H540" s="7" t="inlineStr">
@@ -71826,12 +71914,12 @@
       </c>
       <c r="J540" s="9" t="inlineStr">
         <is>
-          <t>Hero stones / நடுகல்</t>
+          <t>Rock art / பாறை ஓவியம்</t>
         </is>
       </c>
       <c r="K540" s="9" t="inlineStr">
         <is>
-          <t>hero stone</t>
+          <t>rock painting</t>
         </is>
       </c>
       <c r="L540" s="7" t="inlineStr">
@@ -71841,12 +71929,12 @@
       </c>
       <c r="M540" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka rock art cave painting. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N540" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
+          <t>https://www.bradshawfoundation.com/sri_lanka/rock_paintings_engraving_sites/index.php</t>
         </is>
       </c>
     </row>
@@ -71865,22 +71953,18 @@
       <c r="D541" s="11" t="n"/>
       <c r="E541" s="13" t="inlineStr">
         <is>
-          <t>Sources of ancient Tamil history</t>
-        </is>
-      </c>
-      <c r="F541" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Sinhalese Hero Stone Analysis</t>
+        </is>
+      </c>
+      <c r="F541" s="13" t="n"/>
       <c r="G541" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H541" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I541" s="11" t="inlineStr">
@@ -71888,8 +71972,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J541" s="13" t="n"/>
-      <c r="K541" s="13" t="n"/>
+      <c r="J541" s="13" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="K541" s="13" t="inlineStr">
+        <is>
+          <t>hero stone</t>
+        </is>
+      </c>
       <c r="L541" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71897,12 +71989,12 @@
       </c>
       <c r="M541" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Sri Lanka hero stone. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N541" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
+          <t>https://www.scribd.com/document/459454071/srilanka-herostone-pdf</t>
         </is>
       </c>
     </row>
@@ -71921,18 +72013,22 @@
       <c r="D542" s="7" t="n"/>
       <c r="E542" s="9" t="inlineStr">
         <is>
-          <t>Sri Lanka Inscriptions</t>
-        </is>
-      </c>
-      <c r="F542" s="9" t="n"/>
+          <t>Sources of ancient Tamil history</t>
+        </is>
+      </c>
+      <c r="F542" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G542" s="9" t="inlineStr">
         <is>
-          <t>inscriptions.lk</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H542" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I542" s="7" t="inlineStr">
@@ -71940,16 +72036,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J542" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K542" s="9" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions</t>
-        </is>
-      </c>
+      <c r="J542" s="9" t="n"/>
+      <c r="K542" s="9" t="n"/>
       <c r="L542" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -71957,12 +72045,12 @@
       </c>
       <c r="M542" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N542" s="10" t="inlineStr">
         <is>
-          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
+          <t>https://en.wikipedia.org/wiki/Sources_of_ancient_Tamil_history</t>
         </is>
       </c>
     </row>
@@ -71981,13 +72069,13 @@
       <c r="D543" s="11" t="n"/>
       <c r="E543" s="13" t="inlineStr">
         <is>
-          <t>Tamil Brahmi - Aksharamukha</t>
+          <t>Sri Lanka Inscriptions</t>
         </is>
       </c>
       <c r="F543" s="13" t="n"/>
       <c r="G543" s="13" t="inlineStr">
         <is>
-          <t>aksharamukha.com</t>
+          <t>inscriptions.lk</t>
         </is>
       </c>
       <c r="H543" s="11" t="inlineStr">
@@ -72002,12 +72090,12 @@
       </c>
       <c r="J543" s="13" t="inlineStr">
         <is>
-          <t>Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K543" s="13" t="inlineStr">
         <is>
-          <t>brahmi</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L543" s="11" t="inlineStr">
@@ -72017,12 +72105,12 @@
       </c>
       <c r="M543" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N543" s="14" t="inlineStr">
         <is>
-          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
+          <t>https://www.inscriptions.lk/db/VInscriptionsView/116?language=en-US</t>
         </is>
       </c>
     </row>
@@ -72041,13 +72129,13 @@
       <c r="D544" s="7" t="n"/>
       <c r="E544" s="9" t="inlineStr">
         <is>
-          <t>Tamil Brahmi Research Papers - Academia.edu</t>
+          <t>Tamil Brahmi - Aksharamukha</t>
         </is>
       </c>
       <c r="F544" s="9" t="n"/>
       <c r="G544" s="9" t="inlineStr">
         <is>
-          <t>academia.edu</t>
+          <t>aksharamukha.com</t>
         </is>
       </c>
       <c r="H544" s="7" t="inlineStr">
@@ -72077,12 +72165,12 @@
       </c>
       <c r="M544" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N544" s="10" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
+          <t>https://www.aksharamukha.com/describe/TamilBrahmi</t>
         </is>
       </c>
     </row>
@@ -72101,13 +72189,13 @@
       <c r="D545" s="11" t="n"/>
       <c r="E545" s="13" t="inlineStr">
         <is>
-          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
+          <t>Tamil Brahmi Research Papers - Academia.edu</t>
         </is>
       </c>
       <c r="F545" s="13" t="n"/>
       <c r="G545" s="13" t="inlineStr">
         <is>
-          <t>sangam.org</t>
+          <t>academia.edu</t>
         </is>
       </c>
       <c r="H545" s="11" t="inlineStr">
@@ -72122,10 +72210,14 @@
       </c>
       <c r="J545" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K545" s="13" t="n"/>
+          <t>Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K545" s="13" t="inlineStr">
+        <is>
+          <t>brahmi</t>
+        </is>
+      </c>
       <c r="L545" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72133,12 +72225,12 @@
       </c>
       <c r="M545" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-19 (ddg); review.</t>
         </is>
       </c>
       <c r="N545" s="14" t="inlineStr">
         <is>
-          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
+          <t>https://www.academia.edu/Documents/in/Tamil_Brahmi</t>
         </is>
       </c>
     </row>
@@ -72157,13 +72249,13 @@
       <c r="D546" s="7" t="n"/>
       <c r="E546" s="9" t="inlineStr">
         <is>
-          <t>Tamil Identity in Vanni Monuments</t>
+          <t>Tamil Coin Issued by King Ellalan during the Anuradhapura Era</t>
         </is>
       </c>
       <c r="F546" s="9" t="n"/>
       <c r="G546" s="9" t="inlineStr">
         <is>
-          <t>scribd.com</t>
+          <t>sangam.org</t>
         </is>
       </c>
       <c r="H546" s="7" t="inlineStr">
@@ -72178,7 +72270,7 @@
       </c>
       <c r="J546" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Coins / நாணயம்</t>
         </is>
       </c>
       <c r="K546" s="9" t="n"/>
@@ -72189,12 +72281,12 @@
       </c>
       <c r="M546" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-16 (ddg); review.</t>
         </is>
       </c>
       <c r="N546" s="10" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/933772684/MC-13</t>
+          <t>https://sangam.org/tamil-coin-issued-by-king-ellalan-during-the-anuradhapura-era/</t>
         </is>
       </c>
     </row>
@@ -72213,7 +72305,7 @@
       <c r="D547" s="11" t="n"/>
       <c r="E547" s="13" t="inlineStr">
         <is>
-          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
+          <t>Tamil Identity in Vanni Monuments</t>
         </is>
       </c>
       <c r="F547" s="13" t="n"/>
@@ -72234,14 +72326,10 @@
       </c>
       <c r="J547" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
-        </is>
-      </c>
-      <c r="K547" s="13" t="inlineStr">
-        <is>
-          <t>inscription; inscriptions; brahmi</t>
-        </is>
-      </c>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K547" s="13" t="n"/>
       <c r="L547" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72249,12 +72337,12 @@
       </c>
       <c r="M547" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-26 (ddg); review.</t>
         </is>
       </c>
       <c r="N547" s="14" t="inlineStr">
         <is>
-          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
+          <t>https://www.scribd.com/document/933772684/MC-13</t>
         </is>
       </c>
     </row>
@@ -72273,13 +72361,13 @@
       <c r="D548" s="7" t="n"/>
       <c r="E548" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
+          <t>Tamil Influence on Early Brahmi Inscriptions | PDF | Sri Lanka</t>
         </is>
       </c>
       <c r="F548" s="9" t="n"/>
       <c r="G548" s="9" t="inlineStr">
         <is>
-          <t>en.bharatpedia.org</t>
+          <t>scribd.com</t>
         </is>
       </c>
       <c r="H548" s="7" t="inlineStr">
@@ -72294,12 +72382,12 @@
       </c>
       <c r="J548" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K548" s="9" t="inlineStr">
         <is>
-          <t>inscription; inscriptions</t>
+          <t>inscription; inscriptions; brahmi</t>
         </is>
       </c>
       <c r="L548" s="7" t="inlineStr">
@@ -72309,12 +72397,12 @@
       </c>
       <c r="M548" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N548" s="10" t="inlineStr">
         <is>
-          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://www.scribd.com/document/375399590/Tamil-Influence-in-Ancient-Sri-Lanka-With-Special-Reference-to-Early-Brahmi-Inscriptions-All-Parts-A-Veluppillai-1979-and-1980</t>
         </is>
       </c>
     </row>
@@ -72333,13 +72421,13 @@
       <c r="D549" s="11" t="n"/>
       <c r="E549" s="13" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
+          <t>Tamil inscriptions in Sri Lanka - Bharatpedia</t>
         </is>
       </c>
       <c r="F549" s="13" t="n"/>
       <c r="G549" s="13" t="inlineStr">
         <is>
-          <t>grokipedia.com</t>
+          <t>en.bharatpedia.org</t>
         </is>
       </c>
       <c r="H549" s="11" t="inlineStr">
@@ -72369,12 +72457,12 @@
       </c>
       <c r="M549" s="13" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N549" s="14" t="inlineStr">
         <is>
-          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
+          <t>https://en.bharatpedia.org/wiki/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -72393,13 +72481,13 @@
       <c r="D550" s="7" t="n"/>
       <c r="E550" s="9" t="inlineStr">
         <is>
-          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
+          <t>Tamil inscriptions in Sri Lanka - Grokipedia</t>
         </is>
       </c>
       <c r="F550" s="9" t="n"/>
       <c r="G550" s="9" t="inlineStr">
         <is>
-          <t>wikiwand.com</t>
+          <t>grokipedia.com</t>
         </is>
       </c>
       <c r="H550" s="7" t="inlineStr">
@@ -72434,7 +72522,7 @@
       </c>
       <c r="N550" s="10" t="inlineStr">
         <is>
-          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
+          <t>https://grokipedia.com/page/tamil_inscriptions_in_sri_lanka</t>
         </is>
       </c>
     </row>
@@ -72453,13 +72541,13 @@
       <c r="D551" s="11" t="n"/>
       <c r="E551" s="13" t="inlineStr">
         <is>
-          <t>The Inscription at Fort Frederick, Trincomalee</t>
+          <t>Tamil inscriptions in Sri Lanka - Wikiwand</t>
         </is>
       </c>
       <c r="F551" s="13" t="n"/>
       <c r="G551" s="13" t="inlineStr">
         <is>
-          <t>jstor.org</t>
+          <t>wikiwand.com</t>
         </is>
       </c>
       <c r="H551" s="11" t="inlineStr">
@@ -72479,7 +72567,7 @@
       </c>
       <c r="K551" s="13" t="inlineStr">
         <is>
-          <t>inscription</t>
+          <t>inscription; inscriptions</t>
         </is>
       </c>
       <c r="L551" s="11" t="inlineStr">
@@ -72489,12 +72577,12 @@
       </c>
       <c r="M551" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N551" s="14" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/43483806</t>
+          <t>https://www.wikiwand.com/en/Tamil_inscriptions_in_Sri_Lanka</t>
         </is>
       </c>
     </row>
@@ -72513,13 +72601,13 @@
       <c r="D552" s="7" t="n"/>
       <c r="E552" s="9" t="inlineStr">
         <is>
-          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
+          <t>The Inscription at Fort Frederick, Trincomalee</t>
         </is>
       </c>
       <c r="F552" s="9" t="n"/>
       <c r="G552" s="9" t="inlineStr">
         <is>
-          <t>ir.lib.pdn.ac.lk</t>
+          <t>jstor.org</t>
         </is>
       </c>
       <c r="H552" s="7" t="inlineStr">
@@ -72532,8 +72620,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J552" s="9" t="n"/>
-      <c r="K552" s="9" t="n"/>
+      <c r="J552" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K552" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L552" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72541,12 +72637,12 @@
       </c>
       <c r="M552" s="9" t="inlineStr">
         <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-17 (ddg); review.</t>
         </is>
       </c>
       <c r="N552" s="10" t="inlineStr">
         <is>
-          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
+          <t>https://www.jstor.org/stable/43483806</t>
         </is>
       </c>
     </row>
@@ -72565,13 +72661,13 @@
       <c r="D553" s="11" t="n"/>
       <c r="E553" s="13" t="inlineStr">
         <is>
-          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
+          <t>The Origin of The Tamil Vanni Chieftaincies Of</t>
         </is>
       </c>
       <c r="F553" s="13" t="n"/>
       <c r="G553" s="13" t="inlineStr">
         <is>
-          <t>cambridge.org</t>
+          <t>ir.lib.pdn.ac.lk</t>
         </is>
       </c>
       <c r="H553" s="11" t="inlineStr">
@@ -72593,12 +72689,12 @@
       </c>
       <c r="M553" s="13" t="inlineStr">
         <is>
-          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N553" s="14" t="inlineStr">
         <is>
-          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
+          <t>https://ir.lib.pdn.ac.lk/bitstreams/98390e3c-9f21-449b-b076-6276cf94f4e8/download</t>
         </is>
       </c>
     </row>
@@ -72617,13 +72713,13 @@
       <c r="D554" s="7" t="n"/>
       <c r="E554" s="9" t="inlineStr">
         <is>
-          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
+          <t>The antiquity of Jaffna Fort: new evidence from post-disaster ...</t>
         </is>
       </c>
       <c r="F554" s="9" t="n"/>
       <c r="G554" s="9" t="inlineStr">
         <is>
-          <t>unesco.org</t>
+          <t>cambridge.org</t>
         </is>
       </c>
       <c r="H554" s="7" t="inlineStr">
@@ -72636,16 +72732,8 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J554" s="9" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K554" s="9" t="inlineStr">
-        <is>
-          <t>inscription</t>
-        </is>
-      </c>
+      <c r="J554" s="9" t="n"/>
+      <c r="K554" s="9" t="n"/>
       <c r="L554" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72653,12 +72741,12 @@
       </c>
       <c r="M554" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Jaffna archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N554" s="10" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
+          <t>https://www.cambridge.org/core/journals/antiquity/article/antiquity-of-jaffna-fort-new-evidence-from-postdisaster-archaeological-investigations-in-northern-sri-lanka/C55CDA3934CC5C18EE40B903734C7215</t>
         </is>
       </c>
     </row>
@@ -72677,13 +72765,13 @@
       <c r="D555" s="11" t="n"/>
       <c r="E555" s="13" t="inlineStr">
         <is>
-          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+          <t>Trilingual Inscription (TribhashaSellipiya) - Memory of the World - UNESCO</t>
         </is>
       </c>
       <c r="F555" s="13" t="n"/>
       <c r="G555" s="13" t="inlineStr">
         <is>
-          <t>libcat.lib.jfn.ac.lk</t>
+          <t>unesco.org</t>
         </is>
       </c>
       <c r="H555" s="11" t="inlineStr">
@@ -72713,12 +72801,12 @@
       </c>
       <c r="M555" s="13" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N555" s="14" t="inlineStr">
         <is>
-          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
+          <t>https://www.unesco.org/en/memory-world/trilingual-inscription-tribhashasellipiya</t>
         </is>
       </c>
     </row>
@@ -72737,22 +72825,18 @@
       <c r="D556" s="7" t="n"/>
       <c r="E556" s="9" t="inlineStr">
         <is>
-          <t>Vallipuram</t>
-        </is>
-      </c>
-      <c r="F556" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>UOJ Online catalog › Details for: A tamil slab-inscription from ...</t>
+        </is>
+      </c>
+      <c r="F556" s="9" t="n"/>
       <c r="G556" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (en)</t>
+          <t>libcat.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H556" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I556" s="7" t="inlineStr">
@@ -72760,8 +72844,16 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J556" s="9" t="n"/>
-      <c r="K556" s="9" t="n"/>
+      <c r="J556" s="9" t="inlineStr">
+        <is>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K556" s="9" t="inlineStr">
+        <is>
+          <t>inscription</t>
+        </is>
+      </c>
       <c r="L556" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72769,12 +72861,12 @@
       </c>
       <c r="M556" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N556" s="10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
+          <t>http://libcat.lib.jfn.ac.lk/cgi-bin/koha/opac-detail.pl?biblionumber=54703</t>
         </is>
       </c>
     </row>
@@ -72793,18 +72885,22 @@
       <c r="D557" s="11" t="n"/>
       <c r="E557" s="13" t="inlineStr">
         <is>
-          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
-        </is>
-      </c>
-      <c r="F557" s="13" t="n"/>
+          <t>Vallipuram</t>
+        </is>
+      </c>
+      <c r="F557" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G557" s="13" t="inlineStr">
         <is>
-          <t>AmazingLanka.com</t>
+          <t>Wikipedia (en)</t>
         </is>
       </c>
       <c r="H557" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I557" s="11" t="inlineStr">
@@ -72812,25 +72908,21 @@
           <t>English</t>
         </is>
       </c>
-      <c r="J557" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K557" s="13" t="inlineStr">
-        <is>
-          <t>memorial stone; Vanni</t>
-        </is>
-      </c>
+      <c r="J557" s="13" t="n"/>
+      <c r="K557" s="13" t="n"/>
       <c r="L557" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M557" s="13" t="n"/>
+      <c r="M557" s="13" t="inlineStr">
+        <is>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+        </is>
+      </c>
       <c r="N557" s="14" t="inlineStr">
         <is>
-          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
+          <t>https://en.wikipedia.org/wiki/Vallipuram</t>
         </is>
       </c>
     </row>
@@ -72849,40 +72941,44 @@
       <c r="D558" s="7" t="n"/>
       <c r="E558" s="9" t="inlineStr">
         <is>
-          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+          <t>Vanni Bandara Stone Memorial in Oddusuddan: A Legacy of Resistance</t>
         </is>
       </c>
       <c r="F558" s="9" t="n"/>
       <c r="G558" s="9" t="inlineStr">
         <is>
-          <t>noolaham.org</t>
+          <t>AmazingLanka.com</t>
         </is>
       </c>
       <c r="H558" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="I558" s="7" t="inlineStr">
         <is>
-          <t>Tamil</t>
-        </is>
-      </c>
-      <c r="J558" s="9" t="n"/>
-      <c r="K558" s="9" t="n"/>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J558" s="9" t="inlineStr">
+        <is>
+          <t>Hero stones / நடுகல்</t>
+        </is>
+      </c>
+      <c r="K558" s="9" t="inlineStr">
+        <is>
+          <t>memorial stone; Vanni</t>
+        </is>
+      </c>
       <c r="L558" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M558" s="9" t="inlineStr">
-        <is>
-          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
-        </is>
-      </c>
+      <c r="M558" s="9" t="n"/>
       <c r="N558" s="10" t="inlineStr">
         <is>
-          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
+          <t>https://amazinglanka.com/wp/vanni-bandara-en/</t>
         </is>
       </c>
     </row>
@@ -72901,22 +72997,18 @@
       <c r="D559" s="11" t="n"/>
       <c r="E559" s="13" t="inlineStr">
         <is>
-          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="F559" s="13" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>Vanni and The Vanniyas - நூலகம் - noolaham.org</t>
+        </is>
+      </c>
+      <c r="F559" s="13" t="n"/>
       <c r="G559" s="13" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>noolaham.org</t>
         </is>
       </c>
       <c r="H559" s="11" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I559" s="11" t="inlineStr">
@@ -72924,16 +73016,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J559" s="13" t="inlineStr">
-        <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K559" s="13" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு</t>
-        </is>
-      </c>
+      <c r="J559" s="13" t="n"/>
+      <c r="K559" s="13" t="n"/>
       <c r="L559" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -72941,12 +73025,12 @@
       </c>
       <c r="M559" s="13" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N559" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://noolaham.org/wiki/index.php/Vanni_and_The_Vanniyas</t>
         </is>
       </c>
     </row>
@@ -72965,18 +73049,22 @@
       <c r="D560" s="7" t="n"/>
       <c r="E560" s="9" t="inlineStr">
         <is>
-          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
-        </is>
-      </c>
-      <c r="F560" s="9" t="n"/>
+          <t>அனுராதபுரம் நான்கு நாட்டார் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F560" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G560" s="9" t="inlineStr">
         <is>
-          <t>ilakku.org</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H560" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I560" s="7" t="inlineStr">
@@ -72986,12 +73074,12 @@
       </c>
       <c r="J560" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K560" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
+          <t>கல்வெட்டு</t>
         </is>
       </c>
       <c r="L560" s="7" t="inlineStr">
@@ -73001,12 +73089,12 @@
       </c>
       <c r="M560" s="9" t="inlineStr">
         <is>
-          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N560" s="10" t="inlineStr">
         <is>
-          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%85%E0%AE%A9%E0%AF%81%E0%AE%B0%E0%AE%BE%E0%AE%A4%E0%AE%AA%E0%AF%81%E0%AE%B0%E0%AE%AE%E0%AF%8D_%E0%AE%A8%E0%AE%BE%E0%AE%A9%E0%AF%8D%E0%AE%95%E0%AF%81_%E0%AE%A8%E0%AE%BE%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AE%BE%E0%AE%B0%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -73025,13 +73113,13 @@
       <c r="D561" s="11" t="n"/>
       <c r="E561" s="13" t="inlineStr">
         <is>
-          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+          <t>இலங்கையில் தமிழ் பிராமி கல்வெட்டுகள் பேராசிரியர் சி.பத்மநாதன் ...</t>
         </is>
       </c>
       <c r="F561" s="13" t="n"/>
       <c r="G561" s="13" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>ilakku.org</t>
         </is>
       </c>
       <c r="H561" s="11" t="inlineStr">
@@ -73046,12 +73134,12 @@
       </c>
       <c r="J561" s="13" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
         </is>
       </c>
       <c r="K561" s="13" t="inlineStr">
         <is>
-          <t>தொல்லியல்</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்; பிராமி</t>
         </is>
       </c>
       <c r="L561" s="11" t="inlineStr">
@@ -73061,12 +73149,12 @@
       </c>
       <c r="M561" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: Sri Lanka Tamil Brahmi. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N561" s="14" t="inlineStr">
         <is>
-          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
+          <t>https://www.ilakku.org/tamil-brahmi-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -73085,22 +73173,18 @@
       <c r="D562" s="7" t="n"/>
       <c r="E562" s="9" t="inlineStr">
         <is>
-          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
-        </is>
-      </c>
-      <c r="F562" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>ஈழத்தின் தொன்ம மொழியும் தொல்லியல் ஆதாரங்களும் - Tamil Heritage</t>
+        </is>
+      </c>
+      <c r="F562" s="9" t="n"/>
       <c r="G562" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H562" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I562" s="7" t="inlineStr">
@@ -73108,8 +73192,16 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J562" s="9" t="n"/>
-      <c r="K562" s="9" t="n"/>
+      <c r="J562" s="9" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K562" s="9" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
       <c r="L562" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73117,12 +73209,12 @@
       </c>
       <c r="M562" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N562" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
+          <t>https://telibrary.com/ancient-language-of-eelam-and-archaeological-evidence/</t>
         </is>
       </c>
     </row>
@@ -73141,18 +73233,22 @@
       <c r="D563" s="11" t="n"/>
       <c r="E563" s="13" t="inlineStr">
         <is>
-          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
-        </is>
-      </c>
-      <c r="F563" s="13" t="n"/>
+          <t>கோப்பாய் சங்கிலியன் கோட்டை</t>
+        </is>
+      </c>
+      <c r="F563" s="13" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G563" s="13" t="inlineStr">
         <is>
-          <t>ngmtamil.in</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H563" s="11" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I563" s="11" t="inlineStr">
@@ -73160,16 +73256,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J563" s="13" t="inlineStr">
-        <is>
-          <t>Hero stones / நடுகல்</t>
-        </is>
-      </c>
-      <c r="K563" s="13" t="inlineStr">
-        <is>
-          <t>நடுகல்</t>
-        </is>
-      </c>
+      <c r="J563" s="13" t="n"/>
+      <c r="K563" s="13" t="n"/>
       <c r="L563" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73177,12 +73265,12 @@
       </c>
       <c r="M563" s="13" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N563" s="14" t="inlineStr">
         <is>
-          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%95%E0%AF%8B%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%AF%E0%AF%8D_%E0%AE%9A%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AE%BF%E0%AE%B2%E0%AE%BF%E0%AE%AF%E0%AE%A9%E0%AF%8D_%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88</t>
         </is>
       </c>
     </row>
@@ -73201,22 +73289,18 @@
       <c r="D564" s="7" t="n"/>
       <c r="E564" s="9" t="inlineStr">
         <is>
-          <t>தமிழ்க் கல்வெட்டுகள்</t>
-        </is>
-      </c>
-      <c r="F564" s="9" t="inlineStr">
-        <is>
-          <t>Wikipedia contributors</t>
-        </is>
-      </c>
+          <t>சங்க இலக்கியங்களில் நடுகல் பற்றிய வகைப்பாடு | Kalanjiyam ...</t>
+        </is>
+      </c>
+      <c r="F564" s="9" t="n"/>
       <c r="G564" s="9" t="inlineStr">
         <is>
-          <t>Wikipedia (ta)</t>
+          <t>ngmtamil.in</t>
         </is>
       </c>
       <c r="H564" s="7" t="inlineStr">
         <is>
-          <t>Encyclopedia article</t>
+          <t>Web page</t>
         </is>
       </c>
       <c r="I564" s="7" t="inlineStr">
@@ -73226,12 +73310,12 @@
       </c>
       <c r="J564" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
+          <t>Hero stones / நடுகல்</t>
         </is>
       </c>
       <c r="K564" s="9" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
+          <t>நடுகல்</t>
         </is>
       </c>
       <c r="L564" s="7" t="inlineStr">
@@ -73241,12 +73325,12 @@
       </c>
       <c r="M564" s="9" t="inlineStr">
         <is>
-          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
+          <t>Web search: இலங்கை நடுகல். Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N564" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://ngmtamil.in/kalanjiyam-tamil/index.php/kalanjiyam/article/view/58</t>
         </is>
       </c>
     </row>
@@ -73265,7 +73349,7 @@
       <c r="D565" s="11" t="n"/>
       <c r="E565" s="13" t="inlineStr">
         <is>
-          <t>தம்பிலுவில் கல்வெட்டு</t>
+          <t>தமிழ்க் கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="F565" s="13" t="inlineStr">
@@ -73295,7 +73379,7 @@
       </c>
       <c r="K565" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="L565" s="11" t="inlineStr">
@@ -73310,7 +73394,7 @@
       </c>
       <c r="N565" s="14" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -73329,18 +73413,22 @@
       <c r="D566" s="7" t="n"/>
       <c r="E566" s="9" t="inlineStr">
         <is>
-          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
-        </is>
-      </c>
-      <c r="F566" s="9" t="n"/>
+          <t>தம்பிலுவில் கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="F566" s="9" t="inlineStr">
+        <is>
+          <t>Wikipedia contributors</t>
+        </is>
+      </c>
       <c r="G566" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>Wikipedia (ta)</t>
         </is>
       </c>
       <c r="H566" s="7" t="inlineStr">
         <is>
-          <t>Web page</t>
+          <t>Encyclopedia article</t>
         </is>
       </c>
       <c r="I566" s="7" t="inlineStr">
@@ -73365,12 +73453,12 @@
       </c>
       <c r="M566" s="9" t="inlineStr">
         <is>
-          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Date = page creation. Auto-collected 2026-10-14 (wikipedia); review.</t>
         </is>
       </c>
       <c r="N566" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%A4%E0%AE%AE%E0%AF%8D%E0%AE%AA%E0%AE%BF%E0%AE%B2%E0%AF%81%E0%AE%B5%E0%AE%BF%E0%AE%B2%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81</t>
         </is>
       </c>
     </row>
@@ -73389,13 +73477,13 @@
       <c r="D567" s="11" t="n"/>
       <c r="E567" s="13" t="inlineStr">
         <is>
-          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
+          <t>திருகோணமலையில் மிக அரிய தமிழ்க் கல்வெட்டு கண்டுபிடிப்பு!</t>
         </is>
       </c>
       <c r="F567" s="13" t="n"/>
       <c r="G567" s="13" t="inlineStr">
         <is>
-          <t>ezhunaonline.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="H567" s="11" t="inlineStr">
@@ -73410,10 +73498,14 @@
       </c>
       <c r="J567" s="13" t="inlineStr">
         <is>
-          <t>Coins / நாணயம்</t>
-        </is>
-      </c>
-      <c r="K567" s="13" t="n"/>
+          <t>Inscriptions / கல்வெட்டு</t>
+        </is>
+      </c>
+      <c r="K567" s="13" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு</t>
+        </is>
+      </c>
       <c r="L567" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73421,12 +73513,12 @@
       </c>
       <c r="M567" s="13" t="inlineStr">
         <is>
-          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
+          <t>Web search: Trincomalee Tamil inscription. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N567" s="14" t="inlineStr">
         <is>
-          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
+          <t>https://jvpnews.com/article/rare-tamil-inscription-found-in-trincomalee-1637737357</t>
         </is>
       </c>
     </row>
@@ -73445,13 +73537,13 @@
       <c r="D568" s="7" t="n"/>
       <c r="E568" s="9" t="inlineStr">
         <is>
-          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
+          <t>தென்னிலங்கையில் கிடைத்த பண்டைய தமிழ் நாணயங்களின் வரலாற்றுப் பின்னணி</t>
         </is>
       </c>
       <c r="F568" s="9" t="n"/>
       <c r="G568" s="9" t="inlineStr">
         <is>
-          <t>ta.wikipedia.org</t>
+          <t>ezhunaonline.com</t>
         </is>
       </c>
       <c r="H568" s="7" t="inlineStr">
@@ -73466,14 +73558,10 @@
       </c>
       <c r="J568" s="9" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு</t>
-        </is>
-      </c>
-      <c r="K568" s="9" t="inlineStr">
-        <is>
-          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
-        </is>
-      </c>
+          <t>Coins / நாணயம்</t>
+        </is>
+      </c>
+      <c r="K568" s="9" t="n"/>
       <c r="L568" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73481,12 +73569,12 @@
       </c>
       <c r="M568" s="9" t="inlineStr">
         <is>
-          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
+          <t>Web search: Tamil coins Sri Lanka archaeology. Auto-collected 2026-10-21 (ddg); review.</t>
         </is>
       </c>
       <c r="N568" s="10" t="inlineStr">
         <is>
-          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
+          <t>https://www.ezhunaonline.com/historical-background-of-ancient-tamil-coins-found-in-south-lanka/</t>
         </is>
       </c>
     </row>
@@ -73505,13 +73593,13 @@
       <c r="D569" s="11" t="n"/>
       <c r="E569" s="13" t="inlineStr">
         <is>
-          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
+          <t>பகுப்பு:இலங்கைத் தமிழ்க் கல்வெட்டுகள் - தமிழ் விக்கிப்பீடியா</t>
         </is>
       </c>
       <c r="F569" s="13" t="n"/>
       <c r="G569" s="13" t="inlineStr">
         <is>
-          <t>repo.lib.jfn.ac.lk</t>
+          <t>ta.wikipedia.org</t>
         </is>
       </c>
       <c r="H569" s="11" t="inlineStr">
@@ -73526,12 +73614,12 @@
       </c>
       <c r="J569" s="13" t="inlineStr">
         <is>
-          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+          <t>Inscriptions / கல்வெட்டு</t>
         </is>
       </c>
       <c r="K569" s="13" t="inlineStr">
         <is>
-          <t>கல்வெட்டு; பிராமி</t>
+          <t>கல்வெட்டு; கல்வெட்டுகள்</t>
         </is>
       </c>
       <c r="L569" s="11" t="inlineStr">
@@ -73541,12 +73629,12 @@
       </c>
       <c r="M569" s="13" t="inlineStr">
         <is>
-          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
+          <t>Web search: இலங்கை தமிழ் கல்வெட்டு. Auto-collected 2026-10-25 (ddg); review.</t>
         </is>
       </c>
       <c r="N569" s="14" t="inlineStr">
         <is>
-          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%AA%E0%AE%95%E0%AF%81%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AF%81:%E0%AE%87%E0%AE%B2%E0%AE%99%E0%AF%8D%E0%AE%95%E0%AF%88%E0%AE%A4%E0%AF%8D_%E0%AE%A4%E0%AE%AE%E0%AE%BF%E0%AE%B4%E0%AF%8D%E0%AE%95%E0%AF%8D_%E0%AE%95%E0%AE%B2%E0%AF%8D%E0%AE%B5%E0%AF%86%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%81%E0%AE%95%E0%AE%B3%E0%AF%8D</t>
         </is>
       </c>
     </row>
@@ -73565,13 +73653,13 @@
       <c r="D570" s="7" t="n"/>
       <c r="E570" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
+          <t>பிராமிக் கல்வெட்டுக்களும் தமிழும்</t>
         </is>
       </c>
       <c r="F570" s="9" t="n"/>
       <c r="G570" s="9" t="inlineStr">
         <is>
-          <t>telibrary.com</t>
+          <t>repo.lib.jfn.ac.lk</t>
         </is>
       </c>
       <c r="H570" s="7" t="inlineStr">
@@ -73586,10 +73674,14 @@
       </c>
       <c r="J570" s="9" t="inlineStr">
         <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K570" s="9" t="n"/>
+          <t>Inscriptions / கல்வெட்டு; Brahmi / பிராமி</t>
+        </is>
+      </c>
+      <c r="K570" s="9" t="inlineStr">
+        <is>
+          <t>கல்வெட்டு; பிராமி</t>
+        </is>
+      </c>
       <c r="L570" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73597,12 +73689,12 @@
       </c>
       <c r="M570" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: ஈழம் தொல்லியல் பிராமி. Auto-collected 2026-10-15 (ddg); review.</t>
         </is>
       </c>
       <c r="N570" s="10" t="inlineStr">
         <is>
-          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
+          <t>http://repo.lib.jfn.ac.lk/xmlui/handle/123456789/8444</t>
         </is>
       </c>
     </row>
@@ -73621,13 +73713,13 @@
       <c r="D571" s="11" t="n"/>
       <c r="E571" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
+          <t>யாழ்ப்பாண இராச்சியம் - Tamil Heritage</t>
         </is>
       </c>
       <c r="F571" s="13" t="n"/>
       <c r="G571" s="13" t="inlineStr">
         <is>
-          <t>treasurehouseofjaffna.com</t>
+          <t>telibrary.com</t>
         </is>
       </c>
       <c r="H571" s="11" t="inlineStr">
@@ -73640,7 +73732,11 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J571" s="13" t="n"/>
+      <c r="J571" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
       <c r="K571" s="13" t="n"/>
       <c r="L571" s="11" t="inlineStr">
         <is>
@@ -73654,7 +73750,7 @@
       </c>
       <c r="N571" s="14" t="inlineStr">
         <is>
-          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
+          <t>https://telibrary.com/category/history/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%87%E0%AE%B0%E0%AE%BE%E0%AE%9A%E0%AF%8D%E0%AE%9A%E0%AE%BF%E0%AE%AF%E0%AE%AE%E0%AF%8D/</t>
         </is>
       </c>
     </row>
@@ -73673,13 +73769,13 @@
       <c r="D572" s="7" t="n"/>
       <c r="E572" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
+          <t>யாழ்ப்பாண வரலாறு - யாழ்ப்பாணப் பெட்டகம்</t>
         </is>
       </c>
       <c r="F572" s="9" t="n"/>
       <c r="G572" s="9" t="inlineStr">
         <is>
-          <t>jvpnews.com</t>
+          <t>treasurehouseofjaffna.com</t>
         </is>
       </c>
       <c r="H572" s="7" t="inlineStr">
@@ -73692,16 +73788,8 @@
           <t>Tamil</t>
         </is>
       </c>
-      <c r="J572" s="9" t="inlineStr">
-        <is>
-          <t>Archaeology / தொல்லியல்</t>
-        </is>
-      </c>
-      <c r="K572" s="9" t="inlineStr">
-        <is>
-          <t>தொல்லியல்</t>
-        </is>
-      </c>
+      <c r="J572" s="9" t="n"/>
+      <c r="K572" s="9" t="n"/>
       <c r="L572" s="7" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -73709,12 +73797,12 @@
       </c>
       <c r="M572" s="9" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
         </is>
       </c>
       <c r="N572" s="10" t="inlineStr">
         <is>
-          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
+          <t>https://treasurehouseofjaffna.com/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3-%E0%AE%B5%E0%AE%B0%E0%AE%B2%E0%AE%BE%E0%AE%B1%E0%AF%81/</t>
         </is>
       </c>
     </row>
@@ -73733,13 +73821,13 @@
       <c r="D573" s="11" t="n"/>
       <c r="E573" s="13" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் அகழ்வாய்வின் நிறைவு விழாவும் ...</t>
         </is>
       </c>
       <c r="F573" s="13" t="n"/>
       <c r="G573" s="13" t="inlineStr">
         <is>
-          <t>shritharan.com</t>
+          <t>jvpnews.com</t>
         </is>
       </c>
       <c r="H573" s="11" t="inlineStr">
@@ -73769,12 +73857,12 @@
       </c>
       <c r="M573" s="13" t="inlineStr">
         <is>
-          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-20 (ddg); review.</t>
         </is>
       </c>
       <c r="N573" s="14" t="inlineStr">
         <is>
-          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+          <t>https://jvpnews.com/article/ja-anaikottai-archeological-excavation-ceremony-1721384878</t>
         </is>
       </c>
     </row>
@@ -73793,7 +73881,7 @@
       <c r="D574" s="7" t="n"/>
       <c r="E574" s="9" t="inlineStr">
         <is>
-          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்!</t>
         </is>
       </c>
       <c r="F574" s="9" t="n"/>
@@ -73829,17 +73917,129 @@
       </c>
       <c r="M574" s="9" t="inlineStr">
         <is>
+          <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-14 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N574" s="10" t="inlineStr">
+        <is>
+          <t>https://shritharan.com/parliamentary-work/%E0%AE%AF%E0%AE%BE%E0%AE%B4%E0%AF%8D%E0%AE%AA%E0%AF%8D%E0%AE%AA%E0%AE%BE%E0%AE%A3%E0%AE%AE%E0%AF%8D-%E0%AE%86%E0%AE%A9%E0%AF%88%E0%AE%95%E0%AF%8D%E0%AE%95%E0%AF%8B%E0%AE%9F%E0%AF%8D%E0%AE%9F%E0%AF%88/</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="11" t="inlineStr">
+        <is>
+          <t>ALL-0574</t>
+        </is>
+      </c>
+      <c r="B575" s="11" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C575" s="12" t="n"/>
+      <c r="D575" s="11" t="n"/>
+      <c r="E575" s="13" t="inlineStr">
+        <is>
+          <t>யாழ்ப்பாணம் ஆனைக்கோட்டை தொல்லியல் கண்காட்சி ஆரம்பம்! - shritharan</t>
+        </is>
+      </c>
+      <c r="F575" s="13" t="n"/>
+      <c r="G575" s="13" t="inlineStr">
+        <is>
+          <t>shritharan.com</t>
+        </is>
+      </c>
+      <c r="H575" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I575" s="11" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J575" s="13" t="inlineStr">
+        <is>
+          <t>Archaeology / தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="K575" s="13" t="inlineStr">
+        <is>
+          <t>தொல்லியல்</t>
+        </is>
+      </c>
+      <c r="L575" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M575" s="13" t="inlineStr">
+        <is>
           <t>Web search: யாழ்ப்பாணம் தொல்லியல். Auto-collected 2026-10-23 (ddg); review.</t>
         </is>
       </c>
-      <c r="N574" s="10" t="inlineStr">
+      <c r="N575" s="14" t="inlineStr">
         <is>
           <t>https://shritharan.com/jaffna-anaikotta-archaeological-exhibition-begins/</t>
         </is>
       </c>
     </row>
+    <row r="576">
+      <c r="A576" s="7" t="inlineStr">
+        <is>
+          <t>ALL-0575</t>
+        </is>
+      </c>
+      <c r="B576" s="7" t="inlineStr">
+        <is>
+          <t>Web Articles</t>
+        </is>
+      </c>
+      <c r="C576" s="8" t="n"/>
+      <c r="D576" s="7" t="n"/>
+      <c r="E576" s="9" t="inlineStr">
+        <is>
+          <t>வன்னி (மரம்) - தமிழ் விக்கிப்பீடியா</t>
+        </is>
+      </c>
+      <c r="F576" s="9" t="n"/>
+      <c r="G576" s="9" t="inlineStr">
+        <is>
+          <t>ta.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="H576" s="7" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="I576" s="7" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="J576" s="9" t="n"/>
+      <c r="K576" s="9" t="n"/>
+      <c r="L576" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M576" s="9" t="inlineStr">
+        <is>
+          <t>Web search: Vanni archaeology Tamil. Auto-collected 2026-10-30 (ddg); review.</t>
+        </is>
+      </c>
+      <c r="N576" s="10" t="inlineStr">
+        <is>
+          <t>https://ta.wikipedia.org/wiki/%E0%AE%B5%E0%AE%A9%E0%AF%8D%E0%AE%A9%E0%AE%BF_(%E0%AE%AE%E0%AE%B0%E0%AE%AE%E0%AF%8D)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N574"/>
+  <autoFilter ref="A1:N576"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -74414,6 +74614,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N572" r:id="rId571"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N573" r:id="rId572"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N576" r:id="rId575"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
